--- a/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.940470394182099e-07</v>
+        <v>1.940470394182083e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.897053850294943e-07</v>
+        <v>3.897053850294942e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.956479206225843e-07</v>
+        <v>1.956479206225834e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.939102779565473e-07</v>
+        <v>1.939102779565456e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.953179043565213e-07</v>
+        <v>1.953179043565195e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.938014327037987e-07</v>
+        <v>1.938014327037966e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.953876318818255e-07</v>
+        <v>1.953876318818229e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.962587942820193e-07</v>
+        <v>1.962587942820182e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.944632549972157e-07</v>
+        <v>1.944632549972179e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.985486412118136e-07</v>
+        <v>1.985486412118121e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.944603224623653e-07</v>
+        <v>1.944603224623658e-07</v>
       </c>
       <c r="M2" t="n">
         <v>1.939796277448736e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.980952621550804e-07</v>
+        <v>1.980952621550791e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.050366666286485e-07</v>
+        <v>1.050366666286479e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.946176598844949e-07</v>
+        <v>1.946176598844951e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.954794690282478e-07</v>
+        <v>1.954794690282461e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.950107849186181e-07</v>
+        <v>1.950107849186166e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.945618496755602e-07</v>
+        <v>1.945618496755584e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95984780246252e-07</v>
+        <v>1.9598478024625e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.361766905129647e-07</v>
+        <v>4.361766905129631e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.942702317009305e-07</v>
+        <v>1.942702317009283e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.08301106765316e-07</v>
+        <v>3.083011067653141e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.944278320984651e-07</v>
+        <v>1.944278320984649e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.945863680319266e-07</v>
+        <v>1.945863680319253e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.727637582555305e-07</v>
+        <v>1.727637582555286e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.943263071549481e-07</v>
+        <v>1.943263071549501e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.937644138861867e-07</v>
+        <v>1.937644138861869e-07</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.996865107601688e-07</v>
+        <v>1.99686510760169e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.233983990908423e-07</v>
+        <v>5.233983990908424e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.111730579314796e-07</v>
+        <v>2.111730579314786e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.987239866897492e-07</v>
+        <v>1.987239866897494e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.088288455195998e-07</v>
+        <v>2.088288455196004e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.979426317059299e-07</v>
+        <v>1.979426317059296e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.093437144236659e-07</v>
+        <v>2.093437144236652e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.155597369495313e-07</v>
+        <v>2.155597369495337e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.026710119490257e-07</v>
+        <v>2.026710119490262e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.319210025122277e-07</v>
+        <v>2.319210025122288e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.026488798235872e-07</v>
+        <v>2.026488798235861e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.99338023604059e-07</v>
+        <v>1.993380236040594e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.286360429482652e-07</v>
+        <v>2.286360429482656e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>5.5193259834695e-08</v>
+        <v>5.519325983469363e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.037484376533394e-07</v>
+        <v>2.037484376533399e-07</v>
       </c>
       <c r="Q3" t="n">
         <v>2.099494054027811e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.066280743608313e-07</v>
+        <v>2.066280743608322e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.033577893639663e-07</v>
+        <v>2.033577893639671e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.135887038662887e-07</v>
+        <v>2.135887038662885e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>6.018161619735323e-07</v>
+        <v>6.018161619735314e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.012761269612222e-07</v>
+        <v>2.012761269612239e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.012563259249365e-07</v>
+        <v>4.012563259249369e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.024338570341677e-07</v>
+        <v>2.024338570341661e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.035528358597278e-07</v>
+        <v>2.035528358597287e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.652243621182585e-07</v>
+        <v>1.652243621182583e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.016976908924971e-07</v>
+        <v>2.016976908924939e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.977811955026923e-07</v>
+        <v>1.977811955026925e-07</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.324683471897823e-08</v>
+        <v>3.324683471897905e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.472773116637275e-08</v>
+        <v>3.47277311663719e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.132952436413462e-08</v>
+        <v>5.132952436413515e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.170205109611821e-08</v>
+        <v>3.170205109611755e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.760183882395909e-08</v>
+        <v>4.760183882395944e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.047259389502772e-08</v>
+        <v>3.047259389502716e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.838944329850798e-08</v>
+        <v>4.838944329850807e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.822962336321627e-08</v>
+        <v>5.822962336321701e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.803185860918282e-08</v>
+        <v>3.80318586091831e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.409449781686935e-08</v>
+        <v>8.409449781686903e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.791505682233021e-08</v>
+        <v>3.791505682233172e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.267643793356263e-08</v>
+        <v>3.267643793356391e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.897337280640227e-08</v>
+        <v>7.897337280640031e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.83014672033252e-08</v>
+        <v>3.830146720332553e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.969225538407237e-08</v>
+        <v>3.969225538407249e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.942678611453331e-08</v>
+        <v>4.942678611453312e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>4.413278349092303e-08</v>
+        <v>4.413278349092424e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.906185340016819e-08</v>
+        <v>3.90618534001668e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.513450877652979e-08</v>
+        <v>5.513450877653173e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.829391319861909e-08</v>
+        <v>3.829391319861957e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.63256774850091e-08</v>
+        <v>3.632567748500918e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.99145222024309e-08</v>
+        <v>5.991452220243217e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.754806321576424e-08</v>
+        <v>3.754806321576489e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.935246228778173e-08</v>
+        <v>3.935246228778182e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.462079302455132e-08</v>
+        <v>3.462079302455142e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.640129227498252e-08</v>
+        <v>3.640129227498315e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.021066087005254e-08</v>
+        <v>3.021066087005447e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.451996620131727e-07</v>
+        <v>1.451996620131735e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.901391039374884e-07</v>
+        <v>1.901391039374877e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>5.455885171121829e-07</v>
+        <v>5.455885171121836e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.221440647012483e-07</v>
+        <v>1.221440647012481e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>4.771361385096601e-07</v>
+        <v>4.7713613850966e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>9.469839278985921e-08</v>
+        <v>9.469839278984736e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.032315480310026e-07</v>
+        <v>5.032315480310037e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.004959514471399e-07</v>
+        <v>7.004959514471384e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.482494349515354e-07</v>
+        <v>2.48249434951534e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.232362603010012e-06</v>
+        <v>1.232362603010014e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.46784012278542e-07</v>
+        <v>2.467840122785407e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.508497002456455e-07</v>
+        <v>1.508497002456471e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.907675825222859e-07</v>
+        <v>2.907675825222855e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>2.348388382460113e-07</v>
+        <v>2.348388382460114e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>2.686846827507167e-07</v>
+        <v>2.686846827507171e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.945493451387681e-07</v>
+        <v>4.945493451387671e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>4.020201474343878e-07</v>
+        <v>4.020201474343886e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.605495664239441e-07</v>
+        <v>2.605495664239434e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>6.2902515973341e-07</v>
+        <v>6.290251597334114e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.500744601410567e-07</v>
+        <v>2.500744601410558e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.945539617861245e-07</v>
+        <v>1.945539617861251e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>6.939278699859761e-07</v>
+        <v>6.939278699859725e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.494158065508071e-07</v>
+        <v>2.494158065508061e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.780479917250211e-07</v>
+        <v>2.780479917250212e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.743255793246626e-07</v>
+        <v>1.743255793246625e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.194411878630021e-07</v>
+        <v>2.194411878630002e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.00060153468154e-07</v>
+        <v>1.000601534681542e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.664943143087372e-08</v>
+        <v>4.245461050594961e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.393550695334086e-08</v>
+        <v>4.393550695334246e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.473212107602975e-08</v>
+        <v>5.473212107602872e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.090982688308746e-08</v>
+        <v>3.510464780801112e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.100443553585419e-08</v>
+        <v>5.680961461093e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.387519060692195e-08</v>
+        <v>3.968036968199771e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.759721908547827e-08</v>
+        <v>5.759721908547863e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.743739915018898e-08</v>
+        <v>6.163222007511052e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.143445532107638e-08</v>
+        <v>4.723963439615367e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.749709452876134e-08</v>
+        <v>8.749709452876268e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.712283260930267e-08</v>
+        <v>4.131765353422529e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.607903464545821e-08</v>
+        <v>3.607903464545748e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>8.242157537409766e-08</v>
+        <v>8.242157537409822e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>4.847606451891378e-08</v>
+        <v>4.847606451891379e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.986707873324714e-08</v>
+        <v>4.986707873324854e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.282938282642773e-08</v>
+        <v>5.282938282642669e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.334055927789558e-08</v>
+        <v>4.753538020281781e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>4.82696291871377e-08</v>
+        <v>4.826962918713737e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.853710548842634e-08</v>
+        <v>5.853710548842524e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.168284713706523e-08</v>
+        <v>4.168284713706428e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.553345327197983e-08</v>
+        <v>4.553345327197974e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.382013739759188e-08</v>
+        <v>7.008925915198511e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.6755839002737e-08</v>
+        <v>4.675583900273546e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.307126139337241e-08</v>
+        <v>4.307126139337296e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.802338973644585e-08</v>
+        <v>3.8023389736445e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.560906806195352e-08</v>
+        <v>3.98038889868767e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.360139115301309e-08</v>
+        <v>3.360139115301355e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.79402247210459e-08</v>
+        <v>3.794022472104459e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.942112116843525e-08</v>
+        <v>3.942112116843746e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.602291436620084e-08</v>
+        <v>5.602291436620071e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.639544109817918e-08</v>
+        <v>3.639544109818312e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.229522882602219e-08</v>
+        <v>5.229522882602495e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.51659838970891e-08</v>
+        <v>3.51659838970927e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.308283330057126e-08</v>
+        <v>5.308283330057363e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.292301336528056e-08</v>
+        <v>6.292301336528254e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.272524861124693e-08</v>
+        <v>4.272524861124865e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>8.878788781893581e-08</v>
+        <v>8.878788781893469e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>4.260844682439941e-08</v>
+        <v>4.260844682439729e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.736982793562821e-08</v>
+        <v>3.736982793562946e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>8.366676280846567e-08</v>
+        <v>8.36667628084659e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>4.299459442617373e-08</v>
+        <v>4.299459442617482e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.438538260691735e-08</v>
+        <v>4.438538260692177e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.412017611659931e-08</v>
+        <v>5.412017611659868e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.882617349298731e-08</v>
+        <v>4.882617349298979e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>4.375524340222952e-08</v>
+        <v>4.375524340223233e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.982789877859561e-08</v>
+        <v>5.982789877859729e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>4.297936470632267e-08</v>
+        <v>4.297936470632205e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>4.10190674870736e-08</v>
+        <v>4.101906748707474e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.460791220449549e-08</v>
+        <v>6.460791220449778e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.224145321782752e-08</v>
+        <v>4.224145321783045e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.403218951639163e-08</v>
+        <v>4.403218951639851e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.931418302661456e-08</v>
+        <v>3.931418302661698e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.109468227704537e-08</v>
+        <v>4.109468227704871e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.490405087211768e-08</v>
+        <v>3.490405087212003e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.344019274975788e-08</v>
+        <v>4.344019274976142e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.339587677121684e-08</v>
+        <v>5.339587677121798e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.999766996898189e-08</v>
+        <v>6.999766996898121e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>5.037019670095692e-08</v>
+        <v>4.585762231421019e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.911546970840364e-08</v>
+        <v>5.911546970840642e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.914073949986791e-08</v>
+        <v>5.089804190938757e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7057588903352e-08</v>
+        <v>6.705758890335418e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.689776896806493e-08</v>
+        <v>7.689776896806307e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.670000421402406e-08</v>
+        <v>5.670000421402918e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.027626434217173e-07</v>
+        <v>1.027626434217152e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.658320242717694e-08</v>
+        <v>5.658320242717782e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.1344583538405e-08</v>
+        <v>5.134458353841121e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>9.107214023280235e-08</v>
+        <v>9.107214023280211e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>5.220555677907689e-08</v>
+        <v>5.220555677907698e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.315381687992493e-08</v>
+        <v>5.315381687992497e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.795465496716272e-08</v>
+        <v>5.795465496716602e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>6.280092909576418e-08</v>
+        <v>6.280092909577035e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.772999900501017e-08</v>
+        <v>5.772999900501288e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.380265438137826e-08</v>
+        <v>7.380265438137785e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.173780974155416e-08</v>
+        <v>5.281660513271358e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>5.49938230898533e-08</v>
+        <v>5.268265343366709e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.858433331681497e-08</v>
+        <v>7.858433331681569e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.685266317141824e-08</v>
+        <v>4.685266317141996e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.644117088508312e-08</v>
+        <v>6.644117088508425e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.328893862939381e-08</v>
+        <v>4.465672752761423e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.506943787982687e-08</v>
+        <v>5.506943787982923e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.773143071926139e-08</v>
+        <v>5.773143071926219e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.063228988845211e-08</v>
+        <v>8.063228988845351e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.608752547958723e-08</v>
+        <v>9.608752547958753e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.126893186773472e-07</v>
+        <v>1.126893186773508e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>9.306184540933464e-08</v>
+        <v>8.983662921957876e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.089616331371778e-07</v>
+        <v>7.674696018171139e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.183238820824198e-08</v>
+        <v>9.183239377806507e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.097492376117209e-07</v>
+        <v>1.097492376117237e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.195894176764291e-07</v>
+        <v>1.195894176764327e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>9.939165292239622e-08</v>
+        <v>9.939165292239871e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.454542921300774e-07</v>
+        <v>1.454542921300848e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.927485113554648e-08</v>
+        <v>9.927485113554741e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>9.403623224677906e-08</v>
+        <v>9.403623224677957e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.403331671196143e-07</v>
+        <v>1.40333167119616e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>1.042923466265874e-07</v>
+        <v>1.04292346626593e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>1.066903151513931e-07</v>
+        <v>1.066903151513977e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.107865859975719e-07</v>
+        <v>1.107865859975711e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.054925778041359e-07</v>
+        <v>1.054925778041399e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.004216477133829e-07</v>
+        <v>1.004216477133825e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>1.164943030897453e-07</v>
+        <v>1.164943030897474e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>9.964004473838128e-08</v>
+        <v>9.964004473838635e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.76854717982271e-08</v>
+        <v>1.138115645111915e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.212743165156409e-07</v>
+        <v>1.212743165156479e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>9.890785752897587e-08</v>
+        <v>9.890785752898056e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.006985938275432e-07</v>
+        <v>1.006985938275486e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.598058733776657e-08</v>
+        <v>8.755530569252661e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.776108658819527e-08</v>
+        <v>9.776108658819878e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.157045518327178e-08</v>
+        <v>9.157045518327011e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.919252339906991e-07</v>
+        <v>1.91925233990699e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.874002461935941e-07</v>
+        <v>3.874002461935942e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.922462744884781e-07</v>
+        <v>1.922462744884778e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.920016444077441e-07</v>
+        <v>1.92001644407744e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.919764309244743e-07</v>
+        <v>1.919764309244741e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.922489633678648e-07</v>
+        <v>1.922489633678645e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.926026346960703e-07</v>
+        <v>1.9260263469607e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.921283747294612e-07</v>
+        <v>1.92128374729461e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.923374398818618e-07</v>
+        <v>1.923374398818617e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.923492746069896e-07</v>
+        <v>1.923492746069895e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.921514464251641e-07</v>
+        <v>1.921514464251639e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.921030319441765e-07</v>
+        <v>1.921030319441763e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.924637754762009e-07</v>
+        <v>1.924637754762007e-07</v>
       </c>
       <c r="O2" t="n">
         <v>1.002359734795807e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.923213349221915e-07</v>
+        <v>1.923213349221913e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.920675317903155e-07</v>
+        <v>1.920675317903153e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.921384995080735e-07</v>
+        <v>1.921384995080734e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.923322054419431e-07</v>
+        <v>1.923322054419429e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.921648378271504e-07</v>
+        <v>1.921648378271503e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.328015680703769e-07</v>
+        <v>4.328015680703768e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.925009493409524e-07</v>
+        <v>1.925009493409522e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.050480998252022e-07</v>
+        <v>3.05048099825202e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.925651375738767e-07</v>
+        <v>1.925651375738766e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.922194753567989e-07</v>
+        <v>1.922194753567987e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.696176428218712e-07</v>
+        <v>1.696176428218711e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.929747827871683e-07</v>
+        <v>1.92974782787168e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91947725827275e-07</v>
+        <v>1.919477258272749e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1534,34 +1534,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.950914319204465e-07</v>
+        <v>1.950914319204467e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.195424762328214e-07</v>
+        <v>5.195424762328215e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.973857990415438e-07</v>
+        <v>1.973857990415435e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.956364345837486e-07</v>
+        <v>1.956364345837484e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.954615340067673e-07</v>
+        <v>1.954615340067672e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.973882787108615e-07</v>
+        <v>1.973882787108614e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.999515200997599e-07</v>
+        <v>1.999515200997598e-07</v>
       </c>
       <c r="I3" t="n">
         <v>1.965482251080121e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.980266971572144e-07</v>
+        <v>1.980266971572143e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.981084622703473e-07</v>
+        <v>1.981084622703472e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.967003512193873e-07</v>
@@ -1570,49 +1570,49 @@
         <v>1.964339454702833e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.989430963092208e-07</v>
+        <v>1.989430963092209e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.40943493771963e-08</v>
+        <v>4.409434937719634e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.979016939996372e-07</v>
+        <v>1.979016939996371e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.961070824626988e-07</v>
+        <v>1.961070824626987e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.966235902679491e-07</v>
+        <v>1.966235902679492e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.979799366604207e-07</v>
+        <v>1.979799366604208e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.968093564208191e-07</v>
+        <v>1.968093564208189e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.9447811725508e-07</v>
+        <v>5.944781172550799e-07</v>
       </c>
       <c r="V3" t="n">
         <v>1.991771554484716e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.953363190110624e-07</v>
+        <v>3.953363190110625e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.996552640695811e-07</v>
+        <v>1.996552640695812e-07</v>
       </c>
       <c r="Y3" t="n">
         <v>1.971951665830816e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.606383867311642e-07</v>
+        <v>1.606383867311643e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.025885887589172e-07</v>
+        <v>2.025885887589173e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.953066174309644e-07</v>
+        <v>1.953066174309648e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.477972920624976e-08</v>
+        <v>2.477972920624987e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.846159733796198e-08</v>
+        <v>2.846159733796183e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.840602931458668e-08</v>
+        <v>2.840602931458687e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.564282001730106e-08</v>
+        <v>2.564282001730127e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.535802212499301e-08</v>
+        <v>2.535802212499312e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.843640144420593e-08</v>
+        <v>2.843640144420641e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.243128179313495e-08</v>
+        <v>3.243128179313516e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.707429729992376e-08</v>
+        <v>2.707429729992391e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.951955490650175e-08</v>
+        <v>2.951955490650187e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.956946303557187e-08</v>
+        <v>2.956946303557205e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.733490271639195e-08</v>
+        <v>2.733490271639213e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.691245839804228e-08</v>
+        <v>2.691245839804246e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.530801890766355e-07</v>
+        <v>1.530801890766349e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.55115713209702e-08</v>
+        <v>2.551157132097034e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.925387144288652e-08</v>
+        <v>2.925387144288663e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.638704831313781e-08</v>
+        <v>2.638704831313764e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.718866133197825e-08</v>
+        <v>2.718866133197847e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>2.937665896416645e-08</v>
+        <v>2.937665896416653e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.748616476217818e-08</v>
+        <v>2.748616476217809e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.775529271861269e-08</v>
+        <v>2.775529271861272e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.184120735523902e-08</v>
+        <v>3.184120735523905e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.260666822655171e-08</v>
+        <v>5.260666822655189e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.200773454843175e-08</v>
+        <v>3.200773454843221e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.739717965919896e-08</v>
+        <v>2.739717965919891e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.970849064005921e-08</v>
+        <v>2.970849064005942e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.663486567866772e-08</v>
+        <v>3.663486567866798e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.512239898479422e-08</v>
+        <v>2.512239898479459e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.131049326480091e-08</v>
+        <v>4.131049326480109e-08</v>
       </c>
       <c r="C5" t="n">
         <v>1.067921355623109e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.070463611872904e-07</v>
+        <v>1.070463611872906e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>5.639829412441236e-08</v>
+        <v>5.639829412441245e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.397785052318176e-08</v>
+        <v>5.397785052318198e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.892349142553741e-08</v>
+        <v>9.89234914255382e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.898273519046069e-07</v>
+        <v>1.898273519046071e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.550450277987402e-08</v>
+        <v>8.550450277987405e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.202883676608862e-07</v>
+        <v>1.202883676608859e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.211697648597252e-07</v>
+        <v>1.211697648597253e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>8.361637798084487e-08</v>
+        <v>8.361637798084481e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.212050454018459e-08</v>
+        <v>8.212050454018478e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.530801890766355e-07</v>
+        <v>1.530801890766349e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>5.288688023454683e-08</v>
+        <v>5.288688023454716e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.117731748605941e-07</v>
+        <v>1.117731748605937e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.977177757753581e-08</v>
+        <v>6.977177757753585e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>8.913584593210905e-08</v>
+        <v>8.91358459321093e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.142864985511646e-07</v>
+        <v>1.142864985511645e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>9.325150500392216e-08</v>
+        <v>9.325150500392218e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.003227414484052e-07</v>
+        <v>1.003227414484054e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44869387801804e-07</v>
+        <v>1.448693878018044e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>5.329289047815363e-07</v>
+        <v>5.329289047815364e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.674957163417692e-07</v>
+        <v>1.674957163417694e-07</v>
       </c>
       <c r="Y5" t="n">
         <v>1.020211612083684e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.159157018135571e-07</v>
+        <v>1.159157018135573e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.543435226507763e-07</v>
+        <v>2.543435226507766e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.074705218773597e-08</v>
+        <v>5.074705218773638e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.142211339119844e-08</v>
+        <v>2.72830730414431e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.510398152291059e-08</v>
+        <v>3.096494117315521e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.504841349953526e-08</v>
+        <v>3.504841349953583e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.228520420224971e-08</v>
+        <v>2.81461638524945e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.200040630994168e-08</v>
+        <v>2.786136596018647e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.09397452793993e-08</v>
+        <v>3.507878562915498e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.493462562832833e-08</v>
+        <v>3.907366597808371e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.957764113511711e-08</v>
+        <v>3.371668148487291e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.202289874169497e-08</v>
+        <v>3.616193909145079e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.621184722052054e-08</v>
+        <v>3.207280687076533e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.98382465515853e-08</v>
+        <v>3.397728690134107e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.941580223323559e-08</v>
+        <v>3.355484258299138e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.530801890766355e-07</v>
+        <v>1.530801890766349e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.311721435326594e-08</v>
+        <v>3.311721435326616e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.147425597435923e-08</v>
+        <v>3.684781687483583e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.302943249808625e-08</v>
+        <v>3.30294324980867e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.969200516717164e-08</v>
+        <v>3.383104551692744e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.188000279935979e-08</v>
+        <v>3.60190431491155e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.412854894712675e-08</v>
+        <v>2.998950859737117e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.09647776886685e-08</v>
+        <v>3.510381803842386e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.434455119043226e-08</v>
+        <v>3.848359154018775e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.549862294535867e-08</v>
+        <v>5.549862294535873e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.451107838362529e-08</v>
+        <v>3.451107838362553e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.083676466696549e-08</v>
+        <v>3.08367646669655e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.635087482500787e-08</v>
+        <v>3.221183447525265e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.91382095138609e-08</v>
+        <v>3.913820951386105e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.762567521642575e-08</v>
+        <v>2.762567521642593e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.76884265804301e-08</v>
+        <v>2.768842658043027e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.137029471214228e-08</v>
+        <v>3.137029471214217e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.131472668876695e-08</v>
+        <v>3.131472668876716e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.855151739148139e-08</v>
+        <v>2.855151739148155e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.826671949917337e-08</v>
+        <v>2.826671949917352e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.134509881838621e-08</v>
+        <v>3.13450988183867e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.533997916731532e-08</v>
+        <v>3.533997916731545e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.998299467410401e-08</v>
+        <v>2.998299467410421e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.242825228068203e-08</v>
+        <v>3.242825228068216e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.247816040975217e-08</v>
+        <v>3.247816040975239e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.024360009057221e-08</v>
+        <v>3.024360009057241e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.982115577222255e-08</v>
+        <v>2.982115577222275e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.530801890766355e-07</v>
+        <v>1.530801890766349e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>2.842022720304352e-08</v>
+        <v>2.842022720304368e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.216252732495978e-08</v>
+        <v>3.216252732495998e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.929574568731791e-08</v>
+        <v>2.929574568731802e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.009735870615853e-08</v>
+        <v>3.009735870615871e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.228535633834671e-08</v>
+        <v>3.228535633834677e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.039486213635845e-08</v>
+        <v>3.039486213635839e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.11533905840599e-08</v>
+        <v>3.115339058406005e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.47499047294193e-08</v>
+        <v>3.474990472941932e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.551536560073204e-08</v>
+        <v>5.551536560073227e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.491643192261226e-08</v>
+        <v>3.491643192261248e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.101201816824147e-08</v>
+        <v>3.101201816824151e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.26171880142395e-08</v>
+        <v>3.261718801423968e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.954356305284797e-08</v>
+        <v>3.95435630528482e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.803109635897457e-08</v>
+        <v>2.803109635897492e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.148813330228429e-08</v>
+        <v>3.148813330228456e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.083664752258923e-08</v>
+        <v>4.083664752258935e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.078107949921396e-08</v>
+        <v>4.078107949921433e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.801787020192831e-08</v>
+        <v>3.500054831999123e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.294922345150013e-08</v>
+        <v>3.294922345150015e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.08114516288333e-08</v>
+        <v>4.198646760824311e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.480633197776218e-08</v>
+        <v>4.480633197776246e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.944934748455101e-08</v>
+        <v>3.944934748455136e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.189460509112901e-08</v>
+        <v>4.18946050911291e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.19445132201991e-08</v>
+        <v>4.194451322019945e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.970995290101918e-08</v>
+        <v>3.970995290101945e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.928750858266951e-08</v>
+        <v>3.928750858265503e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.530801890766355e-07</v>
+        <v>1.530801890766349e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.470114703222253e-08</v>
+        <v>3.470114703222281e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.814755183093248e-08</v>
+        <v>3.814755183093279e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.198182712412816e-08</v>
+        <v>3.198182712412832e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.956371151660548e-08</v>
+        <v>3.956371151660583e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.17517091487937e-08</v>
+        <v>4.175170914879389e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.986121494680531e-08</v>
+        <v>3.986121494680555e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.719183512044739e-08</v>
+        <v>3.790273317763901e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.421625753986621e-08</v>
+        <v>4.248224863778409e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.498283204649963e-08</v>
+        <v>6.498283204649993e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.812187271910566e-08</v>
+        <v>3.812187271910579e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.582529766684321e-08</v>
+        <v>4.582529766684351e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.208354082468655e-08</v>
+        <v>3.631163387776668e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.900991586329505e-08</v>
+        <v>4.900991586329528e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.341673482465122e-08</v>
+        <v>4.341673482465137e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.284488316156757e-08</v>
+        <v>5.284488316156746e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.489949327772251e-08</v>
+        <v>6.489949327772252e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.484392525434733e-08</v>
+        <v>6.484392525434741e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.208071595706174e-08</v>
+        <v>6.014832393335178e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.179591806475375e-08</v>
+        <v>4.249445811411496e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.487429738396661e-08</v>
+        <v>6.487430086094649e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.886917773289567e-08</v>
+        <v>6.886917773289561e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.351219323968444e-08</v>
+        <v>6.351219323968449e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.595745084626239e-08</v>
+        <v>6.595745084626246e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.600735897533256e-08</v>
+        <v>6.600735897533252e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.377279865615261e-08</v>
+        <v>6.377279865615265e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.335035433780293e-08</v>
+        <v>6.335035433780297e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.530801890766355e-07</v>
+        <v>1.530801890766349e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>6.472418762045021e-08</v>
+        <v>6.472418762045037e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>6.906994105823876e-08</v>
+        <v>6.906994105823896e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.282494772987823e-08</v>
+        <v>6.282494772987829e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.362655727173895e-08</v>
+        <v>6.362655727173897e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>6.581455490392714e-08</v>
+        <v>6.581455490392724e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.392406070193862e-08</v>
+        <v>6.392406070193868e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.489932979323588e-08</v>
+        <v>6.489932979323577e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.827910329499957e-08</v>
+        <v>7.794107194528794e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.904456416631243e-08</v>
+        <v>8.904456416631245e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>6.844563048819253e-08</v>
+        <v>6.844563048819258e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.454121673382168e-08</v>
+        <v>6.454121673382179e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.614638657981971e-08</v>
+        <v>6.109836907713754e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.30727616184283e-08</v>
+        <v>7.307276161842842e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.156029492455498e-08</v>
+        <v>6.156029492455503e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.932088916912401e-07</v>
+        <v>1.93208891691239e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.889770041259029e-07</v>
+        <v>3.889770041259026e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.936404817908353e-07</v>
+        <v>1.936404817908343e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.934660444625423e-07</v>
+        <v>1.934660444625412e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.939558370218122e-07</v>
+        <v>1.939558370218112e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.931530493530419e-07</v>
+        <v>1.93153049353041e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.941398764040934e-07</v>
+        <v>1.941398764040924e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.946603471445557e-07</v>
+        <v>1.946603471445547e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.936610577505529e-07</v>
+        <v>1.936610577505549e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.97037736665442e-07</v>
+        <v>1.970377366654409e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.932803222523402e-07</v>
+        <v>1.932803222523392e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.932327661931984e-07</v>
+        <v>1.932327661931986e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.957814223033672e-07</v>
+        <v>1.957814223033661e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.035012203380032e-07</v>
+        <v>1.035012203380043e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.937363494056304e-07</v>
+        <v>1.937363494056295e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.942554086116692e-07</v>
+        <v>1.942554086116732e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.942925889465708e-07</v>
+        <v>1.942925889465698e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.937347748501689e-07</v>
+        <v>1.93734774850168e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.939568657475584e-07</v>
+        <v>1.939568657475574e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.348922301204053e-07</v>
+        <v>4.348922301204075e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.934942424655199e-07</v>
+        <v>1.93494242465519e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.085445847999652e-07</v>
+        <v>3.085445847999673e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.938711781183533e-07</v>
+        <v>1.938711781183523e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.940900022947075e-07</v>
+        <v>1.940900022947098e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.71911156189164e-07</v>
+        <v>1.719111561891661e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.936718258199004e-07</v>
+        <v>1.936718258199049e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.931618844533096e-07</v>
+        <v>1.931618844533098e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.974065565662278e-07</v>
+        <v>1.974065565662293e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.218898114440516e-07</v>
+        <v>5.218898114440522e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.005103855384423e-07</v>
+        <v>2.005103855384438e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.992481802534383e-07</v>
+        <v>1.992481802534394e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.027696223246938e-07</v>
+        <v>2.027696223246956e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.970112485661393e-07</v>
+        <v>1.970112485661406e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.041056406243075e-07</v>
+        <v>2.041056406243087e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.078199270604526e-07</v>
+        <v>2.078199270604541e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.006400867066929e-07</v>
+        <v>2.006400867066969e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.247048435703795e-07</v>
+        <v>2.247048435703807e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.979232803199715e-07</v>
+        <v>1.97923280319973e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.976816210740912e-07</v>
+        <v>1.976816210740917e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.158009793096574e-07</v>
+        <v>2.158009793096588e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>5.099581169685183e-08</v>
+        <v>5.099581169685458e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.011596116545718e-07</v>
+        <v>2.011596116545733e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.048976136000397e-07</v>
+        <v>2.048976136000426e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.05193266381243e-07</v>
+        <v>2.051932663812443e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.011515935765007e-07</v>
+        <v>2.011515935765043e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.027749424184483e-07</v>
+        <v>2.027749424184496e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.97812247964571e-07</v>
+        <v>5.978122479645733e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.994320630991939e-07</v>
+        <v>1.994320630991951e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.080034260152383e-07</v>
+        <v>4.080034260152407e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.021549253633562e-07</v>
+        <v>2.021549253633598e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.03701160050359e-07</v>
+        <v>2.037011600503614e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.637133544834043e-07</v>
+        <v>1.637133544834059e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.007195651074153e-07</v>
+        <v>2.007195651074177e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.971483464943192e-07</v>
+        <v>1.971483464943194e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.923043458350005e-08</v>
+        <v>2.923043458350029e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.195649832990494e-08</v>
+        <v>3.195649832990515e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.410544329968407e-08</v>
+        <v>3.410544329968431e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.213509343147916e-08</v>
+        <v>3.213509343147936e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.766752570414104e-08</v>
+        <v>3.766752570414122e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.859966968480838e-08</v>
+        <v>2.859966968480885e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.974633518930625e-08</v>
+        <v>3.974633518930643e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.562529163119704e-08</v>
+        <v>4.562529163119726e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.442165611863511e-08</v>
+        <v>3.442165611863547e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.247899992281963e-08</v>
+        <v>7.247899992281977e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.003727563080742e-08</v>
+        <v>3.003727563080805e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.966093782849564e-08</v>
+        <v>2.966093782849596e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.828835127002536e-08</v>
+        <v>5.828835127002552e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.269403742354878e-08</v>
+        <v>3.269403742354898e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.518831211007734e-08</v>
+        <v>3.518831211007757e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.105132462137358e-08</v>
+        <v>4.105132462137379e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>4.147129360782874e-08</v>
+        <v>4.147129360782896e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.517052678180794e-08</v>
+        <v>3.517052678180816e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.767914563468142e-08</v>
+        <v>3.76791456346816e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.225647495211217e-08</v>
+        <v>3.225647495211246e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.301212235051611e-08</v>
+        <v>3.301212235051643e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>7.081679380824816e-08</v>
+        <v>7.081679380824842e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.671126444455307e-08</v>
+        <v>3.671126444455327e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.920172899253628e-08</v>
+        <v>3.920172899253652e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.224911274188423e-08</v>
+        <v>3.224911274188443e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.445948852700135e-08</v>
+        <v>3.445948852700156e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.88061494426463e-08</v>
+        <v>2.880614944264653e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.639502671857442e-08</v>
+        <v>8.639502671857496e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.448810783608419e-07</v>
+        <v>1.448810783608421e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.91668008538883e-07</v>
+        <v>1.916680085388831e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.448262153884486e-07</v>
+        <v>1.44826215388449e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>2.637639359367672e-07</v>
+        <v>2.637639359367678e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.627138040314559e-08</v>
+        <v>7.627138040315756e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.155944456617562e-07</v>
+        <v>3.155944456617559e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.265645541526183e-07</v>
+        <v>4.265645541526182e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.86608006541069e-07</v>
+        <v>1.866080065410739e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.883564793667161e-07</v>
+        <v>8.883564793667145e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.054994285076506e-07</v>
+        <v>1.054994285076587e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.041502368366038e-07</v>
+        <v>1.041502368366063e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.708411763244969e-07</v>
+        <v>1.708411763244978e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.440249298612975e-07</v>
+        <v>1.440249298612977e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.926853405460894e-07</v>
+        <v>1.926853405460902e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.221462009274725e-07</v>
+        <v>3.221462009274727e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>3.469354987769928e-07</v>
+        <v>3.469354987769935e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.941396465794063e-07</v>
+        <v>1.941396465794074e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6285911953639e-07</v>
+        <v>2.628591195363897e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.447905551946523e-07</v>
+        <v>1.447905551946534e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.417479910468919e-07</v>
+        <v>1.417479910468924e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>8.811054553996581e-07</v>
+        <v>8.811054553996613e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.398533697339526e-07</v>
+        <v>2.398533697339536e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.779544979856354e-07</v>
+        <v>2.779544979856367e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.414664783401771e-07</v>
+        <v>1.414664783401772e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.902845235734799e-07</v>
+        <v>1.902845235734808e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.911742738953746e-08</v>
+        <v>8.911742738953778e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.748648812634936e-08</v>
+        <v>3.238165192711076e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.021255187275423e-08</v>
+        <v>4.021255187275414e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.725666064329485e-08</v>
+        <v>4.236149684253325e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.528631077508993e-08</v>
+        <v>3.528631077508985e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.592357924699033e-08</v>
+        <v>4.08187430477517e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.685572322765769e-08</v>
+        <v>3.175088702841933e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.289755253291703e-08</v>
+        <v>4.800238873215536e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.877650897480783e-08</v>
+        <v>4.87765089748077e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.267770966148441e-08</v>
+        <v>4.267770966148437e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.563021726643042e-08</v>
+        <v>8.073505346566877e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.318849297441822e-08</v>
+        <v>3.31884929744185e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.281215517210643e-08</v>
+        <v>3.28121551721064e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.145106799961616e-08</v>
+        <v>6.14510679996163e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>4.181843391164526e-08</v>
+        <v>4.181843391164592e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.431042360285544e-08</v>
+        <v>4.431042360285597e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.420254196498466e-08</v>
+        <v>4.930737816422274e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.462251095143951e-08</v>
+        <v>4.97273471506779e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.83217441254187e-08</v>
+        <v>4.342658032465715e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.59351991775307e-08</v>
+        <v>4.083036297829208e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.049378368303019e-08</v>
+        <v>3.538894748379162e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.126817589336541e-08</v>
+        <v>4.126817589336539e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.994225531886606e-08</v>
+        <v>7.994225531886689e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.986248178816385e-08</v>
+        <v>4.496731798740225e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.26032513075901e-08</v>
+        <v>4.260325130759074e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.540033008549501e-08</v>
+        <v>4.050516628473339e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.271554206985064e-08</v>
+        <v>3.761070587061205e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.193551907580385e-08</v>
+        <v>3.193551907580415e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.323586913387705e-08</v>
+        <v>3.323586913387728e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.596193288028187e-08</v>
+        <v>3.596193288028215e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.8110877850061e-08</v>
+        <v>3.811087785006127e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.614052798185611e-08</v>
+        <v>3.614052798185636e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>4.167296025451796e-08</v>
+        <v>4.167296025451825e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.260510423518537e-08</v>
+        <v>3.260510423518587e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.375176973968319e-08</v>
+        <v>4.375176973968342e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.963072618157397e-08</v>
+        <v>4.963072618157425e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.842709066901207e-08</v>
+        <v>3.842709066901245e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.648443447319656e-08</v>
+        <v>7.648443447319675e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.404271018118436e-08</v>
+        <v>3.404271018118504e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.366637237887256e-08</v>
+        <v>3.366637237887293e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.229378582040225e-08</v>
+        <v>6.22937858204025e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>3.669925029847477e-08</v>
+        <v>3.669925029847495e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.919352498500321e-08</v>
+        <v>3.919352498500351e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.505675917175052e-08</v>
+        <v>4.505675917175078e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.547672815820569e-08</v>
+        <v>4.547672815820595e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.917596133218485e-08</v>
+        <v>3.917596133218514e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.168458018505833e-08</v>
+        <v>4.168458018505857e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.624008400978027e-08</v>
+        <v>3.624008400978069e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.701755690089312e-08</v>
+        <v>3.701755690089341e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.482222835862516e-08</v>
+        <v>7.482222835862537e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.071669899493003e-08</v>
+        <v>4.071669899493028e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.318841873098205e-08</v>
+        <v>4.318841873098224e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.625454729226119e-08</v>
+        <v>3.625454729226144e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.846492307737833e-08</v>
+        <v>3.846492307737854e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.281158399302331e-08</v>
+        <v>3.281158399302352e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.804388134014367e-08</v>
+        <v>3.804388134014405e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.814662810448178e-08</v>
+        <v>4.814662810448232e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.029557307426092e-08</v>
+        <v>5.02955730742615e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.832522320605599e-08</v>
+        <v>4.4397357102942e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.763017345868675e-08</v>
+        <v>4.763017345868714e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.478979945938535e-08</v>
+        <v>4.631940273568492e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.59364649638831e-08</v>
+        <v>5.593646496388364e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>6.181542140577389e-08</v>
+        <v>6.181542140577442e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.061178589321184e-08</v>
+        <v>5.061178589321262e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.866912969739645e-08</v>
+        <v>8.866912969739704e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.622740540538427e-08</v>
+        <v>4.622740540538522e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.585106760307249e-08</v>
+        <v>4.585106760307056e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>6.876031760653674e-08</v>
+        <v>6.876031760653713e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.473740470886192e-08</v>
+        <v>4.473740470886252e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.684649105394831e-08</v>
+        <v>4.684649105394877e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.841508480764982e-08</v>
+        <v>4.841508480765023e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.76614233824056e-08</v>
+        <v>5.766142338240611e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.136065655638478e-08</v>
+        <v>5.136065655638535e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.386927540925827e-08</v>
+        <v>5.386927540925879e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.388655279621652e-08</v>
+        <v>4.482518371412913e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.920225212509306e-08</v>
+        <v>4.718364960652e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.700837328540109e-08</v>
+        <v>8.700837328540191e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.475111227054824e-08</v>
+        <v>4.475111227054867e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.270379162053041e-08</v>
+        <v>6.2703791620531e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.843924251646108e-08</v>
+        <v>4.092553382656291e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.064961830157824e-08</v>
+        <v>5.064961830157873e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.270184143255005e-08</v>
+        <v>5.270184143255049e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.710381656389929e-08</v>
+        <v>6.710381656390141e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.107727604205826e-08</v>
+        <v>8.107727604205778e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.322622101183735e-08</v>
+        <v>8.322622101183697e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.125587114363241e-08</v>
+        <v>7.866002147467426e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.678830341629431e-08</v>
+        <v>6.085998079884486e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.772044739696226e-08</v>
+        <v>7.772045180234521e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.886711290145959e-08</v>
+        <v>8.88671129014591e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.474606934335034e-08</v>
+        <v>9.474606934334987e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.354243383078618e-08</v>
+        <v>8.35424338307881e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.215997776349729e-07</v>
+        <v>1.215997776349725e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>7.915805334296071e-08</v>
+        <v>7.915805334296068e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.878171554064892e-08</v>
+        <v>7.878171554064858e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.074091289821786e-07</v>
+        <v>1.074091289821781e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>8.554219321931766e-08</v>
+        <v>8.55421932193162e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.884710772989809e-08</v>
+        <v>8.884710772989888e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.017210673891217e-08</v>
+        <v>9.017210673891006e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>9.059207131998208e-08</v>
+        <v>9.059207131998156e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.429130449396119e-08</v>
+        <v>8.429130449396083e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.679992334683471e-08</v>
+        <v>8.679992334683421e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.135850785233415e-08</v>
+        <v>8.135850785233383e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.213290006267126e-08</v>
+        <v>9.511215764214849e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.199375715204015e-07</v>
+        <v>1.199375715204011e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>8.583204215670641e-08</v>
+        <v>8.583204215670593e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.830376189275796e-08</v>
+        <v>8.83037618927579e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.136989045403752e-08</v>
+        <v>7.458871273457135e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.358026623915694e-08</v>
+        <v>8.358026623915424e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.792692715480048e-08</v>
+        <v>7.792692715479921e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.92580741546474e-07</v>
+        <v>1.925807415464741e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.89289735914209e-07</v>
+        <v>3.892897359142094e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.933495865085497e-07</v>
+        <v>1.933495865085498e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.933031138471579e-07</v>
+        <v>1.93303113847158e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.927681778823581e-07</v>
+        <v>1.927681778823583e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.926704296488886e-07</v>
+        <v>1.926704296488888e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.933011697889114e-07</v>
+        <v>1.933011697889116e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.930679133317214e-07</v>
+        <v>1.930679133317215e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.93042554109675e-07</v>
+        <v>1.930425541096752e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.928297760218945e-07</v>
+        <v>1.928297760218946e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.925512191916411e-07</v>
+        <v>1.925512191916414e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9274094658752e-07</v>
+        <v>1.927409465875204e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.941144717659464e-07</v>
+        <v>1.941144717659465e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.020892522780097e-07</v>
+        <v>1.020892522780101e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.931360296650206e-07</v>
+        <v>1.931360296650207e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.931607784101148e-07</v>
+        <v>1.931607784101149e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.933010731988189e-07</v>
+        <v>1.933010731988191e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.931156723954669e-07</v>
+        <v>1.931156723954672e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.928849268404215e-07</v>
+        <v>1.928849268404216e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.339936156601399e-07</v>
+        <v>4.339936156601404e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.929845032461251e-07</v>
+        <v>1.929845032461252e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.071701960494647e-07</v>
+        <v>3.07170196049465e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.932147396683464e-07</v>
+        <v>1.932147396683465e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.930744062654064e-07</v>
+        <v>1.930744062654067e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.709658596698547e-07</v>
+        <v>1.709658596698549e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.930733113624449e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.926398077034692e-07</v>
+        <v>1.926398077034695e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3254,76 +3254,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.960371055544751e-07</v>
+        <v>1.960371055544753e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.268546032392325e-07</v>
+        <v>5.268546032392329e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.01544683947029e-07</v>
+        <v>2.015446839470293e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.011950063189716e-07</v>
+        <v>2.011950063189717e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.973855304289103e-07</v>
+        <v>1.973855304289106e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.966753444070227e-07</v>
+        <v>1.966753444070232e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.01218200844733e-07</v>
+        <v>2.012182008447334e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.995338202544107e-07</v>
+        <v>1.995338202544112e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.993338945173684e-07</v>
+        <v>1.993338945173687e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.978134170814204e-07</v>
+        <v>1.978134170814205e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.958293665656496e-07</v>
+        <v>1.958293665656498e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.972684156711951e-07</v>
+        <v>1.972684156711954e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.070036490973967e-07</v>
+        <v>2.070036490973968e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.759009417295351e-08</v>
+        <v>4.759009417295371e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99984348634879e-07</v>
+        <v>1.999843486348792e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.001826330141804e-07</v>
+        <v>2.001826330141806e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.012099682299264e-07</v>
+        <v>2.012099682299266e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.998429769982604e-07</v>
+        <v>1.998429769982608e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.982218891157534e-07</v>
+        <v>1.982218891157535e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.973343332472774e-07</v>
+        <v>5.97334333247278e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.989016752077975e-07</v>
+        <v>1.989016752077976e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.045292561580305e-07</v>
+        <v>4.045292561580309e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.005754897835145e-07</v>
+        <v>2.005754897835146e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9956392403949e-07</v>
+        <v>1.995639240394904e-07</v>
       </c>
       <c r="Z3" t="n">
         <v>1.623573678558734e-07</v>
@@ -3332,7 +3332,7 @@
         <v>1.995576532385865e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.965210841791569e-07</v>
+        <v>1.965210841791572e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.647993195265372e-08</v>
+        <v>2.647993195265379e-08</v>
       </c>
       <c r="C4" t="n">
         <v>3.909344141930494e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.516438948545565e-08</v>
+        <v>3.516438948545575e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.463945939655415e-08</v>
+        <v>3.46394593965542e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.859711159144088e-08</v>
+        <v>2.859711159144093e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.749300032799325e-08</v>
+        <v>2.749300032799335e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.46175003643503e-08</v>
+        <v>3.461750036435039e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1982761377117e-08</v>
+        <v>3.198276137711713e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.17800771912018e-08</v>
+        <v>3.178007719120198e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.929289091404685e-08</v>
+        <v>2.929289091404697e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.614646337386344e-08</v>
+        <v>2.614646337386359e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.842772367575333e-08</v>
+        <v>2.842772367575345e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.380412033235278e-08</v>
+        <v>4.380412033235286e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>2.840283186581383e-08</v>
+        <v>2.840283186581396e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.275216669679246e-08</v>
+        <v>3.275216669679262e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.303171515761625e-08</v>
+        <v>3.303171515761636e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.461640933482183e-08</v>
+        <v>3.461640933482198e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.252222197237859e-08</v>
+        <v>3.252222197237872e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.991584477993976e-08</v>
+        <v>2.991584477993983e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.223814871483106e-08</v>
+        <v>3.223814871483129e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.159898365210982e-08</v>
+        <v>3.159898365211003e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.627812286191754e-08</v>
+        <v>6.627812286191764e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.364123239274898e-08</v>
+        <v>3.364123239274914e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.203609525139767e-08</v>
+        <v>3.203609525139772e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.063100267444712e-08</v>
+        <v>3.06310026744473e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.204373461735392e-08</v>
+        <v>3.204373461735405e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.723672957494561e-08</v>
+        <v>2.723672957494567e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.583805756487045e-08</v>
+        <v>5.583805756487093e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.773202200309237e-07</v>
+        <v>2.773202200309238e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.199536481915362e-07</v>
+        <v>2.199536481915366e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.013413870197211e-07</v>
+        <v>2.013413870197209e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>9.881975700084544e-08</v>
+        <v>9.881975700084563e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.278696776297079e-08</v>
+        <v>7.27869677629712e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.201632657532128e-07</v>
+        <v>2.20163265753213e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.63397220632796e-07</v>
+        <v>1.633972206327964e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.486017946495768e-07</v>
+        <v>1.486017946495769e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.050405920067949e-07</v>
+        <v>1.050405920067952e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>5.147588953195528e-08</v>
+        <v>5.147588953195542e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>9.693719944293069e-08</v>
+        <v>9.69371994429311e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.668950375230852e-07</v>
+        <v>1.668950375230864e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>8.558681701093412e-08</v>
+        <v>8.558681701093434e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.58545593855832e-07</v>
+        <v>1.585455938558329e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.74710134485182e-07</v>
+        <v>1.747101344851824e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.162348726070301e-07</v>
+        <v>2.162348726070299e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.56509673841956e-07</v>
+        <v>1.565096738419569e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.237582859617027e-07</v>
+        <v>1.237582859617033e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.553490727041527e-07</v>
+        <v>1.553490727041538e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.281990197345043e-07</v>
+        <v>1.281990197345035e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>7.652934596483069e-07</v>
+        <v>7.65293459648306e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.894976659678336e-07</v>
+        <v>1.894976659678348e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.562801613754626e-07</v>
+        <v>1.562801613754636e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.206267770798624e-07</v>
+        <v>1.206267770798629e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.568613421576856e-07</v>
+        <v>1.568613421576861e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.633805625817435e-08</v>
+        <v>7.633805625817455e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.39086057939694e-08</v>
+        <v>2.938369098453401e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.199720045118512e-08</v>
+        <v>4.199720045118541e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.259306332677134e-08</v>
+        <v>4.259306332677139e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.754321842843432e-08</v>
+        <v>3.75432184284346e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.150087062332108e-08</v>
+        <v>3.6025785432757e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.492167416930894e-08</v>
+        <v>3.039675935987357e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.752125939623048e-08</v>
+        <v>3.752125939623071e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.941143521843266e-08</v>
+        <v>3.488652040899732e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.920875103251748e-08</v>
+        <v>3.920875103251759e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2196649945927e-08</v>
+        <v>3.672156475536417e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.357513721517913e-08</v>
+        <v>2.905022240574374e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.585639751706905e-08</v>
+        <v>3.585639751706886e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.669164852721467e-08</v>
+        <v>4.669164852721473e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.660691622259522e-08</v>
+        <v>3.129036006067586e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.095148209363014e-08</v>
+        <v>4.095148209363034e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.046038899893193e-08</v>
+        <v>4.04603889989324e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.204508317613751e-08</v>
+        <v>4.204508317613736e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.542598100425874e-08</v>
+        <v>3.542598100425887e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.281960381181996e-08</v>
+        <v>3.281960381182021e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.968682935473624e-08</v>
+        <v>3.516191454530098e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.902765749342551e-08</v>
+        <v>3.902765749342569e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.448321771393809e-08</v>
+        <v>6.961925024466842e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.654499142462918e-08</v>
+        <v>3.654499142462936e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.517194112370253e-08</v>
+        <v>3.517194112370283e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.805967651576279e-08</v>
+        <v>3.353476170632743e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.494749364923412e-08</v>
+        <v>3.947240845866983e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.009788993838338e-08</v>
+        <v>3.009788993838344e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.979664221694109e-08</v>
+        <v>2.979664221694132e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.241015168359233e-08</v>
+        <v>4.241015168359251e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.848109974974306e-08</v>
+        <v>3.848109974974321e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.795616966084154e-08</v>
+        <v>3.79561696608417e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.191382185572827e-08</v>
+        <v>3.191382185572844e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.080971059228062e-08</v>
+        <v>3.080971059228086e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.793421062863767e-08</v>
+        <v>3.7934210628638e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.529947164140438e-08</v>
+        <v>3.529947164140464e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.50967874554892e-08</v>
+        <v>3.509678745548934e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.260960117833422e-08</v>
+        <v>3.260960117833436e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.946317363815081e-08</v>
+        <v>2.946317363815106e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.174443394004072e-08</v>
+        <v>3.174443394004081e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.712083059664017e-08</v>
+        <v>4.712083059664055e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>3.171941502977229e-08</v>
+        <v>3.17194150297728e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.606874986075082e-08</v>
+        <v>3.606874986075104e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.634842542190366e-08</v>
+        <v>3.63484254219039e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.793311959910922e-08</v>
+        <v>3.79331195991096e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.583893223666592e-08</v>
+        <v>3.583893223666627e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.323255504422717e-08</v>
+        <v>3.32325550442276e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.548092654534928e-08</v>
+        <v>3.548092654534971e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.491569391639725e-08</v>
+        <v>3.491569391639745e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.959483312620492e-08</v>
+        <v>6.95948331262051e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.695794265703638e-08</v>
+        <v>3.695794265703646e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.537281231427454e-08</v>
+        <v>3.537281231427482e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.39477129387345e-08</v>
+        <v>3.394771293873445e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.53604448816413e-08</v>
+        <v>3.536044488164158e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.0553439839233e-08</v>
+        <v>3.055343983923344e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.393744279905955e-08</v>
+        <v>3.393744279905975e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.283442268399428e-08</v>
+        <v>5.283442268399466e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.890537075014502e-08</v>
+        <v>4.890537075014482e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.838044066124354e-08</v>
+        <v>4.503467801928107e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.703351368970045e-08</v>
+        <v>3.70335136897004e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.123398159268257e-08</v>
+        <v>4.253690011497278e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.835848162903961e-08</v>
+        <v>4.835848162903977e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.572374264180636e-08</v>
+        <v>4.572374264180618e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.552105845589117e-08</v>
+        <v>4.552105845589141e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.303387217873619e-08</v>
+        <v>4.303387217873669e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.988744463855273e-08</v>
+        <v>3.988744463855291e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.216870494044273e-08</v>
+        <v>4.216870494043937e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.267436081482306e-08</v>
+        <v>5.267436081482332e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.861159419433879e-08</v>
+        <v>3.86115941943391e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.263282497896005e-08</v>
+        <v>4.263282497896029e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.925438066033831e-08</v>
+        <v>3.925438066033846e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.835739059951119e-08</v>
+        <v>4.835739059951131e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.626320323706785e-08</v>
+        <v>4.62632032370686e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.36568260446291e-08</v>
+        <v>4.365682604462909e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.20643500270489e-08</v>
+        <v>4.285955661732787e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.533996491679914e-08</v>
+        <v>4.354240940569698e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.002033898382046e-08</v>
+        <v>8.002033898382077e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.043979042954305e-08</v>
+        <v>4.043979042954334e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.192022278393171e-08</v>
+        <v>5.192022278393192e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.437198393913646e-08</v>
+        <v>3.79717948340872e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.578471588204328e-08</v>
+        <v>4.57847158820435e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.754132108359219e-08</v>
+        <v>4.754132108359213e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.754555514694519e-08</v>
+        <v>5.754555514694523e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.942290753431147e-08</v>
+        <v>7.94229075343122e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.549385560046218e-08</v>
+        <v>7.549385560046211e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.496892551156066e-08</v>
+        <v>7.283087085191228e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.892657770644741e-08</v>
+        <v>4.757088718943278e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.78224664429998e-08</v>
+        <v>6.78224696930143e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.494696647935688e-08</v>
+        <v>7.494696647935884e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.231222749212354e-08</v>
+        <v>7.231222749212325e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.210954330620835e-08</v>
+        <v>7.210954330620928e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.962235702905343e-08</v>
+        <v>6.962235702905467e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.647592948886996e-08</v>
+        <v>6.64759294888693e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.875718979075986e-08</v>
+        <v>6.875718979075975e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.413358644735932e-08</v>
+        <v>8.413358644735869e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.180232772184253e-08</v>
+        <v>7.180232772184331e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.681934064183208e-08</v>
+        <v>7.681934064183099e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.336118452263793e-08</v>
+        <v>7.336118452263775e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.494587544982837e-08</v>
+        <v>7.494587544982741e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.285168808738511e-08</v>
+        <v>7.285168808738577e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.024531089494631e-08</v>
+        <v>7.024531089494606e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.258762162842705e-08</v>
+        <v>7.258762162842669e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.192844976711636e-08</v>
+        <v>8.26187284449296e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06607588976924e-07</v>
+        <v>1.066075889769233e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>7.397069850775551e-08</v>
+        <v>7.39706985077559e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.23855681649937e-08</v>
+        <v>7.238556816499286e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.096046878945362e-08</v>
+        <v>6.53751965718594e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.237320073236046e-08</v>
+        <v>7.237320073236023e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.756619568995215e-08</v>
+        <v>6.756619568995409e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4029,40 +4029,40 @@
         <v>1.9234119550481e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.891186021222809e-07</v>
+        <v>3.891186021222812e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.924247748305905e-07</v>
+        <v>1.924247748305906e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.926744699888825e-07</v>
+        <v>1.926744699888826e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.925957599279823e-07</v>
+        <v>1.925957599279825e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.924352131310106e-07</v>
+        <v>1.924352131310107e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92953228269539e-07</v>
+        <v>1.929532282695389e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.92544633799028e-07</v>
+        <v>1.925446337990281e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.927215819436512e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.924979078848972e-07</v>
+        <v>1.924979078848973e-07</v>
       </c>
       <c r="L2" t="n">
         <v>1.923998400884298e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.924537913178801e-07</v>
+        <v>1.924537913178802e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.933634996302576e-07</v>
+        <v>1.933634996302577e-07</v>
       </c>
       <c r="O2" t="n">
         <v>1.012176236388424e-07</v>
@@ -4074,25 +4074,25 @@
         <v>1.928215805067579e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.929418374919799e-07</v>
+        <v>1.9294183749198e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.92777712635919e-07</v>
+        <v>1.927777126359191e-07</v>
       </c>
       <c r="T2" t="n">
         <v>1.926421495641024e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.333944084178288e-07</v>
+        <v>4.333944084178291e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.927896063606149e-07</v>
+        <v>1.92789606360615e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.059906378693028e-07</v>
+        <v>3.059906378693034e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.927547880326967e-07</v>
+        <v>1.927547880326966e-07</v>
       </c>
       <c r="Y2" t="n">
         <v>1.926534025563647e-07</v>
@@ -4101,10 +4101,10 @@
         <v>1.69909822879766e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.928833969344496e-07</v>
+        <v>1.928833969344497e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.923238018028206e-07</v>
+        <v>1.923238018028205e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4114,46 +4114,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.962090947436803e-07</v>
+        <v>1.962090947436804e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.275754444825438e-07</v>
+        <v>5.275754444825437e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.968143079262802e-07</v>
+        <v>1.968143079262803e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.985825266684259e-07</v>
+        <v>1.985825266684258e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.980392015200332e-07</v>
+        <v>1.980392015200333e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.968771739759057e-07</v>
+        <v>1.968771739759055e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.006172784077921e-07</v>
+        <v>2.006172784077919e-07</v>
       </c>
       <c r="I3" t="n">
         <v>1.976750406267939e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.989251752904594e-07</v>
+        <v>1.989251752904595e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.973296878428774e-07</v>
+        <v>1.973296878428773e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.966305557591779e-07</v>
+        <v>1.966305557591777e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.970882853257323e-07</v>
+        <v>1.970882853257322e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.035245969430181e-07</v>
+        <v>2.035245969430182e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.589642362855311e-08</v>
+        <v>4.589642362855318e-08</v>
       </c>
       <c r="P3" t="n">
         <v>1.994564330157433e-07</v>
@@ -4162,28 +4162,28 @@
         <v>1.996394430937193e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.005276011182622e-07</v>
+        <v>2.005276011182624e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.993132853517427e-07</v>
+        <v>1.993132853517425e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.983741881245468e-07</v>
+        <v>1.983741881245469e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.978264260169373e-07</v>
+        <v>5.978264260169375e-07</v>
       </c>
       <c r="V3" t="n">
         <v>1.993885405490407e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.012791542235227e-07</v>
+        <v>4.012791542235228e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.991680475466366e-07</v>
+        <v>1.991680475466364e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.984462087269922e-07</v>
+        <v>1.98446208726992e-07</v>
       </c>
       <c r="Z3" t="n">
         <v>1.602076401337814e-07</v>
@@ -4192,7 +4192,7 @@
         <v>2.000877387250959e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.961392307488121e-07</v>
+        <v>1.961392307488118e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.64661408644221e-08</v>
+        <v>2.646614086442215e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.998650998821859e-08</v>
+        <v>3.998650998821857e-08</v>
       </c>
       <c r="D4" t="n">
         <v>2.741020779750246e-08</v>
@@ -4214,73 +4214,73 @@
         <v>3.023062947585827e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.934156312957371e-08</v>
+        <v>2.93415631295738e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.75281132026044e-08</v>
+        <v>2.752811320260424e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.337933249101731e-08</v>
+        <v>3.337933249101716e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.876406998385446e-08</v>
+        <v>2.876406998385439e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.084662001218793e-08</v>
+        <v>3.084662001218774e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.823627928876347e-08</v>
+        <v>2.823627928876326e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.712855841424887e-08</v>
+        <v>2.712855841424871e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.785586432397118e-08</v>
+        <v>2.785586432397115e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.80135362444844e-08</v>
+        <v>3.801353624448435e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>2.668211377941399e-08</v>
+        <v>2.668211377941396e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.163544578298383e-08</v>
+        <v>3.16354457829837e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.189231044944278e-08</v>
+        <v>3.189231044944273e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.325066841847147e-08</v>
+        <v>3.325066841847146e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.139680266810003e-08</v>
+        <v>3.139680266809977e-08</v>
       </c>
       <c r="T4" t="n">
         <v>2.986555540983747e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.406634376657465e-08</v>
+        <v>3.406634376657443e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.209044023376811e-08</v>
+        <v>3.209044023376804e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.240544236585592e-08</v>
+        <v>6.240544236585559e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.113785872886401e-08</v>
+        <v>3.113785872886391e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.991061458213052e-08</v>
+        <v>2.991061458213021e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.860728466499928e-08</v>
+        <v>2.860728466499936e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.259055543718238e-08</v>
+        <v>3.25905554371822e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.634406148118363e-08</v>
+        <v>2.634406148118351e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.317764580887519e-08</v>
+        <v>6.317764580887427e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.99293873163323e-07</v>
+        <v>2.992938731633218e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>8.438532738684076e-08</v>
+        <v>8.438532738683967e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.270823728929892e-07</v>
+        <v>1.270823728929883e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.209099335475917e-07</v>
+        <v>1.209099335475911e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>8.044236784545213e-08</v>
+        <v>8.044236784544858e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.062168626383526e-07</v>
+        <v>2.062168626383485e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.110737160837386e-07</v>
+        <v>1.110737160837358e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.39899098794655e-07</v>
+        <v>1.398990987946524e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.558878073871152e-08</v>
+        <v>9.55887807387074e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.640250735112558e-08</v>
+        <v>7.640250735112147e-08</v>
       </c>
       <c r="M5" t="n">
         <v>9.37324097415903e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.94491230804304e-07</v>
+        <v>1.944912308043019e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>6.625388432634783e-08</v>
+        <v>6.625388432634558e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.448144160639107e-07</v>
+        <v>1.448144160639067e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.600898380442706e-07</v>
+        <v>1.600898380442676e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.995981187557503e-07</v>
+        <v>1.995981187557493e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.445524780659763e-07</v>
+        <v>1.445524780659714e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.321994339668262e-07</v>
+        <v>1.32199433966826e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.906260868783359e-07</v>
+        <v>1.90626086878331e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.424969105971435e-07</v>
+        <v>1.424969105971438e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>7.063975330947858e-07</v>
+        <v>7.063975330947763e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.494956435635949e-07</v>
+        <v>1.494956435635915e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.301501323437505e-07</v>
+        <v>1.301501323437433e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.360984789442098e-08</v>
+        <v>9.360984789442106e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.761233593472929e-07</v>
+        <v>1.761233593472884e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.819996750668038e-08</v>
+        <v>6.819996750667585e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.932497571220381e-08</v>
+        <v>3.372373687351901e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.28453448360002e-08</v>
+        <v>4.284534483600041e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.02690426452841e-08</v>
+        <v>3.026904264528432e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.308946432363992e-08</v>
+        <v>3.748822548495513e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.220039797735542e-08</v>
+        <v>3.220039797735567e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.038694805038606e-08</v>
+        <v>3.478570921170111e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.063692850011343e-08</v>
+        <v>3.623816733879904e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.162290483163609e-08</v>
+        <v>3.162290483163624e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.370545485996962e-08</v>
+        <v>3.81042160212846e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.549387529785956e-08</v>
+        <v>3.549387529786009e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.998739326203053e-08</v>
+        <v>3.438615442334555e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.071469917175286e-08</v>
+        <v>3.071469917175302e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.088010900356963e-08</v>
+        <v>4.088010900356945e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.954868653849927e-08</v>
+        <v>3.471755456148491e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.966472869437952e-08</v>
+        <v>3.420845069743945e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.914990645853898e-08</v>
+        <v>3.914990645853958e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.050826442756759e-08</v>
+        <v>4.050826442756833e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.865439867719614e-08</v>
+        <v>3.865439867719663e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.272439025761904e-08</v>
+        <v>3.712315141893434e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.140598832761149e-08</v>
+        <v>3.700722716629709e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.934803624286425e-08</v>
+        <v>3.494927508154991e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.044195419194891e-08</v>
+        <v>7.044195419194847e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.399669357664567e-08</v>
+        <v>3.399669357664577e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.308120080108939e-08</v>
+        <v>3.30812008010891e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.586488067409542e-08</v>
+        <v>3.586488067409621e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.984815144627849e-08</v>
+        <v>3.984815144627905e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.917948254856576e-08</v>
+        <v>2.91794825485655e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.953639104098155e-08</v>
+        <v>2.953639104098148e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.305676016477797e-08</v>
+        <v>4.305676016477789e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.048045797406184e-08</v>
+        <v>3.048045797406179e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.33008796524177e-08</v>
+        <v>3.33008796524176e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.241181330613316e-08</v>
+        <v>3.241181330613312e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.059836337916382e-08</v>
+        <v>3.059836337916357e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.644958266757672e-08</v>
+        <v>3.644958266757647e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183432016041385e-08</v>
+        <v>3.18343201604137e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.391687018874713e-08</v>
+        <v>3.391687018874706e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.130652946532286e-08</v>
+        <v>3.130652946532258e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.019880859080827e-08</v>
+        <v>3.019880859080802e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.092611450053059e-08</v>
+        <v>3.092611450053047e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.108378642104387e-08</v>
+        <v>4.108378642104366e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.975233518866067e-08</v>
+        <v>2.975233518866048e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.470566719223052e-08</v>
+        <v>3.470566719223025e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.496256062600225e-08</v>
+        <v>3.496256062600205e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.632091859503088e-08</v>
+        <v>3.632091859503079e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.446705284465943e-08</v>
+        <v>3.44670528446591e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.293580558639684e-08</v>
+        <v>3.29358055863968e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.696076898971831e-08</v>
+        <v>3.696076898971823e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.516069041032736e-08</v>
+        <v>3.516069041032737e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.547569254241539e-08</v>
+        <v>6.547569254241492e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.420810890542347e-08</v>
+        <v>3.420810890542322e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.306291331063076e-08</v>
+        <v>3.306291331063034e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.167753484155869e-08</v>
+        <v>3.167753484155868e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.566080561374177e-08</v>
+        <v>3.566080561374152e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.941431165774308e-08</v>
+        <v>2.941431165774283e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.358454419187905e-08</v>
+        <v>3.358454419187924e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.312080279691133e-08</v>
+        <v>5.312080279691161e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.054450060619522e-08</v>
+        <v>4.054450060619552e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.336492228455102e-08</v>
+        <v>4.016163859833859e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.739717172624306e-08</v>
+        <v>3.739717172624331e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.066240601129718e-08</v>
+        <v>4.190983988317594e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.651362529971008e-08</v>
+        <v>4.651362529971023e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.18983627925472e-08</v>
+        <v>4.189836279254745e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.398091282088069e-08</v>
+        <v>4.398091282088082e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.137057209745621e-08</v>
+        <v>4.137057209745632e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.026285122294164e-08</v>
+        <v>4.026285122294177e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.099015713266393e-08</v>
+        <v>4.099015713265595e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.648450826263187e-08</v>
+        <v>4.648450826263197e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.64346068291378e-08</v>
+        <v>3.643460682913794e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.107380706326762e-08</v>
+        <v>4.107380706326767e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.782845419445834e-08</v>
+        <v>3.78284541944584e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.638496122716424e-08</v>
+        <v>4.638496122716454e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.45310954767928e-08</v>
+        <v>4.453109547679285e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.29998482185302e-08</v>
+        <v>4.299984821853054e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.33931887485853e-08</v>
+        <v>4.414658640777518e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.522473304246087e-08</v>
+        <v>4.33601004257169e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.5540917444917e-08</v>
+        <v>7.554091744491694e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.762537068367415e-08</v>
+        <v>3.76253706836742e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.876657831567792e-08</v>
+        <v>4.876657831567803e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.174157747369206e-08</v>
+        <v>3.561393975894204e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.572484824587514e-08</v>
+        <v>4.572484824587525e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.576245387075757e-08</v>
+        <v>4.576245387075784e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.444271479292998e-08</v>
+        <v>5.444271479292921e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.634995156986955e-08</v>
+        <v>7.634995156986852e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.377364937915342e-08</v>
+        <v>6.377364937915243e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.659407105750929e-08</v>
+        <v>6.465841822184279e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.570500471122477e-08</v>
+        <v>4.637098236782062e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.389155478425539e-08</v>
+        <v>6.389155739639581e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.97427740726683e-08</v>
+        <v>6.974277407266713e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.512751156550547e-08</v>
+        <v>6.512751156550434e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.721006159383879e-08</v>
+        <v>6.721006159383773e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.459972087041444e-08</v>
+        <v>6.459972087041325e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.349199999589985e-08</v>
+        <v>6.349199999589869e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.421930590562219e-08</v>
+        <v>6.421930590562113e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.437697782613544e-08</v>
+        <v>7.437697782613429e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>6.582495579745104e-08</v>
+        <v>6.582495579744995e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.138275914135902e-08</v>
+        <v>7.138275914135791e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.825575464323524e-08</v>
+        <v>6.825575464323429e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.961411000012249e-08</v>
+        <v>6.961411000012145e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>6.7760244249751e-08</v>
+        <v>6.776024424974977e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.622899699148837e-08</v>
+        <v>6.622899699148744e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.051183390016621e-08</v>
+        <v>7.051183390016521e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.845388181541885e-08</v>
+        <v>7.813214932256797e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.876888394750699e-08</v>
+        <v>9.87688839475056e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>6.750130031051506e-08</v>
+        <v>6.750130031051389e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.635610471572234e-08</v>
+        <v>6.635610471572097e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.497072624665031e-08</v>
+        <v>5.99141918784267e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.895399701883338e-08</v>
+        <v>6.895399701883219e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.270750306283468e-08</v>
+        <v>6.270750306283347e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4886,19 +4886,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.926547419487058e-07</v>
+        <v>1.926547419487059e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.878937528100999e-07</v>
+        <v>3.878937528100998e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.937121797481356e-07</v>
+        <v>1.937121797481357e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.928592733978415e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.926979282893792e-07</v>
+        <v>1.926979282893791e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.925859703361389e-07</v>
@@ -4907,19 +4907,19 @@
         <v>1.933014394763227e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.932425665752588e-07</v>
+        <v>1.932425665752587e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.929457124759053e-07</v>
+        <v>1.929457124759052e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.943504203309354e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.932105454226449e-07</v>
+        <v>1.932105454226452e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.926002662198745e-07</v>
+        <v>1.926002662198744e-07</v>
       </c>
       <c r="N2" t="n">
         <v>1.941485907191142e-07</v>
@@ -4931,40 +4931,40 @@
         <v>1.929006178768941e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.931765871694838e-07</v>
+        <v>1.931765871694839e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.930466288125081e-07</v>
+        <v>1.93046628812508e-07</v>
       </c>
       <c r="S2" t="n">
         <v>1.933374194460989e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.929621082081098e-07</v>
+        <v>1.929621082081097e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.338686002845697e-07</v>
+        <v>4.338686002845699e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.926867578144228e-07</v>
+        <v>1.926867578144229e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.068431177636977e-07</v>
+        <v>3.068431177636979e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.934770550101145e-07</v>
+        <v>1.934770550101147e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.929779478158812e-07</v>
+        <v>1.929779478158811e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.707676436085374e-07</v>
+        <v>1.707676436085375e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.931748650894345e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.926647969157877e-07</v>
+        <v>1.926647969157876e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4974,34 +4974,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.971347434499977e-07</v>
+        <v>1.971347434499974e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.18203240834525e-07</v>
+        <v>5.182032408345246e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.047127880767907e-07</v>
+        <v>2.047127880767908e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.986025413618399e-07</v>
+        <v>1.986025413618396e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.974593460973162e-07</v>
+        <v>1.97459346097316e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.966458485586648e-07</v>
+        <v>1.966458485586649e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.017954544646644e-07</v>
+        <v>2.01795454464664e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.013596980354274e-07</v>
+        <v>2.013596980354272e-07</v>
       </c>
       <c r="J3" t="n">
         <v>1.992127791563439e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.092066399943635e-07</v>
+        <v>2.092066399943633e-07</v>
       </c>
       <c r="L3" t="n">
         <v>2.010763313576812e-07</v>
@@ -5013,46 +5013,46 @@
         <v>2.078005690272588e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.817083115681853e-08</v>
+        <v>4.817083115681851e-08</v>
       </c>
       <c r="P3" t="n">
         <v>1.988840617284664e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.008630493727794e-07</v>
+        <v>2.008630493727791e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.999642359344404e-07</v>
+        <v>1.999642359344403e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.019536569914011e-07</v>
+        <v>2.019536569914013e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.993410607717142e-07</v>
+        <v>1.993410607717143e-07</v>
       </c>
       <c r="U3" t="n">
         <v>5.974201203894794e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.973623695280251e-07</v>
+        <v>1.973623695280253e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.032861876462272e-07</v>
+        <v>4.032861876462276e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.030249163361749e-07</v>
+        <v>2.030249163361748e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.994500584594707e-07</v>
+        <v>1.994500584594706e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.620575060077442e-07</v>
+        <v>1.620575060077444e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.008573116871054e-07</v>
+        <v>2.008573116871052e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.972661848812431e-07</v>
+        <v>1.972661848812429e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.850879406372678e-08</v>
+        <v>2.85087940637268e-08</v>
       </c>
       <c r="C4" t="n">
         <v>2.599892385973869e-08</v>
@@ -5071,58 +5071,58 @@
         <v>4.045304045370653e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.081907087082785e-08</v>
+        <v>3.081907087082784e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.899660364832809e-08</v>
+        <v>2.899660364832808e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.773198706327683e-08</v>
+        <v>2.773198706327686e-08</v>
       </c>
       <c r="H4" t="n">
         <v>3.581354013371907e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.514854363332993e-08</v>
+        <v>3.514854363332995e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.187765221088216e-08</v>
+        <v>3.187765221088217e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.766226144160428e-08</v>
+        <v>4.766226144160426e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.478684998409973e-08</v>
+        <v>3.478684998409974e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.80394644137527e-08</v>
+        <v>2.803946441375271e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.538250312987398e-08</v>
+        <v>4.538250312987401e-08</v>
       </c>
       <c r="O4" t="n">
         <v>2.964959792908656e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.128607578112699e-08</v>
+        <v>3.128607578112701e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.440327589307451e-08</v>
+        <v>3.440327589307449e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.293533646723456e-08</v>
+        <v>3.293533646723455e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.621995044394498e-08</v>
+        <v>3.621995044394499e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.198063735916e-08</v>
+        <v>3.198063735916002e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.281675446571789e-08</v>
+        <v>3.28167544657179e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.94184904297284e-08</v>
+        <v>2.941849042972839e-08</v>
       </c>
       <c r="W4" t="n">
         <v>6.484145724466865e-08</v>
@@ -5131,16 +5131,16 @@
         <v>3.779719837503484e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.210069586121679e-08</v>
+        <v>3.21006958612168e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.0694643419155e-08</v>
+        <v>3.069464341915501e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.438382420672162e-08</v>
+        <v>3.438382420672161e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.869571644289646e-08</v>
+        <v>2.869571644289647e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5150,73 +5150,73 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.003877092237286e-08</v>
+        <v>9.0038770922373e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.941925385234582e-08</v>
+        <v>4.941925385234577e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.331526050845206e-07</v>
+        <v>3.331526050845205e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.381964895756707e-07</v>
+        <v>1.381964895756706e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.083717688281906e-07</v>
+        <v>1.083717688281915e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.642520641012666e-08</v>
+        <v>7.642520641012678e-08</v>
       </c>
       <c r="H5" t="n">
         <v>2.53293471252293e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.320562639335217e-07</v>
+        <v>2.320562639335216e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.530234676247609e-07</v>
+        <v>1.530234676247608e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.353700992965608e-07</v>
+        <v>4.353700992965595e-07</v>
       </c>
       <c r="L5" t="n">
         <v>1.947235029047632e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>8.811416771951723e-08</v>
+        <v>8.811416771951718e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.83473776615895e-07</v>
+        <v>1.834737766158952e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.077855664363182e-07</v>
+        <v>1.077855664363183e-07</v>
       </c>
       <c r="P5" t="n">
         <v>1.394866834494055e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.036436950685631e-07</v>
+        <v>2.036436950685632e-07</v>
       </c>
       <c r="R5" t="n">
         <v>1.918528508441183e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.061477272986591e-07</v>
+        <v>2.061477272986592e-07</v>
       </c>
       <c r="T5" t="n">
         <v>1.627077022843906e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.709668851060378e-07</v>
+        <v>1.709668851060377e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.693919043446499e-08</v>
+        <v>9.693919043446455e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>7.855393004632754e-07</v>
+        <v>7.855393004632743e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.774999397048459e-07</v>
+        <v>2.774999397048456e-07</v>
       </c>
       <c r="Y5" t="n">
         <v>1.638379930580567e-07</v>
@@ -5228,7 +5228,7 @@
         <v>2.069203064599099e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.046003507145915e-07</v>
+        <v>1.046003507145913e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.147335902353867e-08</v>
+        <v>3.147335902353817e-08</v>
       </c>
       <c r="C6" t="n">
         <v>3.380942369978851e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.826354029375632e-08</v>
+        <v>4.341760541351789e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.862957071087765e-08</v>
+        <v>3.378363583063921e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.680710348837789e-08</v>
+        <v>3.680710348837794e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.06965520230887e-08</v>
+        <v>3.554248690332666e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.877810509353088e-08</v>
+        <v>3.877810509353045e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.295904347337972e-08</v>
+        <v>3.811310859314131e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.484221717069397e-08</v>
+        <v>3.484221717069355e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.547276128165408e-08</v>
+        <v>5.062682640141558e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.259734982414955e-08</v>
+        <v>3.775141494391111e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.100402937356447e-08</v>
+        <v>3.584996425380253e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.835031988865985e-08</v>
+        <v>4.835031988865987e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.836205362328609e-08</v>
+        <v>3.836205362328611e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.999633962533397e-08</v>
+        <v>3.393886856106105e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.22137757331243e-08</v>
+        <v>4.221377573312431e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.074583630728436e-08</v>
+        <v>3.589990142704591e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>4.403045028399476e-08</v>
+        <v>3.918451540375634e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.494520231897181e-08</v>
+        <v>3.979113719920982e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.068611146006645e-08</v>
+        <v>3.584017657982801e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.23830553895403e-08</v>
+        <v>3.722899026977821e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.828365109968008e-08</v>
+        <v>6.828365109968026e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.076176333484682e-08</v>
+        <v>4.076176333484621e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.535964659764027e-08</v>
+        <v>3.535964659764025e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.365920837896675e-08</v>
+        <v>3.850514325920481e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.73483891665335e-08</v>
+        <v>4.219432404677147e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.16456563032e-08</v>
+        <v>3.164565630319999e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5326,28 +5326,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.204249389304805e-08</v>
+        <v>3.204249389304808e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.953262368905995e-08</v>
+        <v>2.953262368905997e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.398674028302777e-08</v>
+        <v>4.398674028302781e-08</v>
       </c>
       <c r="E7" t="n">
         <v>3.435277070014911e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.253030347764935e-08</v>
+        <v>3.253030347764933e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.126568689259811e-08</v>
+        <v>3.126568689259813e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.934723996304034e-08</v>
+        <v>3.934723996304036e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.868224346265121e-08</v>
+        <v>3.868224346265119e-08</v>
       </c>
       <c r="J7" t="n">
         <v>3.541135204020344e-08</v>
@@ -5356,7 +5356,7 @@
         <v>5.119596127092552e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.8320549813421e-08</v>
+        <v>3.832054981342103e-08</v>
       </c>
       <c r="M7" t="n">
         <v>3.157316424307398e-08</v>
@@ -5368,7 +5368,7 @@
         <v>3.318318608556474e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.481966393760519e-08</v>
+        <v>3.481966393760523e-08</v>
       </c>
       <c r="Q7" t="n">
         <v>3.793697572239579e-08</v>
@@ -5377,31 +5377,31 @@
         <v>3.646903629655584e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.975365027326624e-08</v>
+        <v>3.975365027326625e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.551433718848126e-08</v>
+        <v>3.551433718848129e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.628366897826343e-08</v>
+        <v>3.628366897826344e-08</v>
       </c>
       <c r="V7" t="n">
         <v>3.295219025904967e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.837515707398991e-08</v>
+        <v>6.837515707398994e-08</v>
       </c>
       <c r="X7" t="n">
         <v>4.133089820435612e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.569325284483679e-08</v>
+        <v>3.569325284483682e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.422834324847626e-08</v>
+        <v>3.422834324847628e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.79175240360429e-08</v>
+        <v>3.791752403604291e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>3.222941627221775e-08</v>
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.65498370697966e-08</v>
+        <v>3.654983706979662e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.081982747498889e-08</v>
+        <v>4.08198274749889e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.527394406895669e-08</v>
+        <v>5.527394406895671e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.563997448607804e-08</v>
+        <v>4.202989871024973e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.809386969630256e-08</v>
+        <v>3.809386969630264e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.255289067852703e-08</v>
+        <v>4.395873894042264e-08</v>
       </c>
       <c r="H8" t="n">
         <v>5.063444374896926e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.996944724858012e-08</v>
+        <v>4.996944724858011e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.669855582613238e-08</v>
+        <v>4.669855582613236e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.248316505685447e-08</v>
+        <v>6.248316505685442e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.960775359934991e-08</v>
+        <v>4.960775359934995e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.28603680290029e-08</v>
+        <v>4.286036802898896e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.49478805202092e-08</v>
+        <v>5.494788052020923e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.065923954544073e-08</v>
+        <v>4.065923954544071e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.194169333881359e-08</v>
+        <v>4.19416933388136e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.111192155364594e-08</v>
+        <v>4.111192155364593e-08</v>
       </c>
       <c r="R8" t="n">
         <v>4.775624008248473e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.104085405919518e-08</v>
+        <v>5.104085405919519e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.680154097441022e-08</v>
+        <v>4.680154097441019e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.343319442753955e-08</v>
+        <v>4.42900724589806e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.42393940449786e-08</v>
+        <v>4.227905527854443e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.966369327053037e-08</v>
+        <v>7.966369327053041e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.512723171614597e-08</v>
+        <v>4.512723171614596e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.355509430768648e-08</v>
+        <v>5.355509430768643e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.551554703440519e-08</v>
+        <v>3.860974703582147e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.920472782197182e-08</v>
+        <v>4.920472782197181e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.059875136276735e-08</v>
+        <v>5.059875136276732e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5505,82 +5505,82 @@
         <v>6.550325313823318e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.395155105561175e-08</v>
+        <v>7.395155105561177e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.840566764957958e-08</v>
+        <v>8.84056676495796e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.877169806670087e-08</v>
+        <v>7.624260104341973e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.694923084420115e-08</v>
+        <v>5.168765664868615e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.568461425914986e-08</v>
+        <v>7.56846187853568e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.376616732959213e-08</v>
+        <v>8.376616732959217e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.310117082920296e-08</v>
+        <v>8.310117082920291e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.98302794067552e-08</v>
+        <v>7.983027940675517e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>9.561488863747729e-08</v>
+        <v>9.561488863747725e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.273947717997282e-08</v>
+        <v>8.273947717997283e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.599209160962571e-08</v>
+        <v>7.599209160962575e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>9.333513032574704e-08</v>
+        <v>9.333513032574706e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.12337537180676e-08</v>
+        <v>8.123375371806772e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.366002574820032e-08</v>
+        <v>8.366002574820041e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.23559076151544e-08</v>
+        <v>8.235590761515443e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.088796366310762e-08</v>
+        <v>8.088796366310766e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.417257763981803e-08</v>
+        <v>8.417257763981806e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.993326455503304e-08</v>
+        <v>7.993326455503307e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.082823881588968e-08</v>
+        <v>8.082823881588972e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.737111762560145e-08</v>
+        <v>9.001661321479816e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.127940844405417e-07</v>
+        <v>1.127940844405418e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>8.574982557090785e-08</v>
+        <v>8.574982557090789e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.011218021138857e-08</v>
+        <v>8.01121802113886e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.864727061502801e-08</v>
+        <v>7.204047147347931e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.233645140259469e-08</v>
+        <v>8.233645140259473e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.664834363876953e-08</v>
+        <v>7.664834363876958e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9185777738189e-07</v>
+        <v>1.918577773818836e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.873472606519904e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.922596097571772e-07</v>
+        <v>1.922596097571697e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.919678490837308e-07</v>
+        <v>1.919678490837233e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.918997825349307e-07</v>
+        <v>1.918997825349225e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.922489649106356e-07</v>
+        <v>1.922489649106278e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.926611956316161e-07</v>
+        <v>1.926611956316103e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.921303631441822e-07</v>
+        <v>1.921303631441809e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.922399857902676e-07</v>
+        <v>1.922399857902617e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.921181251588272e-07</v>
+        <v>1.921181251588194e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.919800268915701e-07</v>
+        <v>1.919800268915675e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.919980865616793e-07</v>
+        <v>1.919980865616794e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.92329464238634e-07</v>
+        <v>1.923294642386263e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.00481163999151e-07</v>
+        <v>1.004811639991439e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.920749777157334e-07</v>
+        <v>1.92074977715725e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.919929061475085e-07</v>
+        <v>1.919929061475005e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.920871851253935e-07</v>
+        <v>1.920871851253863e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.924283175403417e-07</v>
+        <v>1.924283175403332e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.920142308739575e-07</v>
+        <v>1.920142308739491e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.317991207695595e-07</v>
+        <v>4.317991207695533e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.922309296344527e-07</v>
+        <v>1.922309296344448e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.041215075833004e-07</v>
+        <v>3.041215075832967e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.924919217081476e-07</v>
+        <v>1.924919217081393e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.920250195128094e-07</v>
+        <v>1.920250195128009e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.69481061867082e-07</v>
+        <v>1.694810618670728e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.92762143527291e-07</v>
+        <v>1.927621435272832e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.918085140076557e-07</v>
+        <v>1.918085140076564e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.95162801742e-07</v>
+        <v>1.951628017419929e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.184105469113033e-07</v>
+        <v>5.184105469113025e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.980319449601082e-07</v>
+        <v>1.980319449601063e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.959499246779717e-07</v>
+        <v>1.959499246779705e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.954680435288079e-07</v>
+        <v>1.954680435288057e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.979307935736591e-07</v>
+        <v>1.979307935736569e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.009280547030178e-07</v>
+        <v>2.009280547030157e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.971164592681649e-07</v>
+        <v>1.971164592681596e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.97878673848698e-07</v>
+        <v>1.978786738486931e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.970180878210408e-07</v>
+        <v>1.97018087821039e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.960297296828356e-07</v>
+        <v>1.960297296828308e-07</v>
       </c>
       <c r="M3" t="n">
         <v>1.962285066263688e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.985264211493141e-07</v>
+        <v>1.985264211493116e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.491732983385785e-08</v>
+        <v>4.491732983385211e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.967054817009614e-07</v>
+        <v>1.967054817009596e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.961237183831754e-07</v>
+        <v>1.961237183831731e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.968107535127811e-07</v>
+        <v>1.968107535127788e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.991980034202996e-07</v>
+        <v>1.991980034202928e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96283486189987e-07</v>
+        <v>1.962834861899848e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.912062129446353e-07</v>
+        <v>5.912062129446299e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.978088684111036e-07</v>
+        <v>1.978088684111027e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.930098064085043e-07</v>
+        <v>3.930098064084967e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.996837693097383e-07</v>
+        <v>1.99683769309736e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.963596471121435e-07</v>
+        <v>1.963596471121422e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.59726275312615e-07</v>
+        <v>1.597262753126115e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.016204465034471e-07</v>
+        <v>2.016204465034404e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.948643313868302e-07</v>
+        <v>1.948643313868299e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.487743015539849e-08</v>
+        <v>2.48774301553981e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.60241670961883e-08</v>
+        <v>2.602416709618798e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.941631168629125e-08</v>
+        <v>2.941631168629098e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.612074066317639e-08</v>
+        <v>2.612074066317602e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.535189768231695e-08</v>
+        <v>2.535189768231664e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.929607324773382e-08</v>
+        <v>2.929607324773353e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.395240887670895e-08</v>
+        <v>3.395240887670868e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.795641173613409e-08</v>
+        <v>2.79564117361339e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.927706712681731e-08</v>
+        <v>2.927706712681727e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.781817806179795e-08</v>
+        <v>2.781817806179755e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.625829460478833e-08</v>
+        <v>2.625829460478807e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.657799797005731e-08</v>
+        <v>2.657799797005694e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.020535018899932e-08</v>
+        <v>3.020535018899907e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>2.609916779174353e-08</v>
+        <v>2.609916779174351e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.733080784324761e-08</v>
+        <v>2.733080784324727e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.640377172536135e-08</v>
+        <v>2.640377172536112e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.746869615104868e-08</v>
+        <v>2.74686961510485e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.132194370654977e-08</v>
+        <v>3.132194370654961e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.664464432046223e-08</v>
+        <v>2.664464432046212e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.476021753626037e-08</v>
+        <v>2.476021753625996e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.964155472975314e-08</v>
+        <v>2.964155472975294e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.078350381342584e-08</v>
+        <v>5.078350381342534e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.20403820412802e-08</v>
+        <v>3.204038204128013e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.670462836860904e-08</v>
+        <v>2.670462836860885e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.799410736124479e-08</v>
+        <v>2.799410736124466e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.509266179668511e-08</v>
+        <v>3.509266179668515e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.440710382983134e-08</v>
+        <v>2.440710382983118e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.627843256483238e-08</v>
+        <v>4.627843256483156e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.867113483503223e-08</v>
+        <v>6.867113483503196e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.272015032288125e-07</v>
+        <v>1.272015032288113e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>6.906427470951607e-08</v>
+        <v>6.906427470951583e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.749393620121794e-08</v>
+        <v>5.749393620121791e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.120267234053582e-07</v>
+        <v>1.120267234053576e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.229617537594945e-07</v>
+        <v>2.22961753759494e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.049844089627641e-07</v>
+        <v>1.049844089627645e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.165157074988632e-07</v>
+        <v>1.165157074988627e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.682436268621473e-08</v>
+        <v>9.682436268621421e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.781328251191432e-08</v>
+        <v>6.781328251191423e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.710364215360973e-08</v>
+        <v>7.710364215360884e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>5.247976447396561e-08</v>
+        <v>5.247976447396504e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.526534671740916e-08</v>
+        <v>6.526534671740843e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>8.578914311159656e-08</v>
+        <v>8.578914311159603e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.145839314297171e-08</v>
+        <v>7.145839314297134e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>9.763210740479641e-08</v>
+        <v>9.763210740479653e-08</v>
       </c>
       <c r="S5" t="n">
         <v>1.412041958693496e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>7.964270837006604e-08</v>
+        <v>7.964270837006595e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.709651041193191e-08</v>
+        <v>4.70965104119312e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.124934156505696e-07</v>
+        <v>1.124934156505699e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>4.797065572751002e-07</v>
+        <v>4.797065572751001e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.704007549583347e-07</v>
+        <v>1.704007549583341e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.136370997453084e-08</v>
+        <v>8.136370997453138e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.441854908742897e-08</v>
+        <v>9.441854908742824e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.2857810735832e-07</v>
+        <v>2.285781073583191e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.124068089106474e-08</v>
+        <v>4.124068089106444e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.737616699444543e-08</v>
+        <v>2.737616699444457e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.283117236449585e-08</v>
+        <v>2.852290393523494e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.191504852533817e-08</v>
+        <v>3.19150485253377e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.292774593148404e-08</v>
+        <v>3.292774593148401e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.215890295062467e-08</v>
+        <v>3.215890295062345e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.610307851604118e-08</v>
+        <v>3.179481008678003e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.075941414501646e-08</v>
+        <v>3.645114571575548e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.045514857518116e-08</v>
+        <v>3.04551485751805e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.608407239512572e-08</v>
+        <v>3.177580396586392e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.031691490084466e-08</v>
+        <v>3.03169149008447e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.306529987309588e-08</v>
+        <v>3.306529987309652e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.907673480910431e-08</v>
+        <v>3.338500323836434e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.271603355722616e-08</v>
+        <v>3.271603355722643e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.860985115997068e-08</v>
+        <v>2.860985115997061e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.490238846514226e-08</v>
+        <v>2.95800964571071e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.321077699366991e-08</v>
+        <v>2.8902508564408e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.427570141935643e-08</v>
+        <v>3.427570141935612e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.812894897485794e-08</v>
+        <v>3.382068054559629e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.345164958876982e-08</v>
+        <v>3.345164958876928e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.732083296601253e-08</v>
+        <v>2.732083296601197e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.214029156880043e-08</v>
+        <v>3.644855999805957e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.364780886087093e-08</v>
+        <v>5.364780886086927e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.453911888032709e-08</v>
+        <v>3.453911888032706e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.94699047755689e-08</v>
+        <v>2.946990477556855e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.480111262955247e-08</v>
+        <v>3.480111262955499e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.759139863573219e-08</v>
+        <v>4.189966706499226e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.689431449072345e-08</v>
+        <v>2.689431449072339e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.775480875557562e-08</v>
+        <v>2.775480875557503e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.89015456963657e-08</v>
+        <v>2.890154569636446e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.229369028646846e-08</v>
+        <v>3.229369028646761e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.899811926335362e-08</v>
+        <v>2.899811926335294e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.822927628249384e-08</v>
+        <v>2.822927628249354e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.217345184791052e-08</v>
+        <v>3.217345184791032e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.682978747688603e-08</v>
+        <v>3.682978747688553e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.083379033631094e-08</v>
+        <v>3.083379033631093e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.215444572699411e-08</v>
+        <v>3.215444572699385e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.069555666197467e-08</v>
+        <v>3.069555666197456e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.913567320496537e-08</v>
+        <v>2.913567320496476e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.945537657023464e-08</v>
+        <v>2.945537657023385e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.308272878917656e-08</v>
+        <v>3.308272878917569e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.897647106200304e-08</v>
+        <v>2.897647106200234e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.020811111350696e-08</v>
+        <v>3.020811111350639e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.928115032553821e-08</v>
+        <v>2.928115032553766e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.034607475122569e-08</v>
+        <v>3.034607475122548e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.419932230672707e-08</v>
+        <v>3.419932230672669e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.952202292063928e-08</v>
+        <v>2.952202292063865e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.752229056119145e-08</v>
+        <v>2.752229056119073e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.251893332993002e-08</v>
+        <v>3.251893332992977e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.366088241360286e-08</v>
+        <v>5.366088241360239e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.491776064145761e-08</v>
+        <v>3.491776064145679e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.964388555949138e-08</v>
+        <v>2.964388555949059e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.087148596142181e-08</v>
+        <v>3.087148596142128e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.79700403968626e-08</v>
+        <v>3.797004039686203e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.728448243000846e-08</v>
+        <v>2.728448243000814e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.147653679999104e-08</v>
+        <v>3.147653679999085e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.816941135482252e-08</v>
+        <v>3.816941135482186e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.156155594492542e-08</v>
+        <v>4.156155594492419e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.826598492181043e-08</v>
+        <v>3.53128302474301e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.281502774561373e-08</v>
+        <v>3.281502774561325e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.144131750636782e-08</v>
+        <v>4.259134526866406e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.609765313534322e-08</v>
+        <v>4.609765313534178e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.010165599476778e-08</v>
+        <v>4.010165599476747e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.142231138545161e-08</v>
+        <v>4.142231138545083e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.996342232043221e-08</v>
+        <v>3.996342232043109e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.840353886342201e-08</v>
+        <v>3.84035388634217e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.872324222869127e-08</v>
+        <v>3.872324222865552e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.805140994261792e-08</v>
+        <v>3.805140994261749e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.512668076545932e-08</v>
+        <v>3.512668076545883e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.606871808598633e-08</v>
+        <v>3.606871808598574e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.19129357501571e-08</v>
+        <v>3.191293575015681e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.961394040968247e-08</v>
+        <v>3.961394040968176e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.346718796518392e-08</v>
+        <v>4.34671879651831e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.878988857909648e-08</v>
+        <v>3.878988857909548e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.342565561378727e-08</v>
+        <v>3.412308962670152e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.178679898838736e-08</v>
+        <v>4.011956769188945e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.292983802560758e-08</v>
+        <v>6.292983802560643e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.805786058559906e-08</v>
+        <v>3.805786058559861e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.419134623183496e-08</v>
+        <v>4.419134623183456e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.013935161987913e-08</v>
+        <v>3.449019165410442e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.723790605531907e-08</v>
+        <v>4.723790605531844e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.234575256684156e-08</v>
+        <v>4.2345752566841e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.560807129384217e-08</v>
+        <v>5.560807129384158e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.58424795751839e-08</v>
+        <v>6.584247957518427e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.923462416528637e-08</v>
+        <v>6.923462416528909e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.593905314217117e-08</v>
+        <v>6.384165809256072e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.517021016131225e-08</v>
+        <v>4.422064334065381e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.911438572673111e-08</v>
+        <v>6.911438888304979e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.377072135570423e-08</v>
+        <v>7.377072135570799e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.777472421512967e-08</v>
+        <v>6.777472421512822e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.909537960581389e-08</v>
+        <v>6.909537960581382e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.76364905407948e-08</v>
+        <v>6.763649054079357e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.607660708378378e-08</v>
+        <v>6.607660708378518e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.639631044905255e-08</v>
+        <v>6.639631044905073e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.002366266799476e-08</v>
+        <v>7.002366266799462e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>6.892912685602672e-08</v>
+        <v>6.892912685603049e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.081574768223308e-08</v>
+        <v>7.081574768223594e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.622208736067778e-08</v>
+        <v>6.62220873606765e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.728700863004453e-08</v>
+        <v>6.728700863004317e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.11402561855456e-08</v>
+        <v>7.114025618554626e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.646295679945612e-08</v>
+        <v>6.646295679945732e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.464040860596112e-08</v>
+        <v>6.464040860596295e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.94598672087496e-08</v>
+        <v>7.994684847493045e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.060181629242152e-08</v>
+        <v>9.060181629242328e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.185869452027544e-08</v>
+        <v>7.185869452027729e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.658481943830895e-08</v>
+        <v>6.658481943830887e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.781241984023965e-08</v>
+        <v>6.233336338249348e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.491097427568065e-08</v>
+        <v>7.491097427568389e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.42254163088268e-08</v>
+        <v>6.422541630883071e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.913341662172316e-07</v>
+        <v>1.913341662172314e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.866251865372947e-07</v>
+        <v>3.866251865372946e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.916468344807999e-07</v>
+        <v>1.916468344807998e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.913956894975486e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.913854912555596e-07</v>
+        <v>1.913854912555597e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.915663228549716e-07</v>
@@ -6630,31 +6630,31 @@
         <v>1.915139080894949e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.916316182663675e-07</v>
+        <v>1.916316182663676e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.914759051469314e-07</v>
+        <v>1.914759051469315e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.914134544952545e-07</v>
+        <v>1.914134544952546e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.915200428009644e-07</v>
+        <v>1.915200428009643e-07</v>
       </c>
       <c r="N2" t="n">
         <v>1.917257107021091e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.936372320121815e-08</v>
+        <v>9.93637232012182e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.914332078842669e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.913920517118234e-07</v>
+        <v>1.913920517118233e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.914640333737635e-07</v>
+        <v>1.914640333737634e-07</v>
       </c>
       <c r="S2" t="n">
         <v>1.91716001395068e-07</v>
@@ -6663,13 +6663,13 @@
         <v>1.914996261936098e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.307342904486767e-07</v>
+        <v>4.307342904486766e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.91860458509421e-07</v>
+        <v>1.918604585094209e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.023257017324193e-07</v>
+        <v>3.023257017324194e-07</v>
       </c>
       <c r="X2" t="n">
         <v>1.919688281181968e-07</v>
@@ -6678,10 +6678,10 @@
         <v>1.914058793555727e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.684550903730727e-07</v>
+        <v>1.684550903730728e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9219287175202e-07</v>
+        <v>1.921928717520202e-07</v>
       </c>
       <c r="AB2" t="n">
         <v>1.913591437621497e-07</v>
@@ -6694,22 +6694,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.948200796537643e-07</v>
+        <v>1.948200796537645e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.173649039152519e-07</v>
+        <v>5.173649039152513e-07</v>
       </c>
       <c r="D3" t="n">
         <v>1.970565604257785e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.952596342634006e-07</v>
+        <v>1.952596342634007e-07</v>
       </c>
       <c r="F3" t="n">
         <v>1.951932506140078e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96466779076882e-07</v>
+        <v>1.964667790768821e-07</v>
       </c>
       <c r="H3" t="n">
         <v>1.997412934715881e-07</v>
@@ -6718,7 +6718,7 @@
         <v>1.961116142363037e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.969386206577891e-07</v>
+        <v>1.969386206577892e-07</v>
       </c>
       <c r="K3" t="n">
         <v>1.958345334931227e-07</v>
@@ -6733,7 +6733,7 @@
         <v>1.976169020657211e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.335384724744271e-08</v>
+        <v>4.33538472474427e-08</v>
       </c>
       <c r="P3" t="n">
         <v>1.955224204822172e-07</v>
@@ -6745,34 +6745,34 @@
         <v>1.957569911280159e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.975290213158148e-07</v>
+        <v>1.975290213158146e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.960074288410241e-07</v>
+        <v>1.960074288410239e-07</v>
       </c>
       <c r="U3" t="n">
         <v>5.907579267191712e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.985556068854811e-07</v>
+        <v>1.98555606885481e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.879743221370162e-07</v>
+        <v>3.879743221370164e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.993410419607721e-07</v>
+        <v>1.993410419607719e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.953358236671589e-07</v>
+        <v>1.953358236671588e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.579148352989493e-07</v>
+        <v>1.579148352989495e-07</v>
       </c>
       <c r="AA3" t="n">
         <v>2.009536344590291e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.950344774884105e-07</v>
+        <v>1.950344774884103e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6785,67 +6785,67 @@
         <v>2.429672361217204e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.466971670616806e-08</v>
+        <v>2.466971670616805e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.782845548368564e-08</v>
+        <v>2.782845548368566e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.499165736546238e-08</v>
+        <v>2.499165736546236e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.487646353077372e-08</v>
+        <v>2.487646353077373e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.691903963277785e-08</v>
+        <v>2.691903963277795e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.204473631486794e-08</v>
+        <v>3.2044736314868e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.632699074473542e-08</v>
+        <v>2.632699074473543e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.774066466261851e-08</v>
+        <v>2.774066466261855e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.589773002626314e-08</v>
+        <v>2.589773002626315e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.519232118685409e-08</v>
+        <v>2.519232118685414e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.64842513423087e-08</v>
+        <v>2.648425134230869e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.871939868822841e-08</v>
+        <v>2.871939868822843e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>2.501925180500766e-08</v>
+        <v>2.50192518050077e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.541544480275589e-08</v>
+        <v>2.541544480275592e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.495056690223148e-08</v>
+        <v>2.49505669022315e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.576363288704566e-08</v>
+        <v>2.576363288704569e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>2.860972759869785e-08</v>
+        <v>2.860972759869789e-08</v>
       </c>
       <c r="T4" t="n">
         <v>2.616567016071499e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.585977906387277e-08</v>
+        <v>2.585977906387274e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.080177242886973e-08</v>
+        <v>3.080177242886974e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.481550709037666e-08</v>
+        <v>4.481550709037668e-08</v>
       </c>
       <c r="X4" t="n">
         <v>3.146552174247516e-08</v>
@@ -6854,10 +6854,10 @@
         <v>2.508631260209149e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.608854826355035e-08</v>
+        <v>2.608854826355036e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.399619765167285e-08</v>
+        <v>3.399619765167281e-08</v>
       </c>
       <c r="AB4" t="n">
         <v>2.46298916367075e-08</v>
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.774664034861347e-08</v>
+        <v>4.774664034861335e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.693561899244902e-08</v>
+        <v>5.693561899244897e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.12777284953447e-07</v>
+        <v>1.127772849534469e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>6.027601734969001e-08</v>
+        <v>6.027601734968989e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.155614948157227e-08</v>
+        <v>6.155614948157225e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.883344118138601e-08</v>
+        <v>8.883344118138594e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.980613845090751e-07</v>
+        <v>1.980613845090749e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.816790295199288e-08</v>
+        <v>8.816790295199273e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.049808122901667e-07</v>
+        <v>1.049808122901665e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>7.754314698017891e-08</v>
+        <v>7.754314698017935e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.265309888773188e-08</v>
+        <v>6.26530988877312e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.923365068509006e-08</v>
+        <v>8.92336506850902e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.613509850381872e-08</v>
+        <v>7.613509850381865e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>5.890811847188486e-08</v>
+        <v>5.890811847188472e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.518837002893081e-08</v>
+        <v>6.518837002893085e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.022382090268805e-08</v>
+        <v>6.02238209026881e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.889593577641655e-08</v>
+        <v>7.889593577641668e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.156158358421587e-07</v>
+        <v>1.156158358421586e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>8.414619317578206e-08</v>
+        <v>8.414619317578241e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.329592277678189e-08</v>
+        <v>7.32959227767821e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42749210441632e-07</v>
+        <v>1.427492104416321e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>3.98283478498235e-07</v>
+        <v>3.982834784982342e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.700553375680763e-07</v>
+        <v>1.70055337568076e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.410680307036102e-08</v>
+        <v>6.410680307036097e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.453762698311908e-08</v>
+        <v>7.453762698311907e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.21853000311057e-07</v>
+        <v>2.218530003110565e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.799412808190577e-08</v>
+        <v>5.799412808190598e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6958,82 +6958,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.058517890325092e-08</v>
+        <v>3.058517890325096e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.095817199724692e-08</v>
+        <v>3.095817199724696e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.411691077476451e-08</v>
+        <v>3.411691077476452e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.128011265654124e-08</v>
+        <v>3.128011265654123e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.720824360495211e-08</v>
+        <v>3.116491882185261e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.925081970695625e-08</v>
+        <v>3.320749492385686e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.437651638904636e-08</v>
+        <v>3.43765163890464e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.261544603581432e-08</v>
+        <v>2.865877081891384e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.40291199536974e-08</v>
+        <v>3.007244473679687e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.822951010044156e-08</v>
+        <v>3.2186185317342e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.148077647793296e-08</v>
+        <v>3.148077647793292e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.277270663338756e-08</v>
+        <v>3.277270663338758e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.107013268650297e-08</v>
+        <v>3.107013268650303e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.736998580328217e-08</v>
+        <v>3.201078261466689e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.240483269288987e-08</v>
+        <v>3.240483269288986e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.123902219331037e-08</v>
+        <v>3.123902219331034e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.205208817812454e-08</v>
+        <v>2.809541296122407e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.094150767287626e-08</v>
+        <v>3.094150767287628e-08</v>
       </c>
       <c r="T6" t="n">
         <v>3.245412545179386e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.216867825227058e-08</v>
+        <v>3.216867825227061e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.313355250304816e-08</v>
+        <v>3.31335525030482e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.180958227749808e-08</v>
+        <v>5.180958227749812e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.775397703355406e-08</v>
+        <v>3.37973018166536e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.763773510267023e-08</v>
+        <v>2.763773510267026e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.237700355462924e-08</v>
+        <v>2.842032833772878e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.028465294275171e-08</v>
+        <v>3.632797772585125e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>2.695761417219341e-08</v>
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.696948266746034e-08</v>
+        <v>2.696948266746036e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.734247576145635e-08</v>
+        <v>2.734247576145637e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.050121453897398e-08</v>
+        <v>3.050121453897394e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.766441642075067e-08</v>
+        <v>2.766441642075062e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.754922258606198e-08</v>
+        <v>2.7549222586062e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.959179868806614e-08</v>
+        <v>2.959179868806629e-08</v>
       </c>
       <c r="H7" t="n">
         <v>3.471749537015624e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.899974980002373e-08</v>
+        <v>2.899974980002375e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.041342371790683e-08</v>
+        <v>3.041342371790682e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.857048908155146e-08</v>
+        <v>2.857048908155134e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.786508024214242e-08</v>
+        <v>2.786508024214238e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.915701039759699e-08</v>
+        <v>2.915701039759693e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.139215774351673e-08</v>
+        <v>3.139215774351674e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.769193506021547e-08</v>
+        <v>2.769193506021549e-08</v>
       </c>
       <c r="P7" t="n">
         <v>2.80881280579637e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.76233259575198e-08</v>
+        <v>2.762332595751979e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.843639194233398e-08</v>
+        <v>2.843639194233395e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.128248665398616e-08</v>
+        <v>3.128248665398613e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88384292160033e-08</v>
+        <v>2.883842921600335e-08</v>
       </c>
       <c r="U7" t="n">
         <v>2.837471241769443e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.347453148415804e-08</v>
+        <v>3.347453148415807e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.748826614566502e-08</v>
+        <v>4.748826614566494e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.413828079776345e-08</v>
+        <v>3.413828079776342e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.777951555469872e-08</v>
+        <v>2.777951555469874e-08</v>
       </c>
       <c r="Z7" t="n">
         <v>2.876130731883865e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.666895670696116e-08</v>
+        <v>3.666895670696112e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.730265069199583e-08</v>
+        <v>2.730265069199582e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.038873978701825e-08</v>
+        <v>3.038873978701822e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.578583572791174e-08</v>
+        <v>3.578583572791168e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.894457450542932e-08</v>
+        <v>3.894457450542934e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.610777638720604e-08</v>
+        <v>3.343258982641466e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.175117620920281e-08</v>
+        <v>3.175117620920284e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.803515865452154e-08</v>
+        <v>3.907693910746098e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.316085533661164e-08</v>
+        <v>4.316085533661162e-08</v>
       </c>
       <c r="I8" t="n">
         <v>3.744310976647911e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.885678368436225e-08</v>
+        <v>3.885678368436217e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.701384904800681e-08</v>
+        <v>3.701384904800678e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.630844020859779e-08</v>
+        <v>3.630844020859776e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.760037036405238e-08</v>
+        <v>3.760037036400568e-08</v>
       </c>
       <c r="N8" t="n">
         <v>3.594099748506093e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.33110985663038e-08</v>
+        <v>3.331109856630382e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.34449479280892e-08</v>
+        <v>3.344494792808917e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.005523220270606e-08</v>
+        <v>3.005523220270603e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.687975190878934e-08</v>
+        <v>3.687975190878933e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>3.972584662044153e-08</v>
+        <v>3.972584662044148e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.728178918245864e-08</v>
+        <v>3.728178918245862e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.377510070928498e-08</v>
+        <v>3.440604860941741e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.191789145061342e-08</v>
+        <v>4.039241273054084e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.593261347507787e-08</v>
+        <v>5.593261347507786e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.703065604134865e-08</v>
+        <v>3.703065604134867e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.098198485218326e-08</v>
+        <v>4.09819848521832e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.720466728529404e-08</v>
+        <v>3.208723915007333e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.511231667341651e-08</v>
+        <v>4.511231667341647e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.099410617472019e-08</v>
+        <v>4.099410617472015e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.17971195430679e-08</v>
+        <v>5.179711954306396e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.027746533416446e-08</v>
+        <v>6.027746533416283e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.343620411168207e-08</v>
+        <v>6.343620411167953e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.059940599345875e-08</v>
+        <v>5.872826363201649e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.048421215877003e-08</v>
+        <v>4.179454881832869e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.252678826077422e-08</v>
+        <v>6.252679030413355e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.765248494286436e-08</v>
+        <v>6.765248494285859e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.19347393727318e-08</v>
+        <v>6.193473937273026e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.334841329061492e-08</v>
+        <v>6.334841329061632e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.150547865425956e-08</v>
+        <v>6.150547865425463e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.080006981485049e-08</v>
+        <v>6.080006981484765e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.209199997030507e-08</v>
+        <v>6.209199997030538e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>6.43271473162248e-08</v>
+        <v>6.432714731622442e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>6.331376922167621e-08</v>
+        <v>6.331376922167764e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>6.429428788937656e-08</v>
+        <v>6.42942878893737e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.0558317573588e-08</v>
+        <v>6.055831757358716e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.137138151504207e-08</v>
+        <v>6.137138151503863e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>6.421747622669422e-08</v>
+        <v>6.421747622669239e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.177341878871138e-08</v>
+        <v>6.177341878870905e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.148797158918809e-08</v>
+        <v>6.148797158918707e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.640952105686615e-08</v>
+        <v>7.576523441157825e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.042325571837312e-08</v>
+        <v>8.042325571837266e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>6.707327037047157e-08</v>
+        <v>6.707327037047247e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.071450512740683e-08</v>
+        <v>6.071450512740476e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.169629689154674e-08</v>
+        <v>5.680828496051855e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.96039462796692e-08</v>
+        <v>6.960394627966361e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.02376402647039e-08</v>
+        <v>6.023764026470307e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7466,58 +7466,58 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.931653450322972e-07</v>
+        <v>1.93165345032297e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.88399967430848e-07</v>
+        <v>3.883999674308483e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.940586687415861e-07</v>
+        <v>1.94058668741586e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.930967370288038e-07</v>
+        <v>1.930967370288037e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.93463413686564e-07</v>
+        <v>1.934634136865639e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.929405588239398e-07</v>
+        <v>1.929405588239396e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.938911958519551e-07</v>
+        <v>1.93891195851955e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.94552250514149e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.934372952475435e-07</v>
+        <v>1.934372952475433e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.957692023539054e-07</v>
+        <v>1.957692023539053e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.930861090174431e-07</v>
+        <v>1.930861090174429e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.930646413506497e-07</v>
+        <v>1.930646413506495e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.960490589259515e-07</v>
+        <v>1.960490589259513e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.031428646303311e-07</v>
+        <v>1.03142864630331e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.93506812288239e-07</v>
+        <v>1.935068122882389e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.938773575574997e-07</v>
+        <v>1.938773575574996e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.938236576660969e-07</v>
+        <v>1.938236576660968e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.936900710882864e-07</v>
+        <v>1.936900710882862e-07</v>
       </c>
       <c r="T2" t="n">
         <v>1.940184229328388e-07</v>
@@ -7526,25 +7526,25 @@
         <v>4.345380924275065e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.933217023742604e-07</v>
+        <v>1.933217023742603e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.071068713281231e-07</v>
+        <v>3.07106871328123e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.938539973215442e-07</v>
+        <v>1.93853997321544e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.935981150097223e-07</v>
+        <v>1.935981150097222e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.715758366508732e-07</v>
+        <v>1.715758366508731e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.935136550620626e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.929595187086814e-07</v>
+        <v>1.929595187086811e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7557,61 +7557,61 @@
         <v>1.982766589209966e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.192355731638164e-07</v>
+        <v>5.192355731638167e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.046941780023091e-07</v>
+        <v>2.046941780023088e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.977989422195069e-07</v>
+        <v>1.977989422195068e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.004311255821007e-07</v>
+        <v>2.004311255821006e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.966808018083427e-07</v>
+        <v>1.966808018083426e-07</v>
       </c>
       <c r="H3" t="n">
         <v>2.03513832450812e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.082279519803816e-07</v>
+        <v>2.082279519803815e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.002262091780548e-07</v>
+        <v>2.002262091780546e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.168066917585314e-07</v>
+        <v>2.168066917585312e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.977205484940351e-07</v>
+        <v>1.97720548494035e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.976576064789179e-07</v>
+        <v>1.976576064789178e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.189000175942429e-07</v>
+        <v>2.189000175942428e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>5.068929841281149e-08</v>
+        <v>5.068929841281143e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.007082075731932e-07</v>
+        <v>2.007082075731929e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.033729086176636e-07</v>
+        <v>2.033729086176635e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.030235003853921e-07</v>
+        <v>2.03023500385392e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.019954651073063e-07</v>
+        <v>2.019954651073061e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.044050402981731e-07</v>
+        <v>2.04405040298173e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.976742655589391e-07</v>
+        <v>5.976742655589393e-07</v>
       </c>
       <c r="V3" t="n">
         <v>1.993855014146048e-07</v>
@@ -7623,16 +7623,16 @@
         <v>2.032203371252022e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.013765002838372e-07</v>
+        <v>2.013765002838369e-07</v>
       </c>
       <c r="Z3" t="n">
         <v>1.633292567249475e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.00776473396297e-07</v>
+        <v>2.007764733962968e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.968880670524648e-07</v>
+        <v>1.968880670524649e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7642,22 +7642,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.054591666365976e-08</v>
+        <v>3.054591666365977e-08</v>
       </c>
       <c r="C4" t="n">
         <v>2.781730365432492e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.063641890928802e-08</v>
+        <v>4.063641890928799e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.977095770296233e-08</v>
+        <v>2.977095770296235e-08</v>
       </c>
       <c r="F4" t="n">
         <v>3.391273923195962e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.800685303349772e-08</v>
+        <v>2.800685303349773e-08</v>
       </c>
       <c r="H4" t="n">
         <v>3.874473557957176e-08</v>
@@ -7669,13 +7669,13 @@
         <v>3.37016890431208e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.995768294477396e-08</v>
+        <v>5.995768294477397e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.965090942551526e-08</v>
+        <v>2.965090942551525e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.956141832999663e-08</v>
+        <v>2.956141832999665e-08</v>
       </c>
       <c r="N4" t="n">
         <v>6.311879166641535e-08</v>
@@ -7687,40 +7687,40 @@
         <v>3.440294640222193e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.858842567776584e-08</v>
+        <v>3.858842567776583e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.798186070120241e-08</v>
+        <v>3.79818607012024e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.647293885197082e-08</v>
+        <v>3.647293885197088e-08</v>
       </c>
       <c r="T4" t="n">
         <v>4.018182398550123e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.254064649606385e-08</v>
+        <v>3.254064649606387e-08</v>
       </c>
       <c r="V4" t="n">
         <v>3.287179271796866e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.964024353272159e-08</v>
+        <v>5.96402435327216e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.832456106640862e-08</v>
+        <v>3.832456106640864e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.544874142977823e-08</v>
+        <v>3.544874142977829e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.197189037263452e-08</v>
+        <v>3.197189037263454e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.448023868039093e-08</v>
+        <v>3.448023868039092e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.832555456452346e-08</v>
+        <v>2.832555456452347e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7733,31 +7733,31 @@
         <v>1.137399289359571e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>7.110908687733891e-08</v>
+        <v>7.110908687733896e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.277902676895798e-07</v>
+        <v>3.277902676895784e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.057286711722577e-07</v>
+        <v>1.057286711722579e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.924911338858094e-07</v>
+        <v>1.924911338858092e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.043285721314113e-08</v>
+        <v>7.043285721314106e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.003185177667334e-07</v>
+        <v>3.003185177667331e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.39355208862461e-07</v>
+        <v>4.393552088624617e-07</v>
       </c>
       <c r="J5" t="n">
         <v>1.76703741432806e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.399189711105188e-07</v>
+        <v>6.399189711105163e-07</v>
       </c>
       <c r="L5" t="n">
         <v>1.02045583241504e-07</v>
@@ -7766,49 +7766,49 @@
         <v>1.043288469533073e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.852318027854073e-07</v>
+        <v>1.852318027854075e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.473014766502683e-07</v>
+        <v>1.473014766502681e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.835982204487218e-07</v>
+        <v>1.835982204487214e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.739160711719178e-07</v>
+        <v>2.739160711719177e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.81273269088942e-07</v>
+        <v>2.812732690889421e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.11241963380611e-07</v>
+        <v>2.112419633806111e-07</v>
       </c>
       <c r="T5" t="n">
         <v>3.181373842050538e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5463916882798e-07</v>
+        <v>1.546391688279803e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4375164557318e-07</v>
+        <v>1.437516455731799e-07</v>
       </c>
       <c r="W5" t="n">
         <v>6.739044842825063e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.767974308312135e-07</v>
+        <v>2.767974308312139e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.123639104766668e-07</v>
+        <v>2.123639104766667e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.392660719471285e-07</v>
+        <v>1.392660719471284e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.958649179942309e-07</v>
+        <v>1.958649179942307e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.488366827538934e-08</v>
+        <v>8.488366827538927e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.863830063730932e-08</v>
+        <v>3.863830063730933e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.085494547313399e-08</v>
+        <v>3.0854945473134e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.872880288293758e-08</v>
+        <v>4.872880288293756e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.78633416766119e-08</v>
+        <v>3.786334167661191e-08</v>
       </c>
       <c r="F6" t="n">
         <v>4.200512320560917e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.10444948523068e-08</v>
+        <v>3.104449485230679e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.683711955322133e-08</v>
+        <v>4.683711955322134e-08</v>
       </c>
       <c r="I6" t="n">
         <v>4.924929390802928e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.179407301677035e-08</v>
+        <v>3.673933086192989e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.299532476358305e-08</v>
+        <v>6.299532476358304e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.268855124432433e-08</v>
+        <v>3.774329339916481e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.765380230364621e-08</v>
+        <v>3.765380230364619e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.61807205593458e-08</v>
+        <v>6.618072055934603e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.571287735513811e-08</v>
+        <v>3.571287735513838e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.338203436163024e-08</v>
+        <v>4.338203436163021e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.16260674965749e-08</v>
+        <v>4.668080965141537e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.607424467485198e-08</v>
+        <v>4.607424467485197e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>4.456532282562038e-08</v>
+        <v>4.456532282562042e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.827420795915078e-08</v>
+        <v>4.321946580431029e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.061854168263771e-08</v>
+        <v>4.061854168263773e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.590943453677773e-08</v>
+        <v>4.096417669161822e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.313995490227646e-08</v>
+        <v>6.3139954902276e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.641694504005816e-08</v>
+        <v>4.136220288521772e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.874596364681993e-08</v>
+        <v>3.874596364682019e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>3.500953219144362e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.257262265404051e-08</v>
+        <v>4.257262265404049e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.135242862392879e-08</v>
+        <v>3.13524286239288e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4347981878452e-08</v>
+        <v>3.434798187845201e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.161936886911715e-08</v>
+        <v>3.161936886911719e-08</v>
       </c>
       <c r="D7" t="n">
         <v>4.443848412408027e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.357302291775458e-08</v>
+        <v>3.357302291775459e-08</v>
       </c>
       <c r="F7" t="n">
         <v>3.771480444675185e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.180891824828995e-08</v>
+        <v>3.180891824828996e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.254680079436399e-08</v>
+        <v>4.2546800794364e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.001371730401247e-08</v>
+        <v>5.001371730401245e-08</v>
       </c>
       <c r="J7" t="n">
         <v>3.750375425791305e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.375974815956614e-08</v>
+        <v>6.375974815956615e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.345297464030749e-08</v>
+        <v>3.345297464030751e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.336348354478885e-08</v>
+        <v>3.336348354478889e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.692085688120759e-08</v>
+        <v>6.692085688120755e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>3.645282147074212e-08</v>
+        <v>3.645282147074216e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.820481941075639e-08</v>
+        <v>3.820481941075638e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.239049089255806e-08</v>
+        <v>4.239049089255808e-08</v>
       </c>
       <c r="R7" t="n">
         <v>4.178392591599466e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>4.027500406676309e-08</v>
+        <v>4.027500406676312e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.398388920029345e-08</v>
+        <v>4.398388920029349e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.629120804416659e-08</v>
+        <v>3.62912080441666e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.66738579327609e-08</v>
+        <v>3.667385793276089e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.344230874751383e-08</v>
+        <v>6.344230874751384e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.212662628120085e-08</v>
+        <v>4.212662628120088e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.923631785749478e-08</v>
+        <v>3.923631785749479e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.577395558742678e-08</v>
+        <v>3.577395558742679e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>3.82823038951832e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.21276197793157e-08</v>
+        <v>3.212761977931572e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.900414495819084e-08</v>
+        <v>3.900414495819082e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.337898994789872e-08</v>
+        <v>4.337898994789876e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.619810520286181e-08</v>
+        <v>5.619810520286183e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.533264399653613e-08</v>
+        <v>4.155026215626517e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.347760325971443e-08</v>
+        <v>4.347760325971441e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.356853932707151e-08</v>
+        <v>4.504148761578261e-08</v>
       </c>
       <c r="H8" t="n">
         <v>5.430642187314555e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>6.177333838279399e-08</v>
+        <v>6.177333838279402e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.926337533669458e-08</v>
+        <v>4.926337533669462e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.551936923834778e-08</v>
+        <v>7.551936923834777e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.521259571908904e-08</v>
+        <v>4.521259571908909e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.512310462357044e-08</v>
+        <v>4.512310462356001e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.317410962115225e-08</v>
+        <v>7.317410962115229e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.421946423357265e-08</v>
+        <v>4.421946423357268e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.560054082621768e-08</v>
+        <v>4.560054082621769e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.565066235415264e-08</v>
+        <v>4.565066235415262e-08</v>
       </c>
       <c r="R8" t="n">
         <v>5.354354699477621e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.203462514554463e-08</v>
+        <v>5.203462514554467e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.574351027907502e-08</v>
+        <v>5.574351027907501e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.368995028862673e-08</v>
+        <v>4.459220427808677e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.843347901154242e-08</v>
+        <v>4.646052170786254e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.52033258324839e-08</v>
+        <v>7.520332583248392e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.603784376671762e-08</v>
+        <v>4.603784376671767e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.800992759602782e-08</v>
+        <v>5.80099275960278e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.753357666620831e-08</v>
+        <v>4.029816829018072e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.004192497396475e-08</v>
+        <v>5.004192497396479e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.130739669464078e-08</v>
+        <v>5.130739669464083e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8082,31 +8082,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.815403041112943e-08</v>
+        <v>6.815403041112946e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.657876721421066e-08</v>
+        <v>7.657876721421068e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.939788246917381e-08</v>
+        <v>8.939788246917375e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.853242126284808e-08</v>
+        <v>7.595827697037314e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.267420279184536e-08</v>
+        <v>5.696268175067273e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.676831659338348e-08</v>
+        <v>7.676832094924387e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.750619913945753e-08</v>
+        <v>8.750619913945751e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.4973115649106e-08</v>
+        <v>9.497311564910593e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.246315260300654e-08</v>
+        <v>8.246315260300663e-08</v>
       </c>
       <c r="K9" t="n">
         <v>1.087191465046597e-07</v>
@@ -8121,46 +8121,46 @@
         <v>1.118802552263011e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>8.510862334524755e-08</v>
+        <v>8.510862334524762e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.766448288441771e-08</v>
+        <v>8.766448288441774e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.734989359351189e-08</v>
+        <v>8.734989359351192e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.674332426108817e-08</v>
+        <v>8.674332426108812e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.523440241185657e-08</v>
+        <v>8.523440241185662e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.894328754538695e-08</v>
+        <v>8.894328754538698e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.128762126887389e-08</v>
+        <v>8.12876212688739e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.163325627785436e-08</v>
+        <v>9.450398708859752e-08</v>
       </c>
       <c r="W9" t="n">
         <v>1.084017070926073e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>8.708602462629432e-08</v>
+        <v>8.708602462629436e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.419571620258829e-08</v>
+        <v>8.419571620258833e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.07333539325203e-08</v>
+        <v>7.400887751985926e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.324170224027665e-08</v>
+        <v>8.32417022402767e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.708701812440921e-08</v>
+        <v>7.708701812440924e-08</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.923238271371329e-07</v>
+        <v>1.923238271371348e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.879538225471038e-07</v>
+        <v>3.879538225471037e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.926730635818157e-07</v>
+        <v>1.926730635818178e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.925757883162934e-07</v>
+        <v>1.925757883162949e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.922977030869603e-07</v>
+        <v>1.922977030869613e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.926552898361001e-07</v>
+        <v>1.926552898361008e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.931529944192909e-07</v>
+        <v>1.93152994419293e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.925367971451357e-07</v>
+        <v>1.925367971451365e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.927346722889953e-07</v>
+        <v>1.927346722889971e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.928890039243935e-07</v>
+        <v>1.928890039243947e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.924622313014738e-07</v>
+        <v>1.924622313014748e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.924345568339907e-07</v>
+        <v>1.924345568339906e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.930616257617597e-07</v>
+        <v>1.93061625761761e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.013069178831536e-07</v>
+        <v>1.013069178831551e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.929331394132283e-07</v>
+        <v>1.929331394132277e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.927713501037433e-07</v>
+        <v>1.927713501037444e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.926239987705891e-07</v>
+        <v>1.9262399877059e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.928935782876492e-07</v>
+        <v>1.928935782876514e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.925132064203857e-07</v>
+        <v>1.92513206420387e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.329731247563351e-07</v>
+        <v>4.329731247563358e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.927263199023973e-07</v>
+        <v>1.927263199023991e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.058150407043077e-07</v>
+        <v>3.0581504070431e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.930539484271675e-07</v>
+        <v>1.930539484271685e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.926580127299902e-07</v>
+        <v>1.926580127299916e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.703556703566105e-07</v>
+        <v>1.703556703566111e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.927654200498061e-07</v>
+        <v>1.927654200498075e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.927125106523974e-07</v>
+        <v>1.927125106523965e-07</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.956877079512838e-07</v>
+        <v>1.956877079512822e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.194667391069759e-07</v>
+        <v>5.194667391069758e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.98188549884027e-07</v>
+        <v>1.981885498840268e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.974880024830793e-07</v>
+        <v>1.974880024830798e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.955074654630886e-07</v>
+        <v>1.955074654630893e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.980372173850499e-07</v>
+        <v>1.980372173850491e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.016475969982559e-07</v>
+        <v>2.016475969982569e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.97219134220291e-07</v>
+        <v>1.972191342202909e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.986140174453728e-07</v>
+        <v>1.986140174453741e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.997075454149361e-07</v>
+        <v>1.997075454149355e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.966730875976784e-07</v>
+        <v>1.9667308759768e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.965506496702565e-07</v>
+        <v>1.965506496702571e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.009648026677134e-07</v>
+        <v>2.009648026677137e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.559478642444521e-08</v>
+        <v>4.559478642444645e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.000159245482239e-07</v>
+        <v>2.000159245482242e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.988720623107108e-07</v>
+        <v>1.988720623107123e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.978465147690621e-07</v>
+        <v>1.978465147690618e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.997270977318905e-07</v>
+        <v>1.997270977318909e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.970483798605959e-07</v>
+        <v>1.970483798605965e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.932981495189373e-07</v>
+        <v>5.93298149518939e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.98542818983431e-07</v>
+        <v>1.985428189834318e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.983651741749764e-07</v>
+        <v>3.983651741749776e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.009035411411719e-07</v>
+        <v>2.009035411411729e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.980756138387652e-07</v>
+        <v>1.980756138387649e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.608922373800612e-07</v>
+        <v>1.608922373800614e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.98843600815929e-07</v>
+        <v>1.988436008159296e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.984914120953758e-07</v>
+        <v>1.984914120953752e-07</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.582948143238493e-08</v>
+        <v>2.582948143238649e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.75935115708779e-08</v>
+        <v>2.759351157087805e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.977426773178532e-08</v>
+        <v>2.977426773178653e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.867549885887388e-08</v>
+        <v>2.867549885887413e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.553439826802238e-08</v>
+        <v>2.553439826802451e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.957350509758923e-08</v>
+        <v>2.95735050975899e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.519530732015244e-08</v>
+        <v>3.519530732015328e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.823507564381662e-08</v>
+        <v>2.823507564381822e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.055330940457798e-08</v>
+        <v>3.055330940457944e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.221341323865916e-08</v>
+        <v>3.221341323865909e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.739282013767635e-08</v>
+        <v>2.739282013767744e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72036999655015e-08</v>
+        <v>2.720369996550222e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.416325630167525e-08</v>
+        <v>3.41632563016759e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>2.613548648377411e-08</v>
+        <v>2.613548648377432e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.271194388837567e-08</v>
+        <v>3.271194388837723e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.088445921098456e-08</v>
+        <v>3.088445921098566e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.922005811804637e-08</v>
+        <v>2.922005811804549e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.226508277595261e-08</v>
+        <v>3.22650827759531e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.796860755549433e-08</v>
+        <v>2.796860755549509e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.656249165554137e-08</v>
+        <v>2.656249165554271e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.092999893188386e-08</v>
+        <v>3.092999893188398e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.739305250990636e-08</v>
+        <v>5.73930525099089e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.407653727571506e-08</v>
+        <v>3.407653727571545e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.956509068610935e-08</v>
+        <v>2.956509068611016e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.887696372524573e-08</v>
+        <v>2.887696372524476e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.081747652380366e-08</v>
+        <v>3.081747652380466e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.023791058371261e-08</v>
+        <v>3.023791058371236e-08</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.110675013884606e-08</v>
+        <v>5.110675013884551e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.438410190716169e-08</v>
+        <v>8.438410190716211e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.251905162427192e-07</v>
+        <v>1.251905162427212e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.024978701756376e-07</v>
+        <v>1.024978701756374e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>4.910390283578253e-08</v>
+        <v>4.91039028357825e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.089533556834794e-07</v>
+        <v>1.089533556834767e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.385641544657042e-07</v>
+        <v>2.385641544657046e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>9.958665473358013e-08</v>
+        <v>9.958665473357836e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.302038872510164e-07</v>
+        <v>1.302038872510161e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.568358499368414e-07</v>
+        <v>1.568358499368424e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>7.750402458676193e-08</v>
+        <v>7.750402458676242e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.829938535702361e-08</v>
+        <v>7.829938535702543e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.230376059245603e-08</v>
+        <v>7.230376059245665e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>5.575126939755392e-08</v>
+        <v>5.575126939755328e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6222354989078e-07</v>
+        <v>1.622235498907816e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.355170176551765e-07</v>
+        <v>1.355170176551783e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.196082506009528e-07</v>
+        <v>1.196082506009535e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.509634854024452e-07</v>
+        <v>1.509634854024466e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>9.363714894805558e-08</v>
+        <v>9.363714894805407e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.47421666968908e-08</v>
+        <v>6.474216669689276e-08</v>
       </c>
       <c r="V5" t="n">
         <v>1.230015889761267e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>6.137979689833139e-07</v>
+        <v>6.137979689833145e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.99519800196593e-07</v>
+        <v>1.995198001965953e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.193244394398406e-07</v>
+        <v>1.193244394398399e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.815976525848641e-08</v>
+        <v>9.815976525848707e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.415157393173494e-07</v>
+        <v>1.415157393173537e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.393548899492536e-07</v>
+        <v>1.393548899492565e-07</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.306923764917088e-08</v>
+        <v>2.853420556496523e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.483326778766174e-08</v>
+        <v>3.483326778766109e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.247899186436495e-08</v>
+        <v>3.247899186436496e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.138022299145308e-08</v>
+        <v>3.591525507565836e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.823912240060275e-08</v>
+        <v>3.277415448481105e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.681326131437405e-08</v>
+        <v>3.227822923016874e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.790003145273183e-08</v>
+        <v>4.243506353693667e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.093979977639713e-08</v>
+        <v>3.547483186060306e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.779306562136399e-08</v>
+        <v>3.325803353715822e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.491813737123644e-08</v>
+        <v>3.94531694554445e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.463257635446193e-08</v>
+        <v>3.0097544270256e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.990842409808118e-08</v>
+        <v>3.444345618228627e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.687377844206796e-08</v>
+        <v>3.687377844206862e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.417760950462833e-08</v>
+        <v>2.884600862416756e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.513735613044494e-08</v>
+        <v>3.513735613044431e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3589183343564e-08</v>
+        <v>3.812421542776934e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.645981433482913e-08</v>
+        <v>3.645981433482847e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.496980690853114e-08</v>
+        <v>3.496980690853138e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.067333168807469e-08</v>
+        <v>3.067333168807359e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.384141862289563e-08</v>
+        <v>2.930638653869041e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.816975514866777e-08</v>
+        <v>3.81697551486677e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.050642808770263e-08</v>
+        <v>6.050642808770318e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.131629349249958e-08</v>
+        <v>3.678126140829423e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.252903759971966e-08</v>
+        <v>3.252903759972049e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.158168785782415e-08</v>
+        <v>3.158168785782321e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.805723274058938e-08</v>
+        <v>3.805723274058775e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.29492795597223e-08</v>
+        <v>3.294927955972267e-08</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.893254298245778e-08</v>
+        <v>2.893254298245512e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.069657312094158e-08</v>
+        <v>3.069657312094672e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.287732928185258e-08</v>
+        <v>3.287732928185504e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.177856040894104e-08</v>
+        <v>3.177856040894284e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.863745981809255e-08</v>
+        <v>2.863745981809329e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.267656664766037e-08</v>
+        <v>3.267656664765884e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.829836887022317e-08</v>
+        <v>3.829836887022135e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.133813719388459e-08</v>
+        <v>3.13381371938872e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.365637095464966e-08</v>
+        <v>3.365637095464822e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.531647478872983e-08</v>
+        <v>3.531647478872783e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.04958816877431e-08</v>
+        <v>3.049588168774622e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.030676151556934e-08</v>
+        <v>3.030676151557174e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.726631785174144e-08</v>
+        <v>3.726631785174486e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.923844025381002e-08</v>
+        <v>2.923844025380826e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.581489765841346e-08</v>
+        <v>3.581489765841141e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.398752076105867e-08</v>
+        <v>3.398752076105457e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.232311966811552e-08</v>
+        <v>3.232311966811408e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.536814432601795e-08</v>
+        <v>3.536814432602185e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.107166910556604e-08</v>
+        <v>3.107166910556379e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.957861195350615e-08</v>
+        <v>2.957861195350779e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.403306048194955e-08</v>
+        <v>3.403306048195284e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.04961140599818e-08</v>
+        <v>6.049611405997703e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.717959882578058e-08</v>
+        <v>3.717959882578378e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.270732298674593e-08</v>
+        <v>3.270732298674842e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.198002527531581e-08</v>
+        <v>3.198002527531347e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.392053807387363e-08</v>
+        <v>3.392053807387355e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.334097213377757e-08</v>
+        <v>3.334097213378124e-08</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.290436028079498e-08</v>
+        <v>3.29043602807973e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.065619402363074e-08</v>
+        <v>4.06561940236326e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.283695018453416e-08</v>
+        <v>4.283695018454093e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.173818131162844e-08</v>
+        <v>3.854985252633337e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.354210693427699e-08</v>
+        <v>3.354210693427734e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.263618755034132e-08</v>
+        <v>4.38777976327033e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.825798977289965e-08</v>
+        <v>4.825798977290729e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.129775809657426e-08</v>
+        <v>4.129775809657279e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.36159918573303e-08</v>
+        <v>4.361599185733334e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.527609569140864e-08</v>
+        <v>4.527609569141348e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.045550259043227e-08</v>
+        <v>4.045550259043146e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.026638241825989e-08</v>
+        <v>4.026638241824223e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.258438921712959e-08</v>
+        <v>4.258438921713288e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.583215750145307e-08</v>
+        <v>3.583215750145631e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.209594969719351e-08</v>
+        <v>4.209594969719414e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.678259799275174e-08</v>
+        <v>3.678259799275169e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.228274057080105e-08</v>
+        <v>4.228274057079998e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.532776522870791e-08</v>
+        <v>4.532776522870698e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.103129000824522e-08</v>
+        <v>4.103129000824982e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.588807018512612e-08</v>
+        <v>3.664412764414224e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.399268138463346e-08</v>
+        <v>4.224841907017609e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.04569117134587e-08</v>
+        <v>7.045691171346017e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.052347014091685e-08</v>
+        <v>4.052347014091892e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.845342966928937e-08</v>
+        <v>4.845342966929652e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.193964617799553e-08</v>
+        <v>3.58406160496943e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.388015897655803e-08</v>
+        <v>4.388015897655884e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.95553545705558e-08</v>
+        <v>4.955535457056122e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.683888818923517e-08</v>
+        <v>5.683888818923975e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.782834312569022e-08</v>
+        <v>6.782834312569289e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.000909928660002e-08</v>
+        <v>7.000909928660021e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.89103304136892e-08</v>
+        <v>6.678114247750701e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.576922982283636e-08</v>
+        <v>4.450210360235853e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.980833665240409e-08</v>
+        <v>6.980833987309109e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.543013887496543e-08</v>
+        <v>7.543013887496565e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.846990719862936e-08</v>
+        <v>6.846990719863114e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.078814095939575e-08</v>
+        <v>7.078814095939517e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.244824479347444e-08</v>
+        <v>7.244824479347271e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.762765169248987e-08</v>
+        <v>6.762765169249195e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.743853152031235e-08</v>
+        <v>6.743853152031633e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.439808785649261e-08</v>
+        <v>7.439808785648859e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>6.94276160249826e-08</v>
+        <v>6.942761602498491e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.666898258677855e-08</v>
+        <v>7.666898258678702e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.111929398648278e-08</v>
+        <v>7.111929398648466e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.945488967285741e-08</v>
+        <v>6.945488967285905e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.249991433077089e-08</v>
+        <v>7.249991433076782e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.820343911030581e-08</v>
+        <v>6.820343911031018e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.68364939609274e-08</v>
+        <v>6.683649396092682e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.116483048669484e-08</v>
+        <v>8.181077623436029e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.762788406471632e-08</v>
+        <v>9.76278840647218e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.431136883052803e-08</v>
+        <v>7.431136883052996e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.983909299149096e-08</v>
+        <v>6.983909299149432e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.911179528005748e-08</v>
+        <v>6.354968576256906e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.105230807861661e-08</v>
+        <v>7.10523080786205e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.047274213852574e-08</v>
+        <v>7.047274213852744e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.940470394182083e-07</v>
+        <v>1.937376697390599e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.897053850294942e-07</v>
+        <v>3.890866605264976e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.956479206225834e-07</v>
+        <v>1.953812730263383e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.939102779565456e-07</v>
+        <v>1.935446813807473e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.953179043565195e-07</v>
+        <v>1.950311452248301e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.938014327037966e-07</v>
+        <v>1.93481145615741e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.953876318818229e-07</v>
+        <v>1.950572978531633e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.962587942820182e-07</v>
+        <v>1.959366685043568e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.944632549972179e-07</v>
+        <v>1.941409688691734e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.985486412118121e-07</v>
+        <v>1.981814820111546e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.944603224623658e-07</v>
+        <v>1.941271393710273e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.939796277448736e-07</v>
+        <v>1.936714387724037e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.980952621550791e-07</v>
+        <v>1.978206827893437e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.050366666286479e-07</v>
+        <v>1.041582447874767e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.946176598844951e-07</v>
+        <v>1.942126642573777e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.954794690282461e-07</v>
+        <v>1.951534738695063e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.950107849186166e-07</v>
+        <v>1.946733442528714e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.945618496755584e-07</v>
+        <v>1.941261299613875e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9598478024625e-07</v>
+        <v>1.95592470674598e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.361766905129631e-07</v>
+        <v>4.359461843083683e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.942702317009283e-07</v>
+        <v>1.939538716416262e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.083011067653141e-07</v>
+        <v>3.081722949565066e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.944278320984649e-07</v>
+        <v>1.940331924003987e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.945863680319253e-07</v>
+        <v>1.942882339033193e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.727637582555286e-07</v>
+        <v>1.723444655621676e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.943263071549501e-07</v>
+        <v>1.940009171154089e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.937644138861869e-07</v>
+        <v>1.935408054179071e-07</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.99686510760169e-07</v>
+        <v>1.992320647706122e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.233983990908424e-07</v>
+        <v>5.225373673376724e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.111730579314786e-07</v>
+        <v>2.110229610640528e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.987239866897494e-07</v>
+        <v>1.978675567217588e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.088288455196004e-07</v>
+        <v>2.085346755782663e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.979426317059296e-07</v>
+        <v>1.974101840758777e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.093437144236652e-07</v>
+        <v>2.087367719284206e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.155597369495337e-07</v>
+        <v>2.150122740965771e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.026710119490262e-07</v>
+        <v>2.021240411052638e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.319210025122288e-07</v>
+        <v>2.310516806947854e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.026488798235861e-07</v>
+        <v>2.020237424801736e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.993380236040594e-07</v>
+        <v>1.988870773153173e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.286360429482656e-07</v>
+        <v>2.284291117446515e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>5.519325983469363e-08</v>
+        <v>5.386259668551138e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.037484376533399e-07</v>
+        <v>2.026134729424547e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.099494054027811e-07</v>
+        <v>2.093748782974641e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.066280743608322e-07</v>
+        <v>2.059705707931029e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.033577893639671e-07</v>
+        <v>2.020033776122375e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.135887038662885e-07</v>
+        <v>2.125388432910108e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>6.018161619735314e-07</v>
+        <v>6.012115333886513e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.012761269612239e-07</v>
+        <v>2.007718486524757e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.012563259249369e-07</v>
+        <v>4.012588995308956e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.024338570341661e-07</v>
+        <v>2.013681576935839e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.035528358597287e-07</v>
+        <v>2.031776939263441e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.652243621182583e-07</v>
+        <v>1.645046565816298e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.016976908924939e-07</v>
+        <v>2.011278775861169e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.977811955026925e-07</v>
+        <v>1.979302489899155e-07</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.324683471897905e-08</v>
+        <v>2.057574690096297e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.47277311663719e-08</v>
+        <v>2.22736222938336e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.132952436413515e-08</v>
+        <v>3.914100212563819e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.170205109611755e-08</v>
+        <v>1.83958546147913e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.760183882395944e-08</v>
+        <v>3.518614754085889e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.047259389502716e-08</v>
+        <v>1.767818892114901e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.838944329850807e-08</v>
+        <v>3.548155350868378e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.822962336321701e-08</v>
+        <v>4.541444954440012e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.80318586091831e-08</v>
+        <v>2.521512917431796e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.409449781686903e-08</v>
+        <v>7.07706507689144e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.791505682233172e-08</v>
+        <v>2.497498555891642e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.267643793356391e-08</v>
+        <v>2.001267405836006e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.897337280640031e-08</v>
+        <v>1.088692553765024e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>3.830146720332553e-08</v>
+        <v>2.57607363428168e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.969225538407249e-08</v>
+        <v>2.594102849363622e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.942678611453312e-08</v>
+        <v>3.656790585643191e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>4.413278349092424e-08</v>
+        <v>3.114462096600542e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.90618534001668e-08</v>
+        <v>2.496358381268368e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.513450877653173e-08</v>
+        <v>4.152657671845093e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.829391319861957e-08</v>
+        <v>2.515413802498499e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.632567748500918e-08</v>
+        <v>2.357720027638972e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.991452220243217e-08</v>
+        <v>4.757242679703041e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.754806321576489e-08</v>
+        <v>2.391381130792548e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.935246228778182e-08</v>
+        <v>2.6916606396595e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.462079302455142e-08</v>
+        <v>2.177716152308213e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.640129227498315e-08</v>
+        <v>2.354924711660156e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.021066087005447e-08</v>
+        <v>1.849017321606566e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.451996620131735e-07</v>
+        <v>1.264357959171261e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.901391039374877e-07</v>
+        <v>1.751387945371531e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>5.455885171121836e-07</v>
+        <v>5.36209342880124e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.221440647012481e-07</v>
+        <v>9.018048544816699e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7713613850966e-07</v>
+        <v>4.628636714390703e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>9.469839278984736e-08</v>
+        <v>7.340152717651824e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.032315480310037e-07</v>
+        <v>4.779914934134477e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.004959514471384e-07</v>
+        <v>6.776560964842377e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.48249434951534e-07</v>
+        <v>2.263459776740756e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.232362603010014e-06</v>
+        <v>1.199009816202515e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.467840122785407e-07</v>
+        <v>2.221672382475185e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.508497002456471e-07</v>
+        <v>1.312465530207743e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.907675825222855e-07</v>
+        <v>1.088692553765024e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.348388382460114e-07</v>
+        <v>2.185760805587542e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>2.686846827507171e-07</v>
+        <v>2.293390787035535e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.945493451387671e-07</v>
+        <v>4.71157247134192e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>4.020201474343886e-07</v>
+        <v>3.75258282621281e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.605495664239434e-07</v>
+        <v>2.141155965494266e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>6.290251597334114e-07</v>
+        <v>5.893338005060406e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.500744601410558e-07</v>
+        <v>2.196325665934421e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.945539617861251e-07</v>
+        <v>1.74236283809884e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>6.939278699859725e-07</v>
+        <v>6.813015079713019e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.494158065508061e-07</v>
+        <v>2.096648280103317e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.780479917250212e-07</v>
+        <v>2.613140558984199e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.743255793246625e-07</v>
+        <v>1.52084350800998e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.194411878630002e-07</v>
+        <v>1.964215218444587e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.000601534681542e-07</v>
+        <v>1.011871061185459e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.245461050594961e-08</v>
+        <v>2.395091057374828e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.393550695334246e-08</v>
+        <v>3.122306362195791e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.473212107602872e-08</v>
+        <v>4.809044345376263e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.510464780801112e-08</v>
+        <v>2.734529594291529e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.680961461093e-08</v>
+        <v>3.856131121364383e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.968036968199771e-08</v>
+        <v>2.662763024927335e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.759721908547863e-08</v>
+        <v>4.443099483680814e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.163222007511052e-08</v>
+        <v>4.878961321718547e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.723963439615367e-08</v>
+        <v>2.859029284710315e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.749709452876268e-08</v>
+        <v>7.972009209703875e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.131765353422529e-08</v>
+        <v>3.39244268870413e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.607903464545748e-08</v>
+        <v>2.896211538648442e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>8.242157537409822e-08</v>
+        <v>1.088692553765024e-06</v>
       </c>
       <c r="O6" t="n">
-        <v>4.847606451891379e-08</v>
+        <v>2.918919126713418e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.986707873324854e-08</v>
+        <v>3.583358399295788e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.282938282642669e-08</v>
+        <v>4.551734718455665e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.753538020281781e-08</v>
+        <v>4.009406229412976e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>4.826962918713737e-08</v>
+        <v>2.833874748546872e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.853710548842524e-08</v>
+        <v>4.49017403912359e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.168284713706428e-08</v>
+        <v>2.840731770947604e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.553345327197974e-08</v>
+        <v>3.252664160451392e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.008925915198511e-08</v>
+        <v>5.746490147416601e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.675583900273546e-08</v>
+        <v>3.286325263605036e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.307126139337296e-08</v>
+        <v>3.04993814503837e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8023389736445e-08</v>
+        <v>2.515232519586741e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.98038889868767e-08</v>
+        <v>3.249868844472616e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.360139115301355e-08</v>
+        <v>2.186767232957515e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.794022472104459e-08</v>
+        <v>2.507314530724995e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.942112116843746e-08</v>
+        <v>2.677102070012076e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.602291436620071e-08</v>
+        <v>4.363840053192515e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.639544109818312e-08</v>
+        <v>2.289325302107834e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.229522882602495e-08</v>
+        <v>3.968354594714542e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.51659838970927e-08</v>
+        <v>2.217558732743619e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.308283330057363e-08</v>
+        <v>3.997895191497094e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.292301336528254e-08</v>
+        <v>4.991184795068734e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.272524861124865e-08</v>
+        <v>2.971252758060495e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>8.878788781893469e-08</v>
+        <v>7.526804917520159e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>4.260844682439729e-08</v>
+        <v>2.947238396520354e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.736982793562946e-08</v>
+        <v>2.451007246464725e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>8.36667628084659e-08</v>
+        <v>1.088692553765024e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>4.299459442617482e-08</v>
+        <v>3.025785193444021e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.438538260692177e-08</v>
+        <v>3.043814408525957e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.412017611659868e-08</v>
+        <v>4.106530426271867e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.882617349298979e-08</v>
+        <v>3.564201937229264e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>4.375524340223233e-08</v>
+        <v>2.946098221897032e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.982789877859729e-08</v>
+        <v>4.602397512473812e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>4.297936470632205e-08</v>
+        <v>2.955887797913913e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>4.101906748707474e-08</v>
+        <v>2.807459868267664e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.460791220449778e-08</v>
+        <v>5.206982520331675e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.224145321783045e-08</v>
+        <v>2.841120971421262e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.403218951639851e-08</v>
+        <v>3.129202081458777e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.931418302661698e-08</v>
+        <v>2.627455992936931e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.109468227704871e-08</v>
+        <v>2.804664552288862e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.490405087212003e-08</v>
+        <v>2.298757162235242e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.344019274976142e-08</v>
+        <v>3.041403534699346e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.339587677121798e-08</v>
+        <v>4.024191331340175e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.999766996898121e-08</v>
+        <v>5.710929314520664e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.585762231421019e-08</v>
+        <v>3.203515908949807e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>5.911546970840642e-08</v>
+        <v>4.629099536724746e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.089804190938757e-08</v>
+        <v>3.733228893446417e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.705758890335418e-08</v>
+        <v>5.344984452825192e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.689776896806307e-08</v>
+        <v>6.338274056396829e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.670000421402918e-08</v>
+        <v>4.318342019388633e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.027626434217152e-07</v>
+        <v>8.87389417884826e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.658320242717782e-08</v>
+        <v>4.294327657848495e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.134458353841121e-08</v>
+        <v>3.798096507794425e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>9.107214023280211e-08</v>
+        <v>1.088692553765024e-06</v>
       </c>
       <c r="O8" t="n">
-        <v>5.220555677907698e-08</v>
+        <v>3.915879035820992e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>5.315381687992497e-08</v>
+        <v>3.891455807135341e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.795465496716602e-08</v>
+        <v>4.480846324573477e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>6.280092909577035e-08</v>
+        <v>4.911291198557361e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.772999900501288e-08</v>
+        <v>4.293187483225152e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.380265438137785e-08</v>
+        <v>5.949486773801953e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.281660513271358e-08</v>
+        <v>3.905524503881662e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>5.268265343366709e-08</v>
+        <v>3.934874747624052e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.858433331681569e-08</v>
+        <v>6.55423155677866e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.685266317141996e-08</v>
+        <v>3.289949957095189e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.644117088508425e-08</v>
+        <v>5.288564342236945e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.465672752761423e-08</v>
+        <v>3.146443099960998e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.506943787982923e-08</v>
+        <v>4.151753813616991e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.773143071926219e-08</v>
+        <v>4.495093171822461e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.063228988845351e-08</v>
+        <v>6.755293188466196e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.608752547958753e-08</v>
+        <v>8.306036499805459e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.126893186773508e-07</v>
+        <v>9.992774482985921e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.983662921957876e-08</v>
+        <v>7.599541172434341e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.674696018171139e-08</v>
+        <v>6.413808392731861e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.183239377806507e-08</v>
+        <v>7.846493682433878e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.097492376117237e-07</v>
+        <v>9.626829621290478e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.195894176764327e-07</v>
+        <v>1.062011922486211e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>9.939165292239871e-08</v>
+        <v>8.600187187853905e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.454542921300848e-07</v>
+        <v>1.315573934731354e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.927485113554741e-08</v>
+        <v>8.576172826313755e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>9.403623224677957e-08</v>
+        <v>8.079941676258104e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.40333167119616e-07</v>
+        <v>1.088692553765024e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>1.04292346626593e-07</v>
+        <v>9.112395531544326e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>1.066903151513977e-07</v>
+        <v>9.229955140484674e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.107865859975711e-07</v>
+        <v>9.735465375962157e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>1.054925778041399e-07</v>
+        <v>9.193136367022644e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.004216477133825e-07</v>
+        <v>8.575032651690423e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.164943030897474e-07</v>
+        <v>1.023133194226722e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>9.964004473838635e-08</v>
+        <v>8.581889674091158e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.138115645111915e-07</v>
+        <v>1.002998809839402e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.212743165156479e-07</v>
+        <v>1.083591695012509e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>9.890785752898056e-08</v>
+        <v>8.470055401214663e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.006985938275486e-07</v>
+        <v>8.758136511252157e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.755530569252661e-08</v>
+        <v>7.423797098006626e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.776108658819878e-08</v>
+        <v>8.43359898208225e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.157045518327011e-08</v>
+        <v>7.927691592028627e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.91925233990699e-07</v>
+        <v>1.910741724282198e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.874002461935942e-07</v>
+        <v>3.864238572939362e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.922462744884778e-07</v>
+        <v>1.913932246208823e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.92001644407744e-07</v>
+        <v>1.911464776496729e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.919764309244741e-07</v>
+        <v>1.911190009808652e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.922489633678645e-07</v>
+        <v>1.913821198760469e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9260263469607e-07</v>
+        <v>1.917487720295379e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.92128374729461e-07</v>
+        <v>1.912254188746507e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.923374398818617e-07</v>
+        <v>1.914751565902747e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.923492746069895e-07</v>
+        <v>1.914232854062945e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.921514464251639e-07</v>
+        <v>1.91292498525787e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.921030319441763e-07</v>
+        <v>1.912555815252655e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.924637754762007e-07</v>
+        <v>1.916133605087268e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.002359734795807e-07</v>
+        <v>9.865473819507281e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.923213349221913e-07</v>
+        <v>1.914637284781292e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.920675317903153e-07</v>
+        <v>1.912159432243185e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.921384995080734e-07</v>
+        <v>1.912515706152422e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.923322054419429e-07</v>
+        <v>1.91452084519144e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.921648378271503e-07</v>
+        <v>1.91249072973241e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.328015680703768e-07</v>
+        <v>4.30864417922751e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.925009493409522e-07</v>
+        <v>1.916428578938135e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.05048099825202e-07</v>
+        <v>3.029084960204571e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.925651375738766e-07</v>
+        <v>1.916930507572006e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.922194753567987e-07</v>
+        <v>1.913534736006376e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.696176428218711e-07</v>
+        <v>1.684525054271869e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.92974782787168e-07</v>
+        <v>1.920951710748797e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.919477258272749e-07</v>
+        <v>1.910774237398702e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.950914319204467e-07</v>
+        <v>1.942870666175447e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.195424762328215e-07</v>
+        <v>5.185230177084128e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.973857990415435e-07</v>
+        <v>1.965670440478424e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.956364345837484e-07</v>
+        <v>1.948028853444946e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.954615340067672e-07</v>
+        <v>1.946114361024028e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.973882787108614e-07</v>
+        <v>1.964720069905047e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.999515200997598e-07</v>
+        <v>1.991267516294283e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.965482251080121e-07</v>
+        <v>1.953725867149548e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.980266971572143e-07</v>
+        <v>1.971423753509826e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.981084622703472e-07</v>
+        <v>1.967718033511545e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.967003512193873e-07</v>
+        <v>1.958399170476609e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.964339454702833e-07</v>
+        <v>1.956480503748272e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.989430963092209e-07</v>
+        <v>1.981431728830523e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.409434937719634e-08</v>
+        <v>4.205020557776966e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.979016939996371e-07</v>
+        <v>1.970509135003371e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.961070824626987e-07</v>
+        <v>1.952988461158904e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.966235902679492e-07</v>
+        <v>1.955620338472952e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.979799366604208e-07</v>
+        <v>1.969693574395657e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.968093564208189e-07</v>
+        <v>1.955418445497854e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.944781172550799e-07</v>
+        <v>5.921231553159903e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.991771554484716e-07</v>
+        <v>1.983229145099023e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.953363190110625e-07</v>
+        <v>3.92296167606342e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.996552640695812e-07</v>
+        <v>1.987008928956649e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.971951665830816e-07</v>
+        <v>1.962839181789905e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.606383867311643e-07</v>
+        <v>1.593116621164197e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.025885887589173e-07</v>
+        <v>2.015801811998528e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.953066174309648e-07</v>
+        <v>1.943609885784474e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.477972920624987e-08</v>
+        <v>1.239241177588999e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.846159733796183e-08</v>
+        <v>1.605772019435696e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.840602931458687e-08</v>
+        <v>1.599625306327206e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.564282001730127e-08</v>
+        <v>1.320913251424855e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.535802212499312e-08</v>
+        <v>1.289877090017345e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.843640144420641e-08</v>
+        <v>1.587081986192123e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.243128179313516e-08</v>
+        <v>2.001232460392618e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.707429729992391e-08</v>
+        <v>1.410080996512923e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.951955490650187e-08</v>
+        <v>1.700550902839728e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.956946303557205e-08</v>
+        <v>1.633580346314738e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.733490271639213e-08</v>
+        <v>1.485850548287838e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.691245839804246e-08</v>
+        <v>1.455295298675494e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.530801890766349e-07</v>
+        <v>1.40353330544085e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.551157132097034e-08</v>
+        <v>1.305261395021328e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.925387144288663e-08</v>
+        <v>1.679262656425297e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.638704831313764e-08</v>
+        <v>1.399377813561295e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.718866133197847e-08</v>
+        <v>1.439620590550474e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>2.937665896416653e-08</v>
+        <v>1.66611026910285e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.748616476217809e-08</v>
+        <v>1.43679938901305e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.775529271861272e-08</v>
+        <v>1.623296583810358e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.184120735523905e-08</v>
+        <v>1.937413788674194e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.260666822655189e-08</v>
+        <v>3.999555440410974e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.200773454843221e-08</v>
+        <v>1.938292719982604e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.739717965919891e-08</v>
+        <v>1.520329611385652e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.970849064005942e-08</v>
+        <v>1.73129306364061e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.663486567866798e-08</v>
+        <v>2.392506117249579e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.512239898479459e-08</v>
+        <v>1.25121458008012e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.131049326480109e-08</v>
+        <v>2.854406187351343e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.067921355623109e-07</v>
+        <v>9.36441362933945e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.070463611872906e-07</v>
+        <v>9.377955168696052e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>5.639829412441245e-08</v>
+        <v>4.287135283556724e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.397785052318198e-08</v>
+        <v>3.9793453515547e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.89234914255382e-08</v>
+        <v>8.338246784216245e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.898273519046071e-07</v>
+        <v>1.762880447537429e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.550450277987405e-08</v>
+        <v>6.190380067535318e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.202883676608859e-07</v>
+        <v>1.053493003171826e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.211697648597253e-07</v>
+        <v>9.471370335281809e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.361637798084481e-08</v>
+        <v>6.938652085326579e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.212050454018478e-08</v>
+        <v>6.97155044960108e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.530801890766349e-07</v>
+        <v>1.40353330544085e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>5.288688023454716e-08</v>
+        <v>3.901063363779124e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.117731748605937e-07</v>
+        <v>9.785258301251269e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.977177757753585e-08</v>
+        <v>5.68431643134042e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>8.91358459321093e-08</v>
+        <v>6.857983803344793e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.142864985511645e-07</v>
+        <v>9.632829564184565e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>9.325150500392218e-08</v>
+        <v>6.685603690682998e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.003227414484054e-07</v>
+        <v>9.539459034400442e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.448693878018044e-07</v>
+        <v>1.308521014284474e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>5.329289047815364e-07</v>
+        <v>5.161471963530945e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.674957163417694e-07</v>
+        <v>1.505560472965066e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.020211612083684e-07</v>
+        <v>8.613826546496742e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.159157018135573e-07</v>
+        <v>1.030469571687278e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.543435226507766e-07</v>
+        <v>2.357290943312004e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.074705218773638e-08</v>
+        <v>3.357249590516044e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.72830730414431e-08</v>
+        <v>1.457205652655461e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.096494117315521e-08</v>
+        <v>2.189964112263381e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.504841349953583e-08</v>
+        <v>1.817589781393666e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.81461638524945e-08</v>
+        <v>1.905105344252544e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.786136596018647e-08</v>
+        <v>1.874069182845029e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.507878562915498e-08</v>
+        <v>1.805046461258586e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.907366597808371e-08</v>
+        <v>2.21919693545908e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.371668148487291e-08</v>
+        <v>1.628045471579385e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.616193909145079e-08</v>
+        <v>2.284742995667417e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.207280687076533e-08</v>
+        <v>1.851544821381198e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.397728690134107e-08</v>
+        <v>2.070042641115504e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.355484258299138e-08</v>
+        <v>1.673259773741957e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.530801890766349e-07</v>
+        <v>1.40353330544085e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.311721435326616e-08</v>
+        <v>1.964117073328505e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.684781687483583e-08</v>
+        <v>1.87618823783621e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.30294324980867e-08</v>
+        <v>1.617342288627762e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.383104551692744e-08</v>
+        <v>1.657585065616935e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.60190431491155e-08</v>
+        <v>2.250302361930529e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.998950859737117e-08</v>
+        <v>1.654763864079513e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.510381803842386e-08</v>
+        <v>2.241883765575958e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.848359154018775e-08</v>
+        <v>2.155378263740647e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.549862294535873e-08</v>
+        <v>4.254138679851767e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.451107838362553e-08</v>
+        <v>2.522484812810293e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.08367646669655e-08</v>
+        <v>1.794628287819225e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.221183447525265e-08</v>
+        <v>1.949257538707075e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.913820951386105e-08</v>
+        <v>2.976698210077258e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.762567521642593e-08</v>
+        <v>1.471532933172439e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.768842658043027e-08</v>
+        <v>1.511694340622377e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.137029471214217e-08</v>
+        <v>1.878225182469073e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.131472668876716e-08</v>
+        <v>1.872078469360579e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.855151739148155e-08</v>
+        <v>1.593366414458229e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.826671949917352e-08</v>
+        <v>1.56233025305072e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.13450988183867e-08</v>
+        <v>1.859535149225499e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.533997916731545e-08</v>
+        <v>2.273685623425987e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.998299467410421e-08</v>
+        <v>1.682534159546293e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.242825228068216e-08</v>
+        <v>1.9730040658731e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.247816040975239e-08</v>
+        <v>1.90603350934811e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.024360009057241e-08</v>
+        <v>1.75830371132121e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.982115577222275e-08</v>
+        <v>1.727748461708869e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.530801890766349e-07</v>
+        <v>1.40353330544085e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>2.842022720304368e-08</v>
+        <v>1.577704668439312e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.216252732495998e-08</v>
+        <v>1.951705929843282e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.929574568731802e-08</v>
+        <v>1.67183097659467e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.009735870615871e-08</v>
+        <v>1.712073753583843e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.228535633834677e-08</v>
+        <v>1.938563432136225e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.039486213635839e-08</v>
+        <v>1.709252552046425e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.115339058406005e-08</v>
+        <v>1.918991567940981e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.474990472941932e-08</v>
+        <v>2.209866951707565e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.551536560073227e-08</v>
+        <v>4.272008603444352e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.491643192261248e-08</v>
+        <v>2.210745883015981e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.101201816824151e-08</v>
+        <v>1.827177863356963e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.261718801423968e-08</v>
+        <v>2.00374622667398e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.95435630528482e-08</v>
+        <v>2.664959280282953e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.803109635897492e-08</v>
+        <v>1.523667743113495e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.148813330228456e-08</v>
+        <v>1.846374260853553e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.083664752258935e-08</v>
+        <v>2.699861647848166e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.078107949921433e-08</v>
+        <v>2.69371493473967e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.500054831999123e-08</v>
+        <v>2.155712884123859e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.294922345150015e-08</v>
+        <v>1.972872311675712e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.198646760824311e-08</v>
+        <v>2.782145226366831e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.480633197776246e-08</v>
+        <v>3.095322088805084e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.944934748455136e-08</v>
+        <v>2.504170624925389e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.18946050911291e-08</v>
+        <v>2.794640531252188e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.194451322019945e-08</v>
+        <v>2.727669974727199e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.970995290101945e-08</v>
+        <v>2.579940176700301e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.928750858265503e-08</v>
+        <v>2.549384927090976e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.530801890766349e-07</v>
+        <v>1.40353330544085e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.470114703222281e-08</v>
+        <v>2.12561103379391e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.814755183093279e-08</v>
+        <v>2.474184879634721e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.198182712412832e-08</v>
+        <v>1.910812821805935e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.956371151660583e-08</v>
+        <v>2.533710218962939e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.175170914879389e-08</v>
+        <v>2.760199897515314e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.986121494680555e-08</v>
+        <v>2.530889017425516e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.790273317763901e-08</v>
+        <v>2.505468465452334e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.248224863778409e-08</v>
+        <v>2.888885766276974e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.498283204649993e-08</v>
+        <v>5.09374076842411e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.812187271910579e-08</v>
+        <v>2.494358262382665e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.582529766684351e-08</v>
+        <v>3.118210719885868e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.631163387776668e-08</v>
+        <v>2.329380679179179e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.900991586329528e-08</v>
+        <v>3.486595745662047e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.341673482465137e-08</v>
+        <v>2.853971037341671e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.284488316156746e-08</v>
+        <v>4.011249427205951e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.489949327772252e-08</v>
+        <v>5.18843677647674e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.484392525434741e-08</v>
+        <v>5.182290063368247e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.014832393335178e-08</v>
+        <v>4.716482007528901e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.249445811411496e-08</v>
+        <v>3.003756984528554e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.487430086094649e-08</v>
+        <v>5.169747021922307e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.886917773289561e-08</v>
+        <v>5.583897217433662e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.351219323968449e-08</v>
+        <v>4.992745753553965e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.595745084626246e-08</v>
+        <v>5.283215659880768e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.600735897533252e-08</v>
+        <v>5.216245103355783e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.377279865615265e-08</v>
+        <v>5.068515305328881e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.335035433780297e-08</v>
+        <v>5.037960055716538e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.530801890766349e-07</v>
+        <v>1.40353330544085e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>6.472418762045037e-08</v>
+        <v>5.156577028204817e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>6.906994105823896e-08</v>
+        <v>5.589005185286959e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.282494772987829e-08</v>
+        <v>4.982042849291489e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.362655727173897e-08</v>
+        <v>5.022285347591516e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>6.581455490392724e-08</v>
+        <v>5.248775026143894e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.392406070193868e-08</v>
+        <v>5.019464146054092e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.489932979323577e-08</v>
+        <v>5.240356429789337e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.794107194528794e-08</v>
+        <v>6.455559073737497e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.904456416631245e-08</v>
+        <v>7.582220197452021e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>6.844563048819258e-08</v>
+        <v>5.520957477023651e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.454121673382179e-08</v>
+        <v>5.137389457364629e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.109836907713754e-08</v>
+        <v>4.825204143758515e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.307276161842842e-08</v>
+        <v>5.97517087429062e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.156029492455503e-08</v>
+        <v>4.833879337121166e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.93208891691239e-07</v>
+        <v>1.926785867156178e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.889770041259026e-07</v>
+        <v>3.881178926690254e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.936404817908343e-07</v>
+        <v>1.931592718854917e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.934660444625412e-07</v>
+        <v>1.928843270528165e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.939558370218112e-07</v>
+        <v>1.934026722780869e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.93153049353041e-07</v>
+        <v>1.925979620502924e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.941398764040924e-07</v>
+        <v>1.93629889915617e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.946603471445547e-07</v>
+        <v>1.940067535775089e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.936610577505549e-07</v>
+        <v>1.931078248153271e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.970377366654409e-07</v>
+        <v>1.964241088050305e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.932803222523392e-07</v>
+        <v>1.927185908995626e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.932327661931986e-07</v>
+        <v>1.927000441576046e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.957814223033661e-07</v>
+        <v>1.953023452018804e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.035012203380043e-07</v>
+        <v>1.022215511351971e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.937363494056295e-07</v>
+        <v>1.930718510631828e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.942554086116732e-07</v>
+        <v>1.937106507425136e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.942925889465698e-07</v>
+        <v>1.93490584715641e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.93734774850168e-07</v>
+        <v>1.930665112634232e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.939568657475574e-07</v>
+        <v>1.932752654221029e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.348922301204075e-07</v>
+        <v>4.343715173926772e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.93494242465519e-07</v>
+        <v>1.929692139125886e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.085445847999673e-07</v>
+        <v>3.081368577565794e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.938711781183523e-07</v>
+        <v>1.93251748249452e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.940900022947098e-07</v>
+        <v>1.935721487027402e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.719111561891661e-07</v>
+        <v>1.712157892110606e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.936718258199049e-07</v>
+        <v>1.930027005464368e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.931618844533098e-07</v>
+        <v>1.92705067192264e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.974065565662293e-07</v>
+        <v>1.967491711481506e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.218898114440522e-07</v>
+        <v>5.208189883377172e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.005103855384438e-07</v>
+        <v>2.002028809445761e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.992481802534394e-07</v>
+        <v>1.982231689769603e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.027696223246956e-07</v>
+        <v>2.019469545119476e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.970112485661406e-07</v>
+        <v>1.961772568961661e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.041056406243087e-07</v>
+        <v>2.035919347454689e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.078199270604541e-07</v>
+        <v>2.062776250648346e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.006400867066969e-07</v>
+        <v>1.998187010402472e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.247048435703807e-07</v>
+        <v>2.234528470328249e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.97923280319973e-07</v>
+        <v>1.970407927193243e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.976816210740917e-07</v>
+        <v>1.970003917998731e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.158009793096588e-07</v>
+        <v>2.155084879062447e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>5.099581169685458e-08</v>
+        <v>4.913410031073832e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.011596116545733e-07</v>
+        <v>1.995473795508021e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.048976136000426e-07</v>
+        <v>2.041356896528111e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.051932663812443e-07</v>
+        <v>2.02586118875638e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.011515935765043e-07</v>
+        <v>1.995121181470986e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.027749424184496e-07</v>
+        <v>2.010330253200395e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.978122479645733e-07</v>
+        <v>5.96855570353437e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.994320630991951e-07</v>
+        <v>1.988123064174483e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.080034260152407e-07</v>
+        <v>4.076682980870622e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.021549253633598e-07</v>
+        <v>2.008588675735754e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.037011600503614e-07</v>
+        <v>2.031317368138015e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.637133544834059e-07</v>
+        <v>1.627237110313731e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.007195651074177e-07</v>
+        <v>1.990702889552974e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.971483464943194e-07</v>
+        <v>1.970058478241831e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.923043458350029e-08</v>
+        <v>1.662451052063324e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.195649832990515e-08</v>
+        <v>1.961963530866568e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.410544329968431e-08</v>
+        <v>2.205407064046236e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.213509343147936e-08</v>
+        <v>1.894844227452332e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.766752570414122e-08</v>
+        <v>2.480339004453836e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.859966968480885e-08</v>
+        <v>1.571381783660579e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.974633518930643e-08</v>
+        <v>2.736991778571772e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.562529163119726e-08</v>
+        <v>3.162676621263643e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.442165611863547e-08</v>
+        <v>2.155731345081775e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.247899992281977e-08</v>
+        <v>5.893190554583797e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.003727563080805e-08</v>
+        <v>1.707637618112327e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.966093782849596e-08</v>
+        <v>1.701885009893355e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.828835127002552e-08</v>
+        <v>6.471981858621278e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>3.269403742354898e-08</v>
+        <v>2.01552765996316e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.518831211007757e-08</v>
+        <v>2.106661223691893e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.105132462137379e-08</v>
+        <v>2.828214847733069e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>4.147129360782896e-08</v>
+        <v>2.579640146842925e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.517052678180816e-08</v>
+        <v>2.100629674220525e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.76791456346816e-08</v>
+        <v>2.33642709961491e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.225647495211246e-08</v>
+        <v>1.915610925721185e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.301212235051643e-08</v>
+        <v>2.04692846514176e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>7.081679380824842e-08</v>
+        <v>5.845965755058171e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.671126444455327e-08</v>
+        <v>2.309863371262241e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.920172899253652e-08</v>
+        <v>2.689071330315154e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.224911274188443e-08</v>
+        <v>1.952019348045302e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.445948852700156e-08</v>
+        <v>2.028552533946225e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.880614944264653e-08</v>
+        <v>1.701134966332461e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.639502671857496e-08</v>
+        <v>6.824543512553588e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.448810783608421e-07</v>
+        <v>1.312543444405238e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.916680085388831e-07</v>
+        <v>1.837184380454916e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.44826215388449e-07</v>
+        <v>1.153110151081202e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>2.637639359367678e-07</v>
+        <v>2.395468935642058e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.627138040315756e-08</v>
+        <v>5.297712899990202e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.155944456617559e-07</v>
+        <v>3.010421497442458e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.265645541526182e-07</v>
+        <v>3.793031644607119e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.866080065410739e-07</v>
+        <v>1.633607036735569e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.883564793667145e-07</v>
+        <v>8.524494052416942e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.054994285076587e-07</v>
+        <v>8.018720023576221e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.041502368366063e-07</v>
+        <v>8.432783209746715e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.708411763244978e-07</v>
+        <v>6.471981858621278e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.440249298612977e-07</v>
+        <v>1.271534451262e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.926853405460902e-07</v>
+        <v>1.474873690208763e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.221462009274727e-07</v>
+        <v>3.001381891726254e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>3.469354987769935e-07</v>
+        <v>2.648457208188228e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.941396465794074e-07</v>
+        <v>1.479314146132727e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.628591195363897e-07</v>
+        <v>2.097666838500192e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.447905551946534e-07</v>
+        <v>1.143521170052274e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.417479910468924e-07</v>
+        <v>1.247124640402611e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>8.811054553996613e-07</v>
+        <v>8.671484659204327e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.398533697339536e-07</v>
+        <v>2.012322089040421e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.779544979856367e-07</v>
+        <v>2.619614499262245e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.414664783401772e-07</v>
+        <v>1.209621347299439e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.902845235734808e-07</v>
+        <v>1.41861845514771e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.911742738953778e-08</v>
+        <v>8.669321937340747e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.238165192711076e-08</v>
+        <v>1.967741746292277e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.021255187275414e-08</v>
+        <v>2.742401000130455e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.236149684253325e-08</v>
+        <v>2.510697758275199e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.528631077508985e-08</v>
+        <v>2.675281696716218e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.08187430477517e-08</v>
+        <v>2.785629698682802e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.175088702841933e-08</v>
+        <v>2.351819252924453e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.800238873215536e-08</v>
+        <v>3.517429247835666e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.87765089748077e-08</v>
+        <v>3.943114090527526e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.267770966148437e-08</v>
+        <v>2.93616881434566e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.073505346566877e-08</v>
+        <v>6.198481248812758e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.31884929744185e-08</v>
+        <v>2.488075087376215e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28121551721064e-08</v>
+        <v>2.482322479157261e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.14510679996163e-08</v>
+        <v>6.471981858621278e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>4.181843391164592e-08</v>
+        <v>2.322669380198207e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.431042360285597e-08</v>
+        <v>2.966938132672065e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.930737816422274e-08</v>
+        <v>3.133505541962035e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.97273471506779e-08</v>
+        <v>3.360077616106806e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>4.342658032465715e-08</v>
+        <v>2.405920368449489e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.083036297829208e-08</v>
+        <v>2.641717793843873e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.538894748379162e-08</v>
+        <v>2.203600712035327e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.126817589336539e-08</v>
+        <v>2.352219159370719e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.994225531886689e-08</v>
+        <v>6.203068293709768e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.496731798740225e-08</v>
+        <v>3.090300840526137e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.260325130759074e-08</v>
+        <v>3.003777945458239e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.050516628473339e-08</v>
+        <v>2.257310042274275e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.761070587061205e-08</v>
+        <v>2.808990003210115e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.193551907580415e-08</v>
+        <v>2.006103096410014e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.323586913387728e-08</v>
+        <v>2.041272944940582e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.596193288028215e-08</v>
+        <v>2.340785423743831e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.811087785006127e-08</v>
+        <v>2.584228956923498e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.614052798185636e-08</v>
+        <v>2.273666120329597e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>4.167296025451825e-08</v>
+        <v>2.8591608973311e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.260510423518587e-08</v>
+        <v>1.950203676537842e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.375176973968342e-08</v>
+        <v>3.115813671449035e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.963072618157425e-08</v>
+        <v>3.541498514140902e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.842709066901245e-08</v>
+        <v>2.534553237959037e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.648443447319675e-08</v>
+        <v>6.272012447461061e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.404271018118504e-08</v>
+        <v>2.086459510989619e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.366637237887293e-08</v>
+        <v>2.080706902770618e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.22937858204025e-08</v>
+        <v>6.471981858621278e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>3.669925029847495e-08</v>
+        <v>2.394324050212681e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.919352498500351e-08</v>
+        <v>2.485457613941414e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.505675917175078e-08</v>
+        <v>3.207036740610333e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.547672815820595e-08</v>
+        <v>2.958462039720186e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.917596133218514e-08</v>
+        <v>2.479451567097789e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.168458018505857e-08</v>
+        <v>2.715248992492175e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.624008400978069e-08</v>
+        <v>2.281442778247519e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.701755690089341e-08</v>
+        <v>2.42575035801896e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.482222835862537e-08</v>
+        <v>6.224787647935428e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.071669899493028e-08</v>
+        <v>2.688685264139508e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.318841873098224e-08</v>
+        <v>3.050592315277596e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.625454729226144e-08</v>
+        <v>2.330841240922568e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.846492307737854e-08</v>
+        <v>2.407374426823487e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.281158399302352e-08</v>
+        <v>2.079956859209724e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.804388134014405e-08</v>
+        <v>2.496260713469118e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.814662810448232e-08</v>
+        <v>3.482451575986322e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.02955730742615e-08</v>
+        <v>3.725895109165989e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4397357102942e-08</v>
+        <v>3.049696289441199e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.763017345868714e-08</v>
+        <v>3.421125132388884e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.631940273568492e-08</v>
+        <v>3.234257064760025e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.593646496388364e-08</v>
+        <v>4.257479823691528e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>6.181542140577442e-08</v>
+        <v>4.683164666383397e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.061178589321262e-08</v>
+        <v>3.676219390201532e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.866912969739704e-08</v>
+        <v>7.413678599703559e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.622740540538522e-08</v>
+        <v>3.228125663232079e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.585106760307056e-08</v>
+        <v>3.222373055015938e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>6.876031760653713e-08</v>
+        <v>6.471981858621278e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>4.473740470886252e-08</v>
+        <v>3.150003163175226e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.684649105394877e-08</v>
+        <v>3.205280433854877e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.841508480765023e-08</v>
+        <v>3.527076534672912e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.766142338240611e-08</v>
+        <v>4.100128191962679e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.136065655638535e-08</v>
+        <v>3.621117719340277e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.386927540925879e-08</v>
+        <v>3.856915144734666e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.482518371412913e-08</v>
+        <v>3.087000087911456e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.718364960652e-08</v>
+        <v>3.383443574674791e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.700837328540191e-08</v>
+        <v>7.366588749871667e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.475111227054867e-08</v>
+        <v>3.071660495119214e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.2703791620531e-08</v>
+        <v>4.880756129425936e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.092553382656291e-08</v>
+        <v>2.773073606119131e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.064961830157873e-08</v>
+        <v>3.549040579065976e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.270184143255049e-08</v>
+        <v>3.938916000246872e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.710381656390141e-08</v>
+        <v>5.400290941993535e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.107727604205778e-08</v>
+        <v>6.801806540400032e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.322622101183697e-08</v>
+        <v>7.045250073579702e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.866002147467426e-08</v>
+        <v>6.480349713533273e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.085998079884486e-08</v>
+        <v>4.779763546388897e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.772045180234521e-08</v>
+        <v>6.411225185239632e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.88671129014591e-08</v>
+        <v>7.576834788105239e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.474606934334987e-08</v>
+        <v>8.002519630797109e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.35424338307881e-08</v>
+        <v>6.995574354615241e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.215997776349725e-07</v>
+        <v>1.073303356411726e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>7.915805334296068e-08</v>
+        <v>6.547480627645807e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.878171554064858e-08</v>
+        <v>6.541728019426819e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.074091289821781e-07</v>
+        <v>6.471981858621278e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>8.55421932193162e-08</v>
+        <v>7.220573582351972e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.884710772989888e-08</v>
+        <v>7.391132428536916e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.017210673891006e-08</v>
+        <v>7.668058249312121e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>9.059207131998156e-08</v>
+        <v>7.419483156376389e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.429130449396083e-08</v>
+        <v>6.940472683753986e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.679992334683421e-08</v>
+        <v>7.176270109148375e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.135850785233383e-08</v>
+        <v>6.738153027339826e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.511215764214849e-08</v>
+        <v>8.158459796084653e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.199375715204011e-07</v>
+        <v>1.068580876459163e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>8.583204215670593e-08</v>
+        <v>7.149706380795712e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.83037618927579e-08</v>
+        <v>7.511613431933796e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.458871273457135e-08</v>
+        <v>6.127452626075785e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.358026623915424e-08</v>
+        <v>6.868395543479688e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.792692715479921e-08</v>
+        <v>6.540977975865927e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.925807415464741e-07</v>
+        <v>1.917026174681164e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.892897359142094e-07</v>
+        <v>3.880253654678995e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.933495865085498e-07</v>
+        <v>1.924669240404151e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.93303113847158e-07</v>
+        <v>1.923684831300555e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.927681778823583e-07</v>
+        <v>1.919212379580074e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.926704296488888e-07</v>
+        <v>1.91761950335334e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.933011697889116e-07</v>
+        <v>1.924489927757834e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.930679133317215e-07</v>
+        <v>1.920165552148338e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.930425541096752e-07</v>
+        <v>1.921305019550926e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.928297760218946e-07</v>
+        <v>1.918138089780575e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.925512191916414e-07</v>
+        <v>1.916462630189776e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.927409465875204e-07</v>
+        <v>1.918609574633404e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.941144717659465e-07</v>
+        <v>1.932068373041279e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.020892522780101e-07</v>
+        <v>1.001652852871011e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.931360296650207e-07</v>
+        <v>1.921236721353695e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.931607784101149e-07</v>
+        <v>1.92258262759668e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.933010731988191e-07</v>
+        <v>1.92230530671781e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.931156723954672e-07</v>
+        <v>1.921091028702131e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.928849268404216e-07</v>
+        <v>1.919083543286905e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.339936156601404e-07</v>
+        <v>4.326076249591105e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.929845032461252e-07</v>
+        <v>1.920914675453777e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.07170196049465e-07</v>
+        <v>3.058355978286847e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.932147396683465e-07</v>
+        <v>1.922327820684067e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.930744062654067e-07</v>
+        <v>1.921698456719161e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.709658596698549e-07</v>
+        <v>1.697191647229168e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.930733113624449e-07</v>
+        <v>1.920174275105572e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.926398077034695e-07</v>
+        <v>1.918168961988408e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.960371055544753e-07</v>
+        <v>1.950851321122885e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.268546032392329e-07</v>
+        <v>5.253422895686061e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.015446839470293e-07</v>
+        <v>2.005590265181215e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.011950063189717e-07</v>
+        <v>1.998391989286724e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.973855304289106e-07</v>
+        <v>1.966553852528992e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.966753444070232e-07</v>
+        <v>1.955075912796632e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.012182008447334e-07</v>
+        <v>2.004505965886481e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.995338202544112e-07</v>
+        <v>1.973397739662496e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.993338945173687e-07</v>
+        <v>1.981398551867873e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.978134170814205e-07</v>
+        <v>1.958812290987464e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.958293665656498e-07</v>
+        <v>1.946854003892505e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.972684156711954e-07</v>
+        <v>1.962941113697649e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.070036490973968e-07</v>
+        <v>2.058398007320942e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.759009417295371e-08</v>
+        <v>4.48560203350848e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.999843486348792e-07</v>
+        <v>1.98078142311287e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.001826330141806e-07</v>
+        <v>1.990557481790725e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.012099682299266e-07</v>
+        <v>1.988769051600189e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.998429769982608e-07</v>
+        <v>1.979772832038237e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.982218891157535e-07</v>
+        <v>1.965638080607934e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.97334333247278e-07</v>
+        <v>5.951326549674431e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.989016752077976e-07</v>
+        <v>1.978443203992381e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.045292561580309e-07</v>
+        <v>4.02800594934771e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.005754897835146e-07</v>
+        <v>1.988801667218091e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.995639240394904e-07</v>
+        <v>1.984226176272983e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.623573678558734e-07</v>
+        <v>1.60708695014882e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.995576532385865e-07</v>
+        <v>1.973358316470882e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.965210841791572e-07</v>
+        <v>1.959530076852537e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.647993195265379e-08</v>
+        <v>1.364723045333715e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.909344141930494e-08</v>
+        <v>2.642197627059918e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.516438948545575e-08</v>
+        <v>2.228042478584354e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.46394593965542e-08</v>
+        <v>2.11684894182775e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.859711159144093e-08</v>
+        <v>1.61166494570498e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.749300032799335e-08</v>
+        <v>1.431742248302555e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.461750036435039e-08</v>
+        <v>2.207788290304069e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.198276137711713e-08</v>
+        <v>1.719330172100773e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.178007719120198e-08</v>
+        <v>1.856430380598005e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.929289091404697e-08</v>
+        <v>1.490318970874261e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.614646337386359e-08</v>
+        <v>1.301068102598705e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.842772367575345e-08</v>
+        <v>1.556017180292423e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.380412033235286e-08</v>
+        <v>3.486358679411037e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.840283186581396e-08</v>
+        <v>1.545351145330426e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.275216669679262e-08</v>
+        <v>1.840323661467546e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.303171515761636e-08</v>
+        <v>1.992349963087395e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.461640933482198e-08</v>
+        <v>1.96102529408004e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.252222197237872e-08</v>
+        <v>1.823867006254093e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.991584477993983e-08</v>
+        <v>1.597112293715093e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.223814871483129e-08</v>
+        <v>1.845177198374528e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.159898365211003e-08</v>
+        <v>1.859857868420318e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.627812286191764e-08</v>
+        <v>5.33991907782551e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.364123239274914e-08</v>
+        <v>1.963568350138156e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.203609525139772e-08</v>
+        <v>1.879968782725015e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.06310026744473e-08</v>
+        <v>1.761416730192499e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.204373461735405e-08</v>
+        <v>1.720315470247998e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.723672957494567e-08</v>
+        <v>1.50084118236931e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.583805756487093e-08</v>
+        <v>3.829038523257481e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.773202200309238e-07</v>
+        <v>2.622294016600645e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.199536481915366e-07</v>
+        <v>2.008290957770622e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.013413870197209e-07</v>
+        <v>1.722233576343643e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>9.881975700084563e-08</v>
+        <v>8.71213335298379e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.27869677629712e-08</v>
+        <v>4.962433569405883e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.20163265753213e-07</v>
+        <v>2.073762352607783e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.633972206327964e-07</v>
+        <v>1.082908620780465e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.486017946495769e-07</v>
+        <v>1.243178799055079e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.050405920067952e-07</v>
+        <v>6.18087987298965e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.147588953195542e-08</v>
+        <v>2.831341894131028e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>9.69371994429311e-08</v>
+        <v>7.797978701034108e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.668950375230864e-07</v>
+        <v>3.486358679411037e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>8.558681701093434e-08</v>
+        <v>6.644205300680939e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.585455938558329e-07</v>
+        <v>1.161491096573995e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.747101344851824e-07</v>
+        <v>1.518606970552733e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.162348726070299e-07</v>
+        <v>1.562093181005575e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.565096738419569e-07</v>
+        <v>1.148566166641675e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.237582859617033e-07</v>
+        <v>8.474122762657906e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.553490727041538e-07</v>
+        <v>1.231977867059924e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.281990197345035e-07</v>
+        <v>1.08213883544381e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>7.65293459648306e-07</v>
+        <v>7.465452665060204e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.894976659678348e-07</v>
+        <v>1.500223162212606e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.562801613754636e-07</v>
+        <v>1.331119872921083e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.206267770798629e-07</v>
+        <v>1.004083783289732e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.568613421576861e-07</v>
+        <v>1.031958523205412e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.633805625817455e-08</v>
+        <v>6.964085241441578e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.938369098453401e-08</v>
+        <v>2.02627068775165e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.199720045118541e-08</v>
+        <v>2.907852239841083e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.259306332677139e-08</v>
+        <v>2.889590121002276e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.75432184284346e-08</v>
+        <v>2.778396584245686e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6025785432757e-08</v>
+        <v>1.877319558486183e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.039675935987357e-08</v>
+        <v>1.69739686108374e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.752125939623071e-08</v>
+        <v>2.473442903085261e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.488652040899732e-08</v>
+        <v>1.984984784881964e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.920875103251759e-08</v>
+        <v>2.517978023015977e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.672156475536417e-08</v>
+        <v>2.151866613292199e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.905022240574374e-08</v>
+        <v>1.962615745016633e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.585639751706886e-08</v>
+        <v>1.821671793073614e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.669164852721473e-08</v>
+        <v>3.486358679411037e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.129036006067586e-08</v>
+        <v>2.276585455555915e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.095148209363034e-08</v>
+        <v>2.570367069103495e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.04603889989324e-08</v>
+        <v>2.653897605505339e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.204508317613736e-08</v>
+        <v>2.226679906861232e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.542598100425887e-08</v>
+        <v>2.485414648672026e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.281960381182021e-08</v>
+        <v>1.862766906496309e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.516191454530098e-08</v>
+        <v>2.123341823515315e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.902765749342569e-08</v>
+        <v>2.521405510838272e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.961925024466842e-08</v>
+        <v>6.071551135200916e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.654499142462936e-08</v>
+        <v>2.229222962919356e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.517194112370283e-08</v>
+        <v>2.178540435732105e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.353476170632743e-08</v>
+        <v>2.42296437261043e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.947240845866983e-08</v>
+        <v>2.381863112665932e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.009788993838344e-08</v>
+        <v>1.764906867659965e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.979664221694132e-08</v>
+        <v>1.670890663734717e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.241015168359251e-08</v>
+        <v>2.948365245460882e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.848109974974321e-08</v>
+        <v>2.534210096985367e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.79561696608417e-08</v>
+        <v>2.423016560228744e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.191382185572844e-08</v>
+        <v>1.917832564105986e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.080971059228086e-08</v>
+        <v>1.737909866703557e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7934210628638e-08</v>
+        <v>2.513955908705062e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.529947164140464e-08</v>
+        <v>2.025497790501769e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.509678745548934e-08</v>
+        <v>2.162597998999039e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.260960117833436e-08</v>
+        <v>1.796486589275256e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.946317363815106e-08</v>
+        <v>1.607235720999702e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.174443394004081e-08</v>
+        <v>1.862184798693416e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.712083059664055e-08</v>
+        <v>3.486358679411037e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>3.17194150297728e-08</v>
+        <v>1.851504376429554e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.606874986075104e-08</v>
+        <v>2.146476892566692e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.63484254219039e-08</v>
+        <v>2.298517581488402e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.79331195991096e-08</v>
+        <v>2.267192912481032e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.583893223666627e-08</v>
+        <v>2.130034624655089e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.32325550442276e-08</v>
+        <v>1.903279912116083e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.548092654534971e-08</v>
+        <v>2.159509110138298e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.491569391639745e-08</v>
+        <v>2.166025486821326e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.95948331262051e-08</v>
+        <v>5.646086696226515e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.695794265703646e-08</v>
+        <v>2.269735968539163e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.537281231427482e-08</v>
+        <v>2.198646413485601e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.394771293873445e-08</v>
+        <v>2.067584348593493e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.536044488164158e-08</v>
+        <v>2.026483088648992e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.055343983923344e-08</v>
+        <v>1.807008800770314e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.393744279905975e-08</v>
+        <v>2.045696078104959e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.283442268399466e-08</v>
+        <v>3.877111673008642e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.890537075014482e-08</v>
+        <v>3.462956524533085e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.503467801928107e-08</v>
+        <v>3.056805738836314e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.70335136897004e-08</v>
+        <v>2.378935514080493e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.253690011497278e-08</v>
+        <v>2.781519571791757e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.835848162903977e-08</v>
+        <v>3.442702336252791e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.572374264180618e-08</v>
+        <v>2.9542442180495e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.552105845589141e-08</v>
+        <v>3.091344426546762e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.303387217873669e-08</v>
+        <v>2.725233016822988e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.988744463855291e-08</v>
+        <v>2.535982148547434e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.216870494043937e-08</v>
+        <v>2.790931226245323e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.267436081482332e-08</v>
+        <v>3.486358679411037e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.86115941943391e-08</v>
+        <v>2.468870244864827e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.263282497896029e-08</v>
+        <v>2.734917616731308e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.925438066033846e-08</v>
+        <v>2.564460944134414e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.835739059951131e-08</v>
+        <v>3.195939340028759e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.62632032370686e-08</v>
+        <v>3.058781052202817e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.365682604462909e-08</v>
+        <v>2.832026339663869e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.285955661732787e-08</v>
+        <v>2.8188733647588e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.354240940569698e-08</v>
+        <v>2.93966916693661e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.002033898382077e-08</v>
+        <v>6.574941987343694e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.043979042954334e-08</v>
+        <v>2.586449124691408e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.192022278393192e-08</v>
+        <v>3.67242148589207e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.79717948340872e-08</v>
+        <v>2.432100024392357e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.57847158820435e-08</v>
+        <v>2.955229516196722e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.754132108359213e-08</v>
+        <v>3.314392934796156e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.754555514694523e-08</v>
+        <v>4.417848974197648e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.94229075343122e-08</v>
+        <v>6.592459002780297e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.549385560046211e-08</v>
+        <v>6.178303854304772e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.283087085191228e-08</v>
+        <v>5.860055327800962e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.757088718943278e-08</v>
+        <v>3.493783905116448e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.78224696930143e-08</v>
+        <v>5.382003899682538e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.494696647935884e-08</v>
+        <v>6.158049666024461e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.231222749212325e-08</v>
+        <v>5.669591547821163e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.210954330620928e-08</v>
+        <v>5.806691756318403e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.962235702905467e-08</v>
+        <v>5.440580346594653e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.64759294888693e-08</v>
+        <v>5.251329478319096e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.875718979075975e-08</v>
+        <v>5.506278556012813e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.413358644735869e-08</v>
+        <v>3.486358679411037e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>7.180232772184331e-08</v>
+        <v>5.792922400453069e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.681934064183099e-08</v>
+        <v>6.152554654430618e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.336118452263775e-08</v>
+        <v>5.942611614467379e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.494587544982741e-08</v>
+        <v>5.911286669800425e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.285168808738577e-08</v>
+        <v>5.774128381974484e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.024531089494606e-08</v>
+        <v>5.547373669435511e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.258762162842669e-08</v>
+        <v>5.807948586454515e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.26187284449296e-08</v>
+        <v>6.845394520161971e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.066075889769233e-07</v>
+        <v>9.29018045354591e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.39706985077559e-08</v>
+        <v>5.913829725858552e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.238556816499286e-08</v>
+        <v>5.842740170804999e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.53751965718594e-08</v>
+        <v>5.170785317316353e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.237320073236023e-08</v>
+        <v>5.670576845968385e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.756619568995409e-08</v>
+        <v>5.451102558089713e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9234119550481e-07</v>
+        <v>1.913094313816484e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.891186021222812e-07</v>
+        <v>3.876761274767929e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.924247748305906e-07</v>
+        <v>1.914242163806325e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.926744699888826e-07</v>
+        <v>1.916200117395173e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.925957599279825e-07</v>
+        <v>1.915815909148843e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.924352131310107e-07</v>
+        <v>1.91374261037114e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.929532282695389e-07</v>
+        <v>1.919403978972842e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.925446337990281e-07</v>
+        <v>1.91373290853518e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.927215819436512e-07</v>
+        <v>1.916572626889626e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.924979078848973e-07</v>
+        <v>1.912986136408562e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.923998400884298e-07</v>
+        <v>1.913452094182789e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.924537913178802e-07</v>
+        <v>1.914226162874084e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.933634996302577e-07</v>
+        <v>1.923425915917717e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.012176236388424e-07</v>
+        <v>9.911293194305184e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.927988399839335e-07</v>
+        <v>1.916597651944829e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.928215805067579e-07</v>
+        <v>1.917611109938484e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9294183749198e-07</v>
+        <v>1.91727955117377e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.927777126359191e-07</v>
+        <v>1.916423715300254e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.926421495641024e-07</v>
+        <v>1.914842377197971e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.333944084178291e-07</v>
+        <v>4.317439663636271e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.92789606360615e-07</v>
+        <v>1.917137749725428e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.059906378693034e-07</v>
+        <v>3.043186507286319e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.927547880326966e-07</v>
+        <v>1.916317377945245e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.926534025563647e-07</v>
+        <v>1.915454552117531e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.69909822879766e-07</v>
+        <v>1.685396850957725e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.928833969344497e-07</v>
+        <v>1.916804138249574e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.923238018028205e-07</v>
+        <v>1.913378556434556e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.962090947436804e-07</v>
+        <v>1.951099085500714e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.275754444825437e-07</v>
+        <v>5.258738634496657e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.968143079262803e-07</v>
+        <v>1.959368012019217e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.985825266684258e-07</v>
+        <v>1.973216437473883e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.980392015200333e-07</v>
+        <v>1.970644992002959e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.968771739759055e-07</v>
+        <v>1.955708376494607e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.006172784077919e-07</v>
+        <v>1.996520225952718e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.976750406267939e-07</v>
+        <v>1.955758979875637e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.989251752904595e-07</v>
+        <v>1.975938089996795e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.973296878428773e-07</v>
+        <v>1.950388272792135e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.966305557591777e-07</v>
+        <v>1.953681027316148e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.970882853257322e-07</v>
+        <v>1.959834498249452e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.035245969430182e-07</v>
+        <v>2.025018619940535e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.589642362855318e-08</v>
+        <v>4.306156185636351e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.994564330157433e-07</v>
+        <v>1.975957692815928e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.996394430937193e-07</v>
+        <v>1.983348702159217e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.005276011182624e-07</v>
+        <v>1.981210525223391e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.993132853517425e-07</v>
+        <v>1.974776615866213e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.983741881245469e-07</v>
+        <v>1.963703812584195e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.978264260169375e-07</v>
+        <v>5.955212835965031e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.993885405490407e-07</v>
+        <v>1.979770968291653e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.012791542235228e-07</v>
+        <v>3.990498081954571e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.991680475466364e-07</v>
+        <v>1.974164464469061e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.98446208726992e-07</v>
+        <v>1.968017744837351e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.602076401337814e-07</v>
+        <v>1.584590393947092e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.000877387250959e-07</v>
+        <v>1.977647871320209e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.961392307488118e-07</v>
+        <v>1.953564966543388e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.646614086442215e-08</v>
+        <v>1.354556144534639e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.998650998821857e-08</v>
+        <v>2.722411736272649e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.741020779750246e-08</v>
+        <v>1.48421108125798e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.023062947585827e-08</v>
+        <v>1.705370946149841e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.93415631295738e-08</v>
+        <v>1.661972857281751e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.752811320260424e-08</v>
+        <v>1.42778422269451e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.337933249101716e-08</v>
+        <v>2.067261849839033e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.876406998385439e-08</v>
+        <v>1.426688355692117e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.084662001218774e-08</v>
+        <v>1.755836169328406e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.823627928876326e-08</v>
+        <v>1.342337008669117e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.712855841424871e-08</v>
+        <v>1.394969082779809e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.785586432397115e-08</v>
+        <v>1.492614468607387e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.801353624448435e-08</v>
+        <v>2.619559071498782e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.668211377941396e-08</v>
+        <v>1.383468799023095e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.16354457829837e-08</v>
+        <v>1.750274302282787e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.189231044944273e-08</v>
+        <v>1.86474904480321e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.325066841847146e-08</v>
+        <v>1.827297957083044e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.139680266809977e-08</v>
+        <v>1.730627358130047e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.986555540983747e-08</v>
+        <v>1.552007944962407e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.406634376657443e-08</v>
+        <v>2.037179094264809e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.209044023376804e-08</v>
+        <v>1.86718670259333e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.240544236585559e-08</v>
+        <v>4.933580197032979e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.113785872886391e-08</v>
+        <v>1.718616064705705e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.991061458213021e-08</v>
+        <v>1.573721899002272e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.860728466499936e-08</v>
+        <v>1.549639060613268e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.25905554371822e-08</v>
+        <v>1.77359788028774e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.634406148118351e-08</v>
+        <v>1.392218202556705e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.317764580887427e-08</v>
+        <v>4.610121648456422e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.992938731633218e-07</v>
+        <v>2.84513910106868e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>8.438532738683967e-08</v>
+        <v>7.300574496402433e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.270823728929883e-07</v>
+        <v>1.056132925479869e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.209099335475911e-07</v>
+        <v>1.067820580569233e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>8.044236784544858e-08</v>
+        <v>5.813898159174613e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.062168626383485e-07</v>
+        <v>1.923007416228702e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.110737160837358e-07</v>
+        <v>6.415586806021733e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.398990987946524e-07</v>
+        <v>1.164056913967183e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.55887807387074e-08</v>
+        <v>4.711443788739935e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.640250735112147e-08</v>
+        <v>5.472302774929416e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>9.37324097415903e-08</v>
+        <v>7.583496477380423e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.944912308043019e-07</v>
+        <v>2.619559071498782e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>6.625388432634558e-08</v>
+        <v>5.039669127311222e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.448144160639067e-07</v>
+        <v>1.085818646042619e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.600898380442676e-07</v>
+        <v>1.370118520718837e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.995981187557493e-07</v>
+        <v>1.422125747275377e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.445524780659714e-07</v>
+        <v>1.08232782814206e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.32199433966826e-07</v>
+        <v>8.769397759291303e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.90626086878331e-07</v>
+        <v>1.671395327926846e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.424969105971438e-07</v>
+        <v>1.177839656116705e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>7.063975330947763e-07</v>
+        <v>6.861905942926527e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.494956435635915e-07</v>
+        <v>1.137150760993179e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.301501323437433e-07</v>
+        <v>9.706382120039998e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.360984789442106e-08</v>
+        <v>7.398187105305882e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.761233593472884e-07</v>
+        <v>1.23925316463998e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.819996750667585e-08</v>
+        <v>5.977827051888936e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.372373687351901e-08</v>
+        <v>1.604369060893163e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.284534483600041e-08</v>
+        <v>2.972224652631134e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.026904264528432e-08</v>
+        <v>2.104189091044735e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.748822548495513e-08</v>
+        <v>2.325348955936598e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.220039797735567e-08</v>
+        <v>1.911785773640238e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.478570921170111e-08</v>
+        <v>1.67759713905302e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.623816733879904e-08</v>
+        <v>2.687239859625766e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.162290483163624e-08</v>
+        <v>1.676501272050581e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.81042160212846e-08</v>
+        <v>2.375814179115179e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.549387529786009e-08</v>
+        <v>1.962315018455875e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.438615442334555e-08</v>
+        <v>1.644781999138345e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.071469917175302e-08</v>
+        <v>1.742427384965859e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.088010900356945e-08</v>
+        <v>2.619559071498782e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.471755456148491e-08</v>
+        <v>1.635505863052908e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.420845069743945e-08</v>
+        <v>2.440123117365548e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.914990645853958e-08</v>
+        <v>2.484727054589941e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.050826442756833e-08</v>
+        <v>2.44727596686979e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.865439867719663e-08</v>
+        <v>1.980440274488488e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.712315141893434e-08</v>
+        <v>2.171985954749206e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.700722716629709e-08</v>
+        <v>2.704591123319797e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.494927508154991e-08</v>
+        <v>2.116999618951829e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.044195419194847e-08</v>
+        <v>5.224743170077295e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.399669357664577e-08</v>
+        <v>1.968428981064146e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.30812008010891e-08</v>
+        <v>1.892635426756052e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.586488067409621e-08</v>
+        <v>1.799451976971745e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.984815144627905e-08</v>
+        <v>2.393575890074478e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.91794825485655e-08</v>
+        <v>1.642698717962802e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.953639104098148e-08</v>
+        <v>1.636726888458649e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.305676016477789e-08</v>
+        <v>3.004582480196649e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.048045797406179e-08</v>
+        <v>1.766381825181979e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.33008796524176e-08</v>
+        <v>1.987541690073853e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.241181330613312e-08</v>
+        <v>1.944143601205752e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.059836337916357e-08</v>
+        <v>1.709954966618523e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.644958266757647e-08</v>
+        <v>2.349432593763034e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.18343201604137e-08</v>
+        <v>1.708859099616108e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.391687018874706e-08</v>
+        <v>2.038006913252413e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.130652946532258e-08</v>
+        <v>1.624507752593128e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.019880859080802e-08</v>
+        <v>1.67713982670381e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.092611450053047e-08</v>
+        <v>1.774785212531387e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.108378642104366e-08</v>
+        <v>2.619559071498782e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>2.975233518866048e-08</v>
+        <v>1.665632558794514e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.470566719223025e-08</v>
+        <v>2.032438062054187e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.496256062600205e-08</v>
+        <v>2.146919788727219e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.632091859503079e-08</v>
+        <v>2.109468701007046e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.44670528446591e-08</v>
+        <v>2.012798102054058e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.29358055863968e-08</v>
+        <v>1.834178688886421e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.696076898971823e-08</v>
+        <v>2.352015538342296e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.516069041032737e-08</v>
+        <v>2.149357446517342e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.547569254241492e-08</v>
+        <v>5.215750940956993e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.420810890542322e-08</v>
+        <v>2.000786808629697e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.306291331063034e-08</v>
+        <v>1.903326662194514e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.167753484155868e-08</v>
+        <v>1.831809804537278e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.566080561374152e-08</v>
+        <v>2.055768624211753e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.941431165774283e-08</v>
+        <v>1.674388946480725e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.358454419187924e-08</v>
+        <v>1.992210312872163e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.312080279691161e-08</v>
+        <v>3.873967591452179e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.054450060619552e-08</v>
+        <v>2.63576693643752e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.016163859833859e-08</v>
+        <v>2.583289312527015e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.739717172624331e-08</v>
+        <v>2.379686902157741e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.190983988317594e-08</v>
+        <v>2.685900940285744e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.651362529971023e-08</v>
+        <v>3.218817705018583e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.189836279254745e-08</v>
+        <v>2.578244210871648e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.398091282088082e-08</v>
+        <v>2.907392024507962e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.137057209745632e-08</v>
+        <v>2.493892863848647e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.026285122294177e-08</v>
+        <v>2.54652493795934e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.099015713265595e-08</v>
+        <v>2.64417032379122e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.648450826263197e-08</v>
+        <v>2.619559071498782e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.643460682913794e-08</v>
+        <v>2.246137598754173e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.107380706326767e-08</v>
+        <v>2.586108691686534e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.78284541944584e-08</v>
+        <v>2.401409802825725e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.638496122716454e-08</v>
+        <v>2.978853812262566e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.453109547679285e-08</v>
+        <v>2.882183213309588e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.299984821853054e-08</v>
+        <v>2.703563800141966e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.414658640777518e-08</v>
+        <v>2.973900741225174e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.33601004257169e-08</v>
+        <v>2.865667853515951e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.554091744491694e-08</v>
+        <v>6.085237047152974e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.76253706836742e-08</v>
+        <v>2.302376932567697e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.876657831567803e-08</v>
+        <v>3.264102572272689e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.561393975894204e-08</v>
+        <v>2.17774724139923e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.572484824587525e-08</v>
+        <v>2.925153735467302e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.576245387075784e-08</v>
+        <v>3.080587340056541e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.444271479292921e-08</v>
+        <v>4.10314206270774e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.634995156986852e-08</v>
+        <v>6.27846386816851e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.377364937915243e-08</v>
+        <v>5.040263213153831e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.465841822184279e-08</v>
+        <v>5.07506333524285e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.637098236782062e-08</v>
+        <v>3.356594706879726e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.389155739639581e-08</v>
+        <v>4.98383657004635e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.974277407266713e-08</v>
+        <v>5.623313981734911e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.512751156550434e-08</v>
+        <v>4.98274048758797e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.721006159383773e-08</v>
+        <v>5.311888301224293e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.459972087041325e-08</v>
+        <v>4.898389140564978e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.349199999589869e-08</v>
+        <v>4.951021214675721e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.421930590562113e-08</v>
+        <v>5.048666600503269e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.437697782613429e-08</v>
+        <v>2.619559071498782e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>6.582495579744995e-08</v>
+        <v>5.207114463717611e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.138275914135791e-08</v>
+        <v>5.632116922371209e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.825575464323429e-08</v>
+        <v>5.420801392155041e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.961411000012145e-08</v>
+        <v>5.383350088978883e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>6.776024424974977e-08</v>
+        <v>5.286679490025898e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.622899699148744e-08</v>
+        <v>5.108060076858295e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.051183390016521e-08</v>
+        <v>5.640665245428915e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.813214932256797e-08</v>
+        <v>6.355037690130556e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.87688839475056e-08</v>
+        <v>8.489632328928842e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>6.750130031051389e-08</v>
+        <v>5.274668196601594e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.635610471572097e-08</v>
+        <v>5.17720805016634e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.99141918784267e-08</v>
+        <v>4.618860953886729e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.895399701883219e-08</v>
+        <v>5.329650012183545e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.270750306283347e-08</v>
+        <v>4.948270334452561e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.926547419487059e-07</v>
+        <v>1.919039232469921e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.878937528100998e-07</v>
+        <v>3.867442059629415e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.937121797481357e-07</v>
+        <v>1.929603303530226e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.928592733978415e-07</v>
+        <v>1.920903450342481e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.926979282893791e-07</v>
+        <v>1.91918325729144e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.925859703361389e-07</v>
+        <v>1.918116143141689e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.933014394763227e-07</v>
+        <v>1.925524688145519e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.932425665752587e-07</v>
+        <v>1.923847078979015e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.929457124759052e-07</v>
+        <v>1.921852070606703e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.943504203309354e-07</v>
+        <v>1.935814665063054e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.932105454226452e-07</v>
+        <v>1.924409944731804e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.926002662198744e-07</v>
+        <v>1.918418307412039e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.941485907191142e-07</v>
+        <v>1.933905813346992e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.020794249602028e-07</v>
+        <v>1.003505885607574e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.929006178768941e-07</v>
+        <v>1.921175540319796e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.931765871694839e-07</v>
+        <v>1.924175618319346e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.93046628812508e-07</v>
+        <v>1.921795071840345e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.933374194460989e-07</v>
+        <v>1.925169364745471e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.929621082081097e-07</v>
+        <v>1.921540030649079e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.338686002845699e-07</v>
+        <v>4.332570109708584e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.926867578144229e-07</v>
+        <v>1.9192723328468e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.068431177636979e-07</v>
+        <v>3.056967473143483e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.934770550101147e-07</v>
+        <v>1.927149930512534e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.929779478158811e-07</v>
+        <v>1.922250556782617e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.707676436085375e-07</v>
+        <v>1.695694688126469e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.931748650894345e-07</v>
+        <v>1.92264260536484e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.926647969157876e-07</v>
+        <v>1.91925301375964e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.971347434499974e-07</v>
+        <v>1.964471788429997e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.182032408345246e-07</v>
+        <v>5.168666521597127e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.047127880767908e-07</v>
+        <v>2.040175242434783e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.986025413618396e-07</v>
+        <v>1.977856597777182e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.97459346097316e-07</v>
+        <v>1.96565616816006e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.966458485586649e-07</v>
+        <v>1.957915672118061e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.01795454464664e-07</v>
+        <v>2.011206569436825e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.013596980354272e-07</v>
+        <v>1.999055570047228e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.992127791563439e-07</v>
+        <v>1.984563887618365e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.092066399943633e-07</v>
+        <v>2.083897656402929e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.010763313576812e-07</v>
+        <v>2.002558227708212e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.968377670801506e-07</v>
+        <v>1.960904827512322e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.078005690272588e-07</v>
+        <v>2.070615130955479e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.817083115681851e-08</v>
+        <v>4.585949345688972e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.988840617284664e-07</v>
+        <v>1.979672390289639e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.008630493727791e-07</v>
+        <v>2.001167880024791e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.999642359344403e-07</v>
+        <v>1.984424627962972e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.019536569914013e-07</v>
+        <v>2.007737408456074e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.993410607717143e-07</v>
+        <v>1.982443741442878e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.974201203894794e-07</v>
+        <v>5.996730791677747e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.973623695280253e-07</v>
+        <v>1.966129688125579e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.032861876462276e-07</v>
+        <v>4.018818483102208e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.030249163361748e-07</v>
+        <v>2.022567164410221e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.994500584594706e-07</v>
+        <v>1.987474943526335e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.620575060077444e-07</v>
+        <v>1.605926456705879e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.008573116871052e-07</v>
+        <v>1.990290435673037e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.972661848812429e-07</v>
+        <v>1.966539692361321e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.85087940637268e-08</v>
+        <v>1.590434211981727e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.599892385973869e-08</v>
+        <v>1.341402877284109e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.045304045370653e-08</v>
+        <v>2.783694635370894e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.081907087082784e-08</v>
+        <v>1.80100619651309e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.899660364832808e-08</v>
+        <v>1.606702478119011e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.773198706327686e-08</v>
+        <v>1.486167025937174e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.581354013371907e-08</v>
+        <v>2.322996265110598e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.514854363332995e-08</v>
+        <v>2.133502592370475e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.187765221088217e-08</v>
+        <v>1.916388470477777e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.766226144160426e-08</v>
+        <v>3.485296494178645e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.478684998409974e-08</v>
+        <v>2.197080868458299e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.803946441375271e-08</v>
+        <v>1.533957026040713e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.538250312987401e-08</v>
+        <v>3.960769572488402e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.964959792908656e-08</v>
+        <v>1.702565428855794e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.128607578112701e-08</v>
+        <v>1.831740011126585e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.440327589307449e-08</v>
+        <v>2.170612622216567e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.293533646723455e-08</v>
+        <v>1.901718946358502e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.621995044394499e-08</v>
+        <v>2.282860852506688e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.198063735916002e-08</v>
+        <v>1.872910870557539e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.28167544657179e-08</v>
+        <v>2.554478131248605e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.941849042972839e-08</v>
+        <v>1.671605798296248e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.484145724466865e-08</v>
+        <v>5.210596970951934e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.779719837503484e-08</v>
+        <v>2.506574866949123e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.21006958612168e-08</v>
+        <v>1.92030081617489e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.069464341915501e-08</v>
+        <v>1.800952934041511e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.438382420672161e-08</v>
+        <v>1.997451756797151e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.869571644289647e-08</v>
+        <v>1.620950027735559e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.0038770922373e-08</v>
+        <v>7.635197002561421e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.941925385234577e-08</v>
+        <v>3.593606907850649e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.331526050845205e-07</v>
+        <v>3.190548505974942e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.381964895756706e-07</v>
+        <v>1.206044507924777e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.083717688281915e-07</v>
+        <v>8.812992787893689e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.642520641012678e-08</v>
+        <v>5.841793176537707e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.53293471252293e-07</v>
+        <v>2.397664065998412e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.320562639335216e-07</v>
+        <v>1.940476726133209e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.530234676247608e-07</v>
+        <v>1.374396649552537e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.353700992965595e-07</v>
+        <v>4.178777058653165e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.947235029047632e-07</v>
+        <v>1.77452552148807e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>8.811416771951718e-08</v>
+        <v>7.248522964372888e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.834737766158952e-07</v>
+        <v>3.960769572488402e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.077855664363183e-07</v>
+        <v>9.378113926831831e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.394866834494055e-07</v>
+        <v>1.194009773772179e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.036436950685632e-07</v>
+        <v>1.881343248886499e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.918528508441183e-07</v>
+        <v>1.510194953701332e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.061477272986592e-07</v>
+        <v>1.802775040177303e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.627077022843906e-07</v>
+        <v>1.366381938618614e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.709668851060377e-07</v>
+        <v>2.574124749947623e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.693919043446455e-08</v>
+        <v>8.15590447446971e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>7.855393004632743e-07</v>
+        <v>7.692646107764856e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.774999397048456e-07</v>
+        <v>2.611940872607636e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.638379930580567e-07</v>
+        <v>1.495964164596302e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.256551870028031e-07</v>
+        <v>1.106246262414643e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.069203064599099e-07</v>
+        <v>1.589384557197868e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.046003507145913e-07</v>
+        <v>9.303008596277018e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.147335902353817e-08</v>
+        <v>1.858766577711818e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.380942369978851e-08</v>
+        <v>1.609735243014214e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.341760541351789e-08</v>
+        <v>3.477226532818673e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.378363583063921e-08</v>
+        <v>2.494538093960873e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.680710348837794e-08</v>
+        <v>1.87503484384911e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.554248690332666e-08</v>
+        <v>1.754499391667282e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.877810509353045e-08</v>
+        <v>3.016528162558379e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.811310859314131e-08</v>
+        <v>2.827034489818267e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.484221717069355e-08</v>
+        <v>2.184720836207853e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.062682640141558e-08</v>
+        <v>4.178828391626438e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.775141494391111e-08</v>
+        <v>2.465413234188408e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.584996425380253e-08</v>
+        <v>2.227488923488488e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.835031988865987e-08</v>
+        <v>3.960769572488402e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.836205362328611e-08</v>
+        <v>2.484621058154617e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.393886856106105e-08</v>
+        <v>2.613155726887915e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.221377573312431e-08</v>
+        <v>2.864144519664338e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.589990142704591e-08</v>
+        <v>2.595250843806293e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.918451540375634e-08</v>
+        <v>2.551193218236785e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.979113719920982e-08</v>
+        <v>2.141243236287647e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.584017657982801e-08</v>
+        <v>2.855677746726105e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.722899026977821e-08</v>
+        <v>2.365137695744021e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.828365109968026e-08</v>
+        <v>5.993060328647737e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.076176333484621e-08</v>
+        <v>2.774907232679215e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.535964659764025e-08</v>
+        <v>2.244636049230037e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.850514325920481e-08</v>
+        <v>2.06928529977161e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.219432404677147e-08</v>
+        <v>2.690983654244931e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.164565630319999e-08</v>
+        <v>1.889868729567677e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.204249389304808e-08</v>
+        <v>1.916780034281226e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.953262368905997e-08</v>
+        <v>1.667748699583624e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.398674028302781e-08</v>
+        <v>3.110040457670407e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.435277070014911e-08</v>
+        <v>2.127352018812605e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.253030347764933e-08</v>
+        <v>1.933048300418535e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.126568689259813e-08</v>
+        <v>1.812512848236698e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.934723996304036e-08</v>
+        <v>2.649342087410113e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.868224346265119e-08</v>
+        <v>2.459848414669988e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.541135204020344e-08</v>
+        <v>2.242734292777287e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.119596127092552e-08</v>
+        <v>3.811642316478157e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.832054981342103e-08</v>
+        <v>2.523426690757818e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.157316424307398e-08</v>
+        <v>1.860302848340229e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.891620295919523e-08</v>
+        <v>3.960769572488402e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>3.318318608556474e-08</v>
+        <v>2.028899705870138e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.481966393760523e-08</v>
+        <v>2.158074288140924e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.793697572239579e-08</v>
+        <v>2.49695844451607e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.646903629655584e-08</v>
+        <v>2.228064768658009e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.975365027326625e-08</v>
+        <v>2.609206674806202e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.551433718848129e-08</v>
+        <v>2.199256692857066e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.628366897826344e-08</v>
+        <v>2.904420630305407e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.295219025904967e-08</v>
+        <v>1.997951620595781e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.837515707398994e-08</v>
+        <v>5.536942793251446e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.133089820435612e-08</v>
+        <v>2.832920689248626e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.569325284483682e-08</v>
+        <v>2.279513888221816e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.422834324847628e-08</v>
+        <v>2.127298756341021e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.791752403604291e-08</v>
+        <v>2.323797579096658e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.222941627221775e-08</v>
+        <v>1.947295850035066e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.654983706979662e-08</v>
+        <v>2.33055834880284e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.08198274749889e-08</v>
+        <v>2.688209762524016e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.527394406895671e-08</v>
+        <v>4.130501520610796e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.202989871024973e-08</v>
+        <v>2.82477241461754e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.809386969630264e-08</v>
+        <v>2.441340696454564e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.395873894042264e-08</v>
+        <v>2.958773531079747e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.063444374896926e-08</v>
+        <v>3.669803150350499e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.996944724858011e-08</v>
+        <v>3.480309477610383e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.669855582613236e-08</v>
+        <v>3.263195355717668e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.248316505685442e-08</v>
+        <v>4.832103379418552e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.960775359934995e-08</v>
+        <v>3.543887753698213e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.286036802898896e-08</v>
+        <v>2.880763911283535e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.494788052020923e-08</v>
+        <v>3.960769572488402e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>4.065923954544071e-08</v>
+        <v>2.708328886242645e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.19416933388136e-08</v>
+        <v>2.805824308458399e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.111192155364593e-08</v>
+        <v>2.791509752615129e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.775624008248473e-08</v>
+        <v>3.248525831598402e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.104085405919519e-08</v>
+        <v>3.629667737746592e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.680154097441019e-08</v>
+        <v>3.219717755797449e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.42900724589806e-08</v>
+        <v>3.630862993695804e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.227905527854443e-08</v>
+        <v>2.844682751920963e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.966369327053041e-08</v>
+        <v>6.557523084791625e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.512723171614596e-08</v>
+        <v>3.183075675549501e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.355509430768643e-08</v>
+        <v>3.890910572791391e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.860974703582147e-08</v>
+        <v>2.529807627489209e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.920472782197181e-08</v>
+        <v>3.344258642037046e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.059875136276732e-08</v>
+        <v>3.601487771907932e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.550325313823318e-08</v>
+        <v>5.236964832141087e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.395155105561177e-08</v>
+        <v>6.05577536318783e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.84056676495796e-08</v>
+        <v>7.498067121274613e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.624260104341973e-08</v>
+        <v>6.268925463474552e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.168765664868615e-08</v>
+        <v>3.859407465158056e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.56846187853568e-08</v>
+        <v>6.200539938286797e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.376616732959217e-08</v>
+        <v>7.037368751014304e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.310117082920291e-08</v>
+        <v>6.8478750782742e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.983027940675517e-08</v>
+        <v>6.630760956381493e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>9.561488863747725e-08</v>
+        <v>8.199668980082369e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.273947717997283e-08</v>
+        <v>6.911453354362019e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.599209160962575e-08</v>
+        <v>6.248329511944431e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>9.333513032574706e-08</v>
+        <v>3.960769572488402e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>8.123375371806772e-08</v>
+        <v>6.77081987861687e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.366002574820041e-08</v>
+        <v>6.976957623690105e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.235590761515443e-08</v>
+        <v>6.884985534566164e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.088796366310766e-08</v>
+        <v>6.616091432262224e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.417257763981806e-08</v>
+        <v>6.997233338410409e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.993326455503307e-08</v>
+        <v>6.587283356461272e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.082823881588972e-08</v>
+        <v>7.301717866899738e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.001661321479816e-08</v>
+        <v>7.618245339854735e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.127940844405418e-07</v>
+        <v>9.924969456855651e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>8.574982557090789e-08</v>
+        <v>7.220947352852831e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.01121802113886e-08</v>
+        <v>6.667540551826036e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.204047147347931e-08</v>
+        <v>5.871511900441922e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.233645140259473e-08</v>
+        <v>6.711824242700867e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.664834363876958e-08</v>
+        <v>6.335322513639273e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.918577773818836e-07</v>
+        <v>1.909473009578243e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.873472606519904e-07</v>
+        <v>3.860542864277071e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.922596097571697e-07</v>
+        <v>1.913113172479399e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.919678490837233e-07</v>
+        <v>1.910290418615062e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.918997825349225e-07</v>
+        <v>1.909806302831251e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.922489649106278e-07</v>
+        <v>1.913214411825556e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.926611956316103e-07</v>
+        <v>1.917507664924305e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.921303631441809e-07</v>
+        <v>1.911594333465388e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.922399857902617e-07</v>
+        <v>1.913191809057546e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.921181251588194e-07</v>
+        <v>1.911926993689487e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.919800268915675e-07</v>
+        <v>1.910649302121804e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.919980865616794e-07</v>
+        <v>1.910928953848861e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.923294642386263e-07</v>
+        <v>1.914118440642808e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.004811639991439e-07</v>
+        <v>9.855863676726074e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92074977715725e-07</v>
+        <v>1.911529523784736e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.919929061475005e-07</v>
+        <v>1.910794744400206e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.920871851253863e-07</v>
+        <v>1.911569953353581e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.924283175403332e-07</v>
+        <v>1.914868180225826e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.920142308739491e-07</v>
+        <v>1.910664271892811e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.317991207695533e-07</v>
+        <v>4.303260855644672e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.922309296344448e-07</v>
+        <v>1.913120451897072e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.041215075832967e-07</v>
+        <v>3.025157686055651e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.924919217081393e-07</v>
+        <v>1.915765036039019e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.920250195128009e-07</v>
+        <v>1.911099075733016e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.694810618670728e-07</v>
+        <v>1.679758073360773e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.927621435272832e-07</v>
+        <v>1.91844625633212e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.918085140076564e-07</v>
+        <v>1.909002319868467e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.951628017419929e-07</v>
+        <v>1.943343136589895e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.184105469113025e-07</v>
+        <v>5.169470436610452e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.980319449601063e-07</v>
+        <v>1.969337693782488e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.959499246779705e-07</v>
+        <v>1.949192063292477e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.954680435288057e-07</v>
+        <v>1.945773112446526e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.979307935736569e-07</v>
+        <v>1.969820611636428e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.009280547030157e-07</v>
+        <v>2.000993623317697e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.971164592681596e-07</v>
+        <v>1.958556311408346e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.978786738486931e-07</v>
+        <v>1.969769760500946e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.97018087821039e-07</v>
+        <v>1.960833624222049e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.960297296828308e-07</v>
+        <v>1.951690034438815e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.962285066263688e-07</v>
+        <v>1.954304206191458e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.985264211493116e-07</v>
+        <v>1.976468624503707e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.491732983385211e-08</v>
+        <v>4.238547601969503e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.967054817009596e-07</v>
+        <v>1.95794989747651e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.961237183831731e-07</v>
+        <v>1.952743335329274e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.968107535127788e-07</v>
+        <v>1.958407640535385e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.991980034202928e-07</v>
+        <v>1.981503856100484e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.962834861899848e-07</v>
+        <v>1.95188827911251e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.912062129446299e-07</v>
+        <v>5.898522867952386e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.978088684111027e-07</v>
+        <v>1.969209551089195e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.930098064084967e-07</v>
+        <v>3.91032868350647e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.99683769309736e-07</v>
+        <v>1.98819917331716e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.963596471121422e-07</v>
+        <v>1.954977977579234e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.597262753126115e-07</v>
+        <v>1.578572808695571e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.016204465034404e-07</v>
+        <v>2.007414382446396e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.948643313868299e-07</v>
+        <v>1.940458325313099e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.48774301553981e-08</v>
+        <v>1.249934958281884e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.602416709618798e-08</v>
+        <v>1.363920556398436e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.941631168629098e-08</v>
+        <v>1.661108103544233e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.612074066317602e-08</v>
+        <v>1.342265069257992e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.535189768231664e-08</v>
+        <v>1.287581964434023e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.929607324773353e-08</v>
+        <v>1.672543553416695e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.395240887670868e-08</v>
+        <v>2.157486240860471e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.79564117361339e-08</v>
+        <v>1.489548249907039e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.927706712681727e-08</v>
+        <v>1.678251512256211e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.781817806179755e-08</v>
+        <v>1.52712375253165e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.625829460478807e-08</v>
+        <v>1.382802612290218e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.657799797005694e-08</v>
+        <v>1.424643878191326e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.020535018899907e-08</v>
+        <v>1.240953718102561e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.609916779174351e-08</v>
+        <v>1.365270174788396e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.733080784324727e-08</v>
+        <v>1.482227698338169e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.640377172536112e-08</v>
+        <v>1.399230986703285e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.74686961510485e-08</v>
+        <v>1.486794404124353e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.132194370654961e-08</v>
+        <v>1.859344301937688e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.664464432046212e-08</v>
+        <v>1.384493516789957e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.476021753625996e-08</v>
+        <v>1.296034328001928e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.964155472975294e-08</v>
+        <v>1.716935092504123e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.078350381342534e-08</v>
+        <v>3.840397162241913e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.204038204128013e-08</v>
+        <v>1.960648291778417e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.670462836860885e-08</v>
+        <v>1.401313464831527e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.799410736124466e-08</v>
+        <v>1.549373052065087e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.509266179668515e-08</v>
+        <v>2.263504458106796e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.440710382983118e-08</v>
+        <v>1.204398954135539e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.627843256483156e-08</v>
+        <v>3.280193240333591e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.867113483503196e-08</v>
+        <v>5.497314255220958e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.272015032288113e-07</v>
+        <v>1.06277829029128e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>6.906427470951583e-08</v>
+        <v>4.991132461114325e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.749393620121791e-08</v>
+        <v>4.211608429402865e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.120267234053576e-07</v>
+        <v>9.588203436812853e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22961753759494e-07</v>
+        <v>2.092139452718082e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.049844089627645e-07</v>
+        <v>7.897389022119145e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.165157074988627e-07</v>
+        <v>1.012377072833716e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.682436268621421e-08</v>
+        <v>8.059815168731026e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.781328251191423e-08</v>
+        <v>5.379559998389618e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.710364215360884e-08</v>
+        <v>6.43674624869362e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>5.247976447396504e-08</v>
+        <v>1.240953718102561e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>6.526534671740843e-08</v>
+        <v>5.079968919692547e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>8.578914311159603e-08</v>
+        <v>7.022374184594773e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.145839314297134e-08</v>
+        <v>5.749266694282195e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>9.763210740479653e-08</v>
+        <v>7.97995524695795e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.412041958693496e-07</v>
+        <v>1.227133758326411e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>7.964270837006595e-08</v>
+        <v>5.883148000373416e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.70965104119312e-08</v>
+        <v>4.613908460337305e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.124934156505699e-07</v>
+        <v>9.764027123011448e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.797065572751001e-07</v>
+        <v>4.661594131620692e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.704007549583341e-07</v>
+        <v>1.558878439014014e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.136370997453138e-08</v>
+        <v>6.681739375257312e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.441854908742824e-08</v>
+        <v>7.913393923445594e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.285781073583191e-07</v>
+        <v>2.135576169130126e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.124068089106444e-08</v>
+        <v>2.785441971593828e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.737616699444457e-08</v>
+        <v>1.815492286707308e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.852290393523494e-08</v>
+        <v>1.56369282702005e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.19150485253377e-08</v>
+        <v>1.860880374165842e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.292774593148401e-08</v>
+        <v>1.542037339879625e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.215890295062345e-08</v>
+        <v>1.85313929285944e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.179481008678003e-08</v>
+        <v>2.238100881842095e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.645114571575548e-08</v>
+        <v>2.723043569285874e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.04551485751805e-08</v>
+        <v>2.055105578332439e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.177580396586392e-08</v>
+        <v>2.243808840681613e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.03169149008447e-08</v>
+        <v>2.092681080957054e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.306529987309652e-08</v>
+        <v>1.582574882911827e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.338500323836434e-08</v>
+        <v>1.990201206616741e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.271603355722643e-08</v>
+        <v>1.240953718102561e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.860985115997061e-08</v>
+        <v>2.004666150950757e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.95800964571071e-08</v>
+        <v>1.663039559192725e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8902508564408e-08</v>
+        <v>1.964788315128705e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.427570141935612e-08</v>
+        <v>1.686566674745958e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.382068054559629e-08</v>
+        <v>2.424901630363115e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.345164958876928e-08</v>
+        <v>1.584265787411576e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.732083296601197e-08</v>
+        <v>1.528099744529471e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.644855999805957e-08</v>
+        <v>1.91670736312575e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.364780886086927e-08</v>
+        <v>4.074811813854292e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.453911888032706e-08</v>
+        <v>2.52620562020383e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.946990477556855e-08</v>
+        <v>1.65303198229942e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.480111262955499e-08</v>
+        <v>1.74914532268672e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.189966706499226e-08</v>
+        <v>2.8290617865322e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.689431449072339e-08</v>
+        <v>1.406172814306377e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.775480875557503e-08</v>
+        <v>1.515762904646682e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.890154569636446e-08</v>
+        <v>1.629748502763218e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.229369028646761e-08</v>
+        <v>1.926936049909009e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.899811926335294e-08</v>
+        <v>1.608093015622794e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.822927628249354e-08</v>
+        <v>1.553409910798824e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.217345184791032e-08</v>
+        <v>1.938371499781472e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.682978747688553e-08</v>
+        <v>2.423314187225251e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.083379033631093e-08</v>
+        <v>1.755376196271817e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.215444572699385e-08</v>
+        <v>1.944079458620993e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.069555666197456e-08</v>
+        <v>1.792951698896433e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.913567320496476e-08</v>
+        <v>1.648630558655e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.945537657023385e-08</v>
+        <v>1.690471824556132e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.308272878917569e-08</v>
+        <v>1.240953718102561e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>2.897647106200234e-08</v>
+        <v>1.631087582098551e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.020811111350639e-08</v>
+        <v>1.748045105648327e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.928115032553766e-08</v>
+        <v>1.665058933068082e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.034607475122548e-08</v>
+        <v>1.75262235048913e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.419932230672669e-08</v>
+        <v>2.125172248302487e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.952202292063865e-08</v>
+        <v>1.650321463154736e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.752229056119073e-08</v>
+        <v>1.584402236662277e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.251893332992977e-08</v>
+        <v>1.982763038868918e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.366088241360239e-08</v>
+        <v>4.106225108606698e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.491776064145679e-08</v>
+        <v>2.226476238143211e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.964388555949059e-08</v>
+        <v>1.699434557102243e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.087148596142128e-08</v>
+        <v>1.815200998429879e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.797004039686203e-08</v>
+        <v>2.529332404471574e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.728448243000814e-08</v>
+        <v>1.47022690050033e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.147653679999085e-08</v>
+        <v>1.845226265489709e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.816941135482186e-08</v>
+        <v>2.437494179791633e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.156155594492419e-08</v>
+        <v>2.734681726937425e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.53128302474301e-08</v>
+        <v>2.161167467979282e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.281502774561325e-08</v>
+        <v>1.957384066542872e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.259134526866406e-08</v>
+        <v>2.845292130691453e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.609765313534178e-08</v>
+        <v>3.231059864253666e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.010165599476747e-08</v>
+        <v>2.563121873300232e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.142231138545083e-08</v>
+        <v>2.751825135649404e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.996342232043109e-08</v>
+        <v>2.600697375924847e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.84035388634217e-08</v>
+        <v>2.456376235683412e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.872324222865552e-08</v>
+        <v>2.498217501584276e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.805140994261749e-08</v>
+        <v>1.240953718102561e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.512668076545883e-08</v>
+        <v>2.169979979467217e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.606871808598574e-08</v>
+        <v>2.261963029769783e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.191293575015681e-08</v>
+        <v>1.900528902853648e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.961394040968176e-08</v>
+        <v>2.560368027517543e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.34671879651831e-08</v>
+        <v>2.932917925330877e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.878988857909548e-08</v>
+        <v>2.458067140183148e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.412308962670152e-08</v>
+        <v>2.160907571199658e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.011956769188945e-08</v>
+        <v>2.651459175132612e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.292983802560643e-08</v>
+        <v>4.914064780527514e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.805786058559861e-08</v>
+        <v>2.505781731780174e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.419134623183456e-08</v>
+        <v>2.969809070069925e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.449019165410442e-08</v>
+        <v>2.135780019798845e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.723790605531844e-08</v>
+        <v>3.337078081499985e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.2345752566841e-08</v>
+        <v>2.777578448926613e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.560807129384158e-08</v>
+        <v>4.281658349934973e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.584247957518427e-08</v>
+        <v>5.277625414686275e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.923462416528909e-08</v>
+        <v>5.574812961832068e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.384165809256072e-08</v>
+        <v>5.052412413950364e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.422064334065381e-08</v>
+        <v>3.168078467877108e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.911438888304979e-08</v>
+        <v>5.586248686491127e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.377072135570799e-08</v>
+        <v>6.071191099148307e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.777472421512822e-08</v>
+        <v>5.403253108194874e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.909537960581382e-08</v>
+        <v>5.591956370544067e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.763649054079357e-08</v>
+        <v>5.440828610819488e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.607660708378518e-08</v>
+        <v>5.296507470578056e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.639631044905073e-08</v>
+        <v>5.338348736479188e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.002366266799462e-08</v>
+        <v>1.240953718102561e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>6.892912685603049e-08</v>
+        <v>5.57126290211315e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.081574768223594e-08</v>
+        <v>5.751787962601899e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.62220873606765e-08</v>
+        <v>5.312936119777732e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.728700863004317e-08</v>
+        <v>5.400499262412185e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.114025618554626e-08</v>
+        <v>5.773049160225546e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.646295679945732e-08</v>
+        <v>5.298198375077802e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.464040860596295e-08</v>
+        <v>5.242032332195697e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.994684847493045e-08</v>
+        <v>6.648427952987235e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.060181629242328e-08</v>
+        <v>7.754102020529756e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.185869452027729e-08</v>
+        <v>5.874353150066267e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.658481943830887e-08</v>
+        <v>5.347311469025305e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.233336338249348e-08</v>
+        <v>4.931321623938931e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.491097427568389e-08</v>
+        <v>6.177209316394628e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.422541630883071e-08</v>
+        <v>5.118103812423392e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.913341662172314e-07</v>
+        <v>1.906297950100281e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.866251865372946e-07</v>
+        <v>3.856192805237958e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.916468344807998e-07</v>
+        <v>1.909451165364546e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.913956894975486e-07</v>
+        <v>1.906686181788065e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.913854912555597e-07</v>
+        <v>1.906721446591395e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.915663228549716e-07</v>
+        <v>1.908644736575054e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92020106647024e-07</v>
+        <v>1.913180623074892e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.915139080894949e-07</v>
+        <v>1.907951014782932e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.916316182663676e-07</v>
+        <v>1.909262211197084e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.914759051469315e-07</v>
+        <v>1.907708535664785e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.914134544952546e-07</v>
+        <v>1.907088379525224e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.915200428009643e-07</v>
+        <v>1.908212218252619e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.917257107021091e-07</v>
+        <v>1.910232813872204e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.93637232012182e-08</v>
+        <v>9.789289591782493e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.914332078842669e-07</v>
+        <v>1.907172059165375e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.913920517118233e-07</v>
+        <v>1.906927725293583e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.914640333737634e-07</v>
+        <v>1.907380475503118e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.91716001395068e-07</v>
+        <v>1.910020727431125e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.914996261936098e-07</v>
+        <v>1.907833225120918e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.307342904486766e-07</v>
+        <v>4.297068706187978e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.918604585094209e-07</v>
+        <v>1.911509576062785e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.023257017324194e-07</v>
+        <v>3.01210107216892e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.919688281181968e-07</v>
+        <v>1.912635102495924e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.914058793555727e-07</v>
+        <v>1.907054400551605e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.684550903730728e-07</v>
+        <v>1.673089909544723e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.921928717520202e-07</v>
+        <v>1.914881136562466e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.913591437621497e-07</v>
+        <v>1.906476683123099e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.948200796537645e-07</v>
+        <v>1.941569811595365e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.173649039152513e-07</v>
+        <v>5.162005078576067e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.970565604257785e-07</v>
+        <v>1.96412063943211e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.952596342634007e-07</v>
+        <v>1.944351313516356e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.951932506140078e-07</v>
+        <v>1.944655271488829e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.964667790768821e-07</v>
+        <v>1.958216607180166e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.997412934715881e-07</v>
+        <v>1.990942773444502e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.961116142363037e-07</v>
+        <v>1.953448304430143e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.969386206577892e-07</v>
+        <v>1.962681126390551e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.958345334931227e-07</v>
+        <v>1.951663780326337e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.953841623910358e-07</v>
+        <v>1.947194723305968e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.961998811233146e-07</v>
+        <v>1.955706455365465e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.976169020657211e-07</v>
+        <v>1.969673702570947e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.33538472474427e-08</v>
+        <v>4.139686336545568e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.955224204822172e-07</v>
+        <v>1.947768986119036e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.952349728727882e-07</v>
+        <v>1.94607965013732e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.957569911280159e-07</v>
+        <v>1.949385711771833e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.975290213158146e-07</v>
+        <v>1.96798195145754e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.960074288410239e-07</v>
+        <v>1.952587438244081e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.907579267191712e-07</v>
+        <v>5.898870184740881e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.98555606885481e-07</v>
+        <v>1.978561728444744e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.879743221370164e-07</v>
+        <v>3.866720986385606e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.993410419607719e-07</v>
+        <v>1.986710390501769e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.953358236671588e-07</v>
+        <v>1.947004552869399e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.579148352989495e-07</v>
+        <v>1.564864784941785e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.009536344590291e-07</v>
+        <v>2.00287454886131e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.950344774884103e-07</v>
+        <v>1.943171945047057e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.429672361217204e-08</v>
+        <v>1.235260598252592e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.466971670616805e-08</v>
+        <v>1.271895377530702e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.782845548368566e-08</v>
+        <v>1.591430767858019e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.499165736546236e-08</v>
+        <v>1.279113153341716e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.487646353077373e-08</v>
+        <v>1.283096475103846e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.691903963277795e-08</v>
+        <v>1.500340926329267e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2044736314868e-08</v>
+        <v>2.012690172594796e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.632699074473543e-08</v>
+        <v>1.421981858631259e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.774066466261855e-08</v>
+        <v>1.578518815115353e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>2.589773002626315e-08</v>
+        <v>1.39459272677746e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.519232118685414e-08</v>
+        <v>1.324543237954925e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.648425134230869e-08</v>
+        <v>1.459287808161997e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.871939868822843e-08</v>
+        <v>1.141496045286518e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.50192518050077e-08</v>
+        <v>1.301532326310219e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.541544480275592e-08</v>
+        <v>1.333995238255232e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.49505669022315e-08</v>
+        <v>1.306396603445117e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.576363288704569e-08</v>
+        <v>1.357536822365791e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>2.860972759869789e-08</v>
+        <v>1.655765423393156e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.616567016071499e-08</v>
+        <v>1.408676974447492e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.585977906387274e-08</v>
+        <v>1.43189131646318e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.080177242886974e-08</v>
+        <v>1.880087134039007e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.481550709037668e-08</v>
+        <v>3.295368211529193e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.146552174247516e-08</v>
+        <v>1.951071113681703e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.508631260209149e-08</v>
+        <v>1.291395938204392e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.608854826355036e-08</v>
+        <v>1.406893899810104e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.399619765167281e-08</v>
+        <v>2.204770993764998e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.46298916367075e-08</v>
+        <v>1.26004491921721e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.774664034861335e-08</v>
+        <v>3.447325312567575e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.693561899244897e-08</v>
+        <v>4.339627213578297e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.127772849534469e-07</v>
+        <v>9.986063933569861e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.027601734968989e-08</v>
+        <v>4.278240289523096e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.155614948157225e-08</v>
+        <v>4.619574751797771e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.883344118138594e-08</v>
+        <v>7.60537545060726e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.980613845090749e-07</v>
+        <v>1.849809937736945e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>8.816790295199273e-08</v>
+        <v>7.166906487561581e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.049808122901665e-07</v>
+        <v>9.145743010028234e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.754314698017935e-08</v>
+        <v>6.40296162050188e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.26530988877312e-08</v>
+        <v>4.941330677683336e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.92336506850902e-08</v>
+        <v>7.671465965043745e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.613509850381865e-08</v>
+        <v>1.141496045286518e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>5.890811847188472e-08</v>
+        <v>4.475395301354928e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.518837002893085e-08</v>
+        <v>4.989505224926234e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.02238209026881e-08</v>
+        <v>4.783743123702676e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.889593577641668e-08</v>
+        <v>6.075671294697067e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.156158358421586e-07</v>
+        <v>1.006840411303248e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>8.414619317578241e-08</v>
+        <v>6.826929610747721e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.32959227767821e-08</v>
+        <v>7.048863346441785e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.427492104416321e-07</v>
+        <v>1.285948698572045e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>3.982834784982342e-07</v>
+        <v>3.863119850442001e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.70055337568076e-07</v>
+        <v>1.565161059380307e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.410680307036097e-08</v>
+        <v>5.144682484687027e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.453762698311907e-08</v>
+        <v>6.022046343253051e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.218530003110565e-07</v>
+        <v>2.083365742036318e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.799412808190598e-08</v>
+        <v>4.283769815715738e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.058517890325096e-08</v>
+        <v>1.770144239720371e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.095817199724696e-08</v>
+        <v>1.806779018998483e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.411691077476452e-08</v>
+        <v>2.126314409325797e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.128011265654123e-08</v>
+        <v>1.469920851212732e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.116491882185261e-08</v>
+        <v>1.817980116571627e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.320749492385686e-08</v>
+        <v>2.035224567797047e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.43765163890464e-08</v>
+        <v>2.547573814062575e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.865877081891384e-08</v>
+        <v>1.956865500099035e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.007244473679687e-08</v>
+        <v>1.769326512986371e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2186185317342e-08</v>
+        <v>1.585400424648476e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.148077647793292e-08</v>
+        <v>1.859426879422705e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.277270663338758e-08</v>
+        <v>1.994171449629776e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.107013268650303e-08</v>
+        <v>1.141496045286518e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.201078261466689e-08</v>
+        <v>1.495518445728785e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.240483269288986e-08</v>
+        <v>1.939213004033056e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.123902219331034e-08</v>
+        <v>1.841280244912897e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.809541296122407e-08</v>
+        <v>1.89242046383357e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.094150767287628e-08</v>
+        <v>2.190649064860937e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.245412545179386e-08</v>
+        <v>1.59948467231851e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.216867825227061e-08</v>
+        <v>1.996084176300062e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.31335525030482e-08</v>
+        <v>2.070894831910022e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.180958227749812e-08</v>
+        <v>3.901968956958579e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.37973018166536e-08</v>
+        <v>2.14187881155272e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.763773510267026e-08</v>
+        <v>1.532118103605814e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.842032833772878e-08</v>
+        <v>1.597701597681121e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.632797772585125e-08</v>
+        <v>2.739654635232779e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.695761417219341e-08</v>
+        <v>1.453843853115553e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.696948266746036e-08</v>
+        <v>1.487619004329458e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.734247576145637e-08</v>
+        <v>1.52425378360757e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.050121453897394e-08</v>
+        <v>1.843789173934887e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.766441642075062e-08</v>
+        <v>1.531471559418582e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7549222586062e-08</v>
+        <v>1.535454881180714e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.959179868806629e-08</v>
+        <v>1.752699332406135e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.471749537015624e-08</v>
+        <v>2.265048578671664e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.899974980002375e-08</v>
+        <v>1.674340264708125e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.041342371790682e-08</v>
+        <v>1.830877221192219e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.857048908155134e-08</v>
+        <v>1.646951132854328e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.786508024214238e-08</v>
+        <v>1.576901644031792e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.915701039759693e-08</v>
+        <v>1.711646214238863e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.139215774351674e-08</v>
+        <v>1.141496045286518e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>2.769193506021549e-08</v>
+        <v>1.553880127683766e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.80881280579637e-08</v>
+        <v>1.586343039628778e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.762332595751979e-08</v>
+        <v>1.558755009521984e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.843639194233395e-08</v>
+        <v>1.609895228442659e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.128248665398613e-08</v>
+        <v>1.908123829470024e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.883842921600335e-08</v>
+        <v>1.661035380524362e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.837471241769443e-08</v>
+        <v>1.703730304104338e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.347453148415807e-08</v>
+        <v>2.132445540115873e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.748826614566494e-08</v>
+        <v>3.547726617606056e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.413828079776342e-08</v>
+        <v>2.203429519758572e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.777951555469874e-08</v>
+        <v>1.573063562650364e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.876130731883865e-08</v>
+        <v>1.659252305886971e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.666895670696112e-08</v>
+        <v>2.457129399841866e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.730265069199582e-08</v>
+        <v>1.512403325294077e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.038873978701822e-08</v>
+        <v>1.796366432112693e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.578583572791168e-08</v>
+        <v>2.277624917374642e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.894457450542934e-08</v>
+        <v>2.597160307701961e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.343258982641466e-08</v>
+        <v>2.048093685530027e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.175117620920284e-08</v>
+        <v>1.913469485799421e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.907693910746098e-08</v>
+        <v>2.598266087984018e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.316085533661162e-08</v>
+        <v>3.018419712438737e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.744310976647911e-08</v>
+        <v>2.427711398475197e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.885678368436217e-08</v>
+        <v>2.584248354959295e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.701384904800678e-08</v>
+        <v>2.400322266621399e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.630844020859776e-08</v>
+        <v>2.330272777798864e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.760037036400568e-08</v>
+        <v>2.465017348003733e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.594099748506093e-08</v>
+        <v>1.141496045286518e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.331109856630382e-08</v>
+        <v>2.057319053334215e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.344494792808917e-08</v>
+        <v>2.066565044044946e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.005523220270603e-08</v>
+        <v>1.780123731305642e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.687975190878933e-08</v>
+        <v>2.363266362209732e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>3.972584662044148e-08</v>
+        <v>2.661494963237098e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.728178918245862e-08</v>
+        <v>2.414406514291434e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.440604860941741e-08</v>
+        <v>2.242306443626938e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.039241273054084e-08</v>
+        <v>2.755902099534397e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.593261347507786e-08</v>
+        <v>4.301185131631144e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.703065604134867e-08</v>
+        <v>2.465548887039507e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.09819848521832e-08</v>
+        <v>2.755497596818145e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.208723915007333e-08</v>
+        <v>1.959740620139254e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.511231667341647e-08</v>
+        <v>3.210500533608941e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.099410617472015e-08</v>
+        <v>2.730221097848324e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.179711954306396e-08</v>
+        <v>3.961224868487959e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.027746533416283e-08</v>
+        <v>4.790086111296434e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.343620411167953e-08</v>
+        <v>5.10962150162375e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.872826363201649e-08</v>
+        <v>4.614461386918203e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.179454881832869e-08</v>
+        <v>2.97498876026346e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.252679030413355e-08</v>
+        <v>5.01853183711004e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.765248494285859e-08</v>
+        <v>5.530880906360528e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.193473937273026e-08</v>
+        <v>4.940172592396989e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.334841329061632e-08</v>
+        <v>5.096709548881085e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.150547865425463e-08</v>
+        <v>4.91278346054319e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.080006981484765e-08</v>
+        <v>4.842733971720655e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.209199997030538e-08</v>
+        <v>4.977478541927727e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>6.432714731622442e-08</v>
+        <v>1.141496045286518e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>6.331376922167764e-08</v>
+        <v>5.082266108435316e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>6.42942878893737e-08</v>
+        <v>5.171827590420739e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.055831757358716e-08</v>
+        <v>4.824587514225889e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.137138151503863e-08</v>
+        <v>4.87572755613152e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>6.421747622669239e-08</v>
+        <v>5.173956157158887e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.177341878870905e-08</v>
+        <v>4.926867708213221e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.148797158918707e-08</v>
+        <v>4.979391268598013e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.576523441157825e-08</v>
+        <v>6.312490416957565e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.042325571837266e-08</v>
+        <v>6.813558945294923e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>6.707327037047247e-08</v>
+        <v>5.469261847447431e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.071450512740476e-08</v>
+        <v>4.838895890339226e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.680828496051855e-08</v>
+        <v>4.447442593883505e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.960394627966361e-08</v>
+        <v>5.72296172753073e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.023764026470307e-08</v>
+        <v>4.778235652982938e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.93165345032297e-07</v>
+        <v>1.925485695005698e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.883999674308483e-07</v>
+        <v>3.874390035797492e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.94058668741586e-07</v>
+        <v>1.934176062620633e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.930967370288037e-07</v>
+        <v>1.924391463895074e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.934634136865639e-07</v>
+        <v>1.928179052831027e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.929405588239396e-07</v>
+        <v>1.923013066671215e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93891195851955e-07</v>
+        <v>1.932895357261792e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.94552250514149e-07</v>
+        <v>1.938341188091688e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.934372952475433e-07</v>
+        <v>1.927932006075032e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.957692023539053e-07</v>
+        <v>1.950988045021477e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.930861090174429e-07</v>
+        <v>1.924341699085685e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.930646413506495e-07</v>
+        <v>1.924368722549267e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.960490589259513e-07</v>
+        <v>1.953174520150269e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.03142864630331e-07</v>
+        <v>1.016766982274252e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.935068122882389e-07</v>
+        <v>1.927946241768656e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.938773575574996e-07</v>
+        <v>1.932505709122027e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.938236576660968e-07</v>
+        <v>1.930230438907845e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.936900710882862e-07</v>
+        <v>1.929824414518635e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.940184229328388e-07</v>
+        <v>1.932675586043945e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.345380924275065e-07</v>
+        <v>4.336732248687207e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.933217023742603e-07</v>
+        <v>1.927066733063338e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.07106871328123e-07</v>
+        <v>3.062666133962426e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.93853997321544e-07</v>
+        <v>1.931472613835278e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.935981150097222e-07</v>
+        <v>1.92982568054539e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.715758366508731e-07</v>
+        <v>1.706943211028291e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.935136550620626e-07</v>
+        <v>1.927526084565181e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.929595187086811e-07</v>
+        <v>1.924034321552729e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.982766589209966e-07</v>
+        <v>1.975837145785955e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.192355731638167e-07</v>
+        <v>5.180671361022309e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.046941780023088e-07</v>
+        <v>2.038260414491866e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.977989422195068e-07</v>
+        <v>1.968141121503988e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.004311255821006e-07</v>
+        <v>1.995313615247307e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.966808018083426e-07</v>
+        <v>1.958283356225133e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.03513832450812e-07</v>
+        <v>2.029275668326758e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.082279519803815e-07</v>
+        <v>2.068081038671034e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.002262091780546e-07</v>
+        <v>1.993383437613525e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.168066917585312e-07</v>
+        <v>2.157319074975373e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.97720548494035e-07</v>
+        <v>1.967767293817028e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.976576064789178e-07</v>
+        <v>1.968807645809488e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.189000175942428e-07</v>
+        <v>2.173855048181006e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>5.068929841281143e-08</v>
+        <v>4.85233779962726e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.007082075731929e-07</v>
+        <v>1.993363580258483e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.033729086176635e-07</v>
+        <v>2.026076731843538e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.03023500385392e-07</v>
+        <v>2.010109860114896e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.019954651073061e-07</v>
+        <v>2.006583312217624e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04405040298173e-07</v>
+        <v>2.027510367740984e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.976742655589393e-07</v>
+        <v>5.964422944068193e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.993855014146048e-07</v>
+        <v>1.987050520313799e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.005076126216816e-07</v>
+        <v>3.995114079774397e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.032203371252022e-07</v>
+        <v>2.018829886187439e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.013765002838369e-07</v>
+        <v>2.006915777390763e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.633292567249475e-07</v>
+        <v>1.621492264193269e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.007764733962968e-07</v>
+        <v>1.990529526116654e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.968880670524649e-07</v>
+        <v>1.96619082662675e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.054591666365977e-08</v>
+        <v>1.792692443957686e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.781730365432492e-08</v>
+        <v>1.539154419558338e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.063641890928799e-08</v>
+        <v>2.774309443730843e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.977095770296235e-08</v>
+        <v>1.669094006300969e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.391273923195962e-08</v>
+        <v>2.096919600386661e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.800685303349773e-08</v>
+        <v>1.513397698925499e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.874473557957176e-08</v>
+        <v>2.629647881914003e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.621165208922019e-08</v>
+        <v>3.244779526210146e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.37016890431208e-08</v>
+        <v>2.077447414808423e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.995768294477397e-08</v>
+        <v>4.673300194846096e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.965090942551525e-08</v>
+        <v>1.663472842150916e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.956141832999665e-08</v>
+        <v>1.680954266926039e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.311879166641535e-08</v>
+        <v>7.103138991320338e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>3.265094846220768e-08</v>
+        <v>1.98843901451491e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.440294640222193e-08</v>
+        <v>2.070622519908061e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.858842567776583e-08</v>
+        <v>2.58563533205758e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.79818607012024e-08</v>
+        <v>2.328633094605599e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.647293885197088e-08</v>
+        <v>2.282770772039838e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>4.018182398550123e-08</v>
+        <v>2.604823711860597e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.254064649606387e-08</v>
+        <v>1.96478595832922e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.287179271796866e-08</v>
+        <v>2.027467535130826e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.96402435327216e-08</v>
+        <v>4.71580345481766e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.832456106640864e-08</v>
+        <v>2.468942466946158e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.544874142977829e-08</v>
+        <v>2.283605071486874e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.197189037263454e-08</v>
+        <v>1.924937286092796e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.448023868039092e-08</v>
+        <v>2.023163830957108e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.832555456452347e-08</v>
+        <v>1.637431663253409e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.137399289359571e-07</v>
+        <v>9.663135425360804e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.110908687733896e-08</v>
+        <v>5.715170677477657e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.277902676895784e-07</v>
+        <v>3.044629528497315e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.057286711722579e-07</v>
+        <v>7.957701697499004e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.924911338858092e-07</v>
+        <v>1.682717250817663e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.043285721314106e-08</v>
+        <v>4.902160015537674e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.003185177667331e-07</v>
+        <v>2.857704311834078e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.393552088624617e-07</v>
+        <v>3.986421491914392e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.76703741432806e-07</v>
+        <v>1.537924581831906e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.399189711105163e-07</v>
+        <v>6.118393031673936e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.02045583241504e-07</v>
+        <v>7.747673948068946e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.043288469533073e-07</v>
+        <v>8.431521673912464e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.852318027854075e-07</v>
+        <v>7.103138991320338e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.473014766502681e-07</v>
+        <v>1.278332107413651e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.835982204487214e-07</v>
+        <v>1.472572403199394e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.739160711719177e-07</v>
+        <v>2.5420151154077e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.812732690889421e-07</v>
+        <v>2.207265068410055e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.112419633806111e-07</v>
+        <v>1.770878537097452e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>3.181373842050538e-07</v>
+        <v>2.701326006597793e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.546391688279803e-07</v>
+        <v>1.32386191216995e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.437516455731799e-07</v>
+        <v>1.270351017462407e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>6.739044842825063e-07</v>
+        <v>6.589376799850935e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.767974308312139e-07</v>
+        <v>2.391674846502815e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.123639104766667e-07</v>
+        <v>1.951024958812261e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.392660719471284e-07</v>
+        <v>1.203110674814963e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.958649179942307e-07</v>
+        <v>1.474396625705864e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.488366827538927e-08</v>
+        <v>8.066047423840372e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.863830063730933e-08</v>
+        <v>2.08032228218753e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0854945473134e-08</v>
+        <v>1.826784257788155e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.872880288293756e-08</v>
+        <v>3.061939281960655e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.786334167661191e-08</v>
+        <v>2.419011101251882e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.200512320560917e-08</v>
+        <v>2.384549438616463e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.104449485230679e-08</v>
+        <v>2.263314793876348e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.683711955322134e-08</v>
+        <v>2.91727772014381e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.924929390802928e-08</v>
+        <v>3.532409364439961e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.673933086192989e-08</v>
+        <v>2.365077253038228e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.299532476358304e-08</v>
+        <v>5.423217289796991e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.774329339916481e-08</v>
+        <v>2.413389937101751e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.765380230364619e-08</v>
+        <v>1.968584105155856e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.618072055934603e-08</v>
+        <v>7.103138991320338e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>3.571287735513838e-08</v>
+        <v>2.823196655820198e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.338203436163021e-08</v>
+        <v>2.904729651874407e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.668080965141537e-08</v>
+        <v>2.873265170287403e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.607424467485197e-08</v>
+        <v>3.078550189556441e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>4.456532282562042e-08</v>
+        <v>2.570400610269668e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.321946580431029e-08</v>
+        <v>2.892453550090412e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.061854168263773e-08</v>
+        <v>2.714011757378984e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.096417669161822e-08</v>
+        <v>2.31509737336065e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.3139954902276e-08</v>
+        <v>5.048778014250887e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>4.136220288521772e-08</v>
+        <v>3.218859561897042e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.874596364682019e-08</v>
+        <v>2.597478744371015e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.500953219144362e-08</v>
+        <v>2.674854381043701e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.257262265404049e-08</v>
+        <v>2.773080925907984e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.13524286239288e-08</v>
+        <v>1.925931932330252e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.434798187845201e-08</v>
+        <v>2.149606700497598e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.161936886911719e-08</v>
+        <v>1.896068676098238e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.443848412408027e-08</v>
+        <v>3.131223700270756e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.357302291775459e-08</v>
+        <v>2.026008262840875e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.771480444675185e-08</v>
+        <v>2.453833856926559e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.180891824828996e-08</v>
+        <v>1.870311955465412e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2546800794364e-08</v>
+        <v>2.986562138453908e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.001371730401245e-08</v>
+        <v>3.601693782750053e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.750375425791305e-08</v>
+        <v>2.434361671348329e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.375974815956615e-08</v>
+        <v>5.030214451386002e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.345297464030751e-08</v>
+        <v>2.020387098690821e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.336348354478889e-08</v>
+        <v>2.037868523465945e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.692085688120755e-08</v>
+        <v>7.103138991320338e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>3.645282147074216e-08</v>
+        <v>2.345332667974617e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.820481941075638e-08</v>
+        <v>2.427516173367766e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.239049089255808e-08</v>
+        <v>2.942549588597479e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.178392591599466e-08</v>
+        <v>2.685547351145498e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>4.027500406676312e-08</v>
+        <v>2.639685028579745e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.398388920029349e-08</v>
+        <v>2.961737968400496e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.62912080441666e-08</v>
+        <v>2.320479025318774e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.667385793276089e-08</v>
+        <v>2.384381791670731e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.344230874751384e-08</v>
+        <v>5.072717711357559e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.212662628120088e-08</v>
+        <v>2.82585672348606e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.923631785749479e-08</v>
+        <v>2.639828032125635e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.577395558742679e-08</v>
+        <v>2.281851542632696e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.82823038951832e-08</v>
+        <v>2.380078087497013e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.212761977931572e-08</v>
+        <v>1.9943459197933e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.900414495819082e-08</v>
+        <v>2.586574378114078e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.337898994789876e-08</v>
+        <v>2.98692878444213e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.619810520286183e-08</v>
+        <v>4.222083808614603e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.155026215626517e-08</v>
+        <v>2.768689940868771e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.347760325971441e-08</v>
+        <v>2.992670332785098e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.504148761578261e-08</v>
+        <v>3.096760918862423e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.430642187314555e-08</v>
+        <v>4.077422246797765e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>6.177333838279402e-08</v>
+        <v>4.69255389109394e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.926337533669462e-08</v>
+        <v>3.525221779692183e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.551936923834777e-08</v>
+        <v>6.121074559729872e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.521259571908909e-08</v>
+        <v>3.111247207034693e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.512310462356001e-08</v>
+        <v>3.128728631811925e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.317410962115229e-08</v>
+        <v>7.103138991320338e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>4.421946423357268e-08</v>
+        <v>3.068631283747201e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.560054082621769e-08</v>
+        <v>3.116670480576253e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.565066235415262e-08</v>
+        <v>3.251012479783784e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.354354699477621e-08</v>
+        <v>3.776407459489372e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.203462514554467e-08</v>
+        <v>3.730545136923618e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.574351027907501e-08</v>
+        <v>4.052598076744384e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.459220427808677e-08</v>
+        <v>3.092318170284426e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.646052170786254e-08</v>
+        <v>3.296087908935439e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.520332583248392e-08</v>
+        <v>6.163706326116204e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.603784376671767e-08</v>
+        <v>3.194250153912482e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.80099275960278e-08</v>
+        <v>4.380163304405808e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.029816829018072e-08</v>
+        <v>2.706672832815494e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.004192497396479e-08</v>
+        <v>3.470938195840879e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.130739669464083e-08</v>
+        <v>3.768251347617728e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.815403041112946e-08</v>
+        <v>5.50090283553509e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.657876721421068e-08</v>
+        <v>6.337945750244648e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.939788246917375e-08</v>
+        <v>7.573100774417152e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.595827697037314e-08</v>
+        <v>6.216184010296351e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.696268175067273e-08</v>
+        <v>4.381623699976151e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.676832094924387e-08</v>
+        <v>6.312189426979442e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.750619913945751e-08</v>
+        <v>7.428439212600293e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.497311564910593e-08</v>
+        <v>8.043570856896456e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.246315260300663e-08</v>
+        <v>6.876238745494713e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.087191465046597e-07</v>
+        <v>9.472091525532416e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.841237298540097e-08</v>
+        <v>6.46226417283722e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.832288188988238e-08</v>
+        <v>6.47974559761235e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.118802552263011e-07</v>
+        <v>7.103138991320338e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>8.510862334524762e-08</v>
+        <v>7.148647969482561e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.766448288441774e-08</v>
+        <v>7.309433520854228e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.734989359351192e-08</v>
+        <v>7.384427060111513e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.674332426108812e-08</v>
+        <v>7.127424425291915e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.523440241185662e-08</v>
+        <v>7.081562102726154e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.894328754538698e-08</v>
+        <v>7.403615042546901e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.12876212688739e-08</v>
+        <v>6.762885993114399e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.450398708859752e-08</v>
+        <v>8.084766279665012e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.084017070926073e-07</v>
+        <v>9.514594785503961e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>8.708602462629436e-08</v>
+        <v>7.267733797632472e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.419571620258833e-08</v>
+        <v>7.08170510627204e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.400887751985926e-08</v>
+        <v>6.066205446527605e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.32417022402767e-08</v>
+        <v>6.821955161643411e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.708701812440924e-08</v>
+        <v>6.436222993939706e-08</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.923238271371348e-07</v>
+        <v>1.914031731661056e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.879538225471037e-07</v>
+        <v>3.866094855063514e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.926730635818178e-07</v>
+        <v>1.917342583615848e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.925757883162949e-07</v>
+        <v>1.916324828784902e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.922977030869613e-07</v>
+        <v>1.913705170559155e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.926552898361008e-07</v>
+        <v>1.916742924003952e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93152994419293e-07</v>
+        <v>1.922318115789256e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.925367971451365e-07</v>
+        <v>1.915639215321421e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.927346722889971e-07</v>
+        <v>1.917820686677881e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.928890039243947e-07</v>
+        <v>1.918736682173332e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.924622313014748e-07</v>
+        <v>1.915164123602483e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.924345568339906e-07</v>
+        <v>1.915041244382291e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.93061625761761e-07</v>
+        <v>1.921250765529018e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.013069178831551e-07</v>
+        <v>9.929433433599352e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.929331394132277e-07</v>
+        <v>1.919357067822419e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.927713501037444e-07</v>
+        <v>1.918178743232619e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9262399877059e-07</v>
+        <v>1.916551109538884e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.928935782876514e-07</v>
+        <v>1.919259766721305e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92513206420387e-07</v>
+        <v>1.9150832581089e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.329731247563358e-07</v>
+        <v>4.314549636322188e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.927263199023991e-07</v>
+        <v>1.917945453927383e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0581504070431e-07</v>
+        <v>3.042148538077041e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.930539484271685e-07</v>
+        <v>1.921036545096477e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.926580127299916e-07</v>
+        <v>1.916983029470542e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.703556703566111e-07</v>
+        <v>1.689553006858138e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.927654200498075e-07</v>
+        <v>1.917776190974781e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.927125106523965e-07</v>
+        <v>1.917714520749582e-07</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.956877079512822e-07</v>
+        <v>1.948526070018769e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.194667391069758e-07</v>
+        <v>5.178985807329346e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.981885498840268e-07</v>
+        <v>1.972235330727296e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.974880024830798e-07</v>
+        <v>1.964911953446453e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.955074654630893e-07</v>
+        <v>1.946254382578552e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.980372173850491e-07</v>
+        <v>1.967746751539993e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.016475969982569e-07</v>
+        <v>2.008082752686063e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.972191342202909e-07</v>
+        <v>1.960098351997298e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.986140174453741e-07</v>
+        <v>1.975519993480854e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.997075454149355e-07</v>
+        <v>1.981998873980761e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9667308759768e-07</v>
+        <v>1.956593222078442e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.965506496702571e-07</v>
+        <v>1.95638679199515e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.009648026677137e-07</v>
+        <v>2.000158816880158e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.559478642444645e-08</v>
+        <v>4.289787179058362e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.000159245482242e-07</v>
+        <v>1.98635408619303e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.988720623107123e-07</v>
+        <v>1.978035496000494e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.978465147690618e-07</v>
+        <v>1.966653646442059e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.997270977318909e-07</v>
+        <v>1.985592130267098e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.970483798605965e-07</v>
+        <v>1.956105989745831e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.93298149518939e-07</v>
+        <v>5.915746490871457e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.985428189834318e-07</v>
+        <v>1.976289254198998e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.983651741749776e-07</v>
+        <v>3.963588949776906e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.009035411411729e-07</v>
+        <v>1.998566913793225e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.980756138387649e-07</v>
+        <v>1.969617106347858e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.608922373800614e-07</v>
+        <v>1.592030472095016e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.988436008159296e-07</v>
+        <v>1.975289648137752e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.984914120953752e-07</v>
+        <v>1.975053914123104e-07</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.582948143238649e-08</v>
+        <v>1.333277496436037e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.759351157087805e-08</v>
+        <v>1.502791984702443e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.977426773178653e-08</v>
+        <v>1.707253455401142e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.867549885887413e-08</v>
+        <v>1.592293365342357e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.553439826802451e-08</v>
+        <v>1.296390917720953e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.95735050975899e-08</v>
+        <v>1.639519143667115e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.519530732015328e-08</v>
+        <v>2.26926270296657e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.823507564381822e-08</v>
+        <v>1.514850170664249e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.055330940457944e-08</v>
+        <v>1.769601626310085e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.221341323865909e-08</v>
+        <v>1.864723300639324e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.739282013767744e-08</v>
+        <v>1.461186375480507e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.720369996550222e-08</v>
+        <v>1.458354099850347e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.41632563016759e-08</v>
+        <v>1.878970781769274e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.613548648377432e-08</v>
+        <v>1.351534708779791e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.271194388837723e-08</v>
+        <v>1.934798713618552e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.088445921098566e-08</v>
+        <v>1.801701530639696e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.922005811804549e-08</v>
+        <v>1.617852817447546e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.22650827759531e-08</v>
+        <v>1.923808106640713e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.796860755549509e-08</v>
+        <v>1.452052245980528e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.656249165554271e-08</v>
+        <v>1.410854684496589e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.092999893188398e-08</v>
+        <v>1.83092833939712e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.73930525099089e-08</v>
+        <v>4.479485083762302e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.407653727571545e-08</v>
+        <v>2.124503397700564e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.956509068611016e-08</v>
+        <v>1.646712051679093e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.887696372524476e-08</v>
+        <v>1.625086499353754e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.081747652380466e-08</v>
+        <v>1.756231401285032e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.023791058371236e-08</v>
+        <v>1.750279728936279e-08</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.110675013884551e-08</v>
+        <v>3.796820625723563e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.438410190716211e-08</v>
+        <v>6.996559347618126e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.251905162427212e-07</v>
+        <v>1.082342570934904e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.024978701756374e-07</v>
+        <v>8.481251452942556e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.91039028357825e-08</v>
+        <v>3.450149458262947e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.089533556834767e-07</v>
+        <v>8.543490185612423e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.385641544657046e-07</v>
+        <v>2.250887148731524e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>9.958665473357836e-08</v>
+        <v>7.524337911009924e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.302038872510161e-07</v>
+        <v>1.112575403972645e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.568358499368424e-07</v>
+        <v>1.264356577452355e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>7.750402458676242e-08</v>
+        <v>5.982477184514876e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.829938535702543e-08</v>
+        <v>6.296863306929083e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.230376059245665e-08</v>
+        <v>1.878970781769274e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>5.575126939755328e-08</v>
+        <v>4.0724543696042e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.622235498907816e-07</v>
+        <v>1.350719471007234e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.355170176551783e-07</v>
+        <v>1.162562278245025e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.196082506009535e-07</v>
+        <v>9.589985987436867e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.509634854024466e-07</v>
+        <v>1.296293805847621e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>9.363714894805407e-08</v>
+        <v>6.286854239615497e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.474216669689276e-08</v>
+        <v>5.485313192733462e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.230015889761267e-07</v>
+        <v>1.079410947243126e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>6.137979689833145e-07</v>
+        <v>5.987673669554037e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.995198001965953e-07</v>
+        <v>1.803525303709385e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.193244394398399e-07</v>
+        <v>9.835280654962788e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.815976525848707e-08</v>
+        <v>8.305247070496122e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.415157393173537e-07</v>
+        <v>1.148052640359594e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.393548899492565e-07</v>
+        <v>1.214898365474737e-07</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.853420556496523e-08</v>
+        <v>1.956869606385768e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.483326778766109e-08</v>
+        <v>2.126384094652177e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.247899186436496e-08</v>
+        <v>2.330845565350876e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.591525507565836e-08</v>
+        <v>1.826729212101493e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.277415448481105e-08</v>
+        <v>1.530826764480089e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.227822923016874e-08</v>
+        <v>1.873954990426252e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.243506353693667e-08</v>
+        <v>2.503698549725704e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.547483186060306e-08</v>
+        <v>2.138442280613982e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.325803353715822e-08</v>
+        <v>2.393193736259819e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.94531694554445e-08</v>
+        <v>2.099159147398458e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0097544270256e-08</v>
+        <v>2.084778485430239e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.444345618228627e-08</v>
+        <v>1.692789946609482e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.687377844206862e-08</v>
+        <v>1.878970781769274e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>2.884600862416756e-08</v>
+        <v>2.048640747410647e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.513735613044431e-08</v>
+        <v>2.144964456846701e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.812421542776934e-08</v>
+        <v>2.03613737739883e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.645981433482847e-08</v>
+        <v>2.24144492739728e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.496980690853138e-08</v>
+        <v>2.158243953399845e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.067333168807359e-08</v>
+        <v>1.686488092739663e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.930638653869041e-08</v>
+        <v>2.054374903425287e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.81697551486677e-08</v>
+        <v>2.065364186156255e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.050642808770318e-08</v>
+        <v>4.752766648056217e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.678126140829423e-08</v>
+        <v>2.748095507650296e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.252903759972049e-08</v>
+        <v>1.922011907556014e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.158168785782321e-08</v>
+        <v>2.248678609303487e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.805723274058775e-08</v>
+        <v>1.990667248044167e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.294927955972267e-08</v>
+        <v>1.987754699673126e-08</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.893254298245512e-08</v>
+        <v>1.619597307213375e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.069657312094672e-08</v>
+        <v>1.789111795479783e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.287732928185504e-08</v>
+        <v>1.993573266178481e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.177856040894284e-08</v>
+        <v>1.878613176119696e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.863745981809329e-08</v>
+        <v>1.582710728498292e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.267656664765884e-08</v>
+        <v>1.925838954444452e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.829836887022135e-08</v>
+        <v>2.555582513743909e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.13381371938872e-08</v>
+        <v>1.801169981441588e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.365637095464822e-08</v>
+        <v>2.055921437087426e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.531647478872783e-08</v>
+        <v>2.151043111416662e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.049588168774622e-08</v>
+        <v>1.747506186257846e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.030676151557174e-08</v>
+        <v>1.744673910627687e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.726631785174486e-08</v>
+        <v>1.878970781769274e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>2.923844025380826e-08</v>
+        <v>1.637841535532928e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.581489765841141e-08</v>
+        <v>2.221105540371688e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.398752076105457e-08</v>
+        <v>2.088021341417032e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.232311966811408e-08</v>
+        <v>1.904172628224885e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.536814432602185e-08</v>
+        <v>2.210127917418049e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>3.107166910556379e-08</v>
+        <v>1.738372056757867e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.957861195350779e-08</v>
+        <v>1.710735561567702e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>3.403306048195284e-08</v>
+        <v>2.117248150174458e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.049611405997703e-08</v>
+        <v>4.765804894539637e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.717959882578378e-08</v>
+        <v>2.410823208477903e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.270732298674842e-08</v>
+        <v>1.952959971435394e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.198002527531347e-08</v>
+        <v>1.911406310131092e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.392053807387355e-08</v>
+        <v>2.042551212062371e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.334097213378124e-08</v>
+        <v>2.036599539713618e-08</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.29043602807973e-08</v>
+        <v>1.974070716511896e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.06561940236326e-08</v>
+        <v>2.663651136051987e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.283695018454093e-08</v>
+        <v>2.868112606750686e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.854985252633337e-08</v>
+        <v>2.476232749580726e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.354210693427734e-08</v>
+        <v>2.018204331564723e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.38777976327033e-08</v>
+        <v>2.908217353660489e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.825798977290729e-08</v>
+        <v>3.430121854316112e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.129775809657279e-08</v>
+        <v>2.675709322013793e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.361599185733334e-08</v>
+        <v>2.930460777659628e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.527609569141348e-08</v>
+        <v>3.025582451988866e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.045550259043146e-08</v>
+        <v>2.622045526830049e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.026638241824223e-08</v>
+        <v>2.619213251202697e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.258438921713288e-08</v>
+        <v>1.878970781769274e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.583215750145631e-08</v>
+        <v>2.220041607941731e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.209594969719414e-08</v>
+        <v>2.77614932404447e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.678259799275169e-08</v>
+        <v>2.340289925703192e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.228274057079998e-08</v>
+        <v>2.778711968797088e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.532776522870698e-08</v>
+        <v>3.084667257990256e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.103129000824982e-08</v>
+        <v>2.612911397330072e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.664412764414224e-08</v>
+        <v>2.33288046460166e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.224841907017609e-08</v>
+        <v>2.844214337130493e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.045691171346017e-08</v>
+        <v>5.640446441412275e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>4.052347014091892e-08</v>
+        <v>2.710756867798457e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.845342966929652e-08</v>
+        <v>3.33616508853179e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.58406160496943e-08</v>
+        <v>2.25621922788059e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.388015897655884e-08</v>
+        <v>2.917090552634574e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.955535457056122e-08</v>
+        <v>3.454391231275371e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.683888818923975e-08</v>
+        <v>4.38369795041e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.782834312569289e-08</v>
+        <v>5.44596735315976e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.000909928660021e-08</v>
+        <v>5.650428823858459e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.678114247750701e-08</v>
+        <v>5.329424753713395e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.450210360235853e-08</v>
+        <v>3.181522191435174e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.980833987309109e-08</v>
+        <v>5.582694788638215e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.543013887496565e-08</v>
+        <v>6.212438071423889e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.846990719863114e-08</v>
+        <v>5.458025539121568e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.078814095939517e-08</v>
+        <v>5.7127769947674e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.244824479347271e-08</v>
+        <v>5.80789866909664e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.762765169249195e-08</v>
+        <v>5.404361743937824e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.743853152031633e-08</v>
+        <v>5.401529468307664e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.439808785648859e-08</v>
+        <v>1.878970781769274e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>6.942761602498491e-08</v>
+        <v>5.590568255083995e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.666898258678702e-08</v>
+        <v>6.238176277396076e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.111929398648466e-08</v>
+        <v>5.744877175610789e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.945488967285905e-08</v>
+        <v>5.561028185904863e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.249991433076782e-08</v>
+        <v>5.866983475098029e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.820343911031018e-08</v>
+        <v>5.395227614437846e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.683649396092682e-08</v>
+        <v>5.373958161932871e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.181077623436029e-08</v>
+        <v>6.804324027651779e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.76278840647218e-08</v>
+        <v>8.422660452219611e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.431136883052996e-08</v>
+        <v>6.067678766157879e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.983909299149432e-08</v>
+        <v>5.609815529115374e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.354968576256906e-08</v>
+        <v>5.030010151042578e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.10523080786205e-08</v>
+        <v>5.699406769742351e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.047274213852744e-08</v>
+        <v>5.693455097393591e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
@@ -798,7 +798,7 @@
         <v>2.001267405836006e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.088692553765024e-06</v>
+        <v>6.669525758271998e-08</v>
       </c>
       <c r="O4" t="n">
         <v>2.57607363428168e-08</v>
@@ -974,7 +974,7 @@
         <v>2.896211538648442e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.088692553765024e-06</v>
+        <v>7.012384401055483e-08</v>
       </c>
       <c r="O6" t="n">
         <v>2.918919126713418e-08</v>
@@ -1062,7 +1062,7 @@
         <v>2.451007246464725e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.088692553765024e-06</v>
+        <v>7.119265598900689e-08</v>
       </c>
       <c r="O7" t="n">
         <v>3.025785193444021e-08</v>
@@ -1150,7 +1150,7 @@
         <v>3.798096507794425e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.088692553765024e-06</v>
+        <v>7.8361436480964e-08</v>
       </c>
       <c r="O8" t="n">
         <v>3.915879035820992e-08</v>
@@ -1238,7 +1238,7 @@
         <v>8.079941676258104e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.088692553765024e-06</v>
+        <v>1.274820002869407e-07</v>
       </c>
       <c r="O9" t="n">
         <v>9.112395531544326e-08</v>
@@ -1658,7 +1658,7 @@
         <v>1.455295298675494e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.40353330544085e-07</v>
+        <v>1.848278918398809e-08</v>
       </c>
       <c r="O4" t="n">
         <v>1.305261395021328e-08</v>
@@ -1834,7 +1834,7 @@
         <v>1.673259773741957e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.40353330544085e-07</v>
+        <v>2.066311462067745e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.964117073328505e-08</v>
@@ -1922,7 +1922,7 @@
         <v>1.727748461708869e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.40353330544085e-07</v>
+        <v>2.120732081432182e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.577704668439312e-08</v>
@@ -2010,7 +2010,7 @@
         <v>2.549384927090976e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.40353330544085e-07</v>
+        <v>2.564895757920877e-08</v>
       </c>
       <c r="O8" t="n">
         <v>2.12561103379391e-08</v>
@@ -2098,7 +2098,7 @@
         <v>5.037960055716538e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.40353330544085e-07</v>
+        <v>5.430943675439852e-08</v>
       </c>
       <c r="O9" t="n">
         <v>5.156577028204817e-08</v>
@@ -2518,7 +2518,7 @@
         <v>1.701885009893355e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.471981858621278e-07</v>
+        <v>4.626106961150509e-08</v>
       </c>
       <c r="O4" t="n">
         <v>2.01552765996316e-08</v>
@@ -2694,7 +2694,7 @@
         <v>2.482322479157261e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.471981858621278e-07</v>
+        <v>4.930098375375795e-08</v>
       </c>
       <c r="O6" t="n">
         <v>2.322669380198207e-08</v>
@@ -2782,7 +2782,7 @@
         <v>2.080706902770618e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.471981858621278e-07</v>
+        <v>5.004928854027773e-08</v>
       </c>
       <c r="O7" t="n">
         <v>2.394324050212681e-08</v>
@@ -2870,7 +2870,7 @@
         <v>3.222373055015938e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>6.471981858621278e-07</v>
+        <v>5.614304379503869e-08</v>
       </c>
       <c r="O8" t="n">
         <v>3.150003163175226e-08</v>
@@ -2958,7 +2958,7 @@
         <v>6.541728019426819e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>6.471981858621278e-07</v>
+        <v>9.465949970683971e-08</v>
       </c>
       <c r="O9" t="n">
         <v>7.220573582351972e-08</v>
@@ -3166,46 +3166,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.917026174681164e-07</v>
+        <v>1.917026174681165e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.880253654678995e-07</v>
+        <v>3.880253654678997e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.924669240404151e-07</v>
+        <v>1.924669240404152e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.923684831300555e-07</v>
+        <v>1.923684831300556e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.919212379580074e-07</v>
+        <v>1.919212379580075e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.91761950335334e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.924489927757834e-07</v>
+        <v>1.924489927757835e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.920165552148338e-07</v>
+        <v>1.920165552148339e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.921305019550926e-07</v>
+        <v>1.921305019550927e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.918138089780575e-07</v>
+        <v>1.918138089780576e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.916462630189776e-07</v>
+        <v>1.916462630189777e-07</v>
       </c>
       <c r="M2" t="n">
         <v>1.918609574633404e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.932068373041279e-07</v>
+        <v>1.93206837304128e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.001652852871011e-07</v>
+        <v>1.00165285287101e-07</v>
       </c>
       <c r="P2" t="n">
         <v>1.921236721353695e-07</v>
@@ -3214,37 +3214,37 @@
         <v>1.92258262759668e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.92230530671781e-07</v>
+        <v>1.922305306717811e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.921091028702131e-07</v>
+        <v>1.921091028702132e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.919083543286905e-07</v>
+        <v>1.919083543286904e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.326076249591105e-07</v>
+        <v>4.326076249591104e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.920914675453777e-07</v>
+        <v>1.920914675453778e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.058355978286847e-07</v>
+        <v>3.058355978286846e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.922327820684067e-07</v>
+        <v>1.922327820684068e-07</v>
       </c>
       <c r="Y2" t="n">
         <v>1.921698456719161e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.697191647229168e-07</v>
+        <v>1.697191647229169e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.920174275105572e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.918168961988408e-07</v>
+        <v>1.918168961988407e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3254,25 +3254,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.950851321122885e-07</v>
+        <v>1.950851321122884e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.253422895686061e-07</v>
+        <v>5.253422895686063e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.005590265181215e-07</v>
+        <v>2.005590265181212e-07</v>
       </c>
       <c r="E3" t="n">
         <v>1.998391989286724e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.966553852528992e-07</v>
+        <v>1.966553852528989e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.955075912796632e-07</v>
+        <v>1.955075912796633e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.004505965886481e-07</v>
+        <v>2.00450596588648e-07</v>
       </c>
       <c r="I3" t="n">
         <v>1.973397739662496e-07</v>
@@ -3281,55 +3281,55 @@
         <v>1.981398551867873e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.958812290987464e-07</v>
+        <v>1.958812290987462e-07</v>
       </c>
       <c r="L3" t="n">
         <v>1.946854003892505e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.962941113697649e-07</v>
+        <v>1.962941113697647e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.058398007320942e-07</v>
+        <v>2.05839800732094e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.48560203350848e-08</v>
+        <v>4.485602033508471e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98078142311287e-07</v>
+        <v>1.980781423112871e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.990557481790725e-07</v>
+        <v>1.990557481790724e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.988769051600189e-07</v>
+        <v>1.988769051600188e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.979772832038237e-07</v>
+        <v>1.979772832038234e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.965638080607934e-07</v>
+        <v>1.965638080607933e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.951326549674431e-07</v>
+        <v>5.951326549674432e-07</v>
       </c>
       <c r="V3" t="n">
         <v>1.978443203992381e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.02800594934771e-07</v>
+        <v>4.028005949347705e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.988801667218091e-07</v>
+        <v>1.988801667218089e-07</v>
       </c>
       <c r="Y3" t="n">
         <v>1.984226176272983e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.60708695014882e-07</v>
+        <v>1.607086950148821e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.973358316470882e-07</v>
+        <v>1.973358316470883e-07</v>
       </c>
       <c r="AB3" t="n">
         <v>1.959530076852537e-07</v>
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.364723045333715e-08</v>
+        <v>1.36472304533367e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.642197627059918e-08</v>
+        <v>2.642197627059857e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.228042478584354e-08</v>
+        <v>2.228042478584301e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.11684894182775e-08</v>
+        <v>2.116848941827695e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.61166494570498e-08</v>
+        <v>1.611664945704941e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.431742248302555e-08</v>
+        <v>1.431742248302499e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.207788290304069e-08</v>
+        <v>2.207788290304019e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.719330172100773e-08</v>
+        <v>1.719330172100714e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.856430380598005e-08</v>
+        <v>1.856430380597977e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.490318970874261e-08</v>
+        <v>1.490318970874214e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.301068102598705e-08</v>
+        <v>1.301068102598649e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.556017180292423e-08</v>
+        <v>1.556017180292362e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.486358679411037e-07</v>
+        <v>3.063808547639732e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.545351145330426e-08</v>
+        <v>1.54535114533037e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.840323661467546e-08</v>
+        <v>1.840323661467511e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.992349963087395e-08</v>
+        <v>1.992349963087358e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.96102529408004e-08</v>
+        <v>1.961025294079989e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.823867006254093e-08</v>
+        <v>1.823867006254041e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.597112293715093e-08</v>
+        <v>1.597112293715054e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.845177198374528e-08</v>
+        <v>1.845177198374488e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.859857868420318e-08</v>
+        <v>1.859857868420311e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.33991907782551e-08</v>
+        <v>5.339919077825473e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.963568350138156e-08</v>
+        <v>1.963568350138113e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.879968782725015e-08</v>
+        <v>1.879968782724981e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.761416730192499e-08</v>
+        <v>1.76141673019244e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.720315470247998e-08</v>
+        <v>1.720315470247938e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.50084118236931e-08</v>
+        <v>1.500841182369274e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.829038523257481e-08</v>
+        <v>3.829038523257432e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.622294016600645e-07</v>
+        <v>2.622294016600641e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.008290957770622e-07</v>
+        <v>2.008290957770615e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.722233576343643e-07</v>
+        <v>1.722233576343637e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>8.71213335298379e-08</v>
+        <v>8.712133352983729e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.962433569405883e-08</v>
+        <v>4.962433569405892e-08</v>
       </c>
       <c r="H5" t="n">
         <v>2.073762352607783e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.082908620780465e-07</v>
+        <v>1.08290862078046e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.243178799055079e-07</v>
+        <v>1.243178799055077e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.18087987298965e-08</v>
+        <v>6.180879872989584e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.831341894131028e-08</v>
+        <v>2.831341894130943e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.797978701034108e-08</v>
+        <v>7.79797870103401e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.486358679411037e-07</v>
+        <v>3.48635867941103e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>6.644205300680939e-08</v>
+        <v>6.644205300680902e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.161491096573995e-07</v>
+        <v>1.161491096573993e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.518606970552733e-07</v>
+        <v>1.518606970552726e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.562093181005575e-07</v>
+        <v>1.562093181005571e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.148566166641675e-07</v>
+        <v>1.148566166641666e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>8.474122762657906e-08</v>
+        <v>8.474122762657863e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.231977867059924e-07</v>
+        <v>1.231977867059936e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08213883544381e-07</v>
+        <v>1.082138835443811e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>7.465452665060204e-07</v>
+        <v>7.465452665060183e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.500223162212606e-07</v>
+        <v>1.5002231622126e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.331119872921083e-07</v>
+        <v>1.331119872921079e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.004083783289732e-07</v>
+        <v>1.004083783289725e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.031958523205412e-07</v>
+        <v>1.031958523205406e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.964085241441578e-08</v>
+        <v>6.964085241441559e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.02627068775165e-08</v>
+        <v>2.026270687751613e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.907852239841083e-08</v>
+        <v>2.907852239841056e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.889590121002276e-08</v>
+        <v>2.889590121002225e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.778396584245686e-08</v>
+        <v>2.778396584245642e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.877319558486183e-08</v>
+        <v>1.877319558486142e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.69739686108374e-08</v>
+        <v>1.697396861083708e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.473442903085261e-08</v>
+        <v>2.473442903085223e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.984984784881964e-08</v>
+        <v>1.984984784881925e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.517978023015977e-08</v>
+        <v>2.517978023015907e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.151866613292199e-08</v>
+        <v>2.151866613292138e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.962615745016633e-08</v>
+        <v>1.962615745016585e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.821671793073614e-08</v>
+        <v>1.821671793073573e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.486358679411037e-07</v>
+        <v>3.32561959810361e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.276585455555915e-08</v>
+        <v>2.276585455555849e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.570367069103495e-08</v>
+        <v>2.570367069103419e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.653897605505339e-08</v>
+        <v>2.653897605505287e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.226679906861232e-08</v>
+        <v>2.22667990686119e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.485414648672026e-08</v>
+        <v>2.485414648671975e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.862766906496309e-08</v>
+        <v>1.862766906496267e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.123341823515315e-08</v>
+        <v>2.123341823515281e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.521405510838272e-08</v>
+        <v>2.521405510838242e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.071551135200916e-08</v>
+        <v>6.071551135200863e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.229222962919356e-08</v>
+        <v>2.229222962919322e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.178540435732105e-08</v>
+        <v>2.178540435732089e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.42296437261043e-08</v>
+        <v>2.422964372610383e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.381863112665932e-08</v>
+        <v>2.381863112665878e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.764906867659965e-08</v>
+        <v>1.764906867659916e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.670890663734717e-08</v>
+        <v>1.670890663734652e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.948365245460882e-08</v>
+        <v>2.948365245460837e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.534210096985367e-08</v>
+        <v>2.534210096985287e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.423016560228744e-08</v>
+        <v>2.42301656022868e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.917832564105986e-08</v>
+        <v>1.917832564105924e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.737909866703557e-08</v>
+        <v>1.737909866703485e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.513955908705062e-08</v>
+        <v>2.513955908705005e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.025497790501769e-08</v>
+        <v>2.025497790501702e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.162597998999039e-08</v>
+        <v>2.162597998998958e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.796486589275256e-08</v>
+        <v>1.796486589275204e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.607235720999702e-08</v>
+        <v>1.607235720999635e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.862184798693416e-08</v>
+        <v>1.86218479869335e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.486358679411037e-07</v>
+        <v>3.369976166040704e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.851504376429554e-08</v>
+        <v>1.8515043764295e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.146476892566692e-08</v>
+        <v>2.146476892566636e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.298517581488402e-08</v>
+        <v>2.298517581488333e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.267192912481032e-08</v>
+        <v>2.267192912480971e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.130034624655089e-08</v>
+        <v>2.130034624655026e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.903279912116083e-08</v>
+        <v>1.903279912116039e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.159509110138298e-08</v>
+        <v>2.159509110138247e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.166025486821326e-08</v>
+        <v>2.166025486821294e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.646086696226515e-08</v>
+        <v>5.646086696226454e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.269735968539163e-08</v>
+        <v>2.269735968539085e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.198646413485601e-08</v>
+        <v>2.198646413485539e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.067584348593493e-08</v>
+        <v>2.067584348593422e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.026483088648992e-08</v>
+        <v>2.026483088648924e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.807008800770314e-08</v>
+        <v>1.807008800770246e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.045696078104959e-08</v>
+        <v>2.045696078104937e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.877111673008642e-08</v>
+        <v>3.877111673008605e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.462956524533085e-08</v>
+        <v>3.462956524533048e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.056805738836314e-08</v>
+        <v>3.056805738836288e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.378935514080493e-08</v>
+        <v>2.378935514080446e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.781519571791757e-08</v>
+        <v>2.781519571791696e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.442702336252791e-08</v>
+        <v>3.442702336252763e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9542442180495e-08</v>
+        <v>2.954244218049471e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.091344426546762e-08</v>
+        <v>3.091344426546731e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.725233016822988e-08</v>
+        <v>2.72523301682297e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.535982148547434e-08</v>
+        <v>2.535982148547409e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.790931226245323e-08</v>
+        <v>2.790931226245285e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.486358679411037e-07</v>
+        <v>3.869325635616518e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.468870244864827e-08</v>
+        <v>2.468870244864772e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.734917616731308e-08</v>
+        <v>2.73491761673124e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.564460944134414e-08</v>
+        <v>2.564460944134343e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.195939340028759e-08</v>
+        <v>3.195939340028734e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>3.058781052202817e-08</v>
+        <v>3.05878105220279e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.832026339663869e-08</v>
+        <v>2.832026339663813e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8188733647588e-08</v>
+        <v>2.818873364758735e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.93966916693661e-08</v>
+        <v>2.939669166936599e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.574941987343694e-08</v>
+        <v>6.574941987343638e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.586449124691408e-08</v>
+        <v>2.586449124691345e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.67242148589207e-08</v>
+        <v>3.672421485892001e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.432100024392357e-08</v>
+        <v>2.432100024392352e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.955229516196722e-08</v>
+        <v>2.955229516196702e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.314392934796156e-08</v>
+        <v>3.31439293479609e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.417848974197648e-08</v>
+        <v>4.417848974197612e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.592459002780297e-08</v>
+        <v>6.592459002780264e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.178303854304772e-08</v>
+        <v>6.178303854304706e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.860055327800962e-08</v>
+        <v>5.860055327800939e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.493783905116448e-08</v>
+        <v>3.493783905116439e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.382003899682538e-08</v>
+        <v>5.382003899682509e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.158049666024461e-08</v>
+        <v>6.158049666024421e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.669591547821163e-08</v>
+        <v>5.669591547821138e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.806691756318403e-08</v>
+        <v>5.806691756318386e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.440580346594653e-08</v>
+        <v>5.440580346594621e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.251329478319096e-08</v>
+        <v>5.251329478319065e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>5.506278556012813e-08</v>
+        <v>5.506278556012777e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.486358679411037e-07</v>
+        <v>7.014069923360135e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>5.792922400453069e-08</v>
+        <v>5.792922400453055e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>6.152554654430618e-08</v>
+        <v>6.152554654430567e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.942611614467379e-08</v>
+        <v>5.942611614467359e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>5.911286669800425e-08</v>
+        <v>5.91128666980039e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>5.774128381974484e-08</v>
+        <v>5.774128381974457e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>5.547373669435511e-08</v>
+        <v>5.547373669435467e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>5.807948586454515e-08</v>
+        <v>5.807948586454496e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.845394520161971e-08</v>
+        <v>6.845394520161938e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.29018045354591e-08</v>
+        <v>9.290180453545876e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>5.913829725858552e-08</v>
+        <v>5.913829725858519e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.842740170804999e-08</v>
+        <v>5.842740170804973e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.170785317316353e-08</v>
+        <v>5.170785317316331e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.670576845968385e-08</v>
+        <v>5.670576845968357e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.451102558089713e-08</v>
+        <v>5.45110255808968e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4029,7 +4029,7 @@
         <v>1.913094313816484e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.876761274767929e-07</v>
+        <v>3.876761274767927e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.914242163806325e-07</v>
@@ -4038,25 +4038,25 @@
         <v>1.916200117395173e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.915815909148843e-07</v>
+        <v>1.915815909148844e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.91374261037114e-07</v>
+        <v>1.913742610371139e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.919403978972842e-07</v>
+        <v>1.919403978972843e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.91373290853518e-07</v>
+        <v>1.913732908535179e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.916572626889626e-07</v>
+        <v>1.916572626889625e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.912986136408562e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.913452094182789e-07</v>
+        <v>1.91345209418279e-07</v>
       </c>
       <c r="M2" t="n">
         <v>1.914226162874084e-07</v>
@@ -4065,22 +4065,22 @@
         <v>1.923425915917717e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.911293194305184e-08</v>
+        <v>9.91129319430518e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.916597651944829e-07</v>
+        <v>1.91659765194483e-07</v>
       </c>
       <c r="Q2" t="n">
         <v>1.917611109938484e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.91727955117377e-07</v>
+        <v>1.917279551173769e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.916423715300254e-07</v>
+        <v>1.916423715300256e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.914842377197971e-07</v>
+        <v>1.91484237719797e-07</v>
       </c>
       <c r="U2" t="n">
         <v>4.317439663636271e-07</v>
@@ -4089,19 +4089,19 @@
         <v>1.917137749725428e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.043186507286319e-07</v>
+        <v>3.04318650728632e-07</v>
       </c>
       <c r="X2" t="n">
         <v>1.916317377945245e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.915454552117531e-07</v>
+        <v>1.91545455211753e-07</v>
       </c>
       <c r="Z2" t="n">
         <v>1.685396850957725e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.916804138249574e-07</v>
+        <v>1.916804138249575e-07</v>
       </c>
       <c r="AB2" t="n">
         <v>1.913378556434556e-07</v>
@@ -4117,28 +4117,28 @@
         <v>1.951099085500714e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.258738634496657e-07</v>
+        <v>5.258738634496659e-07</v>
       </c>
       <c r="D3" t="n">
         <v>1.959368012019217e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.973216437473883e-07</v>
+        <v>1.973216437473881e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.970644992002959e-07</v>
+        <v>1.970644992002961e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.955708376494607e-07</v>
+        <v>1.955708376494608e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.996520225952718e-07</v>
+        <v>1.996520225952717e-07</v>
       </c>
       <c r="I3" t="n">
         <v>1.955758979875637e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.975938089996795e-07</v>
+        <v>1.975938089996793e-07</v>
       </c>
       <c r="K3" t="n">
         <v>1.950388272792135e-07</v>
@@ -4147,13 +4147,13 @@
         <v>1.953681027316148e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.959834498249452e-07</v>
+        <v>1.959834498249451e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.025018619940535e-07</v>
+        <v>2.025018619940534e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.306156185636351e-08</v>
+        <v>4.306156185636354e-08</v>
       </c>
       <c r="P3" t="n">
         <v>1.975957692815928e-07</v>
@@ -4162,31 +4162,31 @@
         <v>1.983348702159217e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.981210525223391e-07</v>
+        <v>1.98121052522339e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.974776615866213e-07</v>
+        <v>1.974776615866215e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.963703812584195e-07</v>
+        <v>1.963703812584196e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.955212835965031e-07</v>
+        <v>5.955212835965032e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.979770968291653e-07</v>
+        <v>1.979770968291655e-07</v>
       </c>
       <c r="W3" t="n">
         <v>3.990498081954571e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.974164464469061e-07</v>
+        <v>1.974164464469063e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.968017744837351e-07</v>
+        <v>1.968017744837352e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.584590393947092e-07</v>
+        <v>1.584590393947091e-07</v>
       </c>
       <c r="AA3" t="n">
         <v>1.977647871320209e-07</v>
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.354556144534639e-08</v>
+        <v>1.354556144534682e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.722411736272649e-08</v>
+        <v>2.722411736272675e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.48421108125798e-08</v>
+        <v>1.484211081258005e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.705370946149841e-08</v>
+        <v>1.705370946149877e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.661972857281751e-08</v>
+        <v>1.661972857281848e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42778422269451e-08</v>
+        <v>1.427784222694561e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.067261849839033e-08</v>
+        <v>2.067261849839039e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.426688355692117e-08</v>
+        <v>1.426688355692152e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.755836169328406e-08</v>
+        <v>1.755836169328429e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.342337008669117e-08</v>
+        <v>1.342337008669142e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.394969082779809e-08</v>
+        <v>1.394969082779848e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.492614468607387e-08</v>
+        <v>1.492614468607414e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.619559071498782e-07</v>
+        <v>2.521558129586585e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.383468799023095e-08</v>
+        <v>1.383468799023118e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.750274302282787e-08</v>
+        <v>1.750274302282836e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86474904480321e-08</v>
+        <v>1.864749044803219e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.827297957083044e-08</v>
+        <v>1.827297957083041e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.730627358130047e-08</v>
+        <v>1.730627358130086e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.552007944962407e-08</v>
+        <v>1.552007944962449e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.037179094264809e-08</v>
+        <v>2.037179094264876e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.86718670259333e-08</v>
+        <v>1.867186702593335e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.933580197032979e-08</v>
+        <v>4.933580197032988e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.718616064705705e-08</v>
+        <v>1.71861606470572e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.573721899002272e-08</v>
+        <v>1.573721899002309e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.549639060613268e-08</v>
+        <v>1.549639060613286e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.77359788028774e-08</v>
+        <v>1.773597880287763e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.392218202556705e-08</v>
+        <v>1.392218202556745e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.610121648456422e-08</v>
+        <v>4.610121648456437e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.84513910106868e-07</v>
+        <v>2.845139101068688e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>7.300574496402433e-08</v>
+        <v>7.300574496402344e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.056132925479869e-07</v>
+        <v>1.05613292547987e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.067820580569233e-07</v>
+        <v>1.067820580569231e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>5.813898159174613e-08</v>
+        <v>5.813898159174504e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.923007416228702e-07</v>
+        <v>1.923007416228703e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>6.415586806021733e-08</v>
+        <v>6.415586806021722e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.164056913967183e-07</v>
+        <v>1.164056913967182e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.711443788739935e-08</v>
+        <v>4.711443788739931e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.472302774929416e-08</v>
+        <v>5.472302774929405e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.583496477380423e-08</v>
+        <v>7.583496477380449e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.619559071498782e-07</v>
+        <v>2.61955907149879e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>5.039669127311222e-08</v>
+        <v>5.039669127311126e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.085818646042619e-07</v>
+        <v>1.085818646042603e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.370118520718837e-07</v>
+        <v>1.370118520718842e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.422125747275377e-07</v>
+        <v>1.422125747275374e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.08232782814206e-07</v>
+        <v>1.082327828142058e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>8.769397759291303e-08</v>
+        <v>8.769397759291327e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.671395327926846e-07</v>
+        <v>1.671395327926855e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.177839656116705e-07</v>
+        <v>1.177839656116716e-07</v>
       </c>
       <c r="W5" t="n">
         <v>6.861905942926527e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.137150760993179e-07</v>
+        <v>1.137150760993168e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.706382120039998e-08</v>
+        <v>9.706382120039871e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.398187105305882e-08</v>
+        <v>7.398187105305902e-08</v>
       </c>
       <c r="AA5" t="n">
         <v>1.23925316463998e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.977827051888936e-08</v>
+        <v>5.977827051889014e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.604369060893163e-08</v>
+        <v>1.604369060893107e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.972224652631134e-08</v>
+        <v>2.972224652631129e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.104189091044735e-08</v>
+        <v>2.104189091044759e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.325348955936598e-08</v>
+        <v>2.325348955936699e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.911785773640238e-08</v>
+        <v>1.911785773640218e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.67759713905302e-08</v>
+        <v>1.677597139052997e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.687239859625766e-08</v>
+        <v>2.687239859625862e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.676501272050581e-08</v>
+        <v>1.676501272050598e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.375814179115179e-08</v>
+        <v>2.37581417911521e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.962315018455875e-08</v>
+        <v>1.962315018455966e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.644781999138345e-08</v>
+        <v>1.644781999138287e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.742427384965859e-08</v>
+        <v>1.742427384965867e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.619559071498782e-07</v>
+        <v>2.770962047432293e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.635505863052908e-08</v>
+        <v>1.635505863052925e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.440123117365548e-08</v>
+        <v>2.440123117365619e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.484727054589941e-08</v>
+        <v>2.484727054590032e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.44727596686979e-08</v>
+        <v>2.447275966869888e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.980440274488488e-08</v>
+        <v>1.980440274488481e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.171985954749206e-08</v>
+        <v>2.171985954749216e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.704591123319797e-08</v>
+        <v>2.704591123319883e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.116999618951829e-08</v>
+        <v>2.116999618951742e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.224743170077295e-08</v>
+        <v>5.224743170077342e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.968428981064146e-08</v>
+        <v>1.968428981064155e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.892635426756052e-08</v>
+        <v>1.892635426756122e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.799451976971745e-08</v>
+        <v>1.799451976971738e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.393575890074478e-08</v>
+        <v>2.393575890074476e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.642698717962802e-08</v>
+        <v>1.642698717962874e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.636726888458649e-08</v>
+        <v>1.636726888458658e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.004582480196649e-08</v>
+        <v>3.004582480196679e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.766381825181979e-08</v>
+        <v>1.76638182518201e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.987541690073853e-08</v>
+        <v>1.98754169007388e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.944143601205752e-08</v>
+        <v>1.944143601205825e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.709954966618523e-08</v>
+        <v>1.709954966618568e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.349432593763034e-08</v>
+        <v>2.349432593763042e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.708859099616108e-08</v>
+        <v>1.708859099616157e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.038006913252413e-08</v>
+        <v>2.038006913252432e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.624507752593128e-08</v>
+        <v>1.624507752593148e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.67713982670381e-08</v>
+        <v>1.677139826703853e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.774785212531387e-08</v>
+        <v>1.774785212531416e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.619559071498782e-07</v>
+        <v>2.803728873510612e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.665632558794514e-08</v>
+        <v>1.665632558794552e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.032438062054187e-08</v>
+        <v>2.032438062054177e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.146919788727219e-08</v>
+        <v>2.146919788727253e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.109468701007046e-08</v>
+        <v>2.109468701007044e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.012798102054058e-08</v>
+        <v>2.012798102054088e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.834178688886421e-08</v>
+        <v>1.834178688886456e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.352015538342296e-08</v>
+        <v>2.35201553834233e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.149357446517342e-08</v>
+        <v>2.149357446517339e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.215750940956993e-08</v>
+        <v>5.215750940957018e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.000786808629697e-08</v>
+        <v>2.000786808629699e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.903326662194514e-08</v>
+        <v>1.903326662194554e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.831809804537278e-08</v>
+        <v>1.831809804537293e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.055768624211753e-08</v>
+        <v>2.055768624211765e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.674388946480725e-08</v>
+        <v>1.674388946480799e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.992210312872163e-08</v>
+        <v>1.992210312872188e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.873967591452179e-08</v>
+        <v>3.873967591452199e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.63576693643752e-08</v>
+        <v>2.635766936437549e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.583289312527015e-08</v>
+        <v>2.583289312527022e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.379686902157741e-08</v>
+        <v>2.379686902157789e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.685900940285744e-08</v>
+        <v>2.685900940285771e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.218817705018583e-08</v>
+        <v>3.218817705018563e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.578244210871648e-08</v>
+        <v>2.578244210871668e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.907392024507962e-08</v>
+        <v>2.907392024507988e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.493892863848647e-08</v>
+        <v>2.49389286384867e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.54652493795934e-08</v>
+        <v>2.546524937959374e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.64417032379122e-08</v>
+        <v>2.64417032379124e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.619559071498782e-07</v>
+        <v>3.274754203201049e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.246137598754173e-08</v>
+        <v>2.246137598754203e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.586108691686534e-08</v>
+        <v>2.58610869168655e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.401409802825725e-08</v>
+        <v>2.40140980282579e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.978853812262566e-08</v>
+        <v>2.978853812262639e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.882183213309588e-08</v>
+        <v>2.882183213309641e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.703563800141966e-08</v>
+        <v>2.703563800142004e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.973900741225174e-08</v>
+        <v>2.973900741225154e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.865667853515951e-08</v>
+        <v>2.865667853515953e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.085237047152974e-08</v>
+        <v>6.085237047153014e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.302376932567697e-08</v>
+        <v>2.302376932567742e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.264102572272689e-08</v>
+        <v>3.264102572272715e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.17774724139923e-08</v>
+        <v>2.177747241399257e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.925153735467302e-08</v>
+        <v>2.925153735467303e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.080587340056541e-08</v>
+        <v>3.080587340056581e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.10314206270774e-08</v>
+        <v>4.103142062707783e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.27846386816851e-08</v>
+        <v>6.278463868168543e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.040263213153831e-08</v>
+        <v>5.040263213153918e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.07506333524285e-08</v>
+        <v>5.075063335242846e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.356594706879726e-08</v>
+        <v>3.356594706879782e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.98383657004635e-08</v>
+        <v>4.983836570046419e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.623313981734911e-08</v>
+        <v>5.623313981734909e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.98274048758797e-08</v>
+        <v>4.982740487587989e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.311888301224293e-08</v>
+        <v>5.311888301224299e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.898389140564978e-08</v>
+        <v>4.898389140565013e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.951021214675721e-08</v>
+        <v>4.95102121467571e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>5.048666600503269e-08</v>
+        <v>5.048666600503282e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.619559071498782e-07</v>
+        <v>6.077610261482477e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>5.207114463717611e-08</v>
+        <v>5.207114463717661e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>5.632116922371209e-08</v>
+        <v>5.632116922371259e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.420801392155041e-08</v>
+        <v>5.420801392155073e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>5.383350088978883e-08</v>
+        <v>5.383350088978894e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>5.286679490025898e-08</v>
+        <v>5.286679490025907e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>5.108060076858295e-08</v>
+        <v>5.108060076858369e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>5.640665245428915e-08</v>
+        <v>5.640665245428957e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.355037690130556e-08</v>
+        <v>6.355037690130552e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.489632328928842e-08</v>
+        <v>8.489632328928886e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>5.274668196601594e-08</v>
+        <v>5.274668196601569e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.17720805016634e-08</v>
+        <v>5.177208050166438e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.618860953886729e-08</v>
+        <v>4.618860953886758e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.329650012183545e-08</v>
+        <v>5.329650012183625e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.948270334452561e-08</v>
+        <v>4.948270334452616e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>1.533957026040713e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.960769572488402e-07</v>
+        <v>3.269682911697681e-08</v>
       </c>
       <c r="O4" t="n">
         <v>1.702565428855794e-08</v>
@@ -5274,7 +5274,7 @@
         <v>2.227488923488488e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.960769572488402e-07</v>
+        <v>3.53588588296687e-08</v>
       </c>
       <c r="O6" t="n">
         <v>2.484621058154617e-08</v>
@@ -5362,7 +5362,7 @@
         <v>1.860302848340229e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.960769572488402e-07</v>
+        <v>3.596028733997193e-08</v>
       </c>
       <c r="O7" t="n">
         <v>2.028899705870138e-08</v>
@@ -5450,7 +5450,7 @@
         <v>2.880763911283535e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.960769572488402e-07</v>
+        <v>4.146209170584682e-08</v>
       </c>
       <c r="O8" t="n">
         <v>2.708328886242645e-08</v>
@@ -5538,7 +5538,7 @@
         <v>6.248329511944431e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.960769572488402e-07</v>
+        <v>7.984055397601388e-08</v>
       </c>
       <c r="O9" t="n">
         <v>6.77081987861687e-08</v>
@@ -5809,7 +5809,7 @@
         <v>1.913120451897072e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.025157686055651e-07</v>
+        <v>3.02515768605565e-07</v>
       </c>
       <c r="X2" t="n">
         <v>1.915765036039019e-07</v>
@@ -5949,7 +5949,7 @@
         <v>1.678251512256211e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.52712375253165e-08</v>
+        <v>1.527123752531651e-08</v>
       </c>
       <c r="L4" t="n">
         <v>1.382802612290218e-08</v>
@@ -5958,7 +5958,7 @@
         <v>1.424643878191326e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.240953718102561e-07</v>
+        <v>1.774657767063317e-08</v>
       </c>
       <c r="O4" t="n">
         <v>1.365270174788396e-08</v>
@@ -5985,7 +5985,7 @@
         <v>1.716935092504123e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.840397162241913e-08</v>
+        <v>3.840397162241914e-08</v>
       </c>
       <c r="X4" t="n">
         <v>1.960648291778417e-08</v>
@@ -6128,13 +6128,13 @@
         <v>2.092681080957054e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.582574882911827e-08</v>
+        <v>1.582574882911826e-08</v>
       </c>
       <c r="M6" t="n">
         <v>1.990201206616741e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.240953718102561e-07</v>
+        <v>1.973355122133488e-08</v>
       </c>
       <c r="O6" t="n">
         <v>2.004666150950757e-08</v>
@@ -6173,7 +6173,7 @@
         <v>1.74914532268672e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.8290617865322e-08</v>
+        <v>2.829061786532201e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>1.406172814306377e-08</v>
@@ -6222,7 +6222,7 @@
         <v>1.690471824556132e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.240953718102561e-07</v>
+        <v>2.040485713428107e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.631087582098551e-08</v>
@@ -6310,7 +6310,7 @@
         <v>2.498217501584276e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.240953718102561e-07</v>
+        <v>2.477482580184478e-08</v>
       </c>
       <c r="O8" t="n">
         <v>2.169979979467217e-08</v>
@@ -6398,7 +6398,7 @@
         <v>5.338348736479188e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.240953718102561e-07</v>
+        <v>5.688362625351167e-08</v>
       </c>
       <c r="O9" t="n">
         <v>5.57126290211315e-08</v>
@@ -6818,7 +6818,7 @@
         <v>1.459287808161997e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.141496045286518e-07</v>
+        <v>1.67972156255895e-08</v>
       </c>
       <c r="O4" t="n">
         <v>1.301532326310219e-08</v>
@@ -6994,7 +6994,7 @@
         <v>1.994171449629776e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.141496045286518e-07</v>
+        <v>1.870576495639567e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.495518445728785e-08</v>
@@ -7082,7 +7082,7 @@
         <v>1.711646214238863e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.141496045286518e-07</v>
+        <v>1.932079968635818e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.553880127683766e-08</v>
@@ -7170,7 +7170,7 @@
         <v>2.465017348003733e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.141496045286518e-07</v>
+        <v>2.340793346063369e-08</v>
       </c>
       <c r="O8" t="n">
         <v>2.057319053334215e-08</v>
@@ -7258,7 +7258,7 @@
         <v>4.977478541927727e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.141496045286518e-07</v>
+        <v>5.197912296324683e-08</v>
       </c>
       <c r="O9" t="n">
         <v>5.082266108435316e-08</v>
@@ -7678,7 +7678,7 @@
         <v>1.680954266926039e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.103138991320338e-07</v>
+        <v>4.920272618925585e-08</v>
       </c>
       <c r="O4" t="n">
         <v>1.98843901451491e-08</v>
@@ -7854,7 +7854,7 @@
         <v>1.968584105155856e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.103138991320338e-07</v>
+        <v>5.208119048210089e-08</v>
       </c>
       <c r="O6" t="n">
         <v>2.823196655820198e-08</v>
@@ -7942,7 +7942,7 @@
         <v>2.037868523465945e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.103138991320338e-07</v>
+        <v>5.277186875465503e-08</v>
       </c>
       <c r="O7" t="n">
         <v>2.345332667974617e-08</v>
@@ -8030,7 +8030,7 @@
         <v>3.128728631811925e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.103138991320338e-07</v>
+        <v>5.861170955602721e-08</v>
       </c>
       <c r="O8" t="n">
         <v>3.068631283747201e-08</v>
@@ -8118,7 +8118,7 @@
         <v>6.47974559761235e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.103138991320338e-07</v>
+        <v>9.719063949611895e-08</v>
       </c>
       <c r="O9" t="n">
         <v>7.148647969482561e-08</v>
@@ -8538,7 +8538,7 @@
         <v>1.458354099850347e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.878970781769274e-07</v>
+        <v>2.148700581018878e-08</v>
       </c>
       <c r="O4" t="n">
         <v>1.351534708779791e-08</v>
@@ -8714,7 +8714,7 @@
         <v>1.692789946609482e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.878970781769274e-07</v>
+        <v>2.381086733089905e-08</v>
       </c>
       <c r="O6" t="n">
         <v>2.048640747410647e-08</v>
@@ -8802,7 +8802,7 @@
         <v>1.744673910627687e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.878970781769274e-07</v>
+        <v>2.435020391796218e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.637841535532928e-08</v>
@@ -8890,7 +8890,7 @@
         <v>2.619213251202697e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.878970781769274e-07</v>
+        <v>2.906421630088341e-08</v>
       </c>
       <c r="O8" t="n">
         <v>2.220041607941731e-08</v>
@@ -8978,7 +8978,7 @@
         <v>5.401529468307664e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.878970781769274e-07</v>
+        <v>6.091875949476193e-08</v>
       </c>
       <c r="O9" t="n">
         <v>5.590568255083995e-08</v>

--- a/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.937376697390599e-07</v>
+        <v>1.9373766973906e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.890866605264976e-07</v>
@@ -601,7 +601,7 @@
         <v>1.950311452248301e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.93481145615741e-07</v>
+        <v>1.934811456157409e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.950572978531633e-07</v>
@@ -610,7 +610,7 @@
         <v>1.959366685043568e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.941409688691734e-07</v>
+        <v>1.941409688691735e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.981814820111546e-07</v>
@@ -619,10 +619,10 @@
         <v>1.941271393710273e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.936714387724037e-07</v>
+        <v>1.936714387724038e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.978206827893437e-07</v>
+        <v>1.978206827893438e-07</v>
       </c>
       <c r="O2" t="n">
         <v>1.041582447874767e-07</v>
@@ -634,16 +634,16 @@
         <v>1.951534738695063e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.946733442528714e-07</v>
+        <v>1.946733442528715e-07</v>
       </c>
       <c r="S2" t="n">
         <v>1.941261299613875e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95592470674598e-07</v>
+        <v>1.955924706745981e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.359461843083683e-07</v>
+        <v>4.359461843083687e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.939538716416262e-07</v>
@@ -652,19 +652,19 @@
         <v>3.081722949565066e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.940331924003987e-07</v>
+        <v>1.940331924003988e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.942882339033193e-07</v>
+        <v>1.942882339033192e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.723444655621676e-07</v>
+        <v>1.723444655621678e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.940009171154089e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.935408054179071e-07</v>
+        <v>1.93540805417907e-07</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.992320647706122e-07</v>
+        <v>1.993885307673045e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.225373673376724e-07</v>
+        <v>5.227338820493561e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.110229610640528e-07</v>
+        <v>2.115988798793273e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.978675567217588e-07</v>
+        <v>1.979760184358994e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.085346755782663e-07</v>
+        <v>2.090239557548601e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.974101840758777e-07</v>
+        <v>1.975025503677214e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.087367719284206e-07</v>
+        <v>2.092336122091003e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.150122740965771e-07</v>
+        <v>2.157305295801473e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.021240411052638e-07</v>
+        <v>2.02383234907297e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.310516806947854e-07</v>
+        <v>2.323368920892056e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.020237424801736e-07</v>
+        <v>2.022790403004668e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.988870773153173e-07</v>
+        <v>1.990334288502519e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.284291117446515e-07</v>
+        <v>2.296195544295963e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>5.386259668551138e-08</v>
+        <v>5.413356394831073e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.026134729424547e-07</v>
+        <v>2.028882035877399e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.093748782974641e-07</v>
+        <v>2.098916890054441e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.059705707931029e-07</v>
+        <v>2.063681928494125e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.020033776122375e-07</v>
+        <v>2.02257681358051e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.125388432910108e-07</v>
+        <v>2.131687783116448e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>6.012115333886513e-07</v>
+        <v>6.014678723014178e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.007718486524757e-07</v>
+        <v>2.00982679352271e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.012588995308956e-07</v>
+        <v>4.020187828262545e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.013681576935839e-07</v>
+        <v>2.016015449320835e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.031776939263441e-07</v>
+        <v>2.034744200502869e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.645046565816298e-07</v>
+        <v>1.646878929215294e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.011278775861169e-07</v>
+        <v>2.013519141759639e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.979302489899155e-07</v>
+        <v>1.980419267248496e-07</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.057574690096297e-08</v>
+        <v>2.057574690096274e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.22736222938336e-08</v>
+        <v>2.227362229383335e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.914100212563819e-08</v>
+        <v>3.914100212563815e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.83958546147913e-08</v>
+        <v>1.839585461479095e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.518614754085889e-08</v>
+        <v>3.518614754085874e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.767818892114901e-08</v>
+        <v>1.767818892114888e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.548155350868378e-08</v>
+        <v>3.548155350868356e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.541444954440012e-08</v>
+        <v>4.541444954439991e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.521512917431796e-08</v>
+        <v>2.521512917431807e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.07706507689144e-08</v>
+        <v>7.077065076891443e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.497498555891642e-08</v>
+        <v>2.497498555891668e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.001267405836006e-08</v>
+        <v>2.001267405835997e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.669525758271998e-08</v>
+        <v>6.669525758271977e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>2.57607363428168e-08</v>
+        <v>2.576073634281649e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.594102849363622e-08</v>
+        <v>2.594102849363594e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.656790585643191e-08</v>
+        <v>3.656790585643119e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.114462096600542e-08</v>
+        <v>3.114462096600521e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>2.496358381268368e-08</v>
+        <v>2.496358381268338e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>4.152657671845093e-08</v>
+        <v>4.152657671845067e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.515413802498499e-08</v>
+        <v>2.515413802498421e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.357720027638972e-08</v>
+        <v>2.357720027638981e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.757242679703041e-08</v>
+        <v>4.757242679702978e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>2.391381130792548e-08</v>
+        <v>2.391381130792526e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.6916606396595e-08</v>
+        <v>2.691660639659457e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.177716152308213e-08</v>
+        <v>2.177716152308171e-08</v>
       </c>
       <c r="AA4" t="n">
         <v>2.354924711660156e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.849017321606566e-08</v>
+        <v>1.849017321606536e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.264357959171261e-07</v>
+        <v>1.264357959171244e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.751387945371531e-07</v>
+        <v>1.751387945371528e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>5.36209342880124e-07</v>
+        <v>5.362093428801236e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>9.018048544816699e-08</v>
+        <v>9.018048544816712e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.628636714390703e-07</v>
+        <v>4.628636714390708e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.340152717651824e-08</v>
+        <v>7.340152717651816e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.779914934134477e-07</v>
+        <v>4.779914934134474e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>6.776560964842377e-07</v>
+        <v>6.776560964842393e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.263459776740756e-07</v>
+        <v>2.263459776740762e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.199009816202515e-06</v>
+        <v>1.199009816202514e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.221672382475185e-07</v>
+        <v>2.221672382475188e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.312465530207743e-07</v>
+        <v>1.312465530207738e-07</v>
       </c>
       <c r="N5" t="n">
         <v>1.088692553765024e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.185760805587542e-07</v>
+        <v>2.185760805587544e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>2.293390787035535e-07</v>
+        <v>2.293390787035562e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.71157247134192e-07</v>
+        <v>4.711572471341919e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>3.75258282621281e-07</v>
+        <v>3.752582826212806e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.141155965494266e-07</v>
+        <v>2.141155965494302e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>5.893338005060406e-07</v>
+        <v>5.893338005060408e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.196325665934421e-07</v>
+        <v>2.196325665934461e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.74236283809884e-07</v>
+        <v>1.742362838098855e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>6.813015079713019e-07</v>
+        <v>6.813015079713006e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.096648280103317e-07</v>
+        <v>2.096648280103311e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.613140558984199e-07</v>
+        <v>2.613140558984223e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.52084350800998e-07</v>
+        <v>1.520843508009972e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.964215218444587e-07</v>
+        <v>1.964215218444596e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.011871061185459e-07</v>
+        <v>1.011871061185458e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.395091057374828e-08</v>
+        <v>2.395091057374783e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.122306362195791e-08</v>
+        <v>3.12230636219578e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.809044345376263e-08</v>
+        <v>4.809044345376245e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.734529594291529e-08</v>
+        <v>2.734529594291539e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.856131121364383e-08</v>
+        <v>3.856131121364365e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.662763024927335e-08</v>
+        <v>2.662763024927347e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.443099483680814e-08</v>
+        <v>4.443099483680811e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.878961321718547e-08</v>
+        <v>4.878961321718513e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.859029284710315e-08</v>
+        <v>2.859029284710304e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.972009209703875e-08</v>
+        <v>7.972009209703844e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.39244268870413e-08</v>
+        <v>3.392442688704103e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.896211538648442e-08</v>
+        <v>2.896211538648431e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.012384401055483e-08</v>
+        <v>7.012384401055479e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.918919126713418e-08</v>
+        <v>2.918919126713488e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.583358399295788e-08</v>
+        <v>3.583358399295831e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.551734718455665e-08</v>
+        <v>4.551734718455635e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.009406229412976e-08</v>
+        <v>4.00940622941297e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.833874748546872e-08</v>
+        <v>2.833874748546826e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.49017403912359e-08</v>
+        <v>4.490174039123576e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.840731770947604e-08</v>
+        <v>2.840731770947603e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.252664160451392e-08</v>
+        <v>3.252664160451387e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.746490147416601e-08</v>
+        <v>5.746490147416541e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.286325263605036e-08</v>
+        <v>3.286325263604995e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.04993814503837e-08</v>
+        <v>3.049938145038339e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.515232519586741e-08</v>
+        <v>2.515232519586705e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.249868844472616e-08</v>
+        <v>3.24986884447257e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.186767232957515e-08</v>
+        <v>2.186767232957514e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.507314530724995e-08</v>
+        <v>2.507314530724967e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.677102070012076e-08</v>
+        <v>2.67710207001204e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.363840053192515e-08</v>
+        <v>4.363840053192493e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.289325302107834e-08</v>
+        <v>2.28932530210779e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.968354594714542e-08</v>
+        <v>3.968354594714536e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.217558732743619e-08</v>
+        <v>2.217558732743584e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.997895191497094e-08</v>
+        <v>3.997895191497058e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.991184795068734e-08</v>
+        <v>4.991184795068692e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.971252758060495e-08</v>
+        <v>2.971252758060501e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.526804917520159e-08</v>
+        <v>7.526804917520138e-08</v>
       </c>
       <c r="L7" t="n">
         <v>2.947238396520354e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.451007246464725e-08</v>
+        <v>2.451007246464682e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.119265598900689e-08</v>
+        <v>7.119265598900668e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>3.025785193444021e-08</v>
+        <v>3.025785193443993e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>3.043814408525957e-08</v>
+        <v>3.043814408525931e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.106530426271867e-08</v>
+        <v>4.106530426271902e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>3.564201937229264e-08</v>
+        <v>3.564201937229226e-08</v>
       </c>
       <c r="S7" t="n">
         <v>2.946098221897032e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.602397512473812e-08</v>
+        <v>4.602397512473769e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.955887797913913e-08</v>
+        <v>2.955887797913952e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.807459868267664e-08</v>
+        <v>2.807459868267676e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.206982520331675e-08</v>
+        <v>5.206982520331679e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.841120971421262e-08</v>
+        <v>2.841120971421218e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.129202081458777e-08</v>
+        <v>3.129202081458736e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.627455992936931e-08</v>
+        <v>2.627455992936866e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.804664552288862e-08</v>
+        <v>2.80466455228885e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.298757162235242e-08</v>
+        <v>2.29875716223522e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.041403534699346e-08</v>
+        <v>3.04140353469928e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.024191331340175e-08</v>
+        <v>4.02419133134018e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.710929314520664e-08</v>
+        <v>5.710929314520647e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.203515908949807e-08</v>
+        <v>3.203515908949791e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.629099536724746e-08</v>
+        <v>4.629099536724748e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.733228893446417e-08</v>
+        <v>3.733228893446436e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.344984452825192e-08</v>
+        <v>5.344984452825203e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>6.338274056396829e-08</v>
+        <v>6.338274056396859e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.318342019388633e-08</v>
+        <v>4.318342019388644e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.87389417884826e-08</v>
+        <v>8.873894178848302e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.294327657848495e-08</v>
+        <v>4.294327657848475e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.798096507794425e-08</v>
+        <v>3.798096507794439e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.8361436480964e-08</v>
+        <v>7.836143648096409e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.915879035820992e-08</v>
+        <v>3.915879035820963e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.891455807135341e-08</v>
+        <v>3.89145580713527e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.480846324573477e-08</v>
+        <v>4.480846324573501e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.911291198557361e-08</v>
+        <v>4.911291198557366e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.293187483225152e-08</v>
+        <v>4.293187483225132e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.949486773801953e-08</v>
+        <v>5.949486773801906e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.905524503881662e-08</v>
+        <v>3.905524503881696e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>3.934874747624052e-08</v>
+        <v>3.934874747624069e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.55423155677866e-08</v>
+        <v>6.554231556778577e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.289949957095189e-08</v>
+        <v>3.289949957095183e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.288564342236945e-08</v>
+        <v>5.288564342236951e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.146443099960998e-08</v>
+        <v>3.146443099960993e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.151753813616991e-08</v>
+        <v>4.151753813616959e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.495093171822461e-08</v>
+        <v>4.495093171822547e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.755293188466196e-08</v>
+        <v>6.755293188466185e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.306036499805459e-08</v>
+        <v>8.306036499805442e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>9.992774482985921e-08</v>
+        <v>9.99277448298589e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.599541172434341e-08</v>
+        <v>7.599541172434369e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.413808392731861e-08</v>
+        <v>6.413808392731841e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.846493682433878e-08</v>
+        <v>7.846493682433851e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>9.626829621290478e-08</v>
+        <v>9.62682962129046e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.062011922486211e-07</v>
+        <v>1.062011922486209e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>8.600187187853905e-08</v>
+        <v>8.600187187853909e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.315573934731354e-07</v>
+        <v>1.315573934731353e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>8.576172826313755e-08</v>
+        <v>8.576172826313747e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>8.079941676258104e-08</v>
+        <v>8.079941676258073e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.274820002869407e-07</v>
+        <v>1.274820002869409e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>9.112395531544326e-08</v>
+        <v>9.112395531544342e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>9.229955140484674e-08</v>
+        <v>9.229955140484682e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.735465375962157e-08</v>
+        <v>9.73546537596215e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>9.193136367022644e-08</v>
+        <v>9.19313636702262e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.575032651690423e-08</v>
+        <v>8.575032651690424e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.023133194226722e-07</v>
+        <v>1.023133194226716e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>8.581889674091158e-08</v>
+        <v>8.581889674091179e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.002998809839402e-07</v>
+        <v>1.002998809839404e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.083591695012509e-07</v>
+        <v>1.083591695012507e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>8.470055401214663e-08</v>
+        <v>8.470055401214634e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.758136511252157e-08</v>
+        <v>8.758136511252149e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.423797098006626e-08</v>
+        <v>7.423797098006575e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.43359898208225e-08</v>
+        <v>8.43359898208228e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.927691592028627e-08</v>
+        <v>7.927691592028641e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.910741724282198e-07</v>
+        <v>1.9107417242822e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.864238572939362e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.913932246208823e-07</v>
+        <v>1.913932246208822e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.911464776496729e-07</v>
+        <v>1.911464776496731e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.911190009808652e-07</v>
+        <v>1.911190009808653e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.913821198760469e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.917487720295379e-07</v>
+        <v>1.917487720295378e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.912254188746507e-07</v>
+        <v>1.912254188746506e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.914751565902747e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.914232854062945e-07</v>
+        <v>1.914232854062944e-07</v>
       </c>
       <c r="L2" t="n">
         <v>1.91292498525787e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.912555815252655e-07</v>
+        <v>1.912555815252654e-07</v>
       </c>
       <c r="N2" t="n">
         <v>1.916133605087268e-07</v>
@@ -1488,43 +1488,43 @@
         <v>9.865473819507281e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.914637284781292e-07</v>
+        <v>1.914637284781291e-07</v>
       </c>
       <c r="Q2" t="n">
         <v>1.912159432243185e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.912515706152422e-07</v>
+        <v>1.912515706152421e-07</v>
       </c>
       <c r="S2" t="n">
         <v>1.91452084519144e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.91249072973241e-07</v>
+        <v>1.912490729732412e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.30864417922751e-07</v>
+        <v>4.308644179227511e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.916428578938135e-07</v>
+        <v>1.916428578938136e-07</v>
       </c>
       <c r="W2" t="n">
         <v>3.029084960204571e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.916930507572006e-07</v>
+        <v>1.916930507572008e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.913534736006376e-07</v>
+        <v>1.913534736006377e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.684525054271869e-07</v>
+        <v>1.684525054271872e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.920951710748797e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.910774237398702e-07</v>
+        <v>1.910774237398704e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.942870666175447e-07</v>
+        <v>1.943176573920521e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.185230177084128e-07</v>
+        <v>5.186362405262756e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.965670440478424e-07</v>
+        <v>1.966790069391255e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.948028853444946e-07</v>
+        <v>1.948515966225538e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.946114361024028e-07</v>
+        <v>1.946539310527937e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.964720069905047e-07</v>
+        <v>1.965796482788714e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.991267516294283e-07</v>
+        <v>1.993303201810096e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.953725867149548e-07</v>
+        <v>1.954420521863621e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.971423753509826e-07</v>
+        <v>1.972740693733893e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.967718033511545e-07</v>
+        <v>1.968912419426261e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.958399170476609e-07</v>
+        <v>1.959255822140269e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.956480503748272e-07</v>
+        <v>1.957278379366497e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.981431728830523e-07</v>
+        <v>1.983103635662621e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.205020557776966e-08</v>
+        <v>4.209536963326707e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.970509135003371e-07</v>
+        <v>1.9717866699748e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.952988461158904e-07</v>
+        <v>1.953656402346062e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.955620338472952e-07</v>
+        <v>1.956382940345218e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.969693574395657e-07</v>
+        <v>1.970947988056993e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.955418445497854e-07</v>
+        <v>1.956172445275196e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.921231553159903e-07</v>
+        <v>5.922469824494783e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.983229145099023e-07</v>
+        <v>1.984959641571157e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.92296167606342e-07</v>
+        <v>3.929428249294477e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.987008928956649e-07</v>
+        <v>1.98888820155348e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.962839181789905e-07</v>
+        <v>1.963852309441072e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.593116621164197e-07</v>
+        <v>1.594513151802815e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.015801811998528e-07</v>
+        <v>2.018684984969282e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.943609885784474e-07</v>
+        <v>1.943946293744895e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.239241177588999e-08</v>
+        <v>1.239241177588991e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.605772019435696e-08</v>
+        <v>1.605772019435677e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.599625306327206e-08</v>
+        <v>1.599625306327186e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.320913251424855e-08</v>
+        <v>1.320913251424824e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.289877090017345e-08</v>
+        <v>1.289877090017324e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.587081986192123e-08</v>
+        <v>1.58708198619207e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.001232460392618e-08</v>
+        <v>2.001232460392601e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.410080996512923e-08</v>
+        <v>1.410080996512904e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.700550902839728e-08</v>
+        <v>1.700550902839692e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.633580346314738e-08</v>
+        <v>1.633580346314715e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.485850548287838e-08</v>
+        <v>1.485850548287812e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.455295298675494e-08</v>
+        <v>1.455295298675473e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.848278918398809e-08</v>
+        <v>1.848278918398813e-08</v>
       </c>
       <c r="O4" t="n">
         <v>1.305261395021328e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.679262656425297e-08</v>
+        <v>1.679262656425283e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.399377813561295e-08</v>
+        <v>1.399377813561278e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.439620590550474e-08</v>
+        <v>1.439620590550472e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.66611026910285e-08</v>
+        <v>1.666110269102852e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.43679938901305e-08</v>
+        <v>1.436799389013041e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.623296583810358e-08</v>
+        <v>1.623296583810328e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.937413788674194e-08</v>
+        <v>1.937413788674176e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.999555440410974e-08</v>
+        <v>3.999555440410973e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.938292719982604e-08</v>
+        <v>1.938292719982585e-08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.520329611385652e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.73129306364061e-08</v>
+        <v>1.731293063640591e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.392506117249579e-08</v>
+        <v>2.392506117249568e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25121458008012e-08</v>
+        <v>1.251214580080101e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.854406187351343e-08</v>
+        <v>2.854406187351311e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.36441362933945e-08</v>
+        <v>9.364413629339476e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.377955168696052e-08</v>
+        <v>9.377955168696047e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.287135283556724e-08</v>
+        <v>4.28713528355673e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9793453515547e-08</v>
+        <v>3.97934535155468e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.338246784216245e-08</v>
+        <v>8.338246784216306e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.762880447537429e-07</v>
+        <v>1.762880447537427e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>6.190380067535318e-08</v>
+        <v>6.190380067535293e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.053493003171826e-07</v>
+        <v>1.053493003171827e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.471370335281809e-08</v>
+        <v>9.471370335281788e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.938652085326579e-08</v>
+        <v>6.938652085326572e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.97155044960108e-08</v>
+        <v>6.971550449601057e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.40353330544085e-07</v>
+        <v>1.403533305440849e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>3.901063363779124e-08</v>
+        <v>3.901063363779123e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.785258301251269e-08</v>
+        <v>9.785258301251252e-08</v>
       </c>
       <c r="Q5" t="n">
         <v>5.68431643134042e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.857983803344793e-08</v>
+        <v>6.857983803344796e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>9.632829564184565e-08</v>
+        <v>9.632829564184566e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.685603690682998e-08</v>
+        <v>6.685603690682982e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>9.539459034400442e-08</v>
+        <v>9.539459034400465e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.308521014284474e-07</v>
+        <v>1.308521014284472e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>5.161471963530945e-07</v>
+        <v>5.161471963530916e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.505560472965066e-07</v>
+        <v>1.505560472965063e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.613826546496742e-08</v>
+        <v>8.61382654649675e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.030469571687278e-07</v>
+        <v>1.030469571687277e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.357290943312004e-07</v>
+        <v>2.357290943312013e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.357249590516044e-08</v>
+        <v>3.357249590516033e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.457205652655461e-08</v>
+        <v>1.457205652655449e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.189964112263381e-08</v>
+        <v>2.189964112263371e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.817589781393666e-08</v>
+        <v>1.817589781393651e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.905105344252544e-08</v>
+        <v>1.905105344252506e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.874069182845029e-08</v>
+        <v>1.874069182845027e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.805046461258586e-08</v>
+        <v>1.805046461258563e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.21919693545908e-08</v>
+        <v>2.219196935459084e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.628045471579385e-08</v>
+        <v>1.628045471579375e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.284742995667417e-08</v>
+        <v>2.284742995667391e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.851544821381198e-08</v>
+        <v>1.851544821381184e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.070042641115504e-08</v>
+        <v>2.070042641115515e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.673259773741957e-08</v>
+        <v>1.67325977374194e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.066311462067745e-08</v>
+        <v>2.066311462067735e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.964117073328505e-08</v>
+        <v>1.964117073328487e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87618823783621e-08</v>
+        <v>1.876188237836199e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.617342288627762e-08</v>
+        <v>1.617342288627746e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.657585065616935e-08</v>
+        <v>1.6575850656169e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.250302361930529e-08</v>
+        <v>2.250302361930501e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.654763864079513e-08</v>
+        <v>1.654763864079517e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.241883765575958e-08</v>
+        <v>2.24188376557597e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.155378263740647e-08</v>
+        <v>2.15537826374064e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>4.254138679851767e-08</v>
+        <v>4.254138679851624e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.522484812810293e-08</v>
+        <v>2.522484812810268e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.794628287819225e-08</v>
+        <v>1.794628287819185e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.949257538707075e-08</v>
+        <v>1.949257538707059e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.976698210077258e-08</v>
+        <v>2.976698210077261e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.471532933172439e-08</v>
+        <v>1.471532933172425e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.511694340622377e-08</v>
+        <v>1.511694340622362e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.878225182469073e-08</v>
+        <v>1.878225182469055e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.872078469360579e-08</v>
+        <v>1.872078469360557e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.593366414458229e-08</v>
+        <v>1.593366414458212e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.56233025305072e-08</v>
+        <v>1.562330253050704e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.859535149225499e-08</v>
+        <v>1.859535149225464e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.273685623425987e-08</v>
+        <v>2.273685623425982e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.682534159546293e-08</v>
+        <v>1.682534159546277e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9730040658731e-08</v>
+        <v>1.973004065873078e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.90603350934811e-08</v>
+        <v>1.906033509348095e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.75830371132121e-08</v>
+        <v>1.758303711321192e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.727748461708869e-08</v>
+        <v>1.727748461708854e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.120732081432182e-08</v>
+        <v>2.120732081432179e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.577704668439312e-08</v>
+        <v>1.577704668439293e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.951705929843282e-08</v>
+        <v>1.951705929843294e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67183097659467e-08</v>
+        <v>1.671830976594654e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.712073753583843e-08</v>
+        <v>1.712073753583833e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.938563432136225e-08</v>
+        <v>1.938563432136203e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.709252552046425e-08</v>
+        <v>1.709252552046429e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.918991567940981e-08</v>
+        <v>1.918991567940946e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.209866951707565e-08</v>
+        <v>2.209866951707549e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.272008603444352e-08</v>
+        <v>4.272008603444299e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.210745883015981e-08</v>
+        <v>2.210745883015972e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.827177863356963e-08</v>
+        <v>1.827177863356928e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.00374622667398e-08</v>
+        <v>2.003746226673969e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.664959280282953e-08</v>
+        <v>2.664959280282939e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.523667743113495e-08</v>
+        <v>1.523667743113476e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.846374260853553e-08</v>
+        <v>1.846374260853541e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.699861647848166e-08</v>
+        <v>2.699861647848149e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.69371493473967e-08</v>
+        <v>2.693714934739656e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.155712884123859e-08</v>
+        <v>2.155712884123856e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.972872311675712e-08</v>
+        <v>1.972872311675706e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.782145226366831e-08</v>
+        <v>2.782145226366823e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.095322088805084e-08</v>
+        <v>3.095322088805073e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.504170624925389e-08</v>
+        <v>2.504170624925371e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.794640531252188e-08</v>
+        <v>2.794640531252168e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.727669974727199e-08</v>
+        <v>2.727669974727187e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.579940176700301e-08</v>
+        <v>2.579940176700287e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.549384927090976e-08</v>
+        <v>2.549384927090974e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.564895757920877e-08</v>
+        <v>2.564895757920885e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.12561103379391e-08</v>
+        <v>2.125611033793892e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.474184879634721e-08</v>
+        <v>2.474184879634736e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.910812821805935e-08</v>
+        <v>1.910812821805931e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.533710218962939e-08</v>
+        <v>2.533710218962947e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.760199897515314e-08</v>
+        <v>2.760199897515318e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.530889017425516e-08</v>
+        <v>2.530889017425506e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.505468465452334e-08</v>
+        <v>2.505468465452331e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.888885766276974e-08</v>
+        <v>2.888885766276973e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.09374076842411e-08</v>
+        <v>5.093740768424071e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.494358262382665e-08</v>
+        <v>2.494358262382652e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.118210719885868e-08</v>
+        <v>3.118210719885864e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.329380679179179e-08</v>
+        <v>2.329380679179185e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.486595745662047e-08</v>
+        <v>3.486595745662033e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.853971037341671e-08</v>
+        <v>2.853971037341669e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.011249427205951e-08</v>
+        <v>4.011249427205945e-08</v>
       </c>
       <c r="C9" t="n">
         <v>5.18843677647674e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.182290063368247e-08</v>
+        <v>5.182290063368246e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.716482007528901e-08</v>
+        <v>4.716482007528884e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.003756984528554e-08</v>
+        <v>3.003756984528555e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.169747021922307e-08</v>
+        <v>5.169747021922301e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.583897217433662e-08</v>
+        <v>5.583897217433645e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.992745753553965e-08</v>
+        <v>4.992745753553972e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.283215659880768e-08</v>
+        <v>5.283215659880754e-08</v>
       </c>
       <c r="K9" t="n">
         <v>5.216245103355783e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.068515305328881e-08</v>
+        <v>5.068515305328879e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>5.037960055716538e-08</v>
+        <v>5.037960055716543e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>5.430943675439852e-08</v>
+        <v>5.430943675439851e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>5.156577028204817e-08</v>
+        <v>5.156577028204806e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>5.589005185286959e-08</v>
+        <v>5.589005185286957e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.982042849291489e-08</v>
+        <v>4.982042849291461e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>5.022285347591516e-08</v>
+        <v>5.0222853475915e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>5.248775026143894e-08</v>
+        <v>5.248775026143901e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>5.019464146054092e-08</v>
+        <v>5.019464146054097e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>5.240356429789337e-08</v>
+        <v>5.240356429789334e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.455559073737497e-08</v>
+        <v>6.455559073737477e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.582220197452021e-08</v>
+        <v>7.582220197452008e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>5.520957477023651e-08</v>
+        <v>5.520957477023669e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.137389457364629e-08</v>
+        <v>5.137389457364627e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.825204143758515e-08</v>
+        <v>4.825204143758502e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.97517087429062e-08</v>
+        <v>5.975170874290628e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.833879337121166e-08</v>
+        <v>4.83387933712117e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.926785867156178e-07</v>
+        <v>1.926785867156179e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.881178926690254e-07</v>
+        <v>3.881178926690252e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.931592718854917e-07</v>
+        <v>1.931592718854918e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.928843270528165e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.934026722780869e-07</v>
+        <v>1.93402672278087e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.925979620502924e-07</v>
+        <v>1.925979620502926e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93629889915617e-07</v>
+        <v>1.936298899156171e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.940067535775089e-07</v>
+        <v>1.94006753577509e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.931078248153271e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.964241088050305e-07</v>
+        <v>1.964241088050307e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.927185908995626e-07</v>
+        <v>1.927185908995627e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.927000441576046e-07</v>
+        <v>1.927000441576047e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.953023452018804e-07</v>
+        <v>1.953023452018805e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.022215511351971e-07</v>
+        <v>1.022215511351972e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.930718510631828e-07</v>
+        <v>1.930718510631829e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.937106507425136e-07</v>
+        <v>1.937106507425138e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.93490584715641e-07</v>
+        <v>1.934905847156409e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.930665112634232e-07</v>
+        <v>1.930665112634235e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.932752654221029e-07</v>
+        <v>1.93275265422103e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.343715173926772e-07</v>
+        <v>4.343715173926773e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.929692139125886e-07</v>
+        <v>1.929692139125887e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.081368577565794e-07</v>
+        <v>3.081368577565795e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.93251748249452e-07</v>
+        <v>1.932517482494521e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.935721487027402e-07</v>
+        <v>1.935721487027403e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.712157892110606e-07</v>
+        <v>1.712157892110608e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.930027005464368e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.92705067192264e-07</v>
+        <v>1.927050671922661e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.967491711481506e-07</v>
+        <v>1.968404684332761e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.208189883377172e-07</v>
+        <v>5.209785462673753e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.002028809445761e-07</v>
+        <v>2.004173281848032e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.982231689769603e-07</v>
+        <v>1.983664193365698e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.019469545119476e-07</v>
+        <v>2.022244577049041e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.961772568961661e-07</v>
+        <v>1.962484232317743e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.035919347454689e-07</v>
+        <v>2.039280086464103e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.062776250648346e-07</v>
+        <v>2.06708045313604e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.998187010402472e-07</v>
+        <v>2.000188053071067e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.234528470328249e-07</v>
+        <v>2.244949161381665e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.970407927193243e-07</v>
+        <v>1.971425934239711e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.970003917998731e-07</v>
+        <v>1.971019420409014e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.155084879062447e-07</v>
+        <v>2.162640404577601e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.913410031073832e-08</v>
+        <v>4.930339121820507e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.995473795508021e-07</v>
+        <v>1.997366724038536e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.041356896528111e-07</v>
+        <v>2.04489305126979e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.02586118875638e-07</v>
+        <v>2.028857936752597e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.995121181470986e-07</v>
+        <v>1.997009222570599e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.010330253200395e-07</v>
+        <v>2.012770688329171e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.96855570353437e-07</v>
+        <v>5.96999721227052e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.988123064174483e-07</v>
+        <v>1.989765036853402e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.076682980870622e-07</v>
+        <v>4.086935836894648e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.008588675735754e-07</v>
+        <v>2.010965904862531e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.031317368138015e-07</v>
+        <v>2.034492674671016e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.627237110313731e-07</v>
+        <v>1.628792527744964e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.990702889552974e-07</v>
+        <v>1.992439496270081e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.970058478241831e-07</v>
+        <v>1.971069452702792e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.662451052063324e-08</v>
+        <v>1.662451052063272e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.961963530866568e-08</v>
+        <v>1.961963530866527e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.205407064046236e-08</v>
+        <v>2.20540706404621e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.894844227452332e-08</v>
+        <v>1.894844227452293e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.480339004453836e-08</v>
+        <v>2.480339004453796e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.571381783660579e-08</v>
+        <v>1.571381783660559e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.736991778571772e-08</v>
+        <v>2.736991778571744e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.162676621263643e-08</v>
+        <v>3.162676621263627e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.155731345081775e-08</v>
+        <v>2.155731345081756e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.893190554583797e-08</v>
+        <v>5.893190554583742e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.707637618112327e-08</v>
+        <v>1.707637618112369e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.701885009893355e-08</v>
+        <v>1.701885009893332e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.626106961150509e-08</v>
+        <v>4.62610696115046e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>2.01552765996316e-08</v>
+        <v>2.015527659963125e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.106661223691893e-08</v>
+        <v>2.106661223691852e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.828214847733069e-08</v>
+        <v>2.828214847733034e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.579640146842925e-08</v>
+        <v>2.5796401468429e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>2.100629674220525e-08</v>
+        <v>2.100629674220476e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.33642709961491e-08</v>
+        <v>2.336427099614888e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.915610925721185e-08</v>
+        <v>1.915610925721124e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.04692846514176e-08</v>
+        <v>2.046928465141744e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.845965755058171e-08</v>
+        <v>5.84596575505813e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>2.309863371262241e-08</v>
+        <v>2.309863371262228e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.689071330315154e-08</v>
+        <v>2.689071330315112e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.952019348045302e-08</v>
+        <v>1.952019348045268e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.028552533946225e-08</v>
+        <v>2.028552533946202e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.701134966332461e-08</v>
+        <v>1.701134966332419e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.824543512553588e-08</v>
+        <v>6.824543512554649e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.312543444405238e-07</v>
+        <v>1.312543444405232e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.837184380454916e-07</v>
+        <v>1.837184380454913e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.153110151081202e-07</v>
+        <v>1.153110151081222e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>2.395468935642058e-07</v>
+        <v>2.395468935642054e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>5.297712899990202e-08</v>
+        <v>5.297712899990043e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.010421497442458e-07</v>
+        <v>3.01042149744245e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.793031644607119e-07</v>
+        <v>3.793031644607128e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.633607036735569e-07</v>
+        <v>1.633607036735581e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.524494052416942e-07</v>
+        <v>8.524494052416926e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>8.018720023576221e-08</v>
+        <v>8.01872002357802e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.432783209746715e-08</v>
+        <v>8.432783209746672e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.471981858621278e-07</v>
+        <v>6.471981858621276e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.271534451262e-07</v>
+        <v>1.271534451261998e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.474873690208763e-07</v>
+        <v>1.474873690208759e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>3.001381891726254e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.648457208188228e-07</v>
+        <v>2.648457208188225e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.479314146132727e-07</v>
+        <v>1.479314146132694e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.097666838500192e-07</v>
+        <v>2.097666838500185e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.143521170052274e-07</v>
+        <v>1.143521170052265e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.247124640402611e-07</v>
+        <v>1.247124640402614e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>8.671484659204327e-07</v>
+        <v>8.671484659204319e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.012322089040421e-07</v>
+        <v>2.012322089040455e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.619614499262245e-07</v>
+        <v>2.619614499262234e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.209621347299439e-07</v>
+        <v>1.209621347299472e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.41861845514771e-07</v>
+        <v>1.418618455147716e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.669321937340747e-08</v>
+        <v>8.669321937340669e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.967741746292277e-08</v>
+        <v>1.967741746292251e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.742401000130455e-08</v>
+        <v>2.742401000130395e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.510697758275199e-08</v>
+        <v>2.510697758275145e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.675281696716218e-08</v>
+        <v>2.675281696716228e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.785629698682802e-08</v>
+        <v>2.785629698682754e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.351819252924453e-08</v>
+        <v>2.351819252924443e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.517429247835666e-08</v>
+        <v>3.517429247835644e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.943114090527526e-08</v>
+        <v>3.943114090527513e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.93616881434566e-08</v>
+        <v>2.936168814345646e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.198481248812758e-08</v>
+        <v>6.198481248812734e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.488075087376215e-08</v>
+        <v>2.488075087376194e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.482322479157261e-08</v>
+        <v>2.482322479157217e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.930098375375795e-08</v>
+        <v>4.930098375375754e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.322669380198207e-08</v>
+        <v>2.322669380198159e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.966938132672065e-08</v>
+        <v>2.966938132671998e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.133505541962035e-08</v>
+        <v>3.133505541962028e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.360077616106806e-08</v>
+        <v>3.360077616106808e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.405920368449489e-08</v>
+        <v>2.405920368449452e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.641717793843873e-08</v>
+        <v>2.641717793843838e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.203600712035327e-08</v>
+        <v>2.203600712035271e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.352219159370719e-08</v>
+        <v>2.352219159370714e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.203068293709768e-08</v>
+        <v>6.203068293709752e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.090300840526137e-08</v>
+        <v>3.090300840526111e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.003777945458239e-08</v>
+        <v>3.003777945458156e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.257310042274275e-08</v>
+        <v>2.257310042274224e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.808990003210115e-08</v>
+        <v>2.808990003210096e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.006103096410014e-08</v>
+        <v>2.00610309640999e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.041272944940582e-08</v>
+        <v>2.041272944940516e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.340785423743831e-08</v>
+        <v>2.340785423743807e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.584228956923498e-08</v>
+        <v>2.584228956923465e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.273666120329597e-08</v>
+        <v>2.273666120329568e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8591608973311e-08</v>
+        <v>2.859160897331067e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.950203676537842e-08</v>
+        <v>1.950203676537807e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.115813671449035e-08</v>
+        <v>3.115813671449007e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.541498514140902e-08</v>
+        <v>3.541498514140874e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.534553237959037e-08</v>
+        <v>2.534553237958994e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.272012447461061e-08</v>
+        <v>6.272012447461007e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.086459510989619e-08</v>
+        <v>2.08645951098955e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.080706902770618e-08</v>
+        <v>2.080706902770585e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.004928854027773e-08</v>
+        <v>5.004928854027727e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.394324050212681e-08</v>
+        <v>2.394324050212639e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.485457613941414e-08</v>
+        <v>2.485457613941365e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.207036740610333e-08</v>
+        <v>3.207036740610281e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.958462039720186e-08</v>
+        <v>2.958462039720141e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.479451567097789e-08</v>
+        <v>2.479451567097759e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.715248992492175e-08</v>
+        <v>2.715248992492118e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.281442778247519e-08</v>
+        <v>2.281442778247488e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.42575035801896e-08</v>
+        <v>2.425750358019002e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.224787647935428e-08</v>
+        <v>6.224787647935393e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.688685264139508e-08</v>
+        <v>2.688685264139486e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.050592315277596e-08</v>
+        <v>3.050592315277544e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.330841240922568e-08</v>
+        <v>2.330841240922532e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.407374426823487e-08</v>
+        <v>2.407374426823457e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.079956859209724e-08</v>
+        <v>2.079956859209696e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.496260713469118e-08</v>
+        <v>2.496260713469085e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.482451575986322e-08</v>
+        <v>3.482451575986279e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.725895109165989e-08</v>
+        <v>3.725895109165944e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.049696289441199e-08</v>
+        <v>3.049696289441181e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.421125132388884e-08</v>
+        <v>3.421125132388847e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.234257064760025e-08</v>
+        <v>3.234257064759994e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.257479823691528e-08</v>
+        <v>4.257479823691478e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.683164666383397e-08</v>
+        <v>4.683164666383352e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.676219390201532e-08</v>
+        <v>3.676219390201497e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.413678599703559e-08</v>
+        <v>7.413678599703498e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.228125663232079e-08</v>
+        <v>3.228125663232073e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.222373055015938e-08</v>
+        <v>3.222373055015891e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.614304379503869e-08</v>
+        <v>5.614304379503842e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.150003163175226e-08</v>
+        <v>3.150003163175221e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.205280433854877e-08</v>
+        <v>3.205280433854854e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.527076534672912e-08</v>
+        <v>3.52707653467288e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.100128191962679e-08</v>
+        <v>4.100128191962635e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>3.621117719340277e-08</v>
+        <v>3.621117719340248e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.856915144734666e-08</v>
+        <v>3.85691514473462e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.087000087911456e-08</v>
+        <v>3.087000087911427e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>3.383443574674791e-08</v>
+        <v>3.383443574674823e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.366588749871667e-08</v>
+        <v>7.366588749871634e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.071660495119214e-08</v>
+        <v>3.071660495119217e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.880756129425936e-08</v>
+        <v>4.880756129425916e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.773073606119131e-08</v>
+        <v>2.773073606119104e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.549040579065976e-08</v>
+        <v>3.549040579065939e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.938916000246872e-08</v>
+        <v>3.938916000246838e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.400290941993535e-08</v>
+        <v>5.400290941993508e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.801806540400032e-08</v>
+        <v>6.801806540400008e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.045250073579702e-08</v>
+        <v>7.045250073579672e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.480349713533273e-08</v>
+        <v>6.480349713533247e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.779763546388897e-08</v>
+        <v>4.779763546388869e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.411225185239632e-08</v>
+        <v>6.411225185239604e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.576834788105239e-08</v>
+        <v>7.576834788105212e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.002519630797109e-08</v>
+        <v>8.00251963079708e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.995574354615241e-08</v>
+        <v>6.995574354615209e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.073303356411726e-07</v>
+        <v>1.073303356411724e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.547480627645807e-08</v>
+        <v>6.547480627645757e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.541728019426819e-08</v>
+        <v>6.541728019426791e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>9.465949970683971e-08</v>
+        <v>9.465949970683934e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.220573582351972e-08</v>
+        <v>7.220573582351923e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.391132428536916e-08</v>
+        <v>7.391132428536892e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.668058249312121e-08</v>
+        <v>7.66805824931211e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.419483156376389e-08</v>
+        <v>7.419483156376354e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>6.940472683753986e-08</v>
+        <v>6.940472683753972e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.176270109148375e-08</v>
+        <v>7.176270109148347e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.738153027339826e-08</v>
+        <v>6.738153027339799e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.158459796084653e-08</v>
+        <v>8.158459796084655e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.068580876459163e-07</v>
+        <v>1.06858087645916e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>7.149706380795712e-08</v>
+        <v>7.149706380795695e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.511613431933796e-08</v>
+        <v>7.511613431933754e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.127452626075785e-08</v>
+        <v>6.12745262607575e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.868395543479688e-08</v>
+        <v>6.868395543479667e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.540977975865927e-08</v>
+        <v>6.540977975865898e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.917026174681165e-07</v>
+        <v>1.917026174681148e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.880253654678997e-07</v>
+        <v>3.880253654678996e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.924669240404152e-07</v>
+        <v>1.92466924040415e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.923684831300556e-07</v>
+        <v>1.923684831300562e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.919212379580075e-07</v>
+        <v>1.919212379580074e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.91761950335334e-07</v>
+        <v>1.917619503353338e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.924489927757835e-07</v>
+        <v>1.924489927757827e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.920165552148339e-07</v>
+        <v>1.920165552148338e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.921305019550927e-07</v>
+        <v>1.921305019550922e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.918138089780576e-07</v>
+        <v>1.918138089780581e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.916462630189777e-07</v>
+        <v>1.916462630189778e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.918609574633404e-07</v>
+        <v>1.918609574633409e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.93206837304128e-07</v>
+        <v>1.932068373041279e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.00165285287101e-07</v>
+        <v>1.001652852871019e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.921236721353695e-07</v>
+        <v>1.921236721353687e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92258262759668e-07</v>
+        <v>1.922582627596681e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.922305306717811e-07</v>
+        <v>1.922305306717817e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.921091028702132e-07</v>
+        <v>1.921091028702131e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.919083543286904e-07</v>
+        <v>1.919083543286901e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.326076249591104e-07</v>
+        <v>4.326076249591128e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.920914675453778e-07</v>
+        <v>1.920914675453776e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.058355978286846e-07</v>
+        <v>3.058355978286841e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.922327820684068e-07</v>
+        <v>1.922327820684059e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.921698456719161e-07</v>
+        <v>1.921698456719157e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.697191647229169e-07</v>
+        <v>1.697191647229159e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.920174275105572e-07</v>
+        <v>1.920174275105563e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.918168961988407e-07</v>
+        <v>1.918168961988408e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.950851321122884e-07</v>
+        <v>1.951347007438103e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.253422895686063e-07</v>
+        <v>5.256792281615743e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.005590265181212e-07</v>
+        <v>2.008032308559888e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.998391989286724e-07</v>
+        <v>2.000563203872577e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.966553852528989e-07</v>
+        <v>1.967614657547551e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.955075912796633e-07</v>
+        <v>1.955720224944733e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.00450596588648e-07</v>
+        <v>2.006917762011224e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.973397739662496e-07</v>
+        <v>1.974698285872156e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.981398551867873e-07</v>
+        <v>1.9829759394533e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.958812290987462e-07</v>
+        <v>1.959594919007043e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.946854003892505e-07</v>
+        <v>1.947210114123069e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.962941113697647e-07</v>
+        <v>1.963875340275888e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.05839800732094e-07</v>
+        <v>2.062701383234007e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.485602033508471e-08</v>
+        <v>4.494548965330603e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.980781423112871e-07</v>
+        <v>1.982327088457683e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.990557481790724e-07</v>
+        <v>1.992465146257165e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.988769051600188e-07</v>
+        <v>1.990617513323656e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.979772832038234e-07</v>
+        <v>1.981289075088885e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.965638080607933e-07</v>
+        <v>1.966662258063532e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.951326549674432e-07</v>
+        <v>5.952921079384336e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.978443203992381e-07</v>
+        <v>1.979913302480232e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.028005949347705e-07</v>
+        <v>4.037373971165431e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.988801667218089e-07</v>
+        <v>1.990647497080983e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.984226176272983e-07</v>
+        <v>1.985904682258327e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.607086950148821e-07</v>
+        <v>1.608462087445686e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.973358316470883e-07</v>
+        <v>1.974651145105944e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.959530076852537e-07</v>
+        <v>1.960337415041075e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.36472304533367e-08</v>
+        <v>1.364723045333736e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.642197627059857e-08</v>
+        <v>2.642197627059932e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.228042478584301e-08</v>
+        <v>2.228042478584355e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.116848941827695e-08</v>
+        <v>2.116848941827798e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.611664945704941e-08</v>
+        <v>1.611664945704977e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.431742248302499e-08</v>
+        <v>1.431742248302505e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.207788290304019e-08</v>
+        <v>2.207788290304028e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.719330172100714e-08</v>
+        <v>1.719330172100659e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.856430380597977e-08</v>
+        <v>1.8564303805981e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.490318970874214e-08</v>
+        <v>1.49031897087428e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.301068102598649e-08</v>
+        <v>1.301068102598638e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.556017180292362e-08</v>
+        <v>1.556017180292472e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.063808547639732e-08</v>
+        <v>3.063808547639881e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.54535114533037e-08</v>
+        <v>1.545351145330416e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.840323661467511e-08</v>
+        <v>1.840323661467554e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.992349963087358e-08</v>
+        <v>1.992349963087375e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.961025294079989e-08</v>
+        <v>1.961025294079975e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.823867006254041e-08</v>
+        <v>1.823867006254098e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.597112293715054e-08</v>
+        <v>1.597112293715032e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.845177198374488e-08</v>
+        <v>1.84517719837449e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.859857868420311e-08</v>
+        <v>1.859857868420387e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.339919077825473e-08</v>
+        <v>5.339919077825553e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.963568350138113e-08</v>
+        <v>1.963568350138157e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.879968782724981e-08</v>
+        <v>1.879968782725033e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.76141673019244e-08</v>
+        <v>1.761416730192512e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.720315470247938e-08</v>
+        <v>1.720315470248093e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.500841182369274e-08</v>
+        <v>1.50084118236929e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.829038523257432e-08</v>
+        <v>3.829038523257206e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.622294016600641e-07</v>
+        <v>2.622294016600654e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.008290957770615e-07</v>
+        <v>2.008290957770629e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.722233576343637e-07</v>
+        <v>1.722233576343644e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>8.712133352983729e-08</v>
+        <v>8.712133352983624e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.962433569405892e-08</v>
+        <v>4.96243356940607e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.073762352607783e-07</v>
+        <v>2.073762352607759e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.08290862078046e-07</v>
+        <v>1.082908620780461e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.243178799055077e-07</v>
+        <v>1.243178799055073e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.180879872989584e-08</v>
+        <v>6.180879872989785e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.831341894130943e-08</v>
+        <v>2.831341894131008e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.79797870103401e-08</v>
+        <v>7.797978701033814e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.48635867941103e-07</v>
+        <v>3.486358679411042e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>6.644205300680902e-08</v>
+        <v>6.644205300680749e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.161491096573993e-07</v>
+        <v>1.161491096573997e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.518606970552726e-07</v>
+        <v>1.518606970552745e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.562093181005571e-07</v>
+        <v>1.562093181005599e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.148566166641666e-07</v>
+        <v>1.148566166641678e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>8.474122762657863e-08</v>
+        <v>8.474122762657542e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.231977867059936e-07</v>
+        <v>1.231977867059909e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.082138835443811e-07</v>
+        <v>1.082138835443815e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>7.465452665060183e-07</v>
+        <v>7.465452665060181e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.5002231622126e-07</v>
+        <v>1.500223162212597e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.331119872921079e-07</v>
+        <v>1.331119872921086e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.004083783289725e-07</v>
+        <v>1.004083783289731e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.031958523205406e-07</v>
+        <v>1.031958523205384e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.964085241441559e-08</v>
+        <v>6.964085241441749e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.026270687751613e-08</v>
+        <v>2.026270687751599e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.907852239841056e-08</v>
+        <v>2.907852239841036e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.889590121002225e-08</v>
+        <v>2.889590121002125e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.778396584245642e-08</v>
+        <v>2.778396584245706e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.877319558486142e-08</v>
+        <v>1.877319558486261e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.697396861083708e-08</v>
+        <v>1.697396861083842e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.473442903085223e-08</v>
+        <v>2.473442903085368e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.984984784881925e-08</v>
+        <v>1.98498478488198e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.517978023015907e-08</v>
+        <v>2.517978023016713e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.151866613292138e-08</v>
+        <v>2.151866613291946e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.962615745016585e-08</v>
+        <v>1.962615745016398e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.821671793073573e-08</v>
+        <v>1.821671793073495e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.32561959810361e-08</v>
+        <v>3.325619598103655e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.276585455555849e-08</v>
+        <v>2.276585455555847e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.570367069103419e-08</v>
+        <v>2.570367069103371e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.653897605505287e-08</v>
+        <v>2.653897605505744e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.22667990686119e-08</v>
+        <v>2.226679906861205e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.485414648671975e-08</v>
+        <v>2.485414648671574e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.862766906496267e-08</v>
+        <v>1.86276690649635e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.123341823515281e-08</v>
+        <v>2.123341823515257e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.521405510838242e-08</v>
+        <v>2.521405510837985e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.071551135200863e-08</v>
+        <v>6.071551135200914e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.229222962919322e-08</v>
+        <v>2.229222962919486e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.178540435732089e-08</v>
+        <v>2.178540435732071e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.422964372610383e-08</v>
+        <v>2.422964372609538e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.381863112665878e-08</v>
+        <v>2.381863112666787e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.764906867659916e-08</v>
+        <v>1.76490686766007e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.670890663734652e-08</v>
+        <v>1.670890663734792e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.948365245460837e-08</v>
+        <v>2.948365245460802e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.534210096985287e-08</v>
+        <v>2.534210096985435e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.42301656022868e-08</v>
+        <v>2.423016560228711e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.917832564105924e-08</v>
+        <v>1.917832564105968e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.737909866703485e-08</v>
+        <v>1.737909866703658e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.513955908705005e-08</v>
+        <v>2.51395590870501e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.025497790501702e-08</v>
+        <v>2.025497790501967e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.162597998998958e-08</v>
+        <v>2.162597998999023e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.796486589275204e-08</v>
+        <v>1.796486589275314e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.607235720999635e-08</v>
+        <v>1.607235720999685e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.86218479869335e-08</v>
+        <v>1.862184798693545e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.369976166040704e-08</v>
+        <v>3.369976166040882e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8515043764295e-08</v>
+        <v>1.851504376429757e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.146476892566636e-08</v>
+        <v>2.146476892566817e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.298517581488333e-08</v>
+        <v>2.298517581488461e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.267192912480971e-08</v>
+        <v>2.267192912481016e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.130034624655026e-08</v>
+        <v>2.130034624655394e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.903279912116039e-08</v>
+        <v>1.903279912116137e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.159509110138247e-08</v>
+        <v>2.159509110138457e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.166025486821294e-08</v>
+        <v>2.166025486821224e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.646086696226454e-08</v>
+        <v>5.646086696226804e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.269735968539085e-08</v>
+        <v>2.269735968539107e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.198646413485539e-08</v>
+        <v>2.198646413485574e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.067584348593422e-08</v>
+        <v>2.067584348593564e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.026483088648924e-08</v>
+        <v>2.026483088648784e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.807008800770246e-08</v>
+        <v>1.807008800770265e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.045696078104937e-08</v>
+        <v>2.045696078105022e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.877111673008605e-08</v>
+        <v>3.877111673008693e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>3.462956524533048e-08</v>
+        <v>3.462956524532948e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.056805738836288e-08</v>
+        <v>3.056805738836437e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.378935514080446e-08</v>
+        <v>2.378935514080594e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.781519571791696e-08</v>
+        <v>2.781519571791678e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.442702336252763e-08</v>
+        <v>3.442702336252824e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.954244218049471e-08</v>
+        <v>2.954244218049708e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.091344426546731e-08</v>
+        <v>3.091344426546792e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.72523301682297e-08</v>
+        <v>2.72523301682291e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.535982148547409e-08</v>
+        <v>2.535982148547462e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.790931226245285e-08</v>
+        <v>2.790931226245288e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.869325635616518e-08</v>
+        <v>3.869325635616715e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.468870244864772e-08</v>
+        <v>2.468870244864897e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.73491761673124e-08</v>
+        <v>2.734917616731326e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.564460944134343e-08</v>
+        <v>2.564460944134274e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.195939340028734e-08</v>
+        <v>3.195939340028785e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05878105220279e-08</v>
+        <v>3.058781052202874e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.832026339663813e-08</v>
+        <v>2.832026339663754e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.818873364758735e-08</v>
+        <v>2.818873364758839e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.939669166936599e-08</v>
+        <v>2.939669166936466e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.574941987343638e-08</v>
+        <v>6.574941987343675e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.586449124691345e-08</v>
+        <v>2.586449124691213e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.672421485892001e-08</v>
+        <v>3.672421485892076e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.432100024392352e-08</v>
+        <v>2.43210002439236e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.955229516196702e-08</v>
+        <v>2.955229516196567e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.31439293479609e-08</v>
+        <v>3.314392934796047e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.417848974197612e-08</v>
+        <v>4.417848974198003e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.592459002780264e-08</v>
+        <v>6.592459002780366e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.178303854304706e-08</v>
+        <v>6.178303854305292e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.860055327800939e-08</v>
+        <v>5.860055327801095e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.493783905116439e-08</v>
+        <v>3.493783905116235e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.382003899682509e-08</v>
+        <v>5.382003899682704e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.158049666024421e-08</v>
+        <v>6.158049666024738e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.669591547821138e-08</v>
+        <v>5.66959154782112e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.806691756318386e-08</v>
+        <v>5.806691756317389e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.440580346594621e-08</v>
+        <v>5.440580346594479e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.251329478319065e-08</v>
+        <v>5.25132947831983e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>5.506278556012777e-08</v>
+        <v>5.50627855601295e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.014069923360135e-08</v>
+        <v>7.014069923360025e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>5.792922400453055e-08</v>
+        <v>5.79292240045302e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>6.152554654430567e-08</v>
+        <v>6.152554654430724e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.942611614467359e-08</v>
+        <v>5.942611614467959e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>5.91128666980039e-08</v>
+        <v>5.911286669800187e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>5.774128381974457e-08</v>
+        <v>5.774128381974409e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>5.547373669435467e-08</v>
+        <v>5.547373669435356e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>5.807948586454496e-08</v>
+        <v>5.807948586454316e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.845394520161938e-08</v>
+        <v>6.845394520162372e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.290180453545876e-08</v>
+        <v>9.290180453545967e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>5.913829725858519e-08</v>
+        <v>5.913829725858521e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.842740170804973e-08</v>
+        <v>5.842740170805186e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.170785317316331e-08</v>
+        <v>5.17078531731655e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.670576845968357e-08</v>
+        <v>5.670576845968958e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.45110255808968e-08</v>
+        <v>5.451102558089992e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4035,25 +4035,25 @@
         <v>1.914242163806325e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.916200117395173e-07</v>
+        <v>1.916200117395174e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.915815909148844e-07</v>
+        <v>1.915815909148843e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.913742610371139e-07</v>
+        <v>1.91374261037114e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.919403978972843e-07</v>
+        <v>1.919403978972842e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.913732908535179e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.916572626889625e-07</v>
+        <v>1.916572626889626e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.912986136408562e-07</v>
+        <v>1.912986136408563e-07</v>
       </c>
       <c r="L2" t="n">
         <v>1.91345209418279e-07</v>
@@ -4065,40 +4065,40 @@
         <v>1.923425915917717e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.91129319430518e-08</v>
+        <v>9.911293194305169e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91659765194483e-07</v>
+        <v>1.916597651944829e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.917611109938484e-07</v>
+        <v>1.917611109938485e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.917279551173769e-07</v>
+        <v>1.917279551173771e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.916423715300256e-07</v>
+        <v>1.916423715300255e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.91484237719797e-07</v>
+        <v>1.914842377197971e-07</v>
       </c>
       <c r="U2" t="n">
         <v>4.317439663636271e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.917137749725428e-07</v>
+        <v>1.917137749725429e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.04318650728632e-07</v>
+        <v>3.043186507286318e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.916317377945245e-07</v>
+        <v>1.916317377945246e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.91545455211753e-07</v>
+        <v>1.915454552117532e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.685396850957725e-07</v>
+        <v>1.685396850957724e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.916804138249575e-07</v>
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.951099085500714e-07</v>
+        <v>1.951642678392208e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.258738634496659e-07</v>
+        <v>5.26236058038831e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.959368012019217e-07</v>
+        <v>1.960210412924579e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.973216437473881e-07</v>
+        <v>1.974542353763067e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.970644992002961e-07</v>
+        <v>1.971892748428004e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.955708376494608e-07</v>
+        <v>1.956414411618875e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.996520225952717e-07</v>
+        <v>1.998687518142513e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.955758979875637e-07</v>
+        <v>1.956473257080229e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.975938089996793e-07</v>
+        <v>1.977362947476372e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.950388272792135e-07</v>
+        <v>1.950911085634865e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.953681027316148e-07</v>
+        <v>1.954317596403016e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.959834498249451e-07</v>
+        <v>1.960698784879707e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.025018619940534e-07</v>
+        <v>2.028180074201302e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.306156185636354e-08</v>
+        <v>4.312226311876797e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.975957692815928e-07</v>
+        <v>1.977374560843734e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.983348702159217e-07</v>
+        <v>1.985042470435629e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.98121052522339e-07</v>
+        <v>1.98283032137192e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.974776615866215e-07</v>
+        <v>1.976156676729695e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.963703812584196e-07</v>
+        <v>1.964699214994158e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.955212835965032e-07</v>
+        <v>5.95738349239675e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.979770968291655e-07</v>
+        <v>1.981327947185726e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.990498081954571e-07</v>
+        <v>3.999031003142733e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.974164464469063e-07</v>
+        <v>1.975532598487239e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.968017744837352e-07</v>
+        <v>1.969161649349971e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.584590393947091e-07</v>
+        <v>1.585566804294536e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.977647871320209e-07</v>
+        <v>1.979131326226555e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.953564966543388e-07</v>
+        <v>1.954200681254437e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.354556144534682e-08</v>
+        <v>1.35455614453467e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.722411736272675e-08</v>
+        <v>2.722411736272667e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.484211081258005e-08</v>
+        <v>1.484211081257968e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.705370946149877e-08</v>
+        <v>1.705370946149885e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.661972857281848e-08</v>
+        <v>1.661972857281796e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.427784222694561e-08</v>
+        <v>1.427784222694543e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.067261849839039e-08</v>
+        <v>2.067261849839042e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.426688355692152e-08</v>
+        <v>1.426688355692138e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.755836169328429e-08</v>
+        <v>1.755836169328431e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.342337008669142e-08</v>
+        <v>1.342337008669144e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.394969082779848e-08</v>
+        <v>1.394969082779843e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.492614468607414e-08</v>
+        <v>1.492614468607425e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.521558129586585e-08</v>
+        <v>2.521558129586613e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.383468799023118e-08</v>
+        <v>1.383468799023096e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.750274302282836e-08</v>
+        <v>1.750274302282798e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.864749044803219e-08</v>
+        <v>1.864749044803233e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.827297957083041e-08</v>
+        <v>1.827297957083058e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.730627358130086e-08</v>
+        <v>1.730627358130053e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.552007944962449e-08</v>
+        <v>1.552007944962454e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.037179094264876e-08</v>
+        <v>2.037179094264828e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.867186702593335e-08</v>
+        <v>1.867186702593323e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.933580197032988e-08</v>
+        <v>4.93358019703302e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.71861606470572e-08</v>
+        <v>1.718616064705696e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.573721899002309e-08</v>
+        <v>1.573721899002285e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.549639060613286e-08</v>
+        <v>1.549639060613288e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.773597880287763e-08</v>
+        <v>1.773597880287747e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.392218202556745e-08</v>
+        <v>1.392218202556732e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.610121648456437e-08</v>
+        <v>4.610121648456455e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.845139101068688e-07</v>
+        <v>2.845139101068684e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>7.300574496402344e-08</v>
+        <v>7.300574496401696e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.05613292547987e-07</v>
+        <v>1.056132925479868e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.067820580569231e-07</v>
+        <v>1.067820580569232e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>5.813898159174504e-08</v>
+        <v>5.813898159174432e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.923007416228703e-07</v>
+        <v>1.923007416228705e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>6.415586806021722e-08</v>
+        <v>6.415586806021664e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.164056913967182e-07</v>
+        <v>1.164056913967173e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.711443788739931e-08</v>
+        <v>4.711443788739878e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.472302774929405e-08</v>
+        <v>5.472302774929374e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.583496477380449e-08</v>
+        <v>7.583496477380419e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.61955907149879e-07</v>
+        <v>2.619559071498782e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>5.039669127311126e-08</v>
+        <v>5.039669127310881e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.085818646042603e-07</v>
+        <v>1.085818646042593e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.370118520718842e-07</v>
+        <v>1.370118520718843e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.422125747275374e-07</v>
+        <v>1.422125747275375e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.082327828142058e-07</v>
+        <v>1.082327828142038e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>8.769397759291327e-08</v>
+        <v>8.769397759291304e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.671395327926855e-07</v>
+        <v>1.671395327926846e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.177839656116716e-07</v>
+        <v>1.1778396561167e-07</v>
       </c>
       <c r="W5" t="n">
         <v>6.861905942926527e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.137150760993168e-07</v>
+        <v>1.137150760993136e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.706382120039871e-08</v>
+        <v>9.706382120039615e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>7.398187105305902e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.23925316463998e-07</v>
+        <v>1.239253164639977e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.977827051889014e-08</v>
+        <v>5.977827051888943e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.604369060893107e-08</v>
+        <v>1.604369060893073e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.972224652631129e-08</v>
+        <v>2.97222465263108e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.104189091044759e-08</v>
+        <v>2.104189091044716e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.325348955936699e-08</v>
+        <v>2.325348955936625e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.911785773640218e-08</v>
+        <v>1.911785773640221e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.677597139052997e-08</v>
+        <v>1.677597139052941e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.687239859625862e-08</v>
+        <v>2.68723985962583e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.676501272050598e-08</v>
+        <v>1.676501272050544e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.37581417911521e-08</v>
+        <v>2.375814179115178e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.962315018455966e-08</v>
+        <v>1.962315018455891e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.644781999138287e-08</v>
+        <v>1.64478199913826e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.742427384965867e-08</v>
+        <v>1.742427384965816e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.770962047432293e-08</v>
+        <v>2.770962047432287e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.635505863052925e-08</v>
+        <v>1.635505863052904e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.440123117365619e-08</v>
+        <v>2.440123117365575e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.484727054590032e-08</v>
+        <v>2.48472705458998e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.447275966869888e-08</v>
+        <v>2.447275966869798e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.980440274488481e-08</v>
+        <v>1.980440274488465e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.171985954749216e-08</v>
+        <v>2.171985954749249e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.704591123319883e-08</v>
+        <v>2.704591123319821e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.116999618951742e-08</v>
+        <v>2.116999618951733e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.224743170077342e-08</v>
+        <v>5.224743170077296e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.968428981064155e-08</v>
+        <v>1.968428981064108e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.892635426756122e-08</v>
+        <v>1.89263542675609e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.799451976971738e-08</v>
+        <v>1.799451976971712e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.393575890074476e-08</v>
+        <v>2.3935758900745e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.642698717962874e-08</v>
+        <v>1.642698717962817e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.636726888458658e-08</v>
+        <v>1.636726888458655e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.004582480196679e-08</v>
+        <v>3.004582480196672e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.76638182518201e-08</v>
+        <v>1.766381825181968e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.98754169007388e-08</v>
+        <v>1.987541690073884e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.944143601205825e-08</v>
+        <v>1.944143601205802e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.709954966618568e-08</v>
+        <v>1.709954966618563e-08</v>
       </c>
       <c r="H7" t="n">
         <v>2.349432593763042e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.708859099616157e-08</v>
+        <v>1.708859099616158e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.038006913252432e-08</v>
+        <v>2.038006913252435e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.624507752593148e-08</v>
+        <v>1.624507752593149e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.677139826703853e-08</v>
+        <v>1.677139826703849e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.774785212531416e-08</v>
+        <v>1.774785212531452e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.803728873510612e-08</v>
+        <v>2.803728873510604e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.665632558794552e-08</v>
+        <v>1.66563255879449e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.032438062054177e-08</v>
+        <v>2.032438062054166e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.146919788727253e-08</v>
+        <v>2.146919788727233e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.109468701007044e-08</v>
+        <v>2.109468701007064e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.012798102054088e-08</v>
+        <v>2.012798102054053e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.834178688886456e-08</v>
+        <v>1.834178688886474e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.35201553834233e-08</v>
+        <v>2.35201553834232e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.149357446517339e-08</v>
+        <v>2.149357446517326e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.215750940957018e-08</v>
+        <v>5.215750940957001e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.000786808629699e-08</v>
+        <v>2.000786808629696e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.903326662194554e-08</v>
+        <v>1.903326662194521e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.831809804537293e-08</v>
+        <v>1.831809804537286e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.055768624211765e-08</v>
+        <v>2.055768624211755e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.674388946480799e-08</v>
+        <v>1.674388946480746e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.992210312872188e-08</v>
+        <v>1.992210312872191e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.873967591452199e-08</v>
+        <v>3.87396759145219e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.635766936437549e-08</v>
+        <v>2.635766936437504e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.583289312527022e-08</v>
+        <v>2.583289312527041e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.379686902157789e-08</v>
+        <v>2.379686902157779e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.685900940285771e-08</v>
+        <v>2.685900940285769e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.218817705018563e-08</v>
+        <v>3.218817705018573e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.578244210871668e-08</v>
+        <v>2.578244210871654e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.907392024507988e-08</v>
+        <v>2.907392024507956e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.49389286384867e-08</v>
+        <v>2.493892863848673e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.546524937959374e-08</v>
+        <v>2.546524937959379e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.64417032379124e-08</v>
+        <v>2.644170323791215e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.274754203201049e-08</v>
+        <v>3.274754203201013e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.246137598754203e-08</v>
+        <v>2.246137598754181e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.58610869168655e-08</v>
+        <v>2.586108691686554e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.40140980282579e-08</v>
+        <v>2.401409802825749e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.978853812262639e-08</v>
+        <v>2.978853812262579e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.882183213309641e-08</v>
+        <v>2.882183213309578e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.703563800142004e-08</v>
+        <v>2.703563800142005e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.973900741225154e-08</v>
+        <v>2.973900741225159e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.865667853515953e-08</v>
+        <v>2.865667853515933e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.085237047153014e-08</v>
+        <v>6.085237047152991e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.302376932567742e-08</v>
+        <v>2.302376932567691e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.264102572272715e-08</v>
+        <v>3.264102572272666e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.177747241399257e-08</v>
+        <v>2.177747241399242e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.925153735467303e-08</v>
+        <v>2.925153735467284e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.080587340056581e-08</v>
+        <v>3.080587340056543e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.103142062707783e-08</v>
+        <v>4.103142062707797e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.278463868168543e-08</v>
+        <v>6.27846386816851e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.040263213153918e-08</v>
+        <v>5.040263213153808e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.075063335242846e-08</v>
+        <v>5.075063335242826e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.356594706879782e-08</v>
+        <v>3.356594706879748e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.983836570046419e-08</v>
+        <v>4.983836570046374e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.623313981734909e-08</v>
+        <v>5.623313981734907e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.982740487587989e-08</v>
+        <v>4.982740487587996e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.311888301224299e-08</v>
+        <v>5.311888301224278e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.898389140565013e-08</v>
+        <v>4.898389140564985e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.95102121467571e-08</v>
+        <v>4.951021214675682e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>5.048666600503282e-08</v>
+        <v>5.048666600503271e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>6.077610261482477e-08</v>
+        <v>6.077610261482438e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>5.207114463717661e-08</v>
+        <v>5.207114463717555e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>5.632116922371259e-08</v>
+        <v>5.63211692237122e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.420801392155073e-08</v>
+        <v>5.420801392155059e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>5.383350088978894e-08</v>
+        <v>5.3833500889789e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>5.286679490025907e-08</v>
+        <v>5.286679490025886e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>5.108060076858369e-08</v>
+        <v>5.108060076858321e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>5.640665245428957e-08</v>
+        <v>5.640665245428914e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.355037690130552e-08</v>
+        <v>6.355037690130532e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.489632328928886e-08</v>
+        <v>8.489632328928853e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>5.274668196601569e-08</v>
+        <v>5.274668196601526e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.177208050166438e-08</v>
+        <v>5.177208050166354e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.618860953886758e-08</v>
+        <v>4.618860953886738e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.329650012183625e-08</v>
+        <v>5.329650012183587e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.948270334452616e-08</v>
+        <v>4.948270334452573e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.919039232469921e-07</v>
+        <v>1.919039232469922e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.867442059629415e-07</v>
@@ -4895,34 +4895,34 @@
         <v>1.929603303530226e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.920903450342481e-07</v>
+        <v>1.920903450342482e-07</v>
       </c>
       <c r="F2" t="n">
         <v>1.91918325729144e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.918116143141689e-07</v>
+        <v>1.918116143141691e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.925524688145519e-07</v>
+        <v>1.92552468814552e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.923847078979015e-07</v>
+        <v>1.923847078979016e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.921852070606703e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.935814665063054e-07</v>
+        <v>1.935814665063055e-07</v>
       </c>
       <c r="L2" t="n">
         <v>1.924409944731804e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.918418307412039e-07</v>
+        <v>1.91841830741204e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.933905813346992e-07</v>
+        <v>1.933905813346994e-07</v>
       </c>
       <c r="O2" t="n">
         <v>1.003505885607574e-07</v>
@@ -4931,40 +4931,40 @@
         <v>1.921175540319796e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.924175618319346e-07</v>
+        <v>1.924175618319347e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.921795071840345e-07</v>
+        <v>1.921795071840346e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.925169364745471e-07</v>
+        <v>1.925169364745473e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.921540030649079e-07</v>
+        <v>1.92154003064908e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.332570109708584e-07</v>
+        <v>4.332570109708585e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9192723328468e-07</v>
+        <v>1.919272332846801e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.056967473143483e-07</v>
+        <v>3.056967473143484e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.927149930512534e-07</v>
+        <v>1.927149930512536e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.922250556782617e-07</v>
+        <v>1.922250556782618e-07</v>
       </c>
       <c r="Z2" t="n">
         <v>1.695694688126469e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.92264260536484e-07</v>
+        <v>1.922642605364841e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91925301375964e-07</v>
+        <v>1.919253013759641e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.964471788429997e-07</v>
+        <v>1.965416309779068e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.168666521597127e-07</v>
+        <v>5.169063650352248e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.040175242434783e-07</v>
+        <v>2.04381516831329e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.977856597777182e-07</v>
+        <v>1.979273078730819e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.96565616816006e-07</v>
+        <v>1.966654289361903e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.957915672118061e-07</v>
+        <v>1.958629722325691e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.011206569436825e-07</v>
+        <v>2.013827591535034e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.999055570047228e-07</v>
+        <v>2.001237613734718e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.984563887618365e-07</v>
+        <v>1.986222904261788e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.083897656402929e-07</v>
+        <v>2.089107681491172e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.002558227708212e-07</v>
+        <v>2.004859210037247e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.960904827512322e-07</v>
+        <v>1.961737835232576e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.070615130955479e-07</v>
+        <v>2.075328231007163e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.585949345688972e-08</v>
+        <v>4.597865017659404e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.979672390289639e-07</v>
+        <v>1.981148378919212e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.001167880024791e-07</v>
+        <v>2.003424064502106e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.984424627962972e-07</v>
+        <v>1.986087792386739e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.007737408456074e-07</v>
+        <v>2.010221904265292e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.982443741442878e-07</v>
+        <v>1.98403702149616e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.996730791677747e-07</v>
+        <v>5.999898052052918e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.966129688125579e-07</v>
+        <v>1.967133899031721e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.018818483102208e-07</v>
+        <v>4.027846910180456e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.022567164410221e-07</v>
+        <v>2.025581306870426e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.987474943526335e-07</v>
+        <v>1.989237975954972e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.605926456705879e-07</v>
+        <v>1.607338387442705e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.990290435673037e-07</v>
+        <v>1.992151042453308e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.966539692361321e-07</v>
+        <v>1.967565801307436e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.590434211981727e-08</v>
+        <v>1.590434211981726e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.341402877284109e-08</v>
+        <v>1.341402877284119e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.783694635370894e-08</v>
+        <v>2.783694635370902e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.80100619651309e-08</v>
+        <v>1.801006196513099e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.606702478119011e-08</v>
+        <v>1.606702478119024e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.486167025937174e-08</v>
+        <v>1.486167025937193e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.322996265110598e-08</v>
+        <v>2.322996265110603e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.133502592370475e-08</v>
+        <v>2.133502592370485e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.916388470477777e-08</v>
+        <v>1.916388470477784e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.485296494178645e-08</v>
+        <v>3.48529649417865e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.197080868458299e-08</v>
+        <v>2.19708086845831e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.533957026040713e-08</v>
+        <v>1.533957026040717e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.269682911697681e-08</v>
+        <v>3.269682911697683e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.702565428855794e-08</v>
+        <v>1.702565428855789e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.831740011126585e-08</v>
+        <v>1.831740011126589e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.170612622216567e-08</v>
+        <v>2.170612622216565e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.901718946358502e-08</v>
+        <v>1.901718946358508e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>2.282860852506688e-08</v>
+        <v>2.282860852506699e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.872910870557539e-08</v>
+        <v>1.872910870557555e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.554478131248605e-08</v>
+        <v>2.554478131248612e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.671605798296248e-08</v>
+        <v>1.671605798296282e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.210596970951934e-08</v>
+        <v>5.210596970951935e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>2.506574866949123e-08</v>
+        <v>2.506574866949122e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.92030081617489e-08</v>
+        <v>1.920300816174901e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.800952934041511e-08</v>
+        <v>1.800952934041519e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.997451756797151e-08</v>
+        <v>1.997451756797153e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.620950027735559e-08</v>
+        <v>1.620950027735561e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.635197002561421e-08</v>
+        <v>7.635197002561435e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.593606907850649e-08</v>
+        <v>3.593606907850656e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.190548505974942e-07</v>
+        <v>3.19054850597493e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.206044507924777e-07</v>
+        <v>1.206044507924779e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>8.812992787893689e-08</v>
+        <v>8.812992787893672e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.841793176537707e-08</v>
+        <v>5.841793176537766e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.397664065998412e-07</v>
+        <v>2.397664065998409e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.940476726133209e-07</v>
+        <v>1.940476726133207e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.374396649552537e-07</v>
+        <v>1.37439664955254e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>4.178777058653165e-07</v>
+        <v>4.178777058653164e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.77452552148807e-07</v>
+        <v>1.774525521488071e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>7.248522964372888e-08</v>
+        <v>7.248522964372891e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.960769572488402e-07</v>
+        <v>3.960769572488416e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>9.378113926831831e-08</v>
+        <v>9.378113926831763e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.194009773772179e-07</v>
+        <v>1.19400977377219e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.881343248886499e-07</v>
+        <v>1.881343248886498e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.510194953701332e-07</v>
+        <v>1.51019495370134e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.802775040177303e-07</v>
+        <v>1.802775040177306e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.366381938618614e-07</v>
+        <v>1.366381938618617e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.574124749947623e-07</v>
+        <v>2.574124749947616e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>8.15590447446971e-08</v>
+        <v>8.155904474469735e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>7.692646107764856e-07</v>
+        <v>7.692646107764867e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.611940872607636e-07</v>
+        <v>2.611940872607638e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.495964164596302e-07</v>
+        <v>1.495964164596296e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.106246262414643e-07</v>
+        <v>1.106246262414641e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.589384557197868e-07</v>
+        <v>1.589384557197867e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.303008596277018e-08</v>
+        <v>9.303008596277032e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5241,82 +5241,82 @@
         <v>1.858766577711818e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.609735243014214e-08</v>
+        <v>1.609735243014212e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.477226532818673e-08</v>
+        <v>3.477226532818697e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.494538093960873e-08</v>
+        <v>2.494538093960895e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.87503484384911e-08</v>
+        <v>1.875034843849116e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.754499391667282e-08</v>
+        <v>1.754499391667287e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.016528162558379e-08</v>
+        <v>3.0165281625584e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.827034489818267e-08</v>
+        <v>2.827034489818283e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.184720836207853e-08</v>
+        <v>2.184720836207876e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.178828391626438e-08</v>
+        <v>4.178828391626449e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.465413234188408e-08</v>
+        <v>2.465413234188404e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.227488923488488e-08</v>
+        <v>2.227488923488514e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.53588588296687e-08</v>
+        <v>3.535885882966976e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.484621058154617e-08</v>
+        <v>2.48462105815464e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.613155726887915e-08</v>
+        <v>2.613155726887925e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.864144519664338e-08</v>
+        <v>2.864144519664363e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.595250843806293e-08</v>
+        <v>2.595250843806304e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.551193218236785e-08</v>
+        <v>2.551193218236792e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.141243236287647e-08</v>
+        <v>2.141243236287648e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.855677746726105e-08</v>
+        <v>2.855677746726115e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.365137695744021e-08</v>
+        <v>2.365137695744079e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.993060328647737e-08</v>
+        <v>5.993060328647741e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.774907232679215e-08</v>
+        <v>2.774907232679214e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.244636049230037e-08</v>
+        <v>2.244636049230011e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.06928529977161e-08</v>
+        <v>2.069285299771611e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.690983654244931e-08</v>
+        <v>2.69098365424495e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.889868729567677e-08</v>
+        <v>1.889868729567693e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.916780034281226e-08</v>
+        <v>1.916780034281239e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.667748699583624e-08</v>
+        <v>1.667748699583633e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.110040457670407e-08</v>
+        <v>3.110040457670415e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.127352018812605e-08</v>
+        <v>2.127352018812613e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.933048300418535e-08</v>
+        <v>1.933048300418537e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.812512848236698e-08</v>
+        <v>1.812512848236708e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.649342087410113e-08</v>
+        <v>2.649342087410117e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.459848414669988e-08</v>
+        <v>2.459848414669999e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.242734292777287e-08</v>
+        <v>2.242734292777297e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.811642316478157e-08</v>
+        <v>3.811642316478163e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.523426690757818e-08</v>
+        <v>2.523426690757824e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.860302848340229e-08</v>
+        <v>1.86030284834023e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.596028733997193e-08</v>
+        <v>3.596028733997198e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.028899705870138e-08</v>
+        <v>2.028899705870142e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.158074288140924e-08</v>
+        <v>2.158074288140941e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.49695844451607e-08</v>
+        <v>2.496958444516079e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.228064768658009e-08</v>
+        <v>2.228064768658022e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.609206674806202e-08</v>
+        <v>2.609206674806214e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.199256692857066e-08</v>
+        <v>2.199256692857069e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.904420630305407e-08</v>
+        <v>2.904420630305413e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.997951620595781e-08</v>
+        <v>1.997951620595796e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.536942793251446e-08</v>
+        <v>5.536942793251448e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.832920689248626e-08</v>
+        <v>2.832920689248636e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.279513888221816e-08</v>
+        <v>2.279513888221824e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.127298756341021e-08</v>
+        <v>2.127298756341032e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.323797579096658e-08</v>
+        <v>2.323797579096668e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.947295850035066e-08</v>
+        <v>1.947295850035075e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.33055834880284e-08</v>
+        <v>2.330558348802853e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.688209762524016e-08</v>
+        <v>2.688209762524023e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.130501520610796e-08</v>
+        <v>4.130501520610806e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.82477241461754e-08</v>
+        <v>2.824772414617544e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.441340696454564e-08</v>
+        <v>2.441340696454574e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.958773531079747e-08</v>
+        <v>2.958773531079758e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.669803150350499e-08</v>
+        <v>3.669803150350508e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.480309477610383e-08</v>
+        <v>3.480309477610388e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.263195355717668e-08</v>
+        <v>3.263195355717688e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.832103379418552e-08</v>
+        <v>4.832103379418553e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.543887753698213e-08</v>
+        <v>3.543887753698214e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.880763911283535e-08</v>
+        <v>2.880763911283539e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.146209170584682e-08</v>
+        <v>4.146209170584704e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.708328886242645e-08</v>
+        <v>2.708328886242646e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.805824308458399e-08</v>
+        <v>2.805824308458411e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.791509752615129e-08</v>
+        <v>2.791509752615142e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.248525831598402e-08</v>
+        <v>3.24852583159841e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>3.629667737746592e-08</v>
+        <v>3.629667737746602e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.219717755797449e-08</v>
+        <v>3.219717755797458e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.630862993695804e-08</v>
+        <v>3.63086299369582e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.844682751920963e-08</v>
+        <v>2.844682751920973e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.557523084791625e-08</v>
+        <v>6.557523084791631e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.183075675549501e-08</v>
+        <v>3.183075675549499e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.890910572791391e-08</v>
+        <v>3.890910572791407e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.529807627489209e-08</v>
+        <v>2.529807627489205e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.344258642037046e-08</v>
+        <v>3.344258642037057e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.601487771907932e-08</v>
+        <v>3.601487771907939e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.236964832141087e-08</v>
+        <v>5.236964832141097e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.05577536318783e-08</v>
+        <v>6.055775363187841e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.498067121274613e-08</v>
+        <v>7.498067121274627e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.268925463474552e-08</v>
+        <v>6.268925463474559e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.859407465158056e-08</v>
+        <v>3.85940746515806e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.200539938286797e-08</v>
+        <v>6.200539938286803e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.037368751014304e-08</v>
+        <v>7.037368751014326e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>6.8478750782742e-08</v>
+        <v>6.847875078274207e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.630760956381493e-08</v>
+        <v>6.630760956381507e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.199668980082369e-08</v>
+        <v>8.199668980082371e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.911453354362019e-08</v>
+        <v>6.911453354362033e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.248329511944431e-08</v>
+        <v>6.248329511944438e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.984055397601388e-08</v>
+        <v>7.984055397601408e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>6.77081987861687e-08</v>
+        <v>6.770819878616872e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>6.976957623690105e-08</v>
+        <v>6.976957623690124e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.884985534566164e-08</v>
+        <v>6.884985534566175e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>6.616091432262224e-08</v>
+        <v>6.616091432262226e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>6.997233338410409e-08</v>
+        <v>6.997233338410422e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>6.587283356461272e-08</v>
+        <v>6.587283356461279e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.301717866899738e-08</v>
+        <v>7.301717866899743e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.618245339854735e-08</v>
+        <v>7.618245339854745e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.924969456855651e-08</v>
+        <v>9.924969456855655e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.220947352852831e-08</v>
+        <v>7.220947352852846e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.667540551826036e-08</v>
+        <v>6.667540551826034e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.871511900441922e-08</v>
+        <v>5.871511900441921e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.711824242700867e-08</v>
+        <v>6.711824242700877e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.335322513639273e-08</v>
+        <v>6.335322513639284e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.909473009578243e-07</v>
+        <v>1.90947300957824e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.860542864277071e-07</v>
+        <v>3.86054286427707e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.913113172479399e-07</v>
+        <v>1.913113172479397e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.910290418615062e-07</v>
+        <v>1.910290418615061e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.909806302831251e-07</v>
+        <v>1.90980630283125e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.913214411825556e-07</v>
+        <v>1.913214411825555e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.917507664924305e-07</v>
+        <v>1.917507664924304e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.911594333465388e-07</v>
+        <v>1.911594333465385e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.913191809057546e-07</v>
+        <v>1.913191809057545e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.911926993689487e-07</v>
+        <v>1.911926993689484e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.910649302121804e-07</v>
+        <v>1.910649302121802e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.910928953848861e-07</v>
+        <v>1.910928953848859e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.914118440642808e-07</v>
+        <v>1.914118440642805e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.855863676726074e-08</v>
+        <v>9.855863676726054e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.911529523784736e-07</v>
+        <v>1.911529523784734e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.910794744400206e-07</v>
+        <v>1.910794744400204e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.911569953353581e-07</v>
+        <v>1.91156995335358e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.914868180225826e-07</v>
+        <v>1.914868180225824e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.910664271892811e-07</v>
+        <v>1.91066427189281e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.303260855644672e-07</v>
+        <v>4.303260855644671e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.913120451897072e-07</v>
+        <v>1.91312045189707e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.02515768605565e-07</v>
+        <v>3.025157686055649e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.915765036039019e-07</v>
+        <v>1.915765036039017e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.911099075733016e-07</v>
+        <v>1.911099075733013e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.679758073360773e-07</v>
+        <v>1.679758073360772e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.91844625633212e-07</v>
+        <v>1.918446256332119e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.909002319868467e-07</v>
+        <v>1.909002319868465e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.943343136589895e-07</v>
+        <v>1.943711179524451e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.169470436610452e-07</v>
+        <v>5.17009856875194e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.969337693782488e-07</v>
+        <v>1.970634579925519e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.949192063292477e-07</v>
+        <v>1.949765458404119e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.945773112446526e-07</v>
+        <v>1.946232093300308e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.969820611636428e-07</v>
+        <v>1.971124784966369e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.000993623317697e-07</v>
+        <v>2.003422261632648e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.958556311408346e-07</v>
+        <v>1.959469059575283e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.969769760500946e-07</v>
+        <v>1.971075189369901e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.960833624222049e-07</v>
+        <v>1.961828001218911e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.951690034438815e-07</v>
+        <v>1.952355841884208e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.954304206191458e-07</v>
+        <v>1.955072086297788e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.976468624503707e-07</v>
+        <v>1.978014596193533e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.238547601969503e-08</v>
+        <v>4.244775113794795e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95794989747651e-07</v>
+        <v>1.958830545659574e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.952743335329274e-07</v>
+        <v>1.953449887637189e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.958407640535385e-07</v>
+        <v>1.959315896970409e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.981503856100484e-07</v>
+        <v>1.983225898485249e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95188827911251e-07</v>
+        <v>1.952563671212824e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.898522867952386e-07</v>
+        <v>5.899066871692062e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.969209551089195e-07</v>
+        <v>1.9704915163538e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.91032868350647e-07</v>
+        <v>3.916478895791407e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.98819917331716e-07</v>
+        <v>1.990167655457724e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.954977977579234e-07</v>
+        <v>1.955759242605905e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.578572808695571e-07</v>
+        <v>1.579604714518529e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.007414382446396e-07</v>
+        <v>2.010048276260698e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.940458325313099e-07</v>
+        <v>1.940728504067999e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.249934958281884e-08</v>
+        <v>1.249934958281891e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.363920556398436e-08</v>
+        <v>1.36392055639843e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.661108103544233e-08</v>
+        <v>1.661108103544214e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.342265069257992e-08</v>
+        <v>1.342265069257993e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.287581964434023e-08</v>
+        <v>1.287581964434013e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.672543553416695e-08</v>
+        <v>1.672543553416684e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.157486240860471e-08</v>
+        <v>2.157486240860462e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.489548249907039e-08</v>
+        <v>1.489548249907015e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.678251512256211e-08</v>
+        <v>1.678251512256184e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.527123752531651e-08</v>
+        <v>1.52712375253163e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.382802612290218e-08</v>
+        <v>1.382802612290199e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.424643878191326e-08</v>
+        <v>1.424643878191321e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.774657767063317e-08</v>
+        <v>1.77465776706328e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.365270174788396e-08</v>
+        <v>1.365270174788384e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.482227698338169e-08</v>
+        <v>1.482227698338159e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.399230986703285e-08</v>
+        <v>1.399230986703274e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.486794404124353e-08</v>
+        <v>1.48679440412434e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.859344301937688e-08</v>
+        <v>1.859344301937694e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.384493516789957e-08</v>
+        <v>1.384493516789932e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.296034328001928e-08</v>
+        <v>1.296034328001923e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.716935092504123e-08</v>
+        <v>1.716935092504103e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.840397162241914e-08</v>
+        <v>3.840397162241894e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.960648291778417e-08</v>
+        <v>1.9606482917784e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.401313464831527e-08</v>
+        <v>1.401313464831515e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.549373052065087e-08</v>
+        <v>1.549373052065092e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.263504458106796e-08</v>
+        <v>2.263504458106785e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.204398954135539e-08</v>
+        <v>1.204398954135524e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.280193240333591e-08</v>
+        <v>3.280193240333592e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.497314255220958e-08</v>
+        <v>5.497314255220943e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.06277829029128e-07</v>
+        <v>1.062778290291276e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>4.991132461114325e-08</v>
+        <v>4.991132461114299e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.211608429402865e-08</v>
+        <v>4.211608429402864e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.588203436812853e-08</v>
+        <v>9.588203436812873e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.092139452718082e-07</v>
+        <v>2.092139452718083e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.897389022119145e-08</v>
+        <v>7.897389022119111e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.012377072833716e-07</v>
+        <v>1.012377072833712e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.059815168731026e-08</v>
+        <v>8.059815168730982e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.379559998389618e-08</v>
+        <v>5.3795599983896e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.43674624869362e-08</v>
+        <v>6.436746248693571e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.240953718102561e-07</v>
+        <v>1.240953718102563e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>5.079968919692547e-08</v>
+        <v>5.079968919692549e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.022374184594773e-08</v>
+        <v>7.022374184594763e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.749266694282195e-08</v>
+        <v>5.74926669428218e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.97995524695795e-08</v>
+        <v>7.979955246957936e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.227133758326411e-07</v>
+        <v>1.227133758326409e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>5.883148000373416e-08</v>
+        <v>5.883148000373375e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.613908460337305e-08</v>
+        <v>4.613908460337259e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>9.764027123011448e-08</v>
+        <v>9.764027123011419e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.661594131620692e-07</v>
+        <v>4.661594131620686e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.558878439014014e-07</v>
+        <v>1.558878439014011e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.681739375257312e-08</v>
+        <v>6.681739375257279e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.913393923445594e-08</v>
+        <v>7.913393923445573e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.135576169130126e-07</v>
+        <v>2.135576169130122e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.785441971593828e-08</v>
+        <v>2.785441971593769e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.815492286707308e-08</v>
+        <v>1.815492286707289e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.56369282702005e-08</v>
+        <v>1.56369282702001e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.860880374165842e-08</v>
+        <v>1.86088037416579e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.542037339879625e-08</v>
+        <v>1.542037339879576e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.85313929285944e-08</v>
+        <v>1.853139292859427e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.238100881842095e-08</v>
+        <v>2.238100881842082e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.723043569285874e-08</v>
+        <v>2.723043569285859e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.055105578332439e-08</v>
+        <v>2.055105578332414e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.243808840681613e-08</v>
+        <v>2.243808840681599e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.092681080957054e-08</v>
+        <v>2.092681080957045e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.582574882911826e-08</v>
+        <v>1.582574882911853e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.990201206616741e-08</v>
+        <v>1.990201206616738e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.973355122133488e-08</v>
+        <v>1.973355122133453e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.004666150950757e-08</v>
+        <v>2.004666150950714e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.663039559192725e-08</v>
+        <v>1.663039559192705e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.964788315128705e-08</v>
+        <v>1.964788315128688e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.686566674745958e-08</v>
+        <v>1.686566674745925e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.424901630363115e-08</v>
+        <v>2.424901630363091e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.584265787411576e-08</v>
+        <v>1.584265787411573e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.528099744529471e-08</v>
+        <v>1.528099744529456e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.91670736312575e-08</v>
+        <v>1.916707363125725e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>4.074811813854292e-08</v>
+        <v>4.074811813854271e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.52620562020383e-08</v>
+        <v>2.526205620203837e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65303198229942e-08</v>
+        <v>1.653031982299371e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.74914532268672e-08</v>
+        <v>1.749145322686672e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.829061786532201e-08</v>
+        <v>2.829061786532183e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.406172814306377e-08</v>
+        <v>1.406172814306346e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.515762904646682e-08</v>
+        <v>1.515762904646659e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.629748502763218e-08</v>
+        <v>1.629748502763196e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.926936049909009e-08</v>
+        <v>1.92693604990899e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.608093015622794e-08</v>
+        <v>1.608093015622756e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.553409910798824e-08</v>
+        <v>1.553409910798799e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.938371499781472e-08</v>
+        <v>1.93837149978145e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.423314187225251e-08</v>
+        <v>2.423314187225228e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.755376196271817e-08</v>
+        <v>1.755376196271799e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.944079458620993e-08</v>
+        <v>1.944079458620967e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.792951698896433e-08</v>
+        <v>1.792951698896401e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.648630558655e-08</v>
+        <v>1.648630558654956e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.690471824556132e-08</v>
+        <v>1.690471824556097e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.040485713428107e-08</v>
+        <v>2.040485713428075e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.631087582098551e-08</v>
+        <v>1.631087582098511e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.748045105648327e-08</v>
+        <v>1.748045105648296e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.665058933068082e-08</v>
+        <v>1.665058933068058e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.75262235048913e-08</v>
+        <v>1.752622350489102e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.125172248302487e-08</v>
+        <v>2.125172248302461e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.650321463154736e-08</v>
+        <v>1.650321463154704e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.584402236662277e-08</v>
+        <v>1.584402236662239e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.982763038868918e-08</v>
+        <v>1.982763038868876e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.106225108606698e-08</v>
+        <v>4.106225108606678e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.226476238143211e-08</v>
+        <v>2.226476238143172e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.699434557102243e-08</v>
+        <v>1.699434557102213e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.815200998429879e-08</v>
+        <v>1.815200998429859e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.529332404471574e-08</v>
+        <v>2.52933240447155e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47022690050033e-08</v>
+        <v>1.470226900500308e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.845226265489709e-08</v>
+        <v>1.845226265489701e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.437494179791633e-08</v>
+        <v>2.437494179791625e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.734681726937425e-08</v>
+        <v>2.734681726937401e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.161167467979282e-08</v>
+        <v>2.161167467979247e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.957384066542872e-08</v>
+        <v>1.957384066542817e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.845292130691453e-08</v>
+        <v>2.845292130691436e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.231059864253666e-08</v>
+        <v>3.231059864253658e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.563121873300232e-08</v>
+        <v>2.56312187330021e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.751825135649404e-08</v>
+        <v>2.751825135649342e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.600697375924847e-08</v>
+        <v>2.600697375924824e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.456376235683412e-08</v>
+        <v>2.456376235683352e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.498217501584276e-08</v>
+        <v>2.498217501584274e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.477482580184478e-08</v>
+        <v>2.477482580184456e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.169979979467217e-08</v>
+        <v>2.169979979467194e-08</v>
       </c>
       <c r="P8" t="n">
         <v>2.261963029769783e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.900528902853648e-08</v>
+        <v>1.900528902853656e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.560368027517543e-08</v>
+        <v>2.560368027517527e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.932917925330877e-08</v>
+        <v>2.93291792533089e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.458067140183148e-08</v>
+        <v>2.458067140183097e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.160907571199658e-08</v>
+        <v>2.160907571199646e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.651459175132612e-08</v>
+        <v>2.651459175132575e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.914064780527514e-08</v>
+        <v>4.914064780527473e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.505781731780174e-08</v>
+        <v>2.505781731780151e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.969809070069925e-08</v>
+        <v>2.969809070069878e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.135780019798845e-08</v>
+        <v>2.135780019798833e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.337078081499985e-08</v>
+        <v>3.337078081499981e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.777578448926613e-08</v>
+        <v>2.777578448926566e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.281658349934973e-08</v>
+        <v>4.281658349935036e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.277625414686275e-08</v>
+        <v>5.27762541468637e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.574812961832068e-08</v>
+        <v>5.574812961832153e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.052412413950364e-08</v>
+        <v>5.052412413950424e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.168078467877108e-08</v>
+        <v>3.16807846787714e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.586248686491127e-08</v>
+        <v>5.586248686491201e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.071191099148307e-08</v>
+        <v>6.071191099148403e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.403253108194874e-08</v>
+        <v>5.403253108194961e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.591956370544067e-08</v>
+        <v>5.59195637054413e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.440828610819488e-08</v>
+        <v>5.440828610819577e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.296507470578056e-08</v>
+        <v>5.296507470578128e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>5.338348736479188e-08</v>
+        <v>5.338348736479267e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>5.688362625351167e-08</v>
+        <v>5.688362625351252e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>5.57126290211315e-08</v>
+        <v>5.571262902113234e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>5.751787962601899e-08</v>
+        <v>5.751787962602001e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.312936119777732e-08</v>
+        <v>5.312936119777809e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>5.400499262412185e-08</v>
+        <v>5.400499262412274e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>5.773049160225546e-08</v>
+        <v>5.773049160225634e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>5.298198375077802e-08</v>
+        <v>5.298198375077882e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>5.242032332195697e-08</v>
+        <v>5.242032332195775e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.648427952987235e-08</v>
+        <v>6.648427952987314e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.754102020529756e-08</v>
+        <v>7.75410202052985e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>5.874353150066267e-08</v>
+        <v>5.874353150066345e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.347311469025305e-08</v>
+        <v>5.347311469025381e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.931321623938931e-08</v>
+        <v>4.931321623939003e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.177209316394628e-08</v>
+        <v>6.177209316394725e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.118103812423392e-08</v>
+        <v>5.118103812423483e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6609,16 +6609,16 @@
         <v>1.906297950100281e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.856192805237958e-07</v>
+        <v>3.856192805237957e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.909451165364546e-07</v>
+        <v>1.909451165364545e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.906686181788065e-07</v>
+        <v>1.906686181788064e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.906721446591395e-07</v>
+        <v>1.906721446591393e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.908644736575054e-07</v>
@@ -6627,64 +6627,64 @@
         <v>1.913180623074892e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.907951014782932e-07</v>
+        <v>1.907951014782931e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.909262211197084e-07</v>
+        <v>1.909262211197086e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.907708535664785e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.907088379525224e-07</v>
+        <v>1.907088379525225e-07</v>
       </c>
       <c r="M2" t="n">
         <v>1.908212218252619e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.910232813872204e-07</v>
+        <v>1.910232813872203e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.789289591782493e-08</v>
+        <v>9.789289591782482e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.907172059165375e-07</v>
+        <v>1.907172059165374e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.906927725293583e-07</v>
+        <v>1.906927725293584e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.907380475503118e-07</v>
+        <v>1.907380475503117e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.910020727431125e-07</v>
+        <v>1.910020727431124e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.907833225120918e-07</v>
+        <v>1.907833225120917e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.297068706187978e-07</v>
+        <v>4.297068706187977e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.911509576062785e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.01210107216892e-07</v>
+        <v>3.012101072168919e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.912635102495924e-07</v>
+        <v>1.912635102495923e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.907054400551605e-07</v>
+        <v>1.907054400551604e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.673089909544723e-07</v>
+        <v>1.673089909544722e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.914881136562466e-07</v>
+        <v>1.914881136562468e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.906476683123099e-07</v>
+        <v>1.906476683123098e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.941569811595365e-07</v>
+        <v>1.941945462756866e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.162005078576067e-07</v>
+        <v>5.162467494195842e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.96412063943211e-07</v>
+        <v>1.965301878946984e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.944351313516356e-07</v>
+        <v>1.944824600554906e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.944655271488829e-07</v>
+        <v>1.945145406244896e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.958216607180166e-07</v>
+        <v>1.959179517529965e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>1.990942773444502e-07</v>
+        <v>1.993085077288637e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.953448304430143e-07</v>
+        <v>1.954249977372233e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.962681126390551e-07</v>
+        <v>1.963805911733933e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.951663780326337e-07</v>
+        <v>1.952401544672428e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.947194723305968e-07</v>
+        <v>1.947771214992716e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.955706455365465e-07</v>
+        <v>1.95659373972362e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.969673702570947e-07</v>
+        <v>1.971047892751145e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.139686336545568e-08</v>
+        <v>4.144904805296422e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.947768986119036e-07</v>
+        <v>1.948362142625622e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.94607965013732e-07</v>
+        <v>1.946618877293514e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.949385711771833e-07</v>
+        <v>1.950043460068473e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.96798195145754e-07</v>
+        <v>1.969292242909109e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.952587438244081e-07</v>
+        <v>1.953358268631215e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.898870184740881e-07</v>
+        <v>5.899750265939496e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.978561728444744e-07</v>
+        <v>1.980243097350324e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.866720986385606e-07</v>
+        <v>3.871695674401959e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.986710390501769e-07</v>
+        <v>1.988698304075902e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.947004552869399e-07</v>
+        <v>1.947574151651617e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.564864784941785e-07</v>
+        <v>1.565621115548564e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.00287454886131e-07</v>
+        <v>2.005417890851346e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.943171945047057e-07</v>
+        <v>1.943608264564911e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.235260598252592e-08</v>
+        <v>1.235260598252595e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.271895377530702e-08</v>
+        <v>1.271895377530709e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.591430767858019e-08</v>
+        <v>1.591430767858029e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.279113153341716e-08</v>
+        <v>1.279113153341703e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.283096475103846e-08</v>
+        <v>1.283096475103861e-08</v>
       </c>
       <c r="G4" t="n">
         <v>1.500340926329267e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.012690172594796e-08</v>
+        <v>2.012690172594791e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.421981858631259e-08</v>
+        <v>1.421981858631262e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.578518815115353e-08</v>
+        <v>1.578518815115358e-08</v>
       </c>
       <c r="K4" t="n">
         <v>1.39459272677746e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.324543237954925e-08</v>
+        <v>1.324543237954935e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.459287808161997e-08</v>
+        <v>1.459287808162001e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.67972156255895e-08</v>
+        <v>1.679721562558963e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.301532326310219e-08</v>
+        <v>1.301532326310217e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.333995238255232e-08</v>
+        <v>1.33399523825523e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.306396603445117e-08</v>
+        <v>1.306396603445124e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.357536822365791e-08</v>
+        <v>1.357536822365793e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.655765423393156e-08</v>
+        <v>1.655765423393161e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.408676974447492e-08</v>
+        <v>1.408676974447505e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43189131646318e-08</v>
+        <v>1.431891316463184e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.880087134039007e-08</v>
+        <v>1.880087134039018e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.295368211529193e-08</v>
+        <v>3.295368211529189e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.951071113681703e-08</v>
+        <v>1.951071113681706e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.291395938204392e-08</v>
+        <v>1.291395938204403e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.406893899810104e-08</v>
+        <v>1.406893899810109e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.204770993764998e-08</v>
+        <v>2.204770993765007e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.26004491921721e-08</v>
+        <v>1.260044919217208e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.447325312567575e-08</v>
+        <v>3.447325312567578e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.339627213578297e-08</v>
+        <v>4.339627213578302e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.986063933569861e-08</v>
+        <v>9.986063933569857e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.278240289523096e-08</v>
+        <v>4.278240289523076e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.619574751797771e-08</v>
+        <v>4.619574751797783e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.60537545060726e-08</v>
+        <v>7.605375450607267e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.849809937736945e-07</v>
+        <v>1.849809937736942e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.166906487561581e-08</v>
+        <v>7.166906487561579e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.145743010028234e-08</v>
+        <v>9.145743010028246e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.40296162050188e-08</v>
+        <v>6.402961620501891e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.941330677683336e-08</v>
+        <v>4.94133067768334e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.671465965043745e-08</v>
+        <v>7.671465965043757e-08</v>
       </c>
       <c r="N5" t="n">
         <v>1.141496045286518e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>4.475395301354928e-08</v>
+        <v>4.475395301354935e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.989505224926234e-08</v>
+        <v>4.989505224926221e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.783743123702676e-08</v>
+        <v>4.783743123702673e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>6.075671294697067e-08</v>
+        <v>6.075671294697068e-08</v>
       </c>
       <c r="S5" t="n">
         <v>1.006840411303248e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>6.826929610747721e-08</v>
+        <v>6.826929610747741e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.048863346441785e-08</v>
+        <v>7.048863346441793e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.285948698572045e-07</v>
+        <v>1.285948698572044e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>3.863119850442001e-07</v>
+        <v>3.863119850441997e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.565161059380307e-07</v>
+        <v>1.565161059380309e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.144682484687027e-08</v>
+        <v>5.144682484686991e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.022046343253051e-08</v>
+        <v>6.022046343253063e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.083365742036318e-07</v>
+        <v>2.083365742036321e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.283769815715738e-08</v>
+        <v>4.283769815715735e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.770144239720371e-08</v>
+        <v>1.770144239720374e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.806779018998483e-08</v>
+        <v>1.806779018998485e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.126314409325797e-08</v>
+        <v>2.126314409325801e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.469920851212732e-08</v>
+        <v>1.469920851212735e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.817980116571627e-08</v>
+        <v>1.81798011657164e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.035224567797047e-08</v>
+        <v>2.035224567797059e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.547573814062575e-08</v>
+        <v>2.547573814062571e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.956865500099035e-08</v>
+        <v>1.956865500099051e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.769326512986371e-08</v>
+        <v>1.769326512986377e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.585400424648476e-08</v>
+        <v>1.585400424648485e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.859426879422705e-08</v>
+        <v>1.8594268794227e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.994171449629776e-08</v>
+        <v>1.994171449629777e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.870576495639567e-08</v>
+        <v>1.870576495639576e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.495518445728785e-08</v>
+        <v>1.495518445728792e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.939213004033056e-08</v>
+        <v>1.939213004033075e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.841280244912897e-08</v>
+        <v>1.84128024491291e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.89242046383357e-08</v>
+        <v>1.892420463833586e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.190649064860937e-08</v>
+        <v>2.190649064860947e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.59948467231851e-08</v>
+        <v>1.599484672318513e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.996084176300062e-08</v>
+        <v>1.996084176300057e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.070894831910022e-08</v>
+        <v>2.070894831910042e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.901968956958579e-08</v>
+        <v>3.901968956958595e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14187881155272e-08</v>
+        <v>2.141878811552728e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.532118103605814e-08</v>
+        <v>1.532118103605795e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.597701597681121e-08</v>
+        <v>1.597701597681124e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.739654635232779e-08</v>
+        <v>2.739654635232784e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.453843853115553e-08</v>
+        <v>1.453843853115559e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.487619004329458e-08</v>
+        <v>1.487619004329452e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.52425378360757e-08</v>
+        <v>1.524253783607562e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.843789173934887e-08</v>
+        <v>1.843789173934881e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.531471559418582e-08</v>
+        <v>1.531471559418604e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.535454881180714e-08</v>
+        <v>1.535454881180722e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.752699332406135e-08</v>
+        <v>1.752699332406145e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.265048578671664e-08</v>
+        <v>2.265048578671674e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.674340264708125e-08</v>
+        <v>1.674340264708113e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.830877221192219e-08</v>
+        <v>1.830877221192227e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.646951132854328e-08</v>
+        <v>1.646951132854334e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.576901644031792e-08</v>
+        <v>1.576901644031787e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.711646214238863e-08</v>
+        <v>1.711646214238861e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.932079968635818e-08</v>
+        <v>1.932079968635827e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.553880127683766e-08</v>
+        <v>1.553880127683777e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.586343039628778e-08</v>
+        <v>1.58634303962878e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.558755009521984e-08</v>
+        <v>1.558755009521983e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.609895228442659e-08</v>
+        <v>1.609895228442653e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.908123829470024e-08</v>
+        <v>1.908123829470019e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.661035380524362e-08</v>
+        <v>1.661035380524371e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.703730304104338e-08</v>
+        <v>1.703730304104352e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.132445540115873e-08</v>
+        <v>2.132445540115894e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>3.547726617606056e-08</v>
+        <v>3.547726617606052e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.203429519758572e-08</v>
+        <v>2.203429519758562e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.573063562650364e-08</v>
+        <v>1.573063562650367e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.659252305886971e-08</v>
+        <v>1.659252305886964e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.457129399841866e-08</v>
+        <v>2.457129399841863e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.512403325294077e-08</v>
+        <v>1.51240332529407e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7134,31 +7134,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.796366432112693e-08</v>
+        <v>1.796366432112698e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.277624917374642e-08</v>
+        <v>2.277624917374654e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.597160307701961e-08</v>
+        <v>2.597160307701971e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.048093685530027e-08</v>
+        <v>2.048093685530034e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.913469485799421e-08</v>
+        <v>1.913469485799423e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.598266087984018e-08</v>
+        <v>2.598266087984029e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.018419712438737e-08</v>
+        <v>3.018419712438744e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.427711398475197e-08</v>
+        <v>2.427711398475207e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.584248354959295e-08</v>
+        <v>2.584248354959306e-08</v>
       </c>
       <c r="K8" t="n">
         <v>2.400322266621399e-08</v>
@@ -7167,52 +7167,52 @@
         <v>2.330272777798864e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.465017348003733e-08</v>
+        <v>2.465017348003739e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.340793346063369e-08</v>
+        <v>2.340793346063373e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.057319053334215e-08</v>
+        <v>2.057319053334227e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.066565044044946e-08</v>
+        <v>2.066565044044945e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.780123731305642e-08</v>
+        <v>1.780123731305644e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.363266362209732e-08</v>
+        <v>2.363266362209738e-08</v>
       </c>
       <c r="S8" t="n">
         <v>2.661494963237098e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.414406514291434e-08</v>
+        <v>2.414406514291439e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.242306443626938e-08</v>
+        <v>2.242306443626944e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.755902099534397e-08</v>
+        <v>2.755902099534398e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.301185131631144e-08</v>
+        <v>4.301185131631153e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.465548887039507e-08</v>
+        <v>2.465548887039517e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.755497596818145e-08</v>
+        <v>2.755497596818151e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.959740620139254e-08</v>
+        <v>1.95974062013926e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.210500533608941e-08</v>
+        <v>3.210500533608951e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.730221097848324e-08</v>
+        <v>2.730221097848337e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.961224868487959e-08</v>
+        <v>3.961224868487964e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.790086111296434e-08</v>
+        <v>4.790086111296426e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.10962150162375e-08</v>
+        <v>5.109621501623743e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.614461386918203e-08</v>
+        <v>4.61446138691821e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.97498876026346e-08</v>
+        <v>2.974988760263466e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.01853183711004e-08</v>
+        <v>5.018531837110031e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.530880906360528e-08</v>
+        <v>5.530880906360535e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.940172592396989e-08</v>
+        <v>4.94017259239698e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.096709548881085e-08</v>
+        <v>5.096709548881091e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.91278346054319e-08</v>
+        <v>4.912783460543197e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.842733971720655e-08</v>
+        <v>4.842733971720658e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>4.977478541927727e-08</v>
+        <v>4.977478541927716e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>5.197912296324683e-08</v>
+        <v>5.19791229632469e-08</v>
       </c>
       <c r="O9" t="n">
         <v>5.082266108435316e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>5.171827590420739e-08</v>
+        <v>5.171827590420753e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.824587514225889e-08</v>
+        <v>4.824587514225899e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>4.87572755613152e-08</v>
+        <v>4.875727556131512e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>5.173956157158887e-08</v>
+        <v>5.173956157158888e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>4.926867708213221e-08</v>
+        <v>4.926867708213229e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>4.979391268598013e-08</v>
+        <v>4.979391268598023e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.312490416957565e-08</v>
+        <v>6.312490416957589e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>6.813558945294923e-08</v>
+        <v>6.813558945294917e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>5.469261847447431e-08</v>
+        <v>5.46926184744743e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.838895890339226e-08</v>
+        <v>4.83889589033923e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.447442593883505e-08</v>
+        <v>4.447442593883512e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.72296172753073e-08</v>
+        <v>5.722961727530721e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.778235652982938e-08</v>
+        <v>4.778235652982933e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7469,46 +7469,46 @@
         <v>1.925485695005698e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.874390035797492e-07</v>
+        <v>3.874390035797496e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.934176062620633e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.924391463895074e-07</v>
+        <v>1.924391463895072e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.928179052831027e-07</v>
+        <v>1.928179052831026e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.923013066671215e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.932895357261792e-07</v>
+        <v>1.932895357261793e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.938341188091688e-07</v>
+        <v>1.938341188091687e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.927932006075032e-07</v>
+        <v>1.927932006075031e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.950988045021477e-07</v>
+        <v>1.950988045021476e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.924341699085685e-07</v>
+        <v>1.924341699085681e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.924368722549267e-07</v>
+        <v>1.924368722549268e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.953174520150269e-07</v>
+        <v>1.953174520150268e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.016766982274252e-07</v>
+        <v>1.016766982274251e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.927946241768656e-07</v>
+        <v>1.927946241768655e-07</v>
       </c>
       <c r="Q2" t="n">
         <v>1.932505709122027e-07</v>
@@ -7523,19 +7523,19 @@
         <v>1.932675586043945e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.336732248687207e-07</v>
+        <v>4.336732248687208e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.927066733063338e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.062666133962426e-07</v>
+        <v>3.062666133962427e-07</v>
       </c>
       <c r="X2" t="n">
         <v>1.931472613835278e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.92982568054539e-07</v>
+        <v>1.929825680545389e-07</v>
       </c>
       <c r="Z2" t="n">
         <v>1.706943211028291e-07</v>
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.975837145785955e-07</v>
+        <v>1.977089208920805e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.180671361022309e-07</v>
+        <v>5.181369492987155e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.038260414491866e-07</v>
+        <v>2.041735949097202e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.968141121503988e-07</v>
+        <v>1.969122096061152e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.995313615247307e-07</v>
+        <v>1.997274932211751e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.958283356225133e-07</v>
+        <v>1.958917443954997e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.029275668326758e-07</v>
+        <v>2.032446096817103e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.068081038671034e-07</v>
+        <v>2.072622409115341e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.993383437613525e-07</v>
+        <v>1.995260796233874e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.157319074975373e-07</v>
+        <v>2.165053122452796e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.967767293817028e-07</v>
+        <v>1.968738242241166e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.968807645809488e-07</v>
+        <v>1.969828317474819e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.173855048181006e-07</v>
+        <v>2.182120849148399e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.85233779962726e-08</v>
+        <v>4.869175023805804e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.993363580258483e-07</v>
+        <v>1.995227530371381e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.026076731843538e-07</v>
+        <v>2.029120795521659e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.010109860114896e-07</v>
+        <v>2.01259249104712e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.006583312217624e-07</v>
+        <v>2.00892682784921e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.027510367740984e-07</v>
+        <v>2.030606720164552e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.964422944068193e-07</v>
+        <v>5.966062077334145e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.987050520313799e-07</v>
+        <v>1.988700297566563e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.995114079774397e-07</v>
+        <v>4.00289675341275e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.018829886187439e-07</v>
+        <v>2.021616410212888e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.006915777390763e-07</v>
+        <v>2.009273647146615e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.621492264193269e-07</v>
+        <v>1.623038558525271e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.990529526116654e-07</v>
+        <v>1.992305623679264e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.96619082662675e-07</v>
+        <v>1.967110658700925e-07</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.792692443957686e-08</v>
+        <v>1.792692443957652e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.539154419558338e-08</v>
+        <v>1.539154419558345e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>2.774309443730843e-08</v>
+        <v>2.774309443730834e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.669094006300969e-08</v>
+        <v>1.669094006300967e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.096919600386661e-08</v>
+        <v>2.096919600386656e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.513397698925499e-08</v>
+        <v>1.5133976989255e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.629647881914003e-08</v>
+        <v>2.629647881913979e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.244779526210146e-08</v>
+        <v>3.244779526210149e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.077447414808423e-08</v>
+        <v>2.077447414808399e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.673300194846096e-08</v>
+        <v>4.673300194846094e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.663472842150916e-08</v>
+        <v>1.663472842150816e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.680954266926039e-08</v>
+        <v>1.680954266926043e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.920272618925585e-08</v>
+        <v>4.920272618925578e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.98843901451491e-08</v>
+        <v>1.988439014514917e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.070622519908061e-08</v>
+        <v>2.07062251990805e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.58563533205758e-08</v>
+        <v>2.585635332057565e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>2.328633094605599e-08</v>
+        <v>2.328633094605598e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>2.282770772039838e-08</v>
+        <v>2.282770772039841e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.604823711860597e-08</v>
+        <v>2.604823711860596e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96478595832922e-08</v>
+        <v>1.964785958329231e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.027467535130826e-08</v>
+        <v>2.027467535130827e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.71580345481766e-08</v>
+        <v>4.715803454817656e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>2.468942466946158e-08</v>
+        <v>2.468942466946139e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.283605071486874e-08</v>
+        <v>2.283605071486875e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.924937286092796e-08</v>
+        <v>1.92493728609279e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.023163830957108e-08</v>
+        <v>2.023163830957091e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.637431663253409e-08</v>
+        <v>1.637431663253402e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.663135425360804e-08</v>
+        <v>9.663135425360426e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.715170677477657e-08</v>
+        <v>5.715170677477674e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.044629528497315e-07</v>
+        <v>3.044629528497308e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>7.957701697499004e-08</v>
+        <v>7.957701697498914e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.682717250817663e-07</v>
+        <v>1.68271725081766e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>4.902160015537674e-08</v>
+        <v>4.902160015537639e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.857704311834078e-07</v>
+        <v>2.857704311834082e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.986421491914392e-07</v>
+        <v>3.986421491914394e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.537924581831906e-07</v>
+        <v>1.537924581831899e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>6.118393031673936e-07</v>
+        <v>6.118393031673941e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>7.747673948068946e-08</v>
+        <v>7.747673948067295e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.431521673912464e-08</v>
+        <v>8.43152167391246e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.103138991320338e-07</v>
+        <v>7.103138991320337e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.278332107413651e-07</v>
+        <v>1.278332107413652e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.472572403199394e-07</v>
+        <v>1.472572403199393e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5420151154077e-07</v>
+        <v>2.542015115407681e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.207265068410055e-07</v>
+        <v>2.207265068410066e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.770878537097452e-07</v>
+        <v>1.770878537097433e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.701326006597793e-07</v>
+        <v>2.701326006597784e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32386191216995e-07</v>
+        <v>1.323861912169948e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.270351017462407e-07</v>
+        <v>1.27035101746241e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>6.589376799850935e-07</v>
+        <v>6.589376799850918e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.391674846502815e-07</v>
+        <v>2.391674846502805e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.951024958812261e-07</v>
+        <v>1.951024958812256e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.203110674814963e-07</v>
+        <v>1.203110674814929e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.474396625705864e-07</v>
+        <v>1.474396625705856e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.066047423840372e-08</v>
+        <v>8.0660474238403e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.08032228218753e-08</v>
+        <v>2.080322282187494e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.826784257788155e-08</v>
+        <v>1.826784257788169e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.061939281960655e-08</v>
+        <v>3.061939281960658e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.419011101251882e-08</v>
+        <v>2.419011101251844e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.384549438616463e-08</v>
+        <v>2.384549438616478e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.263314793876348e-08</v>
+        <v>2.263314793876373e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.91727772014381e-08</v>
+        <v>2.917277720143804e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.532409364439961e-08</v>
+        <v>3.53240936443997e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.365077253038228e-08</v>
+        <v>2.365077253038222e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.423217289796991e-08</v>
+        <v>5.423217289796969e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.413389937101751e-08</v>
+        <v>2.413389937101638e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.968584105155856e-08</v>
+        <v>1.968584105155865e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.208119048210089e-08</v>
+        <v>5.208119048210057e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.823196655820198e-08</v>
+        <v>2.82319665582019e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.904729651874407e-08</v>
+        <v>2.904729651874413e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.873265170287403e-08</v>
+        <v>2.873265170287383e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.078550189556441e-08</v>
+        <v>3.078550189556472e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.570400610269668e-08</v>
+        <v>2.570400610269662e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.892453550090412e-08</v>
+        <v>2.892453550090421e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.714011757378984e-08</v>
+        <v>2.714011757378964e-08</v>
       </c>
       <c r="V6" t="n">
         <v>2.31509737336065e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.048778014250887e-08</v>
+        <v>5.048778014250863e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.218859561897042e-08</v>
+        <v>3.218859561897009e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.597478744371015e-08</v>
+        <v>2.597478744371007e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.674854381043701e-08</v>
+        <v>2.674854381043662e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.773080925907984e-08</v>
+        <v>2.773080925907962e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.925931932330252e-08</v>
+        <v>1.925931932330232e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.149606700497598e-08</v>
+        <v>2.149606700497567e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.896068676098238e-08</v>
+        <v>1.896068676098249e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.131223700270756e-08</v>
+        <v>3.131223700270741e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.026008262840875e-08</v>
+        <v>2.026008262840868e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.453833856926559e-08</v>
+        <v>2.453833856926558e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.870311955465412e-08</v>
+        <v>1.870311955465404e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.986562138453908e-08</v>
+        <v>2.986562138453884e-08</v>
       </c>
       <c r="I7" t="n">
         <v>3.601693782750053e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.434361671348329e-08</v>
+        <v>2.434361671348301e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.030214451386002e-08</v>
+        <v>5.030214451385992e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.020387098690821e-08</v>
+        <v>2.020387098690672e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.037868523465945e-08</v>
+        <v>2.037868523465946e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.277186875465503e-08</v>
+        <v>5.277186875465478e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.345332667974617e-08</v>
+        <v>2.3453326679746e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.427516173367766e-08</v>
+        <v>2.427516173367734e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.942549588597479e-08</v>
+        <v>2.942549588597464e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.685547351145498e-08</v>
+        <v>2.685547351145501e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.639685028579745e-08</v>
+        <v>2.639685028579744e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.961737968400496e-08</v>
+        <v>2.9617379684005e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.320479025318774e-08</v>
+        <v>2.320479025318755e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.384381791670731e-08</v>
+        <v>2.38438179167073e-08</v>
       </c>
       <c r="W7" t="n">
         <v>5.072717711357559e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.82585672348606e-08</v>
+        <v>2.825856723486039e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.639828032125635e-08</v>
+        <v>2.639828032125636e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.281851542632696e-08</v>
+        <v>2.281851542632698e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.380078087497013e-08</v>
+        <v>2.380078087496996e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9943459197933e-08</v>
+        <v>1.994345919793306e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.586574378114078e-08</v>
+        <v>2.586574378114028e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.98692878444213e-08</v>
+        <v>2.986928784442117e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.222083808614603e-08</v>
+        <v>4.222083808614605e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.768689940868771e-08</v>
+        <v>2.768689940868764e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.992670332785098e-08</v>
+        <v>2.992670332785083e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.096760918862423e-08</v>
+        <v>3.096760918862454e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.077422246797765e-08</v>
+        <v>4.077422246797754e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.69255389109394e-08</v>
+        <v>4.692553891093921e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.525221779692183e-08</v>
+        <v>3.525221779692172e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>6.121074559729872e-08</v>
+        <v>6.121074559729863e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.111247207034693e-08</v>
+        <v>3.111247207034599e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.128728631811925e-08</v>
+        <v>3.128728631811912e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>5.861170955602721e-08</v>
+        <v>5.861170955602704e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.068631283747201e-08</v>
+        <v>3.068631283747175e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.116670480576253e-08</v>
+        <v>3.116670480576249e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.251012479783784e-08</v>
+        <v>3.251012479783773e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.776407459489372e-08</v>
+        <v>3.776407459489367e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>3.730545136923618e-08</v>
+        <v>3.730545136923617e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.052598076744384e-08</v>
+        <v>4.05259807674437e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.092318170284426e-08</v>
+        <v>3.092318170284432e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>3.296087908935439e-08</v>
+        <v>3.296087908935437e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>6.163706326116204e-08</v>
+        <v>6.163706326116202e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.194250153912482e-08</v>
+        <v>3.194250153912459e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.380163304405808e-08</v>
+        <v>4.380163304405812e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.706672832815494e-08</v>
+        <v>2.706672832815482e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.470938195840879e-08</v>
+        <v>3.470938195840858e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.768251347617728e-08</v>
+        <v>3.768251347617695e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.50090283553509e-08</v>
+        <v>5.500902835535051e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>6.337945750244648e-08</v>
+        <v>6.337945750244653e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.573100774417152e-08</v>
+        <v>7.573100774417153e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.216184010296351e-08</v>
+        <v>6.216184010296338e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.381623699976151e-08</v>
+        <v>4.381623699976135e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>6.312189426979442e-08</v>
+        <v>6.312189426979422e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.428439212600293e-08</v>
+        <v>7.428439212600295e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.043570856896456e-08</v>
+        <v>8.04357085689646e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.876238745494713e-08</v>
+        <v>6.876238745494711e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>9.472091525532416e-08</v>
+        <v>9.472091525532401e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.46226417283722e-08</v>
+        <v>6.462264172837066e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.47974559761235e-08</v>
+        <v>6.479745597612347e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>9.719063949611895e-08</v>
+        <v>9.719063949611886e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.148647969482561e-08</v>
+        <v>7.148647969482549e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.309433520854228e-08</v>
+        <v>7.30943352085421e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.384427060111513e-08</v>
+        <v>7.384427060111486e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.127424425291915e-08</v>
+        <v>7.127424425291904e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.081562102726154e-08</v>
+        <v>7.08156210272614e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.403615042546901e-08</v>
+        <v>7.403615042546898e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>6.762885993114399e-08</v>
+        <v>6.762885993114395e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.084766279665012e-08</v>
+        <v>8.084766279665008e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.514594785503961e-08</v>
+        <v>9.514594785503957e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.267733797632472e-08</v>
+        <v>7.267733797632435e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.08170510627204e-08</v>
+        <v>7.081705106272043e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.066205446527605e-08</v>
+        <v>6.066205446527585e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.821955161643411e-08</v>
+        <v>6.821955161643397e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.436222993939706e-08</v>
+        <v>6.436222993939703e-08</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.914031731661056e-07</v>
+        <v>1.914031731661062e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.866094855063514e-07</v>
+        <v>3.866094855063527e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.917342583615848e-07</v>
+        <v>1.917342583615852e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.916324828784902e-07</v>
+        <v>1.916324828784908e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.913705170559155e-07</v>
+        <v>1.913705170559162e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.916742924003952e-07</v>
+        <v>1.916742924003957e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.922318115789256e-07</v>
+        <v>1.922318115789262e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.915639215321421e-07</v>
+        <v>1.915639215321425e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.917820686677881e-07</v>
+        <v>1.917820686677889e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.918736682173332e-07</v>
+        <v>1.918736682173338e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.915164123602483e-07</v>
+        <v>1.915164123602488e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.915041244382291e-07</v>
+        <v>1.915041244382297e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.921250765529018e-07</v>
+        <v>1.921250765529024e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.929433433599352e-08</v>
+        <v>9.92943343359954e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.919357067822419e-07</v>
+        <v>1.919357067822425e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.918178743232619e-07</v>
+        <v>1.918178743232624e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.916551109538884e-07</v>
+        <v>1.91655110953889e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.919259766721305e-07</v>
+        <v>1.919259766721312e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9150832581089e-07</v>
+        <v>1.915083258108905e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.314549636322188e-07</v>
+        <v>4.3145496363222e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.917945453927383e-07</v>
+        <v>1.917945453927387e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.042148538077041e-07</v>
+        <v>3.042148538077065e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.921036545096477e-07</v>
+        <v>1.921036545096482e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.916983029470542e-07</v>
+        <v>1.916983029470547e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.689553006858138e-07</v>
+        <v>1.689553006858146e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.917776190974781e-07</v>
+        <v>1.917776190974788e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.917714520749582e-07</v>
+        <v>1.917714520749589e-07</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.948526070018769e-07</v>
+        <v>1.948997693547882e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.178985807329346e-07</v>
+        <v>5.179843146201694e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>1.972235330727296e-07</v>
+        <v>1.973553182211118e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>1.964911953446453e-07</v>
+        <v>1.965960599696586e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.946254382578552e-07</v>
+        <v>1.946649890738603e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.967746751539993e-07</v>
+        <v>1.9688968178872e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.008082752686063e-07</v>
+        <v>2.010680783726083e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.960098351997298e-07</v>
+        <v>1.96098508458808e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>1.975519993480854e-07</v>
+        <v>1.976947629064886e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.981998873980761e-07</v>
+        <v>1.98366854635399e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.956593222078442e-07</v>
+        <v>1.957351971958961e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>1.95638679199515e-07</v>
+        <v>1.957147506027687e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.000158816880158e-07</v>
+        <v>2.002459886465363e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>4.289787179058362e-08</v>
+        <v>4.294903294259309e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98635408619303e-07</v>
+        <v>1.988153867433449e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.978035496000494e-07</v>
+        <v>1.979562088314274e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.966653646442059e-07</v>
+        <v>1.967774448920561e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.985592130267098e-07</v>
+        <v>1.98737603526871e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.956105989745831e-07</v>
+        <v>1.956850506714081e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>5.915746490871457e-07</v>
+        <v>5.916436949113219e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>1.976289254198998e-07</v>
+        <v>1.977741609652976e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.963588949776906e-07</v>
+        <v>3.971083248007356e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.998566913793225e-07</v>
+        <v>2.000820753198685e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.969617106347858e-07</v>
+        <v>1.970837106740338e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.592030472095016e-07</v>
+        <v>1.593149124223836e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.975289648137752e-07</v>
+        <v>1.976708827228576e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.975053914123104e-07</v>
+        <v>1.976468789914942e-07</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.333277496436037e-08</v>
+        <v>1.333277496436108e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.502791984702443e-08</v>
+        <v>1.502791984702512e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.707253455401142e-08</v>
+        <v>1.707253455401213e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.592293365342357e-08</v>
+        <v>1.592293365342424e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.296390917720953e-08</v>
+        <v>1.296390917721023e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.639519143667115e-08</v>
+        <v>1.639519143667187e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.26926270296657e-08</v>
+        <v>2.269262702966645e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.514850170664249e-08</v>
+        <v>1.514850170664323e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.769601626310085e-08</v>
+        <v>1.769601626310159e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.864723300639324e-08</v>
+        <v>1.864723300639397e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.461186375480507e-08</v>
+        <v>1.461186375480581e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.458354099850347e-08</v>
+        <v>1.458354099850425e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.148700581018878e-08</v>
+        <v>2.148700581018944e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.351534708779791e-08</v>
+        <v>1.351534708779863e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.934798713618552e-08</v>
+        <v>1.934798713618624e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.801701530639696e-08</v>
+        <v>1.801701530639766e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.617852817447546e-08</v>
+        <v>1.617852817447618e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.923808106640713e-08</v>
+        <v>1.923808106640781e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.452052245980528e-08</v>
+        <v>1.452052245980602e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.410854684496589e-08</v>
+        <v>1.41085468449666e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.83092833939712e-08</v>
+        <v>1.830928339397181e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.479485083762302e-08</v>
+        <v>4.479485083762379e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>2.124503397700564e-08</v>
+        <v>2.124503397700636e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.646712051679093e-08</v>
+        <v>1.646712051679161e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.625086499353754e-08</v>
+        <v>1.625086499353824e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.756231401285032e-08</v>
+        <v>1.756231401285105e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.750279728936279e-08</v>
+        <v>1.750279728936354e-08</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.796820625723563e-08</v>
+        <v>3.796820625723718e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.996559347618126e-08</v>
+        <v>6.996559347618266e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.082342570934904e-07</v>
+        <v>1.082342570934923e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.481251452942556e-08</v>
+        <v>8.481251452942698e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.450149458262947e-08</v>
+        <v>3.450149458263111e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.543490185612423e-08</v>
+        <v>8.543490185612596e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.250887148731524e-07</v>
+        <v>2.250887148731548e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>7.524337911009924e-08</v>
+        <v>7.524337911010146e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.112575403972645e-07</v>
+        <v>1.112575403972663e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.264356577452355e-07</v>
+        <v>1.264356577452377e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>5.982477184514876e-08</v>
+        <v>5.982477184515078e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.296863306929083e-08</v>
+        <v>6.296863306929319e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.878970781769274e-07</v>
+        <v>1.878970781769283e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>4.0724543696042e-08</v>
+        <v>4.072454369604362e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.350719471007234e-07</v>
+        <v>1.350719471007251e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.162562278245025e-07</v>
+        <v>1.162562278245045e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>9.589985987436867e-08</v>
+        <v>9.589985987437048e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.296293805847621e-07</v>
+        <v>1.296293805847635e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>6.286854239615497e-08</v>
+        <v>6.286854239615751e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>5.485313192733462e-08</v>
+        <v>5.485313192733642e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.079410947243126e-07</v>
+        <v>1.079410947243132e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>5.987673669554037e-07</v>
+        <v>5.987673669554069e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.803525303709385e-07</v>
+        <v>1.803525303709405e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.835280654962788e-08</v>
+        <v>9.835280654962951e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.305247070496122e-08</v>
+        <v>8.305247070496294e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.148052640359594e-07</v>
+        <v>1.148052640359615e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.214898365474737e-07</v>
+        <v>1.214898365474761e-07</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.956869606385768e-08</v>
+        <v>1.956869606385983e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.126384094652177e-08</v>
+        <v>2.12638409465239e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.330845565350876e-08</v>
+        <v>2.330845565351093e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.826729212101493e-08</v>
+        <v>1.826729212101609e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.530826764480089e-08</v>
+        <v>1.530826764480207e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.873954990426252e-08</v>
+        <v>1.873954990426386e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.503698549725704e-08</v>
+        <v>2.503698549725827e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.138442280613982e-08</v>
+        <v>2.138442280614199e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.393193736259819e-08</v>
+        <v>2.393193736260037e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.099159147398458e-08</v>
+        <v>2.099159147398579e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.084778485430239e-08</v>
+        <v>2.084778485430456e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.692789946609482e-08</v>
+        <v>1.692789946609641e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.381086733089905e-08</v>
+        <v>2.381086733090051e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.048640747410647e-08</v>
+        <v>2.048640747410798e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.144964456846701e-08</v>
+        <v>2.144964456846836e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.03613737739883e-08</v>
+        <v>2.036137377398958e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.24144492739728e-08</v>
+        <v>2.241444927397492e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.158243953399845e-08</v>
+        <v>2.158243953399967e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.686488092739663e-08</v>
+        <v>1.686488092739785e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.054374903425287e-08</v>
+        <v>2.054374903425503e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.065364186156255e-08</v>
+        <v>2.065364186156366e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>4.752766648056217e-08</v>
+        <v>4.752766648056371e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.748095507650296e-08</v>
+        <v>2.748095507650513e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.922011907556014e-08</v>
+        <v>1.922011907556142e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.248678609303487e-08</v>
+        <v>2.2486786093037e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.990667248044167e-08</v>
+        <v>1.990667248044288e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.987754699673126e-08</v>
+        <v>1.987754699673279e-08</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.619597307213375e-08</v>
+        <v>1.619597307213514e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.789111795479783e-08</v>
+        <v>1.789111795479916e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.993573266178481e-08</v>
+        <v>1.993573266178617e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.878613176119696e-08</v>
+        <v>1.87861317611984e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.582710728498292e-08</v>
+        <v>1.58271072849843e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.925838954444452e-08</v>
+        <v>1.9258389544446e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.555582513743909e-08</v>
+        <v>2.555582513744049e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.801169981441588e-08</v>
+        <v>1.801169981441725e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.055921437087426e-08</v>
+        <v>2.055921437087624e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.151043111416662e-08</v>
+        <v>2.151043111416807e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.747506186257846e-08</v>
+        <v>1.747506186257996e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.744673910627687e-08</v>
+        <v>1.744673910627861e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.435020391796218e-08</v>
+        <v>2.435020391796341e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.637841535532928e-08</v>
+        <v>1.637841535533063e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.221105540371688e-08</v>
+        <v>2.221105540371882e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.088021341417032e-08</v>
+        <v>2.088021341417219e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.904172628224885e-08</v>
+        <v>1.904172628225023e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.210127917418049e-08</v>
+        <v>2.210127917418187e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.738372056757867e-08</v>
+        <v>1.738372056758009e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.710735561567702e-08</v>
+        <v>1.710735561567832e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.117248150174458e-08</v>
+        <v>2.117248150174641e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.765804894539637e-08</v>
+        <v>4.765804894539786e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.410823208477903e-08</v>
+        <v>2.410823208478045e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.952959971435394e-08</v>
+        <v>1.952959971435533e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.911406310131092e-08</v>
+        <v>1.911406310131231e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.042551212062371e-08</v>
+        <v>2.04255121206252e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.036599539713618e-08</v>
+        <v>2.03659953971376e-08</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.974070716511896e-08</v>
+        <v>1.97407071651206e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.663651136051987e-08</v>
+        <v>2.663651136052206e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.868112606750686e-08</v>
+        <v>2.868112606750916e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.476232749580726e-08</v>
+        <v>2.476232749580918e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.018204331564723e-08</v>
+        <v>2.018204331564892e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.908217353660489e-08</v>
+        <v>2.908217353660729e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.430121854316112e-08</v>
+        <v>3.430121854316347e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.675709322013793e-08</v>
+        <v>2.67570932201402e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.930460777659628e-08</v>
+        <v>2.930460777659864e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.025582451988866e-08</v>
+        <v>3.025582451989104e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.622045526830049e-08</v>
+        <v>2.622045526830278e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.619213251202697e-08</v>
+        <v>2.619213251202934e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.906421630088341e-08</v>
+        <v>2.90642163008851e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.220041607941731e-08</v>
+        <v>2.220041607941924e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.77614932404447e-08</v>
+        <v>2.776149324044662e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.340289925703192e-08</v>
+        <v>2.340289925703337e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.778711968797088e-08</v>
+        <v>2.778711968797318e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>3.084667257990256e-08</v>
+        <v>3.084667257990481e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.612911397330072e-08</v>
+        <v>2.612911397330296e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.33288046460166e-08</v>
+        <v>2.332880464601854e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.844214337130493e-08</v>
+        <v>2.844214337130701e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.640446441412275e-08</v>
+        <v>5.640446441412522e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.710756867798457e-08</v>
+        <v>2.710756867798617e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.33616508853179e-08</v>
+        <v>3.336165088532085e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25621922788059e-08</v>
+        <v>2.256219227880748e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.917090552634574e-08</v>
+        <v>2.917090552634807e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.454391231275371e-08</v>
+        <v>3.454391231275668e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.38369795041e-08</v>
+        <v>4.383697950410323e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>5.44596735315976e-08</v>
+        <v>5.445967353160149e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.650428823858459e-08</v>
+        <v>5.650428823858851e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.329424753713395e-08</v>
+        <v>5.329424753713768e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.181522191435174e-08</v>
+        <v>3.181522191435398e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.582694788638215e-08</v>
+        <v>5.582694788638604e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.212438071423889e-08</v>
+        <v>6.212438071424279e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>5.458025539121568e-08</v>
+        <v>5.458025539121961e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.7127769947674e-08</v>
+        <v>5.712776994767798e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.80789866909664e-08</v>
+        <v>5.807898669097032e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.404361743937824e-08</v>
+        <v>5.404361743938216e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>5.401529468307664e-08</v>
+        <v>5.401529468308061e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>6.091875949476193e-08</v>
+        <v>6.091875949476588e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>5.590568255083995e-08</v>
+        <v>5.590568255084414e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>6.238176277396076e-08</v>
+        <v>6.238176277396507e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.744877175610789e-08</v>
+        <v>5.744877175611187e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>5.561028185904863e-08</v>
+        <v>5.561028185905254e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>5.866983475098029e-08</v>
+        <v>5.866983475098419e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>5.395227614437846e-08</v>
+        <v>5.39522761443824e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>5.373958161932871e-08</v>
+        <v>5.373958161933259e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.804324027651779e-08</v>
+        <v>6.804324027652257e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.422660452219611e-08</v>
+        <v>8.422660452220016e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>6.067678766157879e-08</v>
+        <v>6.067678766158271e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.609815529115374e-08</v>
+        <v>5.609815529115765e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.030010151042578e-08</v>
+        <v>5.03001015104293e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.699406769742351e-08</v>
+        <v>5.699406769742748e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.693455097393591e-08</v>
+        <v>5.693455097393989e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
@@ -586,31 +586,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.937376697390599e-07</v>
+        <v>1.9373766973906e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.890866605264973e-07</v>
+        <v>3.890866605264975e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.953812730263383e-07</v>
+        <v>1.953812730263382e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.935446813807474e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.950311452248301e-07</v>
+        <v>1.950311452248302e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.934811456157409e-07</v>
+        <v>1.934811456157411e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.950572978531632e-07</v>
+        <v>1.950572978531633e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.959366685043568e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.941409688691734e-07</v>
+        <v>1.941409688691735e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.981814820111546e-07</v>
@@ -637,34 +637,34 @@
         <v>1.946733442528714e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.941261299613875e-07</v>
+        <v>1.941261299613874e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.955924706745981e-07</v>
+        <v>1.95592470674598e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.359461843083687e-07</v>
+        <v>4.359461843083685e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.939538716416262e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.081722949565067e-07</v>
+        <v>3.081722949565066e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.940331924003988e-07</v>
+        <v>1.940331924003989e-07</v>
       </c>
       <c r="Y2" t="n">
         <v>1.942882339033193e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.723444655621677e-07</v>
+        <v>1.723444655621676e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.94000917115409e-07</v>
+        <v>1.940009171154091e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.935408054179072e-07</v>
+        <v>1.935408054179071e-07</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.221214685709081e-07</v>
+        <v>2.13405988320553e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.20980375340076e-07</v>
+        <v>4.099961486506565e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.606656972783901e-07</v>
+        <v>2.270161560778295e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.71355169506452e-07</v>
+        <v>2.656145771738582e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.526678458923634e-07</v>
+        <v>2.24300146310409e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.162193993351715e-07</v>
+        <v>2.114241239395053e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.53357480461322e-07</v>
+        <v>2.246285912703019e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.737370641665508e-07</v>
+        <v>2.316543912256372e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.315644002702073e-07</v>
+        <v>2.167360085278212e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25902017899595e-07</v>
+        <v>2.49741907515986e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.312133985031048e-07</v>
+        <v>2.166126095137477e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.211469280379321e-07</v>
+        <v>2.132022054495236e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.172187227738605e-07</v>
+        <v>2.464885965030176e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42625607166949e-07</v>
+        <v>1.268781886800916e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.330281472794126e-07</v>
+        <v>2.171354053309158e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.552417412677338e-07</v>
+        <v>2.250222822176026e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.442555601551286e-07</v>
+        <v>2.213572934339842e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.311251878228048e-07</v>
+        <v>2.165029696931147e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.656275255128768e-07</v>
+        <v>2.287712354178095e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.731221938547884e-07</v>
+        <v>4.584193765713243e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.271242366344851e-07</v>
+        <v>2.151095102995643e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.896902674340293e-07</v>
+        <v>3.447051510107158e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.2917277941264e-07</v>
+        <v>2.159780846282698e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.350116183890677e-07</v>
+        <v>2.179340358411825e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.030887808746859e-07</v>
+        <v>1.927754322516623e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.283293820666377e-07</v>
+        <v>2.156423645847405e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.179764168301307e-07</v>
+        <v>2.121352915443387e-07</v>
       </c>
     </row>
     <row r="4">
@@ -762,37 +762,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.26435795917126e-07</v>
+        <v>1.264357959171258e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.751387945371528e-07</v>
+        <v>1.751387945371533e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.362093428801236e-07</v>
+        <v>5.362093428801237e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>9.018048544816715e-08</v>
+        <v>9.01804854481674e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.628636714390707e-07</v>
+        <v>4.628636714390699e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>7.340152717651831e-08</v>
+        <v>7.340152717651823e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.77991493413447e-07</v>
+        <v>4.779914934134465e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>6.776560964842392e-07</v>
+        <v>6.776560964842374e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.263459776740757e-07</v>
+        <v>2.263459776740758e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>1.199009816202518e-06</v>
+        <v>1.199009816202515e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>2.221672382475203e-07</v>
+        <v>2.221672382475177e-07</v>
       </c>
       <c r="M4" t="n">
         <v>1.312465530207738e-07</v>
@@ -801,10 +801,10 @@
         <v>1.088692553765025e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>2.185760805587525e-07</v>
+        <v>2.185760805587518e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>2.293390787035535e-07</v>
+        <v>2.293390787035534e-07</v>
       </c>
       <c r="Q4" t="n">
         <v>4.711572471341923e-07</v>
@@ -813,34 +813,34 @@
         <v>3.752582826212816e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.141155965494278e-07</v>
+        <v>2.141155965494281e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>5.893338005060415e-07</v>
+        <v>5.893338005060399e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.19632566593442e-07</v>
+        <v>2.196325665934429e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.74236283809884e-07</v>
+        <v>1.742362838098838e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>6.813015079713009e-07</v>
+        <v>6.813015079713021e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>2.096648280103319e-07</v>
+        <v>2.096648280103309e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.613140558984186e-07</v>
+        <v>2.613140558984195e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.520843508009978e-07</v>
+        <v>1.520843508009977e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.964215218444594e-07</v>
+        <v>1.964215218444593e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.011871061185459e-07</v>
+        <v>1.011871061185458e-07</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.04140353469931e-08</v>
+        <v>3.04140353469924e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.024191331340186e-08</v>
+        <v>4.024191331340144e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.710929314520644e-08</v>
+        <v>5.710929314520627e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.203515908949783e-08</v>
+        <v>3.203515908949758e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.629099536724724e-08</v>
+        <v>4.629099536724684e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.733228893446389e-08</v>
+        <v>3.733228893446362e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.344984452825207e-08</v>
+        <v>5.344984452825175e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.338274056396842e-08</v>
+        <v>6.338274056396813e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.318342019388631e-08</v>
+        <v>4.318342019388625e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.873894178848277e-08</v>
+        <v>8.873894178848313e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.294327657848491e-08</v>
+        <v>4.294327657848462e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.798096507794436e-08</v>
+        <v>3.798096507794448e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.088692553765025e-06</v>
+        <v>7.836143648096365e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.915879035821e-08</v>
+        <v>3.915879035820962e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.891455807135319e-08</v>
+        <v>3.891455807135248e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.480846324573502e-08</v>
+        <v>4.480846324573473e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.911291198557371e-08</v>
+        <v>4.911291198557356e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.293187483225161e-08</v>
+        <v>4.293187483225148e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>5.94948677380191e-08</v>
+        <v>5.949486773801937e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.905524503881674e-08</v>
+        <v>3.905524503881646e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.934874747624054e-08</v>
+        <v>3.934874747624051e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.554231556778629e-08</v>
+        <v>6.554231556778584e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.28994995709518e-08</v>
+        <v>3.28994995709514e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.288564342236916e-08</v>
+        <v>5.288564342236922e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.146443099961009e-08</v>
+        <v>3.146443099960975e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.151753813616994e-08</v>
+        <v>4.15175381361701e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.495093171822476e-08</v>
+        <v>4.495093171822455e-08</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.755293188466195e-08</v>
+        <v>6.755293188466199e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.30603649980545e-08</v>
+        <v>8.306036499805421e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.992774482985911e-08</v>
+        <v>9.992774482985858e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.599541172434356e-08</v>
+        <v>7.599541172434367e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.413808392731843e-08</v>
+        <v>6.413808392731841e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.84649368243388e-08</v>
+        <v>7.846493682433835e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.626829621290474e-08</v>
+        <v>9.626829621290466e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.062011922486211e-07</v>
+        <v>1.062011922486212e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>8.600187187853899e-08</v>
+        <v>8.600187187853858e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.315573934731354e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>8.576172826313758e-08</v>
+        <v>8.576172826313715e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>8.079941676258099e-08</v>
+        <v>8.079941676258079e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.088692553765025e-06</v>
+        <v>1.274820002869404e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>9.112395531544333e-08</v>
+        <v>9.112395531544329e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>9.229955140484671e-08</v>
+        <v>9.229955140484649e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.735465375962166e-08</v>
+        <v>9.735465375962095e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>9.193136367022642e-08</v>
+        <v>9.193136367022588e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>8.575032651690424e-08</v>
+        <v>8.575032651690425e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.023133194226717e-07</v>
+        <v>1.023133194226714e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>8.581889674091161e-08</v>
+        <v>8.581889674091177e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.002998809839402e-07</v>
+        <v>1.002998809839401e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08359169501251e-07</v>
+        <v>1.083591695012511e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>8.470055401214649e-08</v>
+        <v>8.470055401214617e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.758136511252149e-08</v>
+        <v>8.758136511252081e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.423797098006612e-08</v>
+        <v>7.423797098006538e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.433598982082262e-08</v>
+        <v>8.433598982082238e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.927691592028625e-08</v>
+        <v>7.927691592028593e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1182,61 +1182,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.910741724282198e-07</v>
+        <v>1.910741724282199e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.864238572939362e-07</v>
+        <v>3.864238572939364e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.913932246208822e-07</v>
+        <v>1.913932246208824e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.91146477649673e-07</v>
+        <v>1.911464776496732e-07</v>
       </c>
       <c r="F2" t="n">
         <v>1.911190009808653e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.913821198760468e-07</v>
+        <v>1.913821198760469e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.917487720295379e-07</v>
+        <v>1.91748772029538e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.912254188746507e-07</v>
+        <v>1.912254188746509e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.914751565902748e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.914232854062943e-07</v>
+        <v>1.914232854062946e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.91292498525787e-07</v>
+        <v>1.912924985257872e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.912555815252654e-07</v>
+        <v>1.912555815252656e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.916133605087269e-07</v>
+        <v>1.91613360508727e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.865473819507275e-08</v>
+        <v>9.865473819507289e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.914637284781293e-07</v>
+        <v>1.914637284781294e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.912159432243185e-07</v>
+        <v>1.912159432243187e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.912515706152422e-07</v>
+        <v>1.912515706152423e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.91452084519144e-07</v>
+        <v>1.914520845191442e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.91249072973241e-07</v>
+        <v>1.912490729732412e-07</v>
       </c>
       <c r="U2" t="n">
         <v>4.308644179227512e-07</v>
@@ -1251,16 +1251,16 @@
         <v>1.916930507572007e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.913534736006377e-07</v>
+        <v>1.913534736006378e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.68452505427187e-07</v>
+        <v>1.684525054271877e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.920951710748797e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.910774237398705e-07</v>
+        <v>1.910774237398706e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.095483240363497e-07</v>
+        <v>2.075732721493475e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.121585078516905e-07</v>
+        <v>4.05198231304908e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.170180298454098e-07</v>
+        <v>2.10147706059425e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.654320016984793e-07</v>
+        <v>2.623635839147927e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.10634757252154e-07</v>
+        <v>2.07966407544395e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.166382953906556e-07</v>
+        <v>2.099361201382828e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.254257249663183e-07</v>
+        <v>2.131625115867486e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.131149963440166e-07</v>
+        <v>2.0882999937546e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.188447359111495e-07</v>
+        <v>2.107294507905838e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.176984188821255e-07</v>
+        <v>2.10313232281311e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.146100228965255e-07</v>
+        <v>2.092780771400677e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.140493859281377e-07</v>
+        <v>2.091378146479568e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.221109306012083e-07</v>
+        <v>2.119455561330383e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.184126928008956e-07</v>
+        <v>1.155446354098556e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.184957646458748e-07</v>
+        <v>2.105608908541713e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12869345977377e-07</v>
+        <v>2.087071607548543e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.137385487704244e-07</v>
+        <v>2.09060777973564e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.182707150306941e-07</v>
+        <v>2.104805804439055e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.136621501096049e-07</v>
+        <v>2.090224138829946e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.575371578518502e-07</v>
+        <v>4.498493680577051e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.226531929375845e-07</v>
+        <v>2.119440690362176e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.75626734868517e-07</v>
+        <v>3.364935314759444e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.239936696114917e-07</v>
+        <v>2.124995522526699e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.160525735801452e-07</v>
+        <v>2.098333104280901e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.965193623103692e-07</v>
+        <v>1.878133424186407e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.332625205419746e-07</v>
+        <v>2.157843212931048e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.098191876821389e-07</v>
+        <v>2.076941214137347e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.854406187351358e-08</v>
+        <v>2.85440618735134e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>9.36441362933946e-08</v>
+        <v>9.364413629339458e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.377955168696056e-08</v>
+        <v>9.377955168696066e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.28713528355673e-08</v>
+        <v>4.287135283556723e-08</v>
       </c>
       <c r="F4" t="n">
         <v>3.979345351554693e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.338246784216263e-08</v>
+        <v>8.338246784216244e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.762880447537427e-07</v>
+        <v>1.762880447537431e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>6.190380067535324e-08</v>
+        <v>6.190380067535299e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.053493003171825e-07</v>
+        <v>1.053493003171826e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>9.471370335281807e-08</v>
+        <v>9.471370335281817e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.938652085326594e-08</v>
+        <v>6.938652085326587e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.971550449601099e-08</v>
+        <v>6.971550449601089e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.403533305440851e-07</v>
+        <v>1.403533305440849e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>3.901063363779135e-08</v>
+        <v>3.901063363779133e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>9.785258301251288e-08</v>
+        <v>9.785258301251276e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.684316431340423e-08</v>
+        <v>5.684316431340416e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.857983803344795e-08</v>
+        <v>6.857983803344787e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>9.632829564184585e-08</v>
+        <v>9.632829564184562e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.68560369068301e-08</v>
+        <v>6.685603690683011e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>9.539459034400477e-08</v>
+        <v>9.539459034400447e-08</v>
       </c>
       <c r="V4" t="n">
         <v>1.308521014284474e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>5.161471963530928e-07</v>
+        <v>5.16147196353093e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.505560472965065e-07</v>
+        <v>1.505560472965067e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.613826546496759e-08</v>
+        <v>8.61382654649674e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.030469571687277e-07</v>
+        <v>1.03046957168728e-07</v>
       </c>
       <c r="AA4" t="n">
         <v>2.357290943312007e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.357249590516053e-08</v>
+        <v>3.357249590516046e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.846374260853561e-08</v>
+        <v>1.846374260853549e-08</v>
       </c>
       <c r="C5" t="n">
         <v>2.699861647848157e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.693714934739666e-08</v>
+        <v>2.693714934739665e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.155712884123861e-08</v>
+        <v>2.155712884123858e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.972872311675722e-08</v>
+        <v>1.972872311675711e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.782145226366825e-08</v>
+        <v>2.782145226366824e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.095322088805077e-08</v>
+        <v>3.095322088805079e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.504170624925389e-08</v>
+        <v>2.504170624925382e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.794640531252194e-08</v>
+        <v>2.79464053125218e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.727669974727206e-08</v>
+        <v>2.7276699747272e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.579940176700296e-08</v>
+        <v>2.579940176700297e-08</v>
       </c>
       <c r="M5" t="n">
         <v>2.549384927090973e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.403533305440851e-07</v>
+        <v>2.564895757920876e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.125611033793908e-08</v>
+        <v>2.125611033793904e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.474184879634722e-08</v>
+        <v>2.474184879634715e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.910812821805937e-08</v>
+        <v>1.910812821805934e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>2.53371021896293e-08</v>
+        <v>2.533710218962934e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>2.760199897515322e-08</v>
+        <v>2.760199897515313e-08</v>
       </c>
       <c r="T5" t="n">
         <v>2.530889017425512e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>2.505468465452336e-08</v>
+        <v>2.505468465452329e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.888885766276973e-08</v>
+        <v>2.888885766276962e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.093740768424108e-08</v>
+        <v>5.093740768424101e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>2.494358262382673e-08</v>
+        <v>2.494358262382661e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.118210719885867e-08</v>
+        <v>3.118210719885864e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.329380679179199e-08</v>
+        <v>2.329380679179178e-08</v>
       </c>
       <c r="AA5" t="n">
         <v>3.486595745662041e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.853971037341673e-08</v>
+        <v>2.85397103734167e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.011249427205949e-08</v>
+        <v>4.011249427205948e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.188436776476745e-08</v>
+        <v>5.188436776476739e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.182290063368253e-08</v>
+        <v>5.182290063368247e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.716482007528905e-08</v>
+        <v>4.716482007528901e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.003756984528561e-08</v>
+        <v>3.003756984528553e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.169747021922315e-08</v>
+        <v>5.16974702192231e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.583897217433662e-08</v>
+        <v>5.583897217433659e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.992745753553977e-08</v>
+        <v>4.992745753553965e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.283215659880766e-08</v>
+        <v>5.283215659880762e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.21624510335579e-08</v>
+        <v>5.216245103355779e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.068515305328884e-08</v>
+        <v>5.068515305328878e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.037960055716543e-08</v>
+        <v>5.037960055716539e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.403533305440851e-07</v>
+        <v>5.430943675439855e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.156577028204823e-08</v>
+        <v>5.156577028204819e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.589005185286974e-08</v>
+        <v>5.589005185286963e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.98204284929149e-08</v>
+        <v>4.982042849291487e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.02228534759152e-08</v>
+        <v>5.022285347591514e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.248775026143899e-08</v>
+        <v>5.248775026143894e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.019464146054099e-08</v>
+        <v>5.019464146054095e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.240356429789342e-08</v>
+        <v>5.240356429789338e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.455559073737477e-08</v>
+        <v>6.455559073737468e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.582220197452024e-08</v>
+        <v>7.582220197452018e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.520957477023654e-08</v>
+        <v>5.520957477023651e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.137389457364637e-08</v>
+        <v>5.137389457364629e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.825204143758531e-08</v>
+        <v>4.825204143758517e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.975170874290625e-08</v>
+        <v>5.975170874290621e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.83387933712117e-08</v>
+        <v>4.833879337121166e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.926785867156179e-07</v>
+        <v>1.926785867156176e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.881178926690256e-07</v>
+        <v>3.881178926690253e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.931592718854918e-07</v>
+        <v>1.931592718854917e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.928843270528166e-07</v>
+        <v>1.928843270528164e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.934026722780871e-07</v>
+        <v>1.934026722780869e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.925979620502927e-07</v>
+        <v>1.925979620502924e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.936298899156172e-07</v>
+        <v>1.936298899156171e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.940067535775091e-07</v>
+        <v>1.94006753577509e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.931078248153272e-07</v>
+        <v>1.93107824815327e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.964241088050307e-07</v>
+        <v>1.964241088050305e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.927185908995628e-07</v>
+        <v>1.927185908995626e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.927000441576049e-07</v>
+        <v>1.927000441576047e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.953023452018807e-07</v>
+        <v>1.953023452018804e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.022215511351972e-07</v>
+        <v>1.022215511351971e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.930718510631831e-07</v>
+        <v>1.930718510631827e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.937106507425139e-07</v>
+        <v>1.937106507425137e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.93490584715641e-07</v>
+        <v>1.934905847156409e-07</v>
       </c>
       <c r="S2" t="n">
         <v>1.930665112634235e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.932752654221031e-07</v>
+        <v>1.932752654221029e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.343715173926774e-07</v>
+        <v>4.343715173926772e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.929692139125889e-07</v>
+        <v>1.929692139125886e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.081368577565796e-07</v>
+        <v>3.081368577565792e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.932517482494521e-07</v>
+        <v>1.93251748249452e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.935721487027403e-07</v>
+        <v>1.935721487027402e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.712157892110606e-07</v>
+        <v>1.712157892110605e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.93002700546437e-07</v>
+        <v>1.930027005464367e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.927050671922663e-07</v>
+        <v>1.927050671922662e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.155035167449189e-07</v>
+        <v>2.106692936497212e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.169376068674697e-07</v>
+        <v>4.080532108094612e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.268147966859399e-07</v>
+        <v>2.146913890461888e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.740821168813762e-07</v>
+        <v>2.661515533650173e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.325863401150593e-07</v>
+        <v>2.166928704993198e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.136501801338641e-07</v>
+        <v>2.10051739766356e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.379705711199697e-07</v>
+        <v>2.186894733602291e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.466627725663941e-07</v>
+        <v>2.216710431043923e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.255084806433338e-07</v>
+        <v>2.141481964855461e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>3.028181045134179e-07</v>
+        <v>2.404104488100044e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.16466836931256e-07</v>
+        <v>2.110364122209833e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.164166492784707e-07</v>
+        <v>2.110555872681529e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.765978471706851e-07</v>
+        <v>2.319065855316734e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.319145229535241e-07</v>
+        <v>1.222899110246747e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.245377542452963e-07</v>
+        <v>2.137466346579479e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.396146432797813e-07</v>
+        <v>2.190817388118242e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.346380509721866e-07</v>
+        <v>2.174852577500989e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.244765918165918e-07</v>
+        <v>2.137270266890158e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.295326018252512e-07</v>
+        <v>2.156368486068315e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.618490901506666e-07</v>
+        <v>4.538439746469399e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.222092627159733e-07</v>
+        <v>2.129078116892193e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.132094025755601e-07</v>
+        <v>3.521450264026486e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.289533828801727e-07</v>
+        <v>2.154000288497497e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.363046907886572e-07</v>
+        <v>2.178546023824531e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.997009781164153e-07</v>
+        <v>1.909712998651148e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.230757751957723e-07</v>
+        <v>2.133220105832131e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.163912474184961e-07</v>
+        <v>2.11089909007389e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.824543512553563e-08</v>
+        <v>6.8245435125534e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.312543444405236e-07</v>
+        <v>1.312543444405235e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.837184380454918e-07</v>
+        <v>1.837184380454914e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.153110151081215e-07</v>
+        <v>1.153110151081231e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.395468935642055e-07</v>
+        <v>2.395468935642057e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>5.29771289999005e-08</v>
+        <v>5.297712899989935e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.010421497442455e-07</v>
+        <v>3.010421497442459e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.793031644607119e-07</v>
+        <v>3.793031644607121e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.633607036735575e-07</v>
+        <v>1.63360703673558e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>8.524494052416943e-07</v>
+        <v>8.524494052416954e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>8.018720023576498e-08</v>
+        <v>8.018720023578867e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>8.432783209746711e-08</v>
+        <v>8.432783209746746e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.471981858621274e-07</v>
+        <v>6.471981858621278e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.271534451262002e-07</v>
+        <v>1.271534451262001e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>1.474873690208764e-07</v>
+        <v>1.474873690208736e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.001381891726255e-07</v>
+        <v>3.001381891726197e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>2.648457208188233e-07</v>
+        <v>2.648457208188228e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.479314146132731e-07</v>
+        <v>1.479314146132725e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.097666838500189e-07</v>
+        <v>2.097666838500187e-07</v>
       </c>
       <c r="U4" t="n">
         <v>1.143521170052276e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.247124640402616e-07</v>
+        <v>1.247124640402611e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>8.671484659204316e-07</v>
+        <v>8.671484659204312e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>2.012322089040418e-07</v>
+        <v>2.012322089040414e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.619614499262243e-07</v>
+        <v>2.61961449926224e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.20962134729944e-07</v>
+        <v>1.209621347299434e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.418618455147715e-07</v>
+        <v>1.418618455147709e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.669321937340747e-08</v>
+        <v>8.66932193734078e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.49626071346913e-08</v>
+        <v>2.49626071346904e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.482451575986349e-08</v>
+        <v>3.482451575986333e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.725895109166013e-08</v>
+        <v>3.725895109165993e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.049696289441226e-08</v>
+        <v>3.049696289441239e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.421125132388913e-08</v>
+        <v>3.421125132388891e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.234257064760042e-08</v>
+        <v>3.234257064760025e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.257479823691556e-08</v>
+        <v>4.257479823691537e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.683164666383427e-08</v>
+        <v>4.683164666383403e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.676219390201544e-08</v>
+        <v>3.676219390201527e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.413678599703586e-08</v>
+        <v>7.413678599703569e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.228125663232122e-08</v>
+        <v>3.228125663232207e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.222373055015971e-08</v>
+        <v>3.222373055015943e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.471981858621274e-07</v>
+        <v>5.614304379503872e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.150003163175241e-08</v>
+        <v>3.150003163175234e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.205280433854894e-08</v>
+        <v>3.205280433854884e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.527076534672934e-08</v>
+        <v>3.527076534672923e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.100128191962706e-08</v>
+        <v>4.10012819196269e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.621117719340303e-08</v>
+        <v>3.621117719340276e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.856915144734687e-08</v>
+        <v>3.856915144734666e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.087000087911474e-08</v>
+        <v>3.08700008791146e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.38344357467485e-08</v>
+        <v>3.383443574674828e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>7.366588749871686e-08</v>
+        <v>7.366588749871681e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.071660495119233e-08</v>
+        <v>3.07166049511924e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.880756129425963e-08</v>
+        <v>4.880756129425938e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.773073606119142e-08</v>
+        <v>2.773073606119137e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.549040579066003e-08</v>
+        <v>3.549040579065994e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.938916000246914e-08</v>
+        <v>3.938916000246897e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.400290941993551e-08</v>
+        <v>5.400290941993511e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.80180654040005e-08</v>
+        <v>6.80180654040003e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.045250073579717e-08</v>
+        <v>7.045250073579692e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.480349713533284e-08</v>
+        <v>6.480349713533287e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.779763546388908e-08</v>
+        <v>4.779763546388898e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.411225185239647e-08</v>
+        <v>6.411225185239634e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.576834788105253e-08</v>
+        <v>7.576834788105219e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.002519630797124e-08</v>
+        <v>8.002519630797103e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.995574354615259e-08</v>
+        <v>6.995574354615237e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.073303356411728e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>6.547480627645819e-08</v>
+        <v>6.547480627645749e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.541728019426839e-08</v>
+        <v>6.541728019426812e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.471981858621274e-07</v>
+        <v>9.465949970683977e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>7.220573582351997e-08</v>
+        <v>7.220573582351955e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>7.391132428536939e-08</v>
+        <v>7.391132428536915e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.66805824931215e-08</v>
+        <v>7.668058249312108e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.419483156376405e-08</v>
+        <v>7.419483156376393e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>6.940472683754005e-08</v>
+        <v>6.940472683753975e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>7.176270109148392e-08</v>
+        <v>7.17627010914836e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.738153027339844e-08</v>
+        <v>6.73815302733982e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>8.158459796084675e-08</v>
+        <v>8.158459796084638e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.068580876459164e-07</v>
+        <v>1.068580876459161e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>7.149706380795726e-08</v>
+        <v>7.149706380795769e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.511613431933812e-08</v>
+        <v>7.511613431933795e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.127452626075799e-08</v>
+        <v>6.127452626075778e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.868395543479704e-08</v>
+        <v>6.868395543479694e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.540977975865945e-08</v>
+        <v>6.540977975865925e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2374,85 +2374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.917026174681164e-07</v>
+        <v>1.917026174681133e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.880253654678997e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.924669240404151e-07</v>
+        <v>1.924669240404119e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.923684831300555e-07</v>
+        <v>1.923684831300523e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.919212379580076e-07</v>
+        <v>1.919212379580042e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.91761950335334e-07</v>
+        <v>1.917619503353308e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.924489927757834e-07</v>
+        <v>1.924489927757802e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.920165552148339e-07</v>
+        <v>1.920165552148306e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.921305019550926e-07</v>
+        <v>1.921305019550916e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.918138089780574e-07</v>
+        <v>1.918138089780542e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.916462630189777e-07</v>
+        <v>1.916462630189744e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.918609574633404e-07</v>
+        <v>1.918609574633406e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.93206837304128e-07</v>
+        <v>1.932068373041247e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.001652852871011e-07</v>
+        <v>1.001652852870978e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.921236721353695e-07</v>
+        <v>1.921236721353661e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92258262759668e-07</v>
+        <v>1.922582627596648e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.92230530671781e-07</v>
+        <v>1.922305306717778e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.921091028702131e-07</v>
+        <v>1.921091028702098e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.919083543286904e-07</v>
+        <v>1.919083543286871e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.326076249591106e-07</v>
+        <v>4.326076249591081e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.920914675453778e-07</v>
+        <v>1.920914675453746e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.058355978286845e-07</v>
+        <v>3.058355978286817e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.922327820684068e-07</v>
+        <v>1.922327820684036e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.921698456719161e-07</v>
+        <v>1.921698456719128e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.697191647229171e-07</v>
+        <v>1.697191647229136e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.920174275105572e-07</v>
+        <v>1.920174275105539e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.918168961988407e-07</v>
+        <v>1.918168961988408e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.11409249660126e-07</v>
+        <v>2.086711363308364e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.329892347407702e-07</v>
+        <v>4.128794328397752e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.292947825651355e-07</v>
+        <v>2.149300759066171e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.809367757937328e-07</v>
+        <v>2.681088679434086e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.165882531980232e-07</v>
+        <v>2.104971800241319e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.127778741122993e-07</v>
+        <v>2.091377260996676e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.290027887862534e-07</v>
+        <v>2.149381865956808e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.187996292618257e-07</v>
+        <v>2.112905040533467e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.213570294686547e-07</v>
+        <v>2.120994913537127e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.140374206014083e-07</v>
+        <v>2.095804036164729e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.101218395081709e-07</v>
+        <v>2.082398200972522e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.154190253373823e-07</v>
+        <v>2.101022093189729e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.464311603802554e-07</v>
+        <v>2.208451408621333e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.233854228815304e-07</v>
+        <v>1.18195921922766e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.210843665113216e-07</v>
+        <v>2.119436649663904e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.243820279212328e-07</v>
+        <v>2.131532322273288e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.238325599552691e-07</v>
+        <v>2.130787720815767e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.208005276228127e-07</v>
+        <v>2.118521507266752e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.162607990942639e-07</v>
+        <v>2.103963702553836e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.61987809917419e-07</v>
+        <v>4.525953013633898e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.203722093781439e-07</v>
+        <v>2.116567281146485e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.036736019943788e-07</v>
+        <v>3.474990263209796e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.238139819688898e-07</v>
+        <v>2.129977599404205e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.222851697412852e-07</v>
+        <v>2.124293494002555e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.971648624293124e-07</v>
+        <v>1.890250857492975e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.187404652399643e-07</v>
+        <v>2.112183441796475e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.142673325520314e-07</v>
+        <v>2.097367523692956e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.829038523257393e-08</v>
+        <v>3.829038523257512e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.622294016600639e-07</v>
+        <v>2.622294016600642e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.008290957770619e-07</v>
+        <v>2.008290957770622e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.722233576343637e-07</v>
+        <v>1.722233576343639e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>8.71213335298371e-08</v>
+        <v>8.712133352983741e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.962433569405892e-08</v>
+        <v>4.962433569405343e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.073762352607784e-07</v>
+        <v>2.073762352607793e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.082908620780459e-07</v>
+        <v>1.082908620780462e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.243178799055078e-07</v>
+        <v>1.24317879905506e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.180879872989584e-08</v>
+        <v>6.18087987298956e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>2.83134189413108e-08</v>
+        <v>2.831341894131001e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>7.797978701034056e-08</v>
+        <v>7.797978701033979e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.486358679411035e-07</v>
+        <v>3.48635867941104e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>6.644205300680889e-08</v>
+        <v>6.644205300680946e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.161491096573995e-07</v>
+        <v>1.161491096573971e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.518606970552724e-07</v>
+        <v>1.518606970552727e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56209318100557e-07</v>
+        <v>1.562093181005573e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.14856616664167e-07</v>
+        <v>1.148566166641667e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>8.474122762657849e-08</v>
+        <v>8.474122762657881e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.231977867059922e-07</v>
+        <v>1.231977867059923e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.082138835443808e-07</v>
+        <v>1.08213883544381e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>7.465452665060189e-07</v>
+        <v>7.465452665060185e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.500223162212595e-07</v>
+        <v>1.500223162212604e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.331119872921078e-07</v>
+        <v>1.331119872921091e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.004083783289727e-07</v>
+        <v>1.004083783289728e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03195852320541e-07</v>
+        <v>1.031958523205408e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.964085241441586e-08</v>
+        <v>6.964085241441614e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.045696078104941e-08</v>
+        <v>2.045696078104975e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.877111673008596e-08</v>
+        <v>3.877111673008631e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.462956524533033e-08</v>
+        <v>3.462956524533076e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.056805738836268e-08</v>
+        <v>3.05680573883632e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.378935514080435e-08</v>
+        <v>2.378935514080471e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.781519571791728e-08</v>
+        <v>2.78151957179172e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.442702336252788e-08</v>
+        <v>3.442702336252801e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.954244218049467e-08</v>
+        <v>2.954244218049502e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.09134442654673e-08</v>
+        <v>3.091344426546746e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.72523301682297e-08</v>
+        <v>2.725233016822987e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.535982148547384e-08</v>
+        <v>2.535982148547442e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>2.790931226245257e-08</v>
+        <v>2.790931226245314e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.486358679411035e-07</v>
+        <v>3.869325635616546e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.468870244864771e-08</v>
+        <v>2.468870244864813e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.734917616731241e-08</v>
+        <v>2.734917616731266e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.564460944134356e-08</v>
+        <v>2.564460944134362e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.195939340028732e-08</v>
+        <v>3.195939340028767e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.058781052202786e-08</v>
+        <v>3.058781052202822e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.832026339663788e-08</v>
+        <v>2.832026339663839e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>2.818873364758739e-08</v>
+        <v>2.818873364758784e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.939669166936606e-08</v>
+        <v>2.939669166936627e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.574941987343658e-08</v>
+        <v>6.574941987343687e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>2.586449124691348e-08</v>
+        <v>2.586449124691376e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.672421485892016e-08</v>
+        <v>3.672421485892075e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.432100024392372e-08</v>
+        <v>2.432100024392368e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.955229516196698e-08</v>
+        <v>2.955229516196723e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.314392934796116e-08</v>
+        <v>3.314392934796142e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.417848974197613e-08</v>
+        <v>4.417848974197687e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.592459002780256e-08</v>
+        <v>6.59245900278029e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.178303854304706e-08</v>
+        <v>6.178303854304735e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.860055327800941e-08</v>
+        <v>5.860055327800852e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.493783905116446e-08</v>
+        <v>3.493783905116557e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.382003899682472e-08</v>
+        <v>5.38200389968263e-08</v>
       </c>
       <c r="H6" t="n">
         <v>6.158049666024457e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.669591547821137e-08</v>
+        <v>5.669591547821161e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.806691756318386e-08</v>
+        <v>5.806691756318385e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.44058034659463e-08</v>
+        <v>5.440580346594646e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.251329478319065e-08</v>
+        <v>5.251329478319106e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.506278556012772e-08</v>
+        <v>5.506278556012998e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.486358679411035e-07</v>
+        <v>7.014069923360167e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.792922400453057e-08</v>
+        <v>5.792922400453317e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.152554654430574e-08</v>
+        <v>6.152554654430808e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.942611614467376e-08</v>
+        <v>5.942611614467515e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.911286669800409e-08</v>
+        <v>5.911286669800425e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.774128381974449e-08</v>
+        <v>5.774128381974481e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.547373669435473e-08</v>
+        <v>5.547373669435498e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.807948586454485e-08</v>
+        <v>5.807948586454509e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.845394520161967e-08</v>
+        <v>6.845394520162028e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>9.290180453545873e-08</v>
+        <v>9.290180453545907e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.913829725858536e-08</v>
+        <v>5.913829725858563e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.842740170804969e-08</v>
+        <v>5.842740170805003e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.170785317316336e-08</v>
+        <v>5.170785317316553e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.670576845968352e-08</v>
+        <v>5.670576845968384e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.451102558089679e-08</v>
+        <v>5.451102558089709e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2970,82 +2970,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.913094313816486e-07</v>
+        <v>1.913094313816483e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.876761274767926e-07</v>
+        <v>3.876761274767927e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.914242163806326e-07</v>
+        <v>1.914242163806324e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.916200117395174e-07</v>
+        <v>1.916200117395173e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.915815909148849e-07</v>
+        <v>1.915815909148843e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.913742610371141e-07</v>
+        <v>1.913742610371139e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.919403978972845e-07</v>
+        <v>1.919403978972842e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.913732908535181e-07</v>
+        <v>1.913732908535178e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.916572626889627e-07</v>
+        <v>1.916572626889625e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.912986136408564e-07</v>
+        <v>1.912986136408562e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.913452094182792e-07</v>
+        <v>1.913452094182788e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.914226162874085e-07</v>
+        <v>1.914226162874084e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.923425915917717e-07</v>
+        <v>1.923425915917716e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.911293194305202e-08</v>
+        <v>9.911293194305178e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.916597651944832e-07</v>
+        <v>1.916597651944829e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.917611109938486e-07</v>
+        <v>1.917611109938484e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.917279551173773e-07</v>
+        <v>1.91727955117377e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.916423715300256e-07</v>
+        <v>1.916423715300254e-07</v>
       </c>
       <c r="T2" t="n">
         <v>1.914842377197971e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.317439663636273e-07</v>
+        <v>4.317439663636271e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.917137749725431e-07</v>
+        <v>1.917137749725428e-07</v>
       </c>
       <c r="W2" t="n">
         <v>3.043186507286319e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.916317377945247e-07</v>
+        <v>1.916317377945245e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.915454552117534e-07</v>
+        <v>1.91545455211753e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.685396850957727e-07</v>
+        <v>1.685396850957723e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.916804138249575e-07</v>
+        <v>1.916804138249573e-07</v>
       </c>
       <c r="AB2" t="n">
         <v>1.913378556434556e-07</v>
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.119903769092884e-07</v>
+        <v>2.085263610566941e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.354082173891292e-07</v>
+        <v>4.133165492056445e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.14726654565298e-07</v>
+        <v>2.09504082213182e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7340141767141e-07</v>
+        <v>2.651878710492379e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.184420213796182e-07</v>
+        <v>2.107980977692419e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.134854762621054e-07</v>
+        <v>2.090310880037024e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.268968039136846e-07</v>
+        <v>2.138729471154538e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.135496688702935e-07</v>
+        <v>2.091164461649371e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.200912479905335e-07</v>
+        <v>2.113188530195966e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.117908753771949e-07</v>
+        <v>2.084876237075143e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.128425942769303e-07</v>
+        <v>2.088345585658407e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.149145561756604e-07</v>
+        <v>2.095747882275352e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.360681066670781e-07</v>
+        <v>2.169280748844761e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.203527390799268e-07</v>
+        <v>1.164966997061542e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.200335790634197e-07</v>
+        <v>2.112153048488154e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.22549807085911e-07</v>
+        <v>2.121494431325174e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.218706035117186e-07</v>
+        <v>2.120599414648901e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.196852830629766e-07</v>
+        <v>2.111233622735897e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.161359957778603e-07</v>
+        <v>2.100239481504803e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.66740011421936e-07</v>
+        <v>4.533628105597321e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.213083999540467e-07</v>
+        <v>2.116161477891792e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.953574948647239e-07</v>
+        <v>3.438051874741803e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.195571715631646e-07</v>
+        <v>2.111526682731128e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.175098970613175e-07</v>
+        <v>2.104703807352862e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.930236850353593e-07</v>
+        <v>1.868668693573293e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.206356767842482e-07</v>
+        <v>2.115478386153811e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.12828959360336e-07</v>
+        <v>2.088925850551701e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3146,85 +3146,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.610121648456436e-08</v>
+        <v>4.610121648456443e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.84513910106868e-07</v>
+        <v>2.845139101068685e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>7.300574496402431e-08</v>
+        <v>7.300574496402457e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.056132925479869e-07</v>
+        <v>1.056132925479868e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>1.067820580569235e-07</v>
+        <v>1.067820580569236e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>5.813898159174583e-08</v>
+        <v>5.813898159174471e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.923007416228709e-07</v>
+        <v>1.923007416228706e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>6.415586806021706e-08</v>
+        <v>6.415586806021726e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.164056913967182e-07</v>
+        <v>1.164056913967181e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.711443788739984e-08</v>
+        <v>4.71144378873997e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.472302774929395e-08</v>
+        <v>5.472302774929383e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>7.583496477380441e-08</v>
+        <v>7.583496477380448e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.619559071498786e-07</v>
+        <v>2.61955907149879e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>5.039669127311288e-08</v>
+        <v>5.039669127311249e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.08581864604262e-07</v>
+        <v>1.085818646042621e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.370118520718842e-07</v>
+        <v>1.370118520718841e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.422125747275381e-07</v>
+        <v>1.422125747275378e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.082327828142061e-07</v>
+        <v>1.08232782814206e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>8.769397759291344e-08</v>
+        <v>8.769397759291361e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.671395327926858e-07</v>
+        <v>1.67139532792685e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.17783965611673e-07</v>
+        <v>1.177839656116728e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>6.861905942926534e-07</v>
+        <v>6.861905942926529e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.137150760993184e-07</v>
+        <v>1.137150760993181e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.706382120040078e-08</v>
+        <v>9.706382120040057e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.398187105305898e-08</v>
+        <v>7.398187105305891e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.239253164639977e-07</v>
+        <v>1.23925316463998e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.977827051888933e-08</v>
+        <v>5.977827051888952e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3234,85 +3234,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.992210312872145e-08</v>
+        <v>1.992210312872178e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.87396759145222e-08</v>
+        <v>3.873967591452216e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.635766936437521e-08</v>
+        <v>2.635766936437545e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.583289312527055e-08</v>
+        <v>2.583289312527024e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.379686902157745e-08</v>
+        <v>2.379686902157775e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.685900940285762e-08</v>
+        <v>2.685900940285785e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.218817705018589e-08</v>
+        <v>3.218817705018575e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.578244210871693e-08</v>
+        <v>2.578244210871677e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.907392024507938e-08</v>
+        <v>2.90739202450797e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.493892863848689e-08</v>
+        <v>2.493892863848682e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.546524937959396e-08</v>
+        <v>2.546524937959382e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>2.644170323791251e-08</v>
+        <v>2.64417032379125e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.619559071498786e-07</v>
+        <v>3.27475420320102e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.246137598754238e-08</v>
+        <v>2.246137598754201e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.586108691686573e-08</v>
+        <v>2.586108691686548e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.401409802825806e-08</v>
+        <v>2.40140980282577e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>2.978853812262593e-08</v>
+        <v>2.978853812262585e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>2.882183213309616e-08</v>
+        <v>2.882183213309598e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.703563800142006e-08</v>
+        <v>2.703563800142013e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>2.973900741225141e-08</v>
+        <v>2.973900741225171e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.865667853515958e-08</v>
+        <v>2.865667853515955e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.085237047153042e-08</v>
+        <v>6.085237047152998e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>2.302376932567708e-08</v>
+        <v>2.302376932567734e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.264102572272659e-08</v>
+        <v>3.2641025722727e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.177747241399265e-08</v>
+        <v>2.177747241399246e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.925153735467265e-08</v>
+        <v>2.925153735467294e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.080587340056579e-08</v>
+        <v>3.08058734005655e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.103142062707821e-08</v>
+        <v>4.103142062707783e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.278463868168533e-08</v>
+        <v>6.278463868168522e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.040263213153869e-08</v>
+        <v>5.040263213153859e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.075063335242843e-08</v>
+        <v>5.075063335242834e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.356594706879796e-08</v>
+        <v>3.356594706879766e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.983836570046402e-08</v>
+        <v>4.983836570046378e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.623313981734894e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.982740487587988e-08</v>
+        <v>4.982740487587994e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.311888301224284e-08</v>
+        <v>5.311888301224291e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.898389140564975e-08</v>
+        <v>4.898389140565008e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.951021214675676e-08</v>
+        <v>4.951021214675693e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.048666600503261e-08</v>
+        <v>5.048666600503276e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.619559071498786e-07</v>
+        <v>6.07761026148246e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.207114463717626e-08</v>
+        <v>5.207114463717604e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.632116922371274e-08</v>
+        <v>5.632116922371232e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.420801392155076e-08</v>
+        <v>5.420801392155066e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.383350088978912e-08</v>
+        <v>5.38335008897891e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.286679490025872e-08</v>
+        <v>5.286679490025911e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.108060076858311e-08</v>
+        <v>5.10806007685832e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.640665245428928e-08</v>
+        <v>5.640665245428927e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.355037690130563e-08</v>
+        <v>6.355037690130559e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>8.489632328928859e-08</v>
+        <v>8.48963232892887e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.274668196601562e-08</v>
+        <v>5.274668196601574e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.177208050166373e-08</v>
+        <v>5.177208050166392e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.618860953886789e-08</v>
+        <v>4.618860953886758e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.3296500121836e-08</v>
+        <v>5.329650012183602e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.948270334452633e-08</v>
+        <v>4.948270334452588e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.919039232469923e-07</v>
+        <v>1.919039232469922e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.867442059629414e-07</v>
+        <v>3.867442059629415e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.929603303530226e-07</v>
+        <v>1.929603303530227e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.92090345034248e-07</v>
+        <v>1.920903450342481e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.919183257291438e-07</v>
+        <v>1.91918325729144e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.918116143141692e-07</v>
@@ -3587,43 +3587,43 @@
         <v>1.92552468814552e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.923847078979014e-07</v>
+        <v>1.923847078979017e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.921852070606705e-07</v>
+        <v>1.921852070606704e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.935814665063054e-07</v>
+        <v>1.935814665063055e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.924409944731805e-07</v>
+        <v>1.924409944731804e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.918418307412039e-07</v>
+        <v>1.918418307412041e-07</v>
       </c>
       <c r="N2" t="n">
         <v>1.933905813346994e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.003505885607572e-07</v>
+        <v>1.003505885607574e-07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.921175540319795e-07</v>
+        <v>1.921175540319797e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.924175618319344e-07</v>
+        <v>1.924175618319348e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.921795071840344e-07</v>
+        <v>1.921795071840346e-07</v>
       </c>
       <c r="S2" t="n">
         <v>1.925169364745473e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.921540030649077e-07</v>
+        <v>1.92154003064908e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.332570109708584e-07</v>
+        <v>4.332570109708586e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.919272332846801e-07</v>
@@ -3632,19 +3632,19 @@
         <v>3.056967473143483e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.927149930512536e-07</v>
+        <v>1.927149930512535e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.922250556782617e-07</v>
+        <v>1.922250556782619e-07</v>
       </c>
       <c r="Z2" t="n">
         <v>1.695694688126471e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.922642605364839e-07</v>
+        <v>1.922642605364842e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.919253013759641e-07</v>
+        <v>1.919253013759642e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.157030896213088e-07</v>
+        <v>2.101097230772225e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.057190053264023e-07</v>
+        <v>4.035005683072483e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.404647810334714e-07</v>
+        <v>2.187954804270509e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.74125926660909e-07</v>
+        <v>2.657378370975835e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.161735556594708e-07</v>
+        <v>2.103469701187316e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.135804577202295e-07</v>
+        <v>2.093964597278404e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.310824450273994e-07</v>
+        <v>2.156432193141598e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.270609318675555e-07</v>
+        <v>2.141637216770879e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.222674374664613e-07</v>
+        <v>2.123723015463053e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.548422676463275e-07</v>
+        <v>2.232982072813977e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.281549037138202e-07</v>
+        <v>2.142175851501943e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.146447297559858e-07</v>
+        <v>2.097935961251699e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.503386532973279e-07</v>
+        <v>2.220297266356312e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.263241004723473e-07</v>
+        <v>1.191985686378185e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.206046493058057e-07</v>
+        <v>2.117813121848123e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.277391910219194e-07</v>
+        <v>2.1424766198577e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.222912425593319e-07</v>
+        <v>2.125337575393825e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.298370898977966e-07</v>
+        <v>2.146397804798738e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.216445273848372e-07</v>
+        <v>2.122064046177835e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.766183225744501e-07</v>
+        <v>4.575344173613411e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.162487963444625e-07</v>
+        <v>2.102918546417637e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>4.006830102018838e-07</v>
+        <v>3.464385802537933e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.347128285242924e-07</v>
+        <v>2.167578296107403e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.232233712837302e-07</v>
+        <v>2.127426117383383e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.974788096663677e-07</v>
+        <v>1.890027552229167e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.241257699048715e-07</v>
+        <v>2.130691615464579e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.164377692439589e-07</v>
+        <v>2.104718464811421e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3742,85 +3742,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.63519700255795e-08</v>
+        <v>7.635197002561427e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.593606907846045e-08</v>
+        <v>3.593606907850656e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.19054850597469e-07</v>
+        <v>3.190548505974938e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.206044507924988e-07</v>
+        <v>1.206044507924775e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>8.812992787891882e-08</v>
+        <v>8.812992787893677e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.84179317654145e-08</v>
+        <v>5.841793176537713e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.397664065998513e-07</v>
+        <v>2.397664065998409e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.940476726133036e-07</v>
+        <v>1.940476726133209e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.374396649552568e-07</v>
+        <v>1.374396649552534e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.178777058652471e-07</v>
+        <v>4.178777058653158e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>1.774525521486991e-07</v>
+        <v>1.774525521488071e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>7.248522964366338e-08</v>
+        <v>7.24852296437288e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.960769572488257e-07</v>
+        <v>3.960769572488408e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>9.378113926833511e-08</v>
+        <v>9.378113926831771e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.19400977377211e-07</v>
+        <v>1.19400977377219e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.881343248886333e-07</v>
+        <v>1.881343248886498e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.510194953700679e-07</v>
+        <v>1.510194953701333e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.802775040176643e-07</v>
+        <v>1.802775040177308e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.366381938618837e-07</v>
+        <v>1.366381938618615e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.574124749946345e-07</v>
+        <v>2.574124749947624e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>8.155904474469823e-08</v>
+        <v>8.155904474469032e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>7.69264610776437e-07</v>
+        <v>7.692646107764846e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>2.61194087260708e-07</v>
+        <v>2.611940872607638e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.495964164596447e-07</v>
+        <v>1.495964164596294e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.10624626241401e-07</v>
+        <v>1.106246262414641e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.589384557198404e-07</v>
+        <v>1.589384557197867e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.303008596280271e-08</v>
+        <v>9.303008596277028e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3830,85 +3830,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.330558348800562e-08</v>
+        <v>2.330558348802851e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.68820976252371e-08</v>
+        <v>2.688209762524017e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.130501520613749e-08</v>
+        <v>4.130501520610797e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.824772414621697e-08</v>
+        <v>2.824772414617542e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.441340696451791e-08</v>
+        <v>2.441340696454571e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.958773531077056e-08</v>
+        <v>2.958773531079752e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.66980315035222e-08</v>
+        <v>3.669803150350495e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.480309477612077e-08</v>
+        <v>3.480309477610382e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.263195355717817e-08</v>
+        <v>3.263195355717684e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.832103379416406e-08</v>
+        <v>4.832103379418556e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.543887753701716e-08</v>
+        <v>3.543887753698209e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>2.880763911288126e-08</v>
+        <v>2.880763911283535e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.960769572488257e-07</v>
+        <v>4.146209170584698e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.708328886241221e-08</v>
+        <v>2.70832888624264e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.805824308451279e-08</v>
+        <v>2.805824308458412e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.791509752613503e-08</v>
+        <v>2.791509752615136e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.248525831596601e-08</v>
+        <v>3.248525831598401e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.629667737748457e-08</v>
+        <v>3.629667737746601e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.219717755794337e-08</v>
+        <v>3.21971775579745e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.630862993704433e-08</v>
+        <v>3.630862993695816e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.844682751920934e-08</v>
+        <v>2.844682751920967e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.557523084787878e-08</v>
+        <v>6.55752308479163e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.183075675547119e-08</v>
+        <v>3.183075675549495e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.8909105727848e-08</v>
+        <v>3.890910572791399e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.529807627487582e-08</v>
+        <v>2.529807627489198e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.344258642043464e-08</v>
+        <v>3.34425864203705e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.601487771909383e-08</v>
+        <v>3.601487771907934e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3918,85 +3918,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.236964832146271e-08</v>
+        <v>5.236964832141102e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.055775363179281e-08</v>
+        <v>6.055775363187838e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.498067121271165e-08</v>
+        <v>7.498067121274634e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.268925463472081e-08</v>
+        <v>6.268925463474563e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.859407465163727e-08</v>
+        <v>3.859407465158058e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.200539938280013e-08</v>
+        <v>6.200539938286801e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.037368751011476e-08</v>
+        <v>7.037368751014324e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.84787507827133e-08</v>
+        <v>6.847875078274203e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.630760956379851e-08</v>
+        <v>6.630760956381508e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.199668980088573e-08</v>
+        <v>8.199668980082373e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.911453354357293e-08</v>
+        <v>6.911453354362035e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.248329511942375e-08</v>
+        <v>6.248329511944446e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.960769572488257e-07</v>
+        <v>7.984055397601404e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.770819878613577e-08</v>
+        <v>6.77081987861687e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.976957623684101e-08</v>
+        <v>6.97695762369012e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.884985534562964e-08</v>
+        <v>6.884985534566172e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.616091432259543e-08</v>
+        <v>6.616091432262229e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>6.997233338404032e-08</v>
+        <v>6.997233338410427e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>6.587283356459139e-08</v>
+        <v>6.587283356461279e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>7.301717866901217e-08</v>
+        <v>7.301717866899735e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>7.618245339854712e-08</v>
+        <v>7.618245339854747e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>9.924969456851792e-08</v>
+        <v>9.924969456855658e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.22094735284829e-08</v>
+        <v>7.220947352852849e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.667540551825753e-08</v>
+        <v>6.667540551826037e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.871511900436685e-08</v>
+        <v>5.871511900441926e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.71182424269903e-08</v>
+        <v>6.711824242700876e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.335322513634791e-08</v>
+        <v>6.335322513639281e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4165,7 +4165,7 @@
         <v>1.909473009578242e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.86054286427707e-07</v>
+        <v>3.860542864277069e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.913113172479399e-07</v>
@@ -4180,13 +4180,13 @@
         <v>1.913214411825556e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.917507664924306e-07</v>
+        <v>1.917507664924305e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.911594333465389e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.913191809057546e-07</v>
+        <v>1.913191809057547e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.911926993689487e-07</v>
@@ -4195,13 +4195,13 @@
         <v>1.910649302121804e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.910928953848861e-07</v>
+        <v>1.910928953848862e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.914118440642809e-07</v>
+        <v>1.914118440642807e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.85586367672607e-08</v>
+        <v>9.855863676726073e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.911529523784736e-07</v>
@@ -4210,37 +4210,37 @@
         <v>1.910794744400206e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.911569953353582e-07</v>
+        <v>1.911569953353581e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.914868180225827e-07</v>
+        <v>1.914868180225826e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.910664271892812e-07</v>
+        <v>1.910664271892811e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.303260855644673e-07</v>
+        <v>4.303260855644672e-07</v>
       </c>
       <c r="V2" t="n">
         <v>1.913120451897072e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.02515768605565e-07</v>
+        <v>3.025157686055649e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.915765036039019e-07</v>
+        <v>1.915765036039018e-07</v>
       </c>
       <c r="Y2" t="n">
         <v>1.911099075733015e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.679758073360775e-07</v>
+        <v>1.679758073360774e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.91844625633212e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.909002319868468e-07</v>
+        <v>1.909002319868467e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.099334177405232e-07</v>
+        <v>2.075949164520135e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.07323280383634e-07</v>
+        <v>4.034383236829473e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.184570920692905e-07</v>
+        <v>2.105182024534228e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.660938789784834e-07</v>
+        <v>2.625275878025733e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.107599780222655e-07</v>
+        <v>2.079015810216288e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.185405911471727e-07</v>
+        <v>2.104134564872911e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.288473616323474e-07</v>
+        <v>2.142584584224565e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.149309597862787e-07</v>
+        <v>2.093483838111847e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.185478335246727e-07</v>
+        <v>2.10480755810435e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.156773613708625e-07</v>
+        <v>2.095400794716069e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.126658292224055e-07</v>
+        <v>2.084987019676851e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.135827396818674e-07</v>
+        <v>2.088338517577789e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.207543892693638e-07</v>
+        <v>2.112879134920971e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.197877841589644e-07</v>
+        <v>1.158847562769027e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.146561941601433e-07</v>
+        <v>2.091843283180044e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.130332242353325e-07</v>
+        <v>2.086272818901942e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.148884873500793e-07</v>
+        <v>2.093484771009143e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.223717101322371e-07</v>
+        <v>2.116444699159641e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.127502629902251e-07</v>
+        <v>2.085813197948219e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.508587139775338e-07</v>
+        <v>4.474515779366158e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.183379768447686e-07</v>
+        <v>2.1038398606853e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.723654918846363e-07</v>
+        <v>3.34841175223318e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.246236631491635e-07</v>
+        <v>2.12589353347301e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.137314358697752e-07</v>
+        <v>2.089180588122201e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.928025886439239e-07</v>
+        <v>1.863795812791513e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.307779133849295e-07</v>
+        <v>2.147918561446082e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.090241113681356e-07</v>
+        <v>2.073121624751278e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4338,85 +4338,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.280193240333588e-08</v>
+        <v>3.280193240333595e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.497314255220956e-08</v>
+        <v>5.497314255220954e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.062778290291278e-07</v>
+        <v>1.062778290291277e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>4.991132461114311e-08</v>
+        <v>4.991132461114319e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.211608429402859e-08</v>
+        <v>4.211608429402861e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.588203436812878e-08</v>
+        <v>9.588203436812893e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.092139452718081e-07</v>
+        <v>2.092139452718082e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.89738902211913e-08</v>
+        <v>7.897389022119121e-08</v>
       </c>
       <c r="J4" t="n">
         <v>1.012377072833715e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>8.059815168731011e-08</v>
+        <v>8.059815168731018e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.379559998389612e-08</v>
+        <v>5.379559998389602e-08</v>
       </c>
       <c r="M4" t="n">
         <v>6.436746248693611e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.240953718102561e-07</v>
+        <v>1.240953718102563e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>5.079968919692553e-08</v>
+        <v>5.079968919692555e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>7.022374184594779e-08</v>
+        <v>7.022374184594795e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.749266694282201e-08</v>
+        <v>5.749266694282202e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>7.979955246957942e-08</v>
+        <v>7.979955246957936e-08</v>
       </c>
       <c r="S4" t="n">
         <v>1.227133758326411e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>5.883148000373395e-08</v>
+        <v>5.883148000373403e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>4.613908460337274e-08</v>
+        <v>4.613908460337284e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.764027123011444e-08</v>
+        <v>9.764027123011434e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.661594131620692e-07</v>
+        <v>4.661594131620689e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.558878439014007e-07</v>
+        <v>1.558878439014012e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.681739375257308e-08</v>
+        <v>6.681739375257286e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.913393923445589e-08</v>
+        <v>7.913393923445576e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.135576169130119e-07</v>
+        <v>2.13557616913012e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.785441971593815e-08</v>
+        <v>2.785441971593814e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.845226265489703e-08</v>
+        <v>1.845226265489709e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.437494179791623e-08</v>
+        <v>2.437494179791619e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.734681726937426e-08</v>
+        <v>2.734681726937412e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.161167467979279e-08</v>
+        <v>2.161167467979282e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.95738406654287e-08</v>
+        <v>1.957384066542865e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.845292130691465e-08</v>
+        <v>2.84529213069146e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.231059864253666e-08</v>
+        <v>3.231059864253651e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.563121873300226e-08</v>
+        <v>2.56312187330022e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.751825135649393e-08</v>
+        <v>2.751825135649392e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.600697375924848e-08</v>
+        <v>2.600697375924832e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.456376235683412e-08</v>
+        <v>2.456376235683396e-08</v>
       </c>
       <c r="M5" t="n">
         <v>2.498217501584268e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.240953718102561e-07</v>
+        <v>2.477482580184476e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.169979979467214e-08</v>
+        <v>2.169979979467212e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.261963029769788e-08</v>
+        <v>2.261963029769791e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.900528902853668e-08</v>
+        <v>1.900528902853658e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>2.560368027517532e-08</v>
+        <v>2.56036802751753e-08</v>
       </c>
       <c r="S5" t="n">
         <v>2.932917925330882e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.45806714018315e-08</v>
+        <v>2.458067140183138e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>2.160907571199658e-08</v>
+        <v>2.160907571199654e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.651459175132615e-08</v>
+        <v>2.651459175132612e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.914064780527514e-08</v>
+        <v>4.914064780527512e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>2.505781731780161e-08</v>
+        <v>2.505781731780163e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.969809070069918e-08</v>
+        <v>2.969809070069924e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.135780019798845e-08</v>
+        <v>2.135780019798837e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.337078081499979e-08</v>
+        <v>3.337078081499973e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.777578448926606e-08</v>
+        <v>2.777578448926602e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.281658349934969e-08</v>
+        <v>4.281658349934964e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.277625414686275e-08</v>
+        <v>5.277625414686278e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.574812961832061e-08</v>
+        <v>5.574812961832067e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.052412413950354e-08</v>
+        <v>5.052412413950361e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.168078467877097e-08</v>
+        <v>3.168078467877102e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.586248686491129e-08</v>
+        <v>5.586248686491117e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.071191099148303e-08</v>
+        <v>6.071191099148313e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.403253108194882e-08</v>
+        <v>5.403253108194879e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.591956370544045e-08</v>
+        <v>5.591956370544051e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.440828610819491e-08</v>
+        <v>5.44082861081949e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.296507470578049e-08</v>
+        <v>5.296507470578052e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.338348736479173e-08</v>
+        <v>5.338348736479181e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.240953718102561e-07</v>
+        <v>5.688362625351167e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.571262902113164e-08</v>
+        <v>5.571262902113154e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.751787962601909e-08</v>
+        <v>5.751787962601902e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.312936119777723e-08</v>
+        <v>5.312936119777724e-08</v>
       </c>
       <c r="R6" t="n">
         <v>5.400499262412189e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.77304916022555e-08</v>
+        <v>5.773049160225546e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.298198375077784e-08</v>
+        <v>5.298198375077801e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.242032332195689e-08</v>
+        <v>5.242032332195703e-08</v>
       </c>
       <c r="V6" t="n">
         <v>6.648427952987235e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.754102020529751e-08</v>
+        <v>7.754102020529758e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.874353150066265e-08</v>
+        <v>5.874353150066268e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.347311469025319e-08</v>
+        <v>5.347311469025306e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.931321623938935e-08</v>
+        <v>4.931321623938929e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.17720931639462e-08</v>
+        <v>6.177209316394632e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.118103812423386e-08</v>
+        <v>5.118103812423393e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.906297950100283e-07</v>
+        <v>1.906297950100282e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.856192805237957e-07</v>
+        <v>3.856192805237958e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.909451165364546e-07</v>
@@ -4770,73 +4770,73 @@
         <v>1.906686181788065e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.906721446591395e-07</v>
+        <v>1.906721446591394e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.908644736575055e-07</v>
+        <v>1.908644736575054e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.913180623074894e-07</v>
+        <v>1.913180623074893e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.907951014782932e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.909262211197085e-07</v>
+        <v>1.909262211197084e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.907708535664786e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.907088379525225e-07</v>
+        <v>1.907088379525224e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.908212218252619e-07</v>
+        <v>1.90821221825262e-07</v>
       </c>
       <c r="N2" t="n">
         <v>1.910232813872205e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.789289591782495e-08</v>
+        <v>9.78928959178249e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.907172059165376e-07</v>
+        <v>1.907172059165375e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.906927725293586e-07</v>
+        <v>1.906927725293584e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.907380475503117e-07</v>
+        <v>1.907380475503119e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.910020727431126e-07</v>
+        <v>1.910020727431125e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.907833225120919e-07</v>
+        <v>1.907833225120918e-07</v>
       </c>
       <c r="U2" t="n">
         <v>4.297068706187978e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.911509576062785e-07</v>
+        <v>1.911509576062786e-07</v>
       </c>
       <c r="W2" t="n">
         <v>3.012101072168919e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.912635102495925e-07</v>
+        <v>1.912635102495923e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.907054400551606e-07</v>
+        <v>1.907054400551605e-07</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.673089909544723e-07</v>
+        <v>1.673089909544722e-07</v>
       </c>
       <c r="AA2" t="n">
         <v>1.914881136562468e-07</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.906476683123099e-07</v>
+        <v>1.906476683123098e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.098176192140911e-07</v>
+        <v>2.073293690167128e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.055661252747967e-07</v>
+        <v>4.025824970212181e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.172113952557057e-07</v>
+        <v>2.098873836043569e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.650712589978569e-07</v>
+        <v>2.620015025859824e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.108602227463274e-07</v>
+        <v>2.077172065171271e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.152208354659052e-07</v>
+        <v>2.091269479835196e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.260290281106291e-07</v>
+        <v>2.130287568247772e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.137252054123091e-07</v>
+        <v>2.087139210693474e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.167024050806344e-07</v>
+        <v>2.096655415630412e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.131379116153891e-07</v>
+        <v>2.084784620684423e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.116605709454549e-07</v>
+        <v>2.079490646058502e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.144977876294875e-07</v>
+        <v>2.089485932269734e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.189934320819378e-07</v>
+        <v>2.104921621627988e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.183683340451973e-07</v>
+        <v>1.149814183146875e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.118214587424036e-07</v>
+        <v>2.079977530355792e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.113136376873236e-07</v>
+        <v>2.078451755611793e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.124019857071677e-07</v>
+        <v>2.082648919431743e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.184108060150994e-07</v>
+        <v>2.1018508922831e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.134419284917123e-07</v>
+        <v>2.086041558116785e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.533283416904451e-07</v>
+        <v>4.477476432533631e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.218292697545637e-07</v>
+        <v>2.113395521748675e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.608666407754077e-07</v>
+        <v>3.304838641499359e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.246119141633732e-07</v>
+        <v>2.123313285878319e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.115986627591757e-07</v>
+        <v>2.079620910015213e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.898441545631688e-07</v>
+        <v>1.850032752393811e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.297602195652762e-07</v>
+        <v>2.142277215751934e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.103681092359486e-07</v>
+        <v>2.075601823527917e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4934,85 +4934,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.447325312567585e-08</v>
+        <v>3.447325312567592e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.3396272135783e-08</v>
+        <v>4.339627213578269e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.986063933569873e-08</v>
+        <v>9.986063933569854e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.278240289523097e-08</v>
+        <v>4.278240289523077e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.619574751797777e-08</v>
+        <v>4.619574751797775e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.605375450607228e-08</v>
+        <v>7.605375450607308e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.849809937736946e-07</v>
+        <v>1.849809937736947e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.166906487561589e-08</v>
+        <v>7.16690648756161e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.145743010028244e-08</v>
+        <v>9.145743010028228e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.402961620501897e-08</v>
+        <v>6.402961620501896e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.94133067768334e-08</v>
+        <v>4.941330677683344e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>7.671465965043762e-08</v>
+        <v>7.671465965043765e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.141496045286518e-07</v>
+        <v>1.141496045286516e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>4.475395301354934e-08</v>
+        <v>4.475395301354945e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>4.989505224926238e-08</v>
+        <v>4.98950522492621e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.783743123702675e-08</v>
+        <v>4.783743123702669e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.075671294697093e-08</v>
+        <v>6.075671294697047e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.006840411303249e-07</v>
+        <v>1.00684041130325e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>6.826929610747726e-08</v>
+        <v>6.826929610747729e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>7.048863346441798e-08</v>
+        <v>7.048863346441793e-08</v>
       </c>
       <c r="V4" t="n">
         <v>1.285948698572045e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.863119850441992e-07</v>
+        <v>3.863119850441995e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.565161059380309e-07</v>
+        <v>1.565161059380307e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.144682484687007e-08</v>
+        <v>5.144682484687015e-08</v>
       </c>
       <c r="Z4" t="n">
         <v>6.022046343253058e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.083365742036315e-07</v>
+        <v>2.083365742036316e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.283769815715744e-08</v>
+        <v>4.283769815715739e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5022,85 +5022,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.796366432112696e-08</v>
+        <v>1.796366432112694e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.277624917374646e-08</v>
+        <v>2.277624917374643e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.597160307701966e-08</v>
+        <v>2.597160307701961e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.048093685530032e-08</v>
+        <v>2.048093685530037e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.913469485799426e-08</v>
+        <v>1.913469485799404e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.598266087984023e-08</v>
+        <v>2.598266087984043e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.018419712438741e-08</v>
+        <v>3.018419712438731e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.427711398475202e-08</v>
+        <v>2.427711398475232e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.584248354959297e-08</v>
+        <v>2.58424835495931e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.400322266621406e-08</v>
+        <v>2.400322266621411e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.330272777798871e-08</v>
+        <v>2.330272777798886e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>2.465017348003738e-08</v>
+        <v>2.465017348003751e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.141496045286518e-07</v>
+        <v>2.340793346063368e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.057319053334217e-08</v>
+        <v>2.057319053334208e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.066565044044951e-08</v>
+        <v>2.066565044044935e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.780123731305646e-08</v>
+        <v>1.780123731305667e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>2.363266362209736e-08</v>
+        <v>2.363266362209731e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>2.661494963237102e-08</v>
+        <v>2.661494963237116e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.414406514291437e-08</v>
+        <v>2.414406514291424e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>2.242306443626943e-08</v>
+        <v>2.24230644362691e-08</v>
       </c>
       <c r="V5" t="n">
         <v>2.7559020995344e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.301185131631147e-08</v>
+        <v>4.301185131631123e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>2.465548887039512e-08</v>
+        <v>2.465548887039514e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.755497596818153e-08</v>
+        <v>2.755497596818125e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.959740620139259e-08</v>
+        <v>1.959740620139252e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.210500533608943e-08</v>
+        <v>3.210500533608917e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.730221097848329e-08</v>
+        <v>2.730221097848328e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5110,85 +5110,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.961224868487962e-08</v>
+        <v>3.961224868487929e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.790086111296438e-08</v>
+        <v>4.790086111296436e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.109621501623759e-08</v>
+        <v>5.109621501623725e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.61446138691821e-08</v>
+        <v>4.614461386918208e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.974988760263465e-08</v>
+        <v>2.974988760263435e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.018531837110039e-08</v>
+        <v>5.018531837110009e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.530880906360533e-08</v>
+        <v>5.530880906360542e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.940172592396994e-08</v>
+        <v>4.94017259239698e-08</v>
       </c>
       <c r="J6" t="n">
         <v>5.096709548881086e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.912783460543197e-08</v>
+        <v>4.912783460543203e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.842733971720662e-08</v>
+        <v>4.842733971720649e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.977478541927735e-08</v>
+        <v>4.977478541927724e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.141496045286518e-07</v>
+        <v>5.197912296324704e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.08226610843532e-08</v>
+        <v>5.0822661084353e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.171827590420741e-08</v>
+        <v>5.171827590420744e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.824587514225892e-08</v>
+        <v>4.824587514225858e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.875727556131529e-08</v>
+        <v>4.875727556131505e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.173956157158894e-08</v>
+        <v>5.173956157158879e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.926867708213227e-08</v>
+        <v>4.926867708213211e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.979391268598017e-08</v>
+        <v>4.979391268598008e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.312490416957567e-08</v>
+        <v>6.312490416957564e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.813558945294927e-08</v>
+        <v>6.813558945294912e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.46926184744744e-08</v>
+        <v>5.469261847447435e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.838895890339232e-08</v>
+        <v>4.838895890339233e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.447442593883508e-08</v>
+        <v>4.447442593883492e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.722961727530736e-08</v>
+        <v>5.722961727530742e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.778235652982946e-08</v>
+        <v>4.778235652982907e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5357,79 +5357,79 @@
         <v>1.925485695005698e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.87439003579749e-07</v>
+        <v>3.874390035797493e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.934176062620633e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.924391463895075e-07</v>
+        <v>1.924391463895074e-07</v>
       </c>
       <c r="F2" t="n">
         <v>1.928179052831027e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.923013066671214e-07</v>
+        <v>1.923013066671215e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.932895357261792e-07</v>
+        <v>1.932895357261793e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.938341188091688e-07</v>
+        <v>1.93834118809169e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.927932006075033e-07</v>
+        <v>1.927932006075031e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.950988045021478e-07</v>
+        <v>1.950988045021477e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.924341699085683e-07</v>
+        <v>1.924341699085686e-07</v>
       </c>
       <c r="M2" t="n">
-        <v>1.92436872254927e-07</v>
+        <v>1.924368722549269e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.953174520150267e-07</v>
+        <v>1.95317452015027e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>1.016766982274252e-07</v>
+        <v>1.016766982274253e-07</v>
       </c>
       <c r="P2" t="n">
         <v>1.927946241768655e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.932505709122027e-07</v>
+        <v>1.93250570912203e-07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.930230438907847e-07</v>
+        <v>1.930230438907848e-07</v>
       </c>
       <c r="S2" t="n">
         <v>1.929824414518636e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.932675586043944e-07</v>
+        <v>1.932675586043945e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>4.336732248687209e-07</v>
+        <v>4.33673224868721e-07</v>
       </c>
       <c r="V2" t="n">
-        <v>1.927066733063338e-07</v>
+        <v>1.927066733063337e-07</v>
       </c>
       <c r="W2" t="n">
         <v>3.062666133962429e-07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.931472613835278e-07</v>
+        <v>1.93147261383528e-07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.92982568054539e-07</v>
+        <v>1.929825680545389e-07</v>
       </c>
       <c r="Z2" t="n">
         <v>1.706943211028291e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.927526084565181e-07</v>
+        <v>1.927526084565182e-07</v>
       </c>
       <c r="AB2" t="n">
         <v>1.924034321552729e-07</v>
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.185813976337818e-07</v>
+        <v>2.114785146311478e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.085865839706381e-07</v>
+        <v>4.049166876351176e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.390087754872284e-07</v>
+        <v>2.187368380412542e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.699592637544769e-07</v>
+        <v>2.645626116252318e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.250659821466839e-07</v>
+        <v>2.138303744674575e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.128922203194126e-07</v>
+        <v>2.095737242476285e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.36177397650107e-07</v>
+        <v>2.178344592628523e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.487906380506303e-07</v>
+        <v>2.221411451106183e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.243248521742917e-07</v>
+        <v>2.135020370949206e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.780568009574093e-07</v>
+        <v>2.314728331280504e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.159879569743298e-07</v>
+        <v>2.106373996371652e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.164151721910793e-07</v>
+        <v>2.107985178672863e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.830861734662574e-07</v>
+        <v>2.339282021260325e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.315094050069504e-07</v>
+        <v>1.217383977414266e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.242270658522671e-07</v>
+        <v>2.134180803448959e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.350352893401781e-07</v>
+        <v>2.171995943193958e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.298692948114273e-07</v>
+        <v>2.155897436737704e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.286079308312883e-07</v>
+        <v>2.147796561219854e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.355175482116319e-07</v>
+        <v>2.175056759135854e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.63112011650603e-07</v>
+        <v>4.537112917842688e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.222360238276592e-07</v>
+        <v>2.126886341576919e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.898073267914836e-07</v>
+        <v>3.434324282082776e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.326716632631136e-07</v>
+        <v>2.164704923058939e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.28741193362773e-07</v>
+        <v>2.15029627472362e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.993173118776917e-07</v>
+        <v>1.904249467613763e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.233950090117468e-07</v>
+        <v>2.132105924274638e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.155086168915709e-07</v>
+        <v>2.105577074250535e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5530,37 +5530,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.663135425360773e-08</v>
+        <v>9.663135425360843e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.715170677477674e-08</v>
+        <v>5.715170677477684e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.044629528497311e-07</v>
+        <v>3.044629528497316e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.957701697498957e-08</v>
+        <v>7.957701697499017e-08</v>
       </c>
       <c r="F4" t="n">
         <v>1.682717250817662e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.902160015537818e-08</v>
+        <v>4.902160015537729e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.857704311834079e-07</v>
+        <v>2.857704311834078e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.986421491914386e-07</v>
+        <v>3.986421491914388e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.537924581831907e-07</v>
+        <v>1.537924581831906e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.118393031673947e-07</v>
+        <v>6.118393031673946e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>7.74767394806866e-08</v>
+        <v>7.747673948068972e-08</v>
       </c>
       <c r="M4" t="n">
         <v>8.43152167391248e-08</v>
@@ -5569,46 +5569,46 @@
         <v>7.103138991320344e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.278332107413651e-07</v>
+        <v>1.278332107413652e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>1.472572403199394e-07</v>
+        <v>1.472572403199395e-07</v>
       </c>
       <c r="Q4" t="n">
         <v>2.542015115407702e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>2.207265068410057e-07</v>
+        <v>2.207265068410053e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.770878537097452e-07</v>
+        <v>1.770878537097451e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.70132600659779e-07</v>
+        <v>2.701326006597791e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32386191216995e-07</v>
+        <v>1.323861912169963e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.270351017462425e-07</v>
+        <v>1.270351017462413e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>6.589376799850933e-07</v>
+        <v>6.589376799850934e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>2.391674846502816e-07</v>
+        <v>2.391674846502815e-07</v>
       </c>
       <c r="Y4" t="n">
         <v>1.95102495881226e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.203110674814965e-07</v>
+        <v>1.203110674814963e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.474396625705866e-07</v>
+        <v>1.47439662570587e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.066047423840321e-08</v>
+        <v>8.066047423840315e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5618,85 +5618,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.586574378114071e-08</v>
+        <v>2.58657437811407e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.986928784442124e-08</v>
+        <v>2.986928784442125e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.222083808614613e-08</v>
+        <v>4.222083808614619e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.768689940868778e-08</v>
+        <v>2.768689940868783e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.992670332785089e-08</v>
+        <v>2.992670332785091e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.096760918862463e-08</v>
+        <v>3.09676091886246e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.077422246797761e-08</v>
+        <v>4.077422246797763e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.69255389109393e-08</v>
+        <v>4.692553891093928e-08</v>
       </c>
       <c r="J5" t="n">
         <v>3.525221779692185e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.121074559729867e-08</v>
+        <v>6.121074559729871e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.111247207034688e-08</v>
+        <v>3.111247207034692e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.128728631811916e-08</v>
+        <v>3.128728631811915e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.103138991320344e-07</v>
+        <v>5.861170955602705e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.068631283747177e-08</v>
+        <v>3.068631283747181e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.116670480576254e-08</v>
+        <v>3.116670480576257e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.251012479783782e-08</v>
+        <v>3.251012479783783e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.776407459489375e-08</v>
+        <v>3.776407459489374e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.730545136923624e-08</v>
+        <v>3.730545136923627e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.052598076744379e-08</v>
+        <v>4.052598076744378e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.092318170284436e-08</v>
+        <v>3.092318170284449e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.296087908935441e-08</v>
+        <v>3.296087908935442e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.163706326116208e-08</v>
+        <v>6.163706326116211e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.194250153912475e-08</v>
+        <v>3.194250153912484e-08</v>
       </c>
       <c r="Y5" t="n">
         <v>4.380163304405822e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.7066728328155e-08</v>
+        <v>2.706672832815503e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.470938195840872e-08</v>
+        <v>3.470938195840874e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.768251347617708e-08</v>
+        <v>3.768251347617702e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5706,52 +5706,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.500902835535107e-08</v>
+        <v>5.500902835535112e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.337945750244658e-08</v>
+        <v>6.337945750244661e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.573100774417152e-08</v>
+        <v>7.573100774417159e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.216184010296355e-08</v>
+        <v>6.216184010296364e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.381623699976143e-08</v>
+        <v>4.381623699976144e-08</v>
       </c>
       <c r="G6" t="n">
         <v>6.312189426979438e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.428439212600295e-08</v>
+        <v>7.428439212600302e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.043570856896466e-08</v>
+        <v>8.043570856896482e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.876238745494718e-08</v>
+        <v>6.876238745494725e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.4720915255324e-08</v>
+        <v>9.472091525532404e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.462264172837233e-08</v>
+        <v>6.462264172837234e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.479745597612362e-08</v>
+        <v>6.479745597612359e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.103138991320344e-07</v>
+        <v>9.719063949611896e-08</v>
       </c>
       <c r="O6" t="n">
         <v>7.148647969482563e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>7.309433520854222e-08</v>
+        <v>7.309433520854233e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.384427060111499e-08</v>
+        <v>7.384427060111503e-08</v>
       </c>
       <c r="R6" t="n">
         <v>7.127424425291916e-08</v>
@@ -5760,22 +5760,22 @@
         <v>7.081562102726168e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>7.403615042546926e-08</v>
+        <v>7.403615042546918e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.762885993114401e-08</v>
+        <v>6.762885993114409e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>8.084766279665021e-08</v>
+        <v>8.084766279665023e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>9.514594785503973e-08</v>
+        <v>9.514594785503978e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.26773379763249e-08</v>
+        <v>7.267733797632494e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.081705106272045e-08</v>
+        <v>7.081705106272053e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>6.066205446527613e-08</v>
@@ -5784,7 +5784,7 @@
         <v>6.821955161643413e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.436222993939721e-08</v>
+        <v>6.436222993939722e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5950,37 +5950,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.914031731661055e-07</v>
+        <v>1.914031731661057e-07</v>
       </c>
       <c r="C2" t="n">
         <v>3.866094855063515e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.917342583615848e-07</v>
+        <v>1.917342583615846e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.916324828784902e-07</v>
+        <v>1.916324828784901e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.913705170559155e-07</v>
+        <v>1.913705170559154e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.916742924003953e-07</v>
+        <v>1.916742924003951e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.922318115789255e-07</v>
+        <v>1.922318115789257e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.91563921532142e-07</v>
+        <v>1.915639215321419e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.917820686677881e-07</v>
+        <v>1.917820686677882e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.918736682173333e-07</v>
+        <v>1.918736682173331e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.915164123602483e-07</v>
+        <v>1.915164123602482e-07</v>
       </c>
       <c r="M2" t="n">
         <v>1.915041244382291e-07</v>
@@ -5989,22 +5989,22 @@
         <v>1.921250765529018e-07</v>
       </c>
       <c r="O2" t="n">
-        <v>9.929433433599348e-08</v>
+        <v>9.929433433599344e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.919357067822419e-07</v>
+        <v>1.919357067822418e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.918178743232619e-07</v>
+        <v>1.918178743232618e-07</v>
       </c>
       <c r="R2" t="n">
         <v>1.916551109538884e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.919259766721307e-07</v>
+        <v>1.919259766721305e-07</v>
       </c>
       <c r="T2" t="n">
-        <v>1.915083258108899e-07</v>
+        <v>1.9150832581089e-07</v>
       </c>
       <c r="U2" t="n">
         <v>4.314549636322187e-07</v>
@@ -6013,7 +6013,7 @@
         <v>1.917945453927382e-07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.042148538077041e-07</v>
+        <v>3.042148538077039e-07</v>
       </c>
       <c r="X2" t="n">
         <v>1.921036545096477e-07</v>
@@ -6025,7 +6025,7 @@
         <v>1.689553006858137e-07</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.917776190974781e-07</v>
+        <v>1.91777619097478e-07</v>
       </c>
       <c r="AB2" t="n">
         <v>1.917714520749581e-07</v>
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.110394638995504e-07</v>
+        <v>2.083053812288796e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.096315189857305e-07</v>
+        <v>4.045923496130457e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.188085361583495e-07</v>
+        <v>2.110150336128446e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.704927881100586e-07</v>
+        <v>2.642931695986764e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.103311772894331e-07</v>
+        <v>2.08090270281866e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.172805229358576e-07</v>
+        <v>2.103736882150406e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.305647341423761e-07</v>
+        <v>2.152541713850875e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.148472601590791e-07</v>
+        <v>2.096681547573113e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.198298454592267e-07</v>
+        <v>2.112982675320858e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.220264699939674e-07</v>
+        <v>2.11987663149782e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.136763900669954e-07</v>
+        <v>2.091997490729844e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.136732239140349e-07</v>
+        <v>2.09224882892463e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.278634553794308e-07</v>
+        <v>2.141627885277674e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.192831965374635e-07</v>
+        <v>1.163025313033834e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.232748260935041e-07</v>
+        <v>2.124242243314869e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.207171284749619e-07</v>
+        <v>2.115554252465425e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.169965378337495e-07</v>
+        <v>2.104338082088646e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.231027711322295e-07</v>
+        <v>2.122962844096346e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.135407500788145e-07</v>
+        <v>2.092046558025204e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.530152027256924e-07</v>
+        <v>4.489559133985331e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.200595554121271e-07</v>
+        <v>2.11304490686821e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.856934881515872e-07</v>
+        <v>3.40665770753309e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.274075112719132e-07</v>
+        <v>2.13944513803007e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.179189303143734e-07</v>
+        <v>2.106866983570403e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.942839793150556e-07</v>
+        <v>1.875679456006442e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.197546227303426e-07</v>
+        <v>2.113296698430753e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.19709237123811e-07</v>
+        <v>2.114019627891631e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6126,79 +6126,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.796820625723574e-08</v>
+        <v>3.796820625723557e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.996559347618122e-08</v>
+        <v>6.996559347618124e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.082342570934904e-07</v>
+        <v>1.082342570934903e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>8.481251452942522e-08</v>
+        <v>8.481251452942552e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.450149458262933e-08</v>
+        <v>3.450149458262943e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.543490185612345e-08</v>
+        <v>8.543490185612363e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.250887148731523e-07</v>
+        <v>2.250887148731526e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.524337911009904e-08</v>
+        <v>7.52433791100992e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.112575403972643e-07</v>
+        <v>1.112575403972644e-07</v>
       </c>
       <c r="K4" t="n">
         <v>1.264356577452354e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.982477184514884e-08</v>
+        <v>5.982477184514889e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.296863306929066e-08</v>
+        <v>6.296863306929082e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.878970781769269e-07</v>
+        <v>1.87897078176927e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>4.072454369604184e-08</v>
+        <v>4.072454369604245e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.350719471007229e-07</v>
+        <v>1.350719471007232e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.162562278245027e-07</v>
+        <v>1.162562278245024e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>9.589985987436877e-08</v>
+        <v>9.589985987436867e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.296293805847621e-07</v>
+        <v>1.29629380584762e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>6.286854239615528e-08</v>
+        <v>6.286854239615518e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.485313192733448e-08</v>
+        <v>5.485313192733462e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.079410947243117e-07</v>
+        <v>1.079410947243116e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>5.987673669554029e-07</v>
+        <v>5.987673669554026e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.803525303709388e-07</v>
+        <v>1.803525303709386e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.835280654962798e-08</v>
+        <v>9.835280654962772e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.305247070496125e-08</v>
+        <v>8.30524707049611e-08</v>
       </c>
       <c r="AA4" t="n">
         <v>1.148052640359592e-07</v>
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.974070716511887e-08</v>
+        <v>1.974070716511896e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.66365113605199e-08</v>
+        <v>2.663651136051984e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.868112606750669e-08</v>
+        <v>2.868112606750685e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.476232749580723e-08</v>
+        <v>2.476232749580725e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.01820433156473e-08</v>
+        <v>2.01820433156472e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.908217353660473e-08</v>
+        <v>2.908217353660478e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.430121854316121e-08</v>
+        <v>3.43012185431611e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.675709322013799e-08</v>
+        <v>2.67570932201379e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.930460777659602e-08</v>
+        <v>2.930460777659628e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.025582451988876e-08</v>
+        <v>3.025582451988863e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.622045526830056e-08</v>
+        <v>2.622045526830047e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>2.619213251202703e-08</v>
+        <v>2.619213251202694e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.878970781769269e-07</v>
+        <v>2.906421630088339e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.220041607941736e-08</v>
+        <v>2.220041607941729e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.776149324044451e-08</v>
+        <v>2.776149324044469e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.340289925703179e-08</v>
+        <v>2.340289925703192e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>2.778711968797078e-08</v>
+        <v>2.778711968797087e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.084667257990262e-08</v>
+        <v>3.084667257990253e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.612911397330081e-08</v>
+        <v>2.61291139733007e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>2.332880464601667e-08</v>
+        <v>2.332880464601659e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.844214337130488e-08</v>
+        <v>2.844214337130492e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.640446441412272e-08</v>
+        <v>5.640446441412267e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>2.710756867798461e-08</v>
+        <v>2.710756867798458e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.336165088531768e-08</v>
+        <v>3.336165088531788e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.256219227880579e-08</v>
+        <v>2.256219227880589e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.917090552634578e-08</v>
+        <v>2.917090552634571e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.454391231275359e-08</v>
+        <v>3.454391231275368e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6302,85 +6302,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.383697950410006e-08</v>
+        <v>4.383697950409999e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.445967353159746e-08</v>
+        <v>5.445967353159756e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.650428823858471e-08</v>
+        <v>5.650428823858454e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.329424753713391e-08</v>
+        <v>5.329424753713394e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.181522191435164e-08</v>
+        <v>3.181522191435173e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.582694788638208e-08</v>
+        <v>5.582694788638204e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.212438071423863e-08</v>
+        <v>6.212438071423884e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.458025539121581e-08</v>
+        <v>5.458025539121561e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7127769947674e-08</v>
+        <v>5.712776994767396e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.807898669096651e-08</v>
+        <v>5.807898669096635e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.404361743937845e-08</v>
+        <v>5.40436174393782e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.401529468307677e-08</v>
+        <v>5.401529468307661e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.878970781769269e-07</v>
+        <v>6.091875949476191e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.590568255084003e-08</v>
+        <v>5.590568255083993e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.238176277396092e-08</v>
+        <v>6.238176277396076e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.744877175610792e-08</v>
+        <v>5.744877175610788e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.561028185904871e-08</v>
+        <v>5.561028185904859e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.866983475098049e-08</v>
+        <v>5.866983475098025e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.395227614437863e-08</v>
+        <v>5.395227614437842e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.373958161932881e-08</v>
+        <v>5.373958161932865e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.804324027651775e-08</v>
+        <v>6.804324027651776e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>8.422660452219611e-08</v>
+        <v>8.422660452219607e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.067678766157892e-08</v>
+        <v>6.067678766157877e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.609815529115362e-08</v>
+        <v>5.609815529115368e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.030010151042577e-08</v>
+        <v>5.030010151042576e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.699406769742361e-08</v>
+        <v>5.699406769742343e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.693455097393611e-08</v>
+        <v>5.693455097393591e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia ozone depletion results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.13405988320553e-07</v>
+        <v>2.121922843319745e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.099961486506565e-07</v>
+        <v>4.082581675746128e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.270161560778295e-07</v>
+        <v>2.214390650858011e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.656145771738582e-07</v>
+        <v>2.647809373096245e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.24300146310409e-07</v>
+        <v>2.194970138331248e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.114241239395053e-07</v>
+        <v>2.107696255627437e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.246285912703019e-07</v>
+        <v>2.196600237227506e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.316543912256372e-07</v>
+        <v>2.245696291032198e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.167360085278212e-07</v>
+        <v>2.144596906400641e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.49741907515986e-07</v>
+        <v>2.371249796096522e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.166126095137477e-07</v>
+        <v>2.143802212106573e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.132022054495236e-07</v>
+        <v>2.119285638260805e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.464885965030176e-07</v>
+        <v>2.350566495935165e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.268781886800916e-07</v>
+        <v>1.246946187327168e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.171354053309158e-07</v>
+        <v>2.148337999462288e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.250222822176026e-07</v>
+        <v>2.201420579844403e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.213572934339842e-07</v>
+        <v>2.17486200175114e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.165029696931147e-07</v>
+        <v>2.143602591377907e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.287712354178095e-07</v>
+        <v>2.22628222415763e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.584193765713243e-07</v>
+        <v>4.562158966574099e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.151095102995643e-07</v>
+        <v>2.133961350895211e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.447051510107158e-07</v>
+        <v>3.376037986182456e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.159780846282698e-07</v>
+        <v>2.138733074762206e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.179340358411825e-07</v>
+        <v>2.152853145026624e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.927754322516623e-07</v>
+        <v>1.91289054251969e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.156423645847405e-07</v>
+        <v>2.136812319733089e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.121352915443387e-07</v>
+        <v>2.111799400547851e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.075732721493475e-07</v>
+        <v>2.073462872292202e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.05198231304908e-07</v>
+        <v>4.041853706931151e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.10147706059425e-07</v>
+        <v>2.091323269194386e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.623635839147927e-07</v>
+        <v>2.619637713042483e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.07966407544395e-07</v>
+        <v>2.076019973737137e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.099361201382828e-07</v>
+        <v>2.090521363153027e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.131625115867486e-07</v>
+        <v>2.111430546245085e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0882999937546e-07</v>
+        <v>2.081981293908156e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.107294507905838e-07</v>
+        <v>2.095789814562713e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.10313232281311e-07</v>
+        <v>2.092902469809762e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.092780771400677e-07</v>
+        <v>2.085601804029791e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.091378146479568e-07</v>
+        <v>2.084118009022185e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.119455561330383e-07</v>
+        <v>2.103662114303228e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.155446354098556e-07</v>
+        <v>1.151922070643549e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.105608908541713e-07</v>
+        <v>2.095035965918226e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.087071607548543e-07</v>
+        <v>2.081386574539551e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.09060777973564e-07</v>
+        <v>2.083472865990489e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.104805804439055e-07</v>
+        <v>2.094411024612976e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.090224138829946e-07</v>
+        <v>2.083306125441434e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.498493680577051e-07</v>
+        <v>4.488207571563585e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.119440690362176e-07</v>
+        <v>2.104976665551919e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.364935314759444e-07</v>
+        <v>3.303822104495471e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.124995522526699e-07</v>
+        <v>2.108012086349312e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.098333104280901e-07</v>
+        <v>2.08909935189393e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.878133424186407e-07</v>
+        <v>1.866962572870609e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.157843212931048e-07</v>
+        <v>2.130545441940243e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.076941214137347e-07</v>
+        <v>2.074043442301375e-07</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.106692936497212e-07</v>
+        <v>2.100245583931381e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.080532108094612e-07</v>
+        <v>4.066931313662451e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.146913890461888e-07</v>
+        <v>2.127349728532239e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.661515533650173e-07</v>
+        <v>2.649735126651422e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.166928704993198e-07</v>
+        <v>2.141037688033431e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.10051739766356e-07</v>
+        <v>2.095781424473371e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.186894733602291e-07</v>
+        <v>2.153979609823289e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.216710431043923e-07</v>
+        <v>2.17497425880762e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.141481964855461e-07</v>
+        <v>2.124285164804451e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.404104488100044e-07</v>
+        <v>2.309225551647746e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.110364122209833e-07</v>
+        <v>2.102547212159639e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.110555872681529e-07</v>
+        <v>2.102238556282462e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.319065855316734e-07</v>
+        <v>2.247141854775061e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.222899110246747e-07</v>
+        <v>1.209850975906636e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.137466346579479e-07</v>
+        <v>2.122103104850491e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.190817388118242e-07</v>
+        <v>2.158118748247431e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.174852577500989e-07</v>
+        <v>2.146064388800943e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.137270266890158e-07</v>
+        <v>2.1218469070109e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.156368486068315e-07</v>
+        <v>2.133855632077344e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.538439746469399e-07</v>
+        <v>4.526777768014838e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.129078116892193e-07</v>
+        <v>2.11635836801876e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.521450264026486e-07</v>
+        <v>3.424762958455477e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.154000288497497e-07</v>
+        <v>2.132473052227293e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.178546023824531e-07</v>
+        <v>2.150211446741795e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.909712998651148e-07</v>
+        <v>1.897327147970298e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.133220105832131e-07</v>
+        <v>2.118434304701633e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.11089909007389e-07</v>
+        <v>2.102298933416809e-07</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.086711363308364e-07</v>
+        <v>2.083314876861613e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.128794328397752e-07</v>
+        <v>4.098385634039759e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.149300759066171e-07</v>
+        <v>2.126216624748919e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.681088679434086e-07</v>
+        <v>2.66152156205671e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.104971800241319e-07</v>
+        <v>2.095644730629446e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.091377260996676e-07</v>
+        <v>2.086616662813398e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.149381865956808e-07</v>
+        <v>2.125434310020548e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.112905040533467e-07</v>
+        <v>2.101007683106517e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.120994913537127e-07</v>
+        <v>2.107222753411609e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.095804036164729e-07</v>
+        <v>2.089559728726012e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.082398200972522e-07</v>
+        <v>2.080196543942607e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.101022093189729e-07</v>
+        <v>2.092793228612494e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.208451408621333e-07</v>
+        <v>2.167528894822201e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18195921922766e-07</v>
+        <v>1.175192621620578e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.119436649663904e-07</v>
+        <v>2.106688837735321e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.131532322273288e-07</v>
+        <v>2.114410744080698e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.130787720815767e-07</v>
+        <v>2.113069794859617e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.118521507266752e-07</v>
+        <v>2.105917980085997e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.103963702553836e-07</v>
+        <v>2.094922481124134e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.525953013633898e-07</v>
+        <v>4.512325743966703e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.116567281146485e-07</v>
+        <v>2.104859534365045e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.474990263209796e-07</v>
+        <v>3.386078647533312e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.129977599404205e-07</v>
+        <v>2.11305436999505e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.124293494002555e-07</v>
+        <v>2.1094425018199e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.890250857492975e-07</v>
+        <v>1.879415667438436e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.112183441796475e-07</v>
+        <v>2.100939100210061e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.097367523692956e-07</v>
+        <v>2.090134797236908e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.085263610566941e-07</v>
+        <v>2.080880150316926e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.133165492056445e-07</v>
+        <v>4.100033961714379e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.09504082213182e-07</v>
+        <v>2.087381580169457e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.651878710492379e-07</v>
+        <v>2.640331208030643e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.107980977692419e-07</v>
+        <v>2.096228451346686e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.090310880037024e-07</v>
+        <v>2.084481218248003e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.138729471154538e-07</v>
+        <v>2.116555811777594e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.091164461649371e-07</v>
+        <v>2.084563715786007e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.113188530195966e-07</v>
+        <v>2.100325015561562e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.084876237075143e-07</v>
+        <v>2.080347534424557e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.088345585658407e-07</v>
+        <v>2.082910916646082e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.095747882275352e-07</v>
+        <v>2.087737475160611e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.169280748844761e-07</v>
+        <v>2.138777913548961e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.164966997061542e-07</v>
+        <v>1.160071043332352e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.112153048488154e-07</v>
+        <v>2.100283245774253e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.121494431325174e-07</v>
+        <v>2.106134291089663e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.120599414648901e-07</v>
+        <v>2.104526088575142e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.111233622735897e-07</v>
+        <v>2.0993833422474e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.100239481504803e-07</v>
+        <v>2.090788041635353e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.533628105597321e-07</v>
+        <v>4.514695272718467e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.116161477891792e-07</v>
+        <v>2.10326409392866e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.438051874741803e-07</v>
+        <v>3.3563662558941e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.111526682731128e-07</v>
+        <v>2.098959740464751e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.104703807352862e-07</v>
+        <v>2.094142228118323e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.868668693573293e-07</v>
+        <v>1.860968280919393e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.115478386153811e-07</v>
+        <v>2.101675679274119e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.088925850551701e-07</v>
+        <v>2.082840994167134e-07</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.101097230772225e-07</v>
+        <v>2.093636163780402e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.035005683072483e-07</v>
+        <v>4.032065218943522e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.187954804270509e-07</v>
+        <v>2.152986694200634e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.657378370975835e-07</v>
+        <v>2.644893551416453e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.103469701187316e-07</v>
+        <v>2.094624132343093e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.093964597278404e-07</v>
+        <v>2.088516924518191e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.156432193141598e-07</v>
+        <v>2.130365862703251e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.141637216770879e-07</v>
+        <v>2.120794536007783e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.123723015463053e-07</v>
+        <v>2.109369026631767e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.232982072813977e-07</v>
+        <v>2.187070895675487e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.142175851501943e-07</v>
+        <v>2.123387036621471e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.097935961251699e-07</v>
+        <v>2.090868477834986e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.220297266356312e-07</v>
+        <v>2.176727661186652e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.191985686378185e-07</v>
+        <v>1.182580777509659e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.117813121848123e-07</v>
+        <v>2.105508385960526e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1424766198577e-07</v>
+        <v>2.122383024224792e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.125337575393825e-07</v>
+        <v>2.10934743073465e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.146397804798738e-07</v>
+        <v>2.127374511993095e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.122064046177835e-07</v>
+        <v>2.107753766172105e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.575344173613411e-07</v>
+        <v>4.547489586277936e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.102918546417637e-07</v>
+        <v>2.094933567389513e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.464385802537933e-07</v>
+        <v>3.378646984981745e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.167578296107403e-07</v>
+        <v>2.139176677526818e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.127426117383383e-07</v>
+        <v>2.111666924583443e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.890027552229167e-07</v>
+        <v>1.878732230802997e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.130691615464579e-07</v>
+        <v>2.113871667586798e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.104718464811421e-07</v>
+        <v>2.095305796157088e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.075949164520135e-07</v>
+        <v>2.073150641997825e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.034383236829473e-07</v>
+        <v>4.028894376070532e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.105182024534228e-07</v>
+        <v>2.093510413558871e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.625275878025733e-07</v>
+        <v>2.620406825026147e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.079015810216288e-07</v>
+        <v>2.07507397628473e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.104134564872911e-07</v>
+        <v>2.093807415881867e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.142584584224565e-07</v>
+        <v>2.118380317647019e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.093483838111847e-07</v>
+        <v>2.08508549664142e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.10480755810435e-07</v>
+        <v>2.0938026111877e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.095400794716069e-07</v>
+        <v>2.086842743861877e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.084987019676851e-07</v>
+        <v>2.079672944570653e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.088338517577789e-07</v>
+        <v>2.081725609589444e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.112879134920971e-07</v>
+        <v>2.099073550723834e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.158847562769027e-07</v>
+        <v>1.153894298070629e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.091843283180044e-07</v>
+        <v>2.084554899297988e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.086272818901942e-07</v>
+        <v>2.080506828921948e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.093484771009143e-07</v>
+        <v>2.084977287803707e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.116444699159641e-07</v>
+        <v>2.102924231688827e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.085813197948219e-07</v>
+        <v>2.079857094306223e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.474515779366158e-07</v>
+        <v>4.470111443616619e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1038398606853e-07</v>
+        <v>2.093344583228502e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.34841175223318e-07</v>
+        <v>3.293491716436174e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.12589353347301e-07</v>
+        <v>2.108258964776883e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.089180588122201e-07</v>
+        <v>2.082265749222053e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.863795812791513e-07</v>
+        <v>1.855453525892653e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.147918561446082e-07</v>
+        <v>2.123294269738586e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.073121624751278e-07</v>
+        <v>2.07089773997848e-07</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.073293690167128e-07</v>
+        <v>2.070286633645767e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.025824970212181e-07</v>
+        <v>4.021723341293308e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.098873836043569e-07</v>
+        <v>2.087958016171666e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.620015025859824e-07</v>
+        <v>2.616001156314786e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.077172065171271e-07</v>
+        <v>2.072726654858457e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.091269479835196e-07</v>
+        <v>2.083282522614014e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.130287568247772e-07</v>
+        <v>2.109021999154617e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.087139210693474e-07</v>
+        <v>2.079612907319457e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.096655415630412e-07</v>
+        <v>2.086798020229764e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.084784620684423e-07</v>
+        <v>2.078200522002521e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.079490646058502e-07</v>
+        <v>2.074686663276517e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.089485932269734e-07</v>
+        <v>2.081361916536149e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.104921621627988e-07</v>
+        <v>2.092290894188859e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.149814183146875e-07</v>
+        <v>1.14557679090099e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.079977530355792e-07</v>
+        <v>2.0751240135553e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.078451755611793e-07</v>
+        <v>2.073826146145389e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.082648919431743e-07</v>
+        <v>2.07643608964448e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1018508922831e-07</v>
+        <v>2.090912039681537e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.086041558116785e-07</v>
+        <v>2.07893313470694e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.477476432533631e-07</v>
+        <v>4.470151299030523e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.113395521748675e-07</v>
+        <v>2.099173259223301e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.304838641499359e-07</v>
+        <v>3.259459547320958e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.123313285878319e-07</v>
+        <v>2.105610131950887e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.079620910015213e-07</v>
+        <v>2.074551889197863e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.850032752393811e-07</v>
+        <v>1.843951657580812e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.142277215751934e-07</v>
+        <v>2.118269703042956e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.075601823527917e-07</v>
+        <v>2.071556488441197e-07</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.114785146311478e-07</v>
+        <v>2.105123443534419e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.049166876351176e-07</v>
+        <v>4.043908806340178e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.187368380412542e-07</v>
+        <v>2.1541039025684e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.645626116252318e-07</v>
+        <v>2.637849908096167e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.138303744674575e-07</v>
+        <v>2.120465378501059e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.095737242476285e-07</v>
+        <v>2.091417552763678e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.178344592628523e-07</v>
+        <v>2.147135768953168e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.221411451106183e-07</v>
+        <v>2.177481913438798e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.135020370949206e-07</v>
+        <v>2.118884674643222e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.314728331280504e-07</v>
+        <v>2.247089156524415e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.106373996371652e-07</v>
+        <v>2.098841434010615e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.107985178672863e-07</v>
+        <v>2.099658330026779e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.339282021260325e-07</v>
+        <v>2.260199387735988e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.217383977414266e-07</v>
+        <v>1.204236441323654e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.134180803448959e-07</v>
+        <v>2.118815948151318e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.171995943193958e-07</v>
+        <v>2.144497567393763e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.155897436737704e-07</v>
+        <v>2.132082831194395e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.147796561219854e-07</v>
+        <v>2.129128870442057e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.175056759135854e-07</v>
+        <v>2.145682322841006e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.537112917842688e-07</v>
+        <v>4.523393664095948e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.126886341576919e-07</v>
+        <v>2.113880458089958e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.434324282082776e-07</v>
+        <v>3.361121801209563e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.164704923058939e-07</v>
+        <v>2.138859458867168e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.15029627472362e-07</v>
+        <v>2.129481469464432e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.904249467613763e-07</v>
+        <v>1.891922853844269e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.132105924274638e-07</v>
+        <v>2.116662755690695e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.105577074250535e-07</v>
+        <v>2.09763398117068e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.083053812288796e-07</v>
+        <v>2.079675115097256e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.045923496130457e-07</v>
+        <v>4.038668525420678e-07</v>
       </c>
       <c r="D3" t="n">
-        <v>2.110150336128446e-07</v>
+        <v>2.098261572316619e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>2.642931695986764e-07</v>
+        <v>2.633891992385282e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>2.08090270281866e-07</v>
+        <v>2.07792028316473e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.103736882150406e-07</v>
+        <v>2.094677973924822e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>2.152541713850875e-07</v>
+        <v>2.126423810830109e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.096681547573113e-07</v>
+        <v>2.088766865539115e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.112982675320858e-07</v>
+        <v>2.100786928043344e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.11987663149782e-07</v>
+        <v>2.105860974081362e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.091997490729844e-07</v>
+        <v>2.08598651545482e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.09224882892463e-07</v>
+        <v>2.085832066756942e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.141627885277674e-07</v>
+        <v>2.120113326038248e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>1.163025313033834e-07</v>
+        <v>1.159317378876152e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.124242243314869e-07</v>
+        <v>2.109211469435837e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.115554252465425e-07</v>
+        <v>2.102760133641405e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>2.104338082088646e-07</v>
+        <v>2.093912777104638e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.122962844096346e-07</v>
+        <v>2.108614226020834e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>2.092046558025204e-07</v>
+        <v>2.085634538138019e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>4.489559133985331e-07</v>
+        <v>4.484145240271367e-07</v>
       </c>
       <c r="V3" t="n">
-        <v>2.11304490686821e-07</v>
+        <v>2.101351849837401e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.40665770753309e-07</v>
+        <v>3.335566023911119e-07</v>
       </c>
       <c r="X3" t="n">
-        <v>2.13944513803007e-07</v>
+        <v>2.118864726882531e-07</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.106866983570403e-07</v>
+        <v>2.096190305724635e-07</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.875679456006442e-07</v>
+        <v>1.866906846923822e-07</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.113296698430753e-07</v>
+        <v>2.10063002185618e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.114019627891631e-07</v>
+        <v>2.100490245045483e-07</v>
       </c>
     </row>
     <row r="4">
